--- a/tame_output/ON/bt/strategyON_20240930.xlsx
+++ b/tame_output/ON/bt/strategyON_20240930.xlsx
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-593.2%</t>
+          <t>-593.3%</t>
         </is>
       </c>
     </row>
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-98.8%</t>
+          <t>-99.0%</t>
         </is>
       </c>
     </row>
@@ -1390,7 +1390,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>125.2%</t>
+          <t>125.1%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>56.8%</t>
+          <t>56.7%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>119.1%</t>
+          <t>119.0%</t>
         </is>
       </c>
     </row>
@@ -47706,7 +47706,7 @@
         <v>45469</v>
       </c>
       <c r="B2007" t="n">
-        <v>3.714941193321629</v>
+        <v>3.71494119332163</v>
       </c>
       <c r="C2007" t="n">
         <v>3.209131053508234</v>
@@ -47729,7 +47729,7 @@
         <v>45470</v>
       </c>
       <c r="B2008" t="n">
-        <v>3.7278981863477</v>
+        <v>3.727898186347701</v>
       </c>
       <c r="C2008" t="n">
         <v>3.207242866402009</v>
@@ -47752,7 +47752,7 @@
         <v>45471</v>
       </c>
       <c r="B2009" t="n">
-        <v>3.710654104887745</v>
+        <v>3.710654104887746</v>
       </c>
       <c r="C2009" t="n">
         <v>3.202063096004871</v>
@@ -47775,7 +47775,7 @@
         <v>45472</v>
       </c>
       <c r="B2010" t="n">
-        <v>3.712897612343062</v>
+        <v>3.712897612343064</v>
       </c>
       <c r="C2010" t="n">
         <v>3.200497106215023</v>
@@ -47798,7 +47798,7 @@
         <v>45473</v>
       </c>
       <c r="B2011" t="n">
-        <v>3.754596135389345</v>
+        <v>3.754596135389347</v>
       </c>
       <c r="C2011" t="n">
         <v>3.213570513080942</v>
@@ -47821,7 +47821,7 @@
         <v>45474</v>
       </c>
       <c r="B2012" t="n">
-        <v>3.749882691378388</v>
+        <v>3.749882691378389</v>
       </c>
       <c r="C2012" t="n">
         <v>3.205575709863882</v>
@@ -47844,7 +47844,7 @@
         <v>45475</v>
       </c>
       <c r="B2013" t="n">
-        <v>3.715819895006971</v>
+        <v>3.715819895006972</v>
       </c>
       <c r="C2013" t="n">
         <v>3.204099750990884</v>
@@ -47867,7 +47867,7 @@
         <v>45476</v>
       </c>
       <c r="B2014" t="n">
-        <v>3.684895778787384</v>
+        <v>3.684895778787385</v>
       </c>
       <c r="C2014" t="n">
         <v>3.200864194968083</v>
@@ -47890,7 +47890,7 @@
         <v>45477</v>
       </c>
       <c r="B2015" t="n">
-        <v>3.619348081585934</v>
+        <v>3.619348081585935</v>
       </c>
       <c r="C2015" t="n">
         <v>3.267570154558586</v>
@@ -47913,7 +47913,7 @@
         <v>45478</v>
       </c>
       <c r="B2016" t="n">
-        <v>3.640750087814664</v>
+        <v>3.640750087814665</v>
       </c>
       <c r="C2016" t="n">
         <v>3.407881873560433</v>
@@ -47936,7 +47936,7 @@
         <v>45479</v>
       </c>
       <c r="B2017" t="n">
-        <v>3.668289004237093</v>
+        <v>3.668289004237094</v>
       </c>
       <c r="C2017" t="n">
         <v>3.476862142706073</v>
@@ -47959,7 +47959,7 @@
         <v>45480</v>
       </c>
       <c r="B2018" t="n">
-        <v>3.619923016423386</v>
+        <v>3.619923016423387</v>
       </c>
       <c r="C2018" t="n">
         <v>3.462913344826194</v>
@@ -48005,7 +48005,7 @@
         <v>45482</v>
       </c>
       <c r="B2020" t="n">
-        <v>3.674028535973155</v>
+        <v>3.674028535973156</v>
       </c>
       <c r="C2020" t="n">
         <v>3.475994368400552</v>
@@ -48028,7 +48028,7 @@
         <v>45483</v>
       </c>
       <c r="B2021" t="n">
-        <v>3.663509457251942</v>
+        <v>3.663509457251943</v>
       </c>
       <c r="C2021" t="n">
         <v>3.480116110627873</v>
@@ -48051,7 +48051,7 @@
         <v>45484</v>
       </c>
       <c r="B2022" t="n">
-        <v>3.652149152916197</v>
+        <v>3.652149152916198</v>
       </c>
       <c r="C2022" t="n">
         <v>3.475193963364063</v>
@@ -48074,7 +48074,7 @@
         <v>45485</v>
       </c>
       <c r="B2023" t="n">
-        <v>3.667962306830325</v>
+        <v>3.667962306830326</v>
       </c>
       <c r="C2023" t="n">
         <v>3.637398020063107</v>
@@ -48097,7 +48097,7 @@
         <v>45486</v>
       </c>
       <c r="B2024" t="n">
-        <v>3.696539468071547</v>
+        <v>3.696539468071548</v>
       </c>
       <c r="C2024" t="n">
         <v>3.632244658026921</v>
@@ -48120,7 +48120,7 @@
         <v>45487</v>
       </c>
       <c r="B2025" t="n">
-        <v>3.750044015868143</v>
+        <v>3.750044015868144</v>
       </c>
       <c r="C2025" t="n">
         <v>3.642474075595412</v>
@@ -48143,7 +48143,7 @@
         <v>45488</v>
       </c>
       <c r="B2026" t="n">
-        <v>3.783632867332689</v>
+        <v>3.783632867332691</v>
       </c>
       <c r="C2026" t="n">
         <v>3.651399714051315</v>
@@ -48166,7 +48166,7 @@
         <v>45489</v>
       </c>
       <c r="B2027" t="n">
-        <v>3.798296784231805</v>
+        <v>3.798296784231807</v>
       </c>
       <c r="C2027" t="n">
         <v>3.64355260129549</v>
@@ -48350,7 +48350,7 @@
         <v>45497</v>
       </c>
       <c r="B2035" t="n">
-        <v>3.775028860833456</v>
+        <v>3.775028860833457</v>
       </c>
       <c r="C2035" t="n">
         <v>3.480028535180593</v>
@@ -48465,7 +48465,7 @@
         <v>45502</v>
       </c>
       <c r="B2040" t="n">
-        <v>3.815643212108854</v>
+        <v>3.815643212108855</v>
       </c>
       <c r="C2040" t="n">
         <v>3.56132193627621</v>
@@ -48488,7 +48488,7 @@
         <v>45503</v>
       </c>
       <c r="B2041" t="n">
-        <v>3.807356168121463</v>
+        <v>3.807356168121466</v>
       </c>
       <c r="C2041" t="n">
         <v>3.561451189754754</v>
@@ -48511,7 +48511,7 @@
         <v>45504</v>
       </c>
       <c r="B2042" t="n">
-        <v>3.775233033906076</v>
+        <v>3.775233033906079</v>
       </c>
       <c r="C2042" t="n">
         <v>3.54128803549235</v>
@@ -48534,7 +48534,7 @@
         <v>45505</v>
       </c>
       <c r="B2043" t="n">
-        <v>3.785761685912981</v>
+        <v>3.785761685912983</v>
       </c>
       <c r="C2043" t="n">
         <v>3.576254972104409</v>
@@ -48557,7 +48557,7 @@
         <v>45506</v>
       </c>
       <c r="B2044" t="n">
-        <v>3.74376795653989</v>
+        <v>3.743767956539893</v>
       </c>
       <c r="C2044" t="n">
         <v>3.569941540005846</v>
@@ -48580,7 +48580,7 @@
         <v>45507</v>
       </c>
       <c r="B2045" t="n">
-        <v>3.725010844811004</v>
+        <v>3.725010844811008</v>
       </c>
       <c r="C2045" t="n">
         <v>3.571822170189982</v>
@@ -48603,7 +48603,7 @@
         <v>45508</v>
       </c>
       <c r="B2046" t="n">
-        <v>3.612322444382915</v>
+        <v>3.612322444382919</v>
       </c>
       <c r="C2046" t="n">
         <v>3.584673196067865</v>
@@ -48626,7 +48626,7 @@
         <v>45509</v>
       </c>
       <c r="B2047" t="n">
-        <v>3.645256780013422</v>
+        <v>3.645256780013425</v>
       </c>
       <c r="C2047" t="n">
         <v>3.604875866241459</v>
@@ -48649,7 +48649,7 @@
         <v>45510</v>
       </c>
       <c r="B2048" t="n">
-        <v>3.666747201498967</v>
+        <v>3.666747201498968</v>
       </c>
       <c r="C2048" t="n">
         <v>3.588482102308341</v>
@@ -48672,7 +48672,7 @@
         <v>45511</v>
       </c>
       <c r="B2049" t="n">
-        <v>3.670048702800096</v>
+        <v>3.670048702800097</v>
       </c>
       <c r="C2049" t="n">
         <v>3.548734015901807</v>
@@ -48695,7 +48695,7 @@
         <v>45512</v>
       </c>
       <c r="B2050" t="n">
-        <v>3.745573148660848</v>
+        <v>3.745573148660849</v>
       </c>
       <c r="C2050" t="n">
         <v>3.555756634898747</v>
@@ -48718,7 +48718,7 @@
         <v>45513</v>
       </c>
       <c r="B2051" t="n">
-        <v>3.730570473395085</v>
+        <v>3.730570473395087</v>
       </c>
       <c r="C2051" t="n">
         <v>3.654927634471652</v>
@@ -48741,7 +48741,7 @@
         <v>45514</v>
       </c>
       <c r="B2052" t="n">
-        <v>3.741278332791147</v>
+        <v>3.741278332791149</v>
       </c>
       <c r="C2052" t="n">
         <v>3.842393859379944</v>
@@ -48764,7 +48764,7 @@
         <v>45515</v>
       </c>
       <c r="B2053" t="n">
-        <v>3.699115615620433</v>
+        <v>3.699115615620435</v>
       </c>
       <c r="C2053" t="n">
         <v>3.811796810734027</v>
@@ -48787,7 +48787,7 @@
         <v>45516</v>
       </c>
       <c r="B2054" t="n">
-        <v>3.708182519285645</v>
+        <v>3.708182519285647</v>
       </c>
       <c r="C2054" t="n">
         <v>3.815473213395745</v>
@@ -48810,7 +48810,7 @@
         <v>45517</v>
       </c>
       <c r="B2055" t="n">
-        <v>3.740581401399467</v>
+        <v>3.740581401399469</v>
       </c>
       <c r="C2055" t="n">
         <v>3.81309126851924</v>
@@ -48833,7 +48833,7 @@
         <v>45518</v>
       </c>
       <c r="B2056" t="n">
-        <v>3.699404642256368</v>
+        <v>3.69940464225637</v>
       </c>
       <c r="C2056" t="n">
         <v>3.810384507676875</v>
@@ -48856,7 +48856,7 @@
         <v>45519</v>
       </c>
       <c r="B2057" t="n">
-        <v>3.689942600700998</v>
+        <v>3.689942600700999</v>
       </c>
       <c r="C2057" t="n">
         <v>3.811813309820109</v>
@@ -48879,7 +48879,7 @@
         <v>45520</v>
       </c>
       <c r="B2058" t="n">
-        <v>3.71185242968701</v>
+        <v>3.711852429687012</v>
       </c>
       <c r="C2058" t="n">
         <v>3.911744549077862</v>
@@ -48902,7 +48902,7 @@
         <v>45521</v>
       </c>
       <c r="B2059" t="n">
-        <v>3.7148790517908</v>
+        <v>3.714879051790802</v>
       </c>
       <c r="C2059" t="n">
         <v>3.909530246203802</v>
@@ -48925,7 +48925,7 @@
         <v>45522</v>
       </c>
       <c r="B2060" t="n">
-        <v>3.704757949437328</v>
+        <v>3.70475794943733</v>
       </c>
       <c r="C2060" t="n">
         <v>3.909433374278091</v>
@@ -48948,7 +48948,7 @@
         <v>45523</v>
       </c>
       <c r="B2061" t="n">
-        <v>3.736804952298394</v>
+        <v>3.736804952298398</v>
       </c>
       <c r="C2061" t="n">
         <v>3.909427267836134</v>
@@ -48971,7 +48971,7 @@
         <v>45524</v>
       </c>
       <c r="B2062" t="n">
-        <v>3.715372960217996</v>
+        <v>3.715372960218</v>
       </c>
       <c r="C2062" t="n">
         <v>3.907523664398744</v>
@@ -48994,7 +48994,7 @@
         <v>45525</v>
       </c>
       <c r="B2063" t="n">
-        <v>3.736089413353532</v>
+        <v>3.736089413353535</v>
       </c>
       <c r="C2063" t="n">
         <v>3.913257482146471</v>
@@ -49017,7 +49017,7 @@
         <v>45526</v>
       </c>
       <c r="B2064" t="n">
-        <v>3.736822870113275</v>
+        <v>3.736822870113278</v>
       </c>
       <c r="C2064" t="n">
         <v>3.912795845489403</v>
@@ -49040,7 +49040,7 @@
         <v>45527</v>
       </c>
       <c r="B2065" t="n">
-        <v>3.790272500113684</v>
+        <v>3.790272500113687</v>
       </c>
       <c r="C2065" t="n">
         <v>3.932670238339722</v>
@@ -49063,7 +49063,7 @@
         <v>45528</v>
       </c>
       <c r="B2066" t="n">
-        <v>3.794486844016437</v>
+        <v>3.794486844016438</v>
       </c>
       <c r="C2066" t="n">
         <v>3.91637093886445</v>
@@ -49086,7 +49086,7 @@
         <v>45529</v>
       </c>
       <c r="B2067" t="n">
-        <v>3.794705093307669</v>
+        <v>3.79470509330767</v>
       </c>
       <c r="C2067" t="n">
         <v>3.918801888328495</v>
@@ -49109,7 +49109,7 @@
         <v>45530</v>
       </c>
       <c r="B2068" t="n">
-        <v>3.77684655786355</v>
+        <v>3.776846557863551</v>
       </c>
       <c r="C2068" t="n">
         <v>3.901746294407872</v>
@@ -49132,7 +49132,7 @@
         <v>45531</v>
       </c>
       <c r="B2069" t="n">
-        <v>3.72378970539411</v>
+        <v>3.723789705394111</v>
       </c>
       <c r="C2069" t="n">
         <v>3.848662040329044</v>
@@ -49155,7 +49155,7 @@
         <v>45532</v>
       </c>
       <c r="B2070" t="n">
-        <v>3.715607446456727</v>
+        <v>3.715607446456728</v>
       </c>
       <c r="C2070" t="n">
         <v>4.0338602452144</v>
@@ -49178,7 +49178,7 @@
         <v>45533</v>
       </c>
       <c r="B2071" t="n">
-        <v>3.713762536883674</v>
+        <v>3.713762536883677</v>
       </c>
       <c r="C2071" t="n">
         <v>4.025781471042649</v>
@@ -49201,7 +49201,7 @@
         <v>45534</v>
       </c>
       <c r="B2072" t="n">
-        <v>3.717150699236294</v>
+        <v>3.717150699236297</v>
       </c>
       <c r="C2072" t="n">
         <v>4.029449583564437</v>
@@ -49224,7 +49224,7 @@
         <v>45535</v>
       </c>
       <c r="B2073" t="n">
-        <v>3.70520107942768</v>
+        <v>3.705201079427684</v>
       </c>
       <c r="C2073" t="n">
         <v>4.030700665757275</v>
@@ -49247,7 +49247,7 @@
         <v>45536</v>
       </c>
       <c r="B2074" t="n">
-        <v>3.691835499610379</v>
+        <v>3.69183549961038</v>
       </c>
       <c r="C2074" t="n">
         <v>4.013119867577777</v>
@@ -49270,7 +49270,7 @@
         <v>45537</v>
       </c>
       <c r="B2075" t="n">
-        <v>3.715544411667452</v>
+        <v>3.715544411667453</v>
       </c>
       <c r="C2075" t="n">
         <v>4.023284378622827</v>
@@ -49293,7 +49293,7 @@
         <v>45538</v>
       </c>
       <c r="B2076" t="n">
-        <v>3.673978374889187</v>
+        <v>3.673978374889191</v>
       </c>
       <c r="C2076" t="n">
         <v>4.125412636447095</v>
@@ -49316,7 +49316,7 @@
         <v>45539</v>
       </c>
       <c r="B2077" t="n">
-        <v>3.682476099409563</v>
+        <v>3.682476099409566</v>
       </c>
       <c r="C2077" t="n">
         <v>4.1284449751785</v>
@@ -49339,7 +49339,7 @@
         <v>45540</v>
       </c>
       <c r="B2078" t="n">
-        <v>3.672895177452569</v>
+        <v>3.67289517745257</v>
       </c>
       <c r="C2078" t="n">
         <v>4.341349808456558</v>
@@ -49362,7 +49362,7 @@
         <v>45541</v>
       </c>
       <c r="B2079" t="n">
-        <v>3.623960959762282</v>
+        <v>3.623960959762287</v>
       </c>
       <c r="C2079" t="n">
         <v>4.340528475368647</v>
@@ -49385,7 +49385,7 @@
         <v>45542</v>
       </c>
       <c r="B2080" t="n">
-        <v>3.633213467988013</v>
+        <v>3.633213467988018</v>
       </c>
       <c r="C2080" t="n">
         <v>4.334760461313001</v>
@@ -49408,7 +49408,7 @@
         <v>45543</v>
       </c>
       <c r="B2081" t="n">
-        <v>3.64790724274092</v>
+        <v>3.647907242740922</v>
       </c>
       <c r="C2081" t="n">
         <v>4.334760461313001</v>
@@ -49431,7 +49431,7 @@
         <v>45544</v>
       </c>
       <c r="B2082" t="n">
-        <v>3.881065366663623</v>
+        <v>3.881065366663625</v>
       </c>
       <c r="C2082" t="n">
         <v>4.347488069294093</v>
@@ -49454,7 +49454,7 @@
         <v>45545</v>
       </c>
       <c r="B2083" t="n">
-        <v>3.717071158424767</v>
+        <v>3.717071158424769</v>
       </c>
       <c r="C2083" t="n">
         <v>4.349434067718481</v>
@@ -49477,7 +49477,7 @@
         <v>45546</v>
       </c>
       <c r="B2084" t="n">
-        <v>3.741942347149216</v>
+        <v>3.741942347149218</v>
       </c>
       <c r="C2084" t="n">
         <v>4.34308820373625</v>
@@ -49500,7 +49500,7 @@
         <v>45547</v>
       </c>
       <c r="B2085" t="n">
-        <v>3.735300721383088</v>
+        <v>3.73530072138309</v>
       </c>
       <c r="C2085" t="n">
         <v>4.342396881175246</v>
@@ -49523,7 +49523,7 @@
         <v>45548</v>
       </c>
       <c r="B2086" t="n">
-        <v>3.778232147720994</v>
+        <v>3.778232147720995</v>
       </c>
       <c r="C2086" t="n">
         <v>4.355179067083832</v>
@@ -49546,7 +49546,7 @@
         <v>45549</v>
       </c>
       <c r="B2087" t="n">
-        <v>3.775357097455268</v>
+        <v>3.77535709745527</v>
       </c>
       <c r="C2087" t="n">
         <v>4.544333332582559</v>
@@ -49569,7 +49569,7 @@
         <v>45550</v>
       </c>
       <c r="B2088" t="n">
-        <v>3.749078058963129</v>
+        <v>3.749078058963131</v>
       </c>
       <c r="C2088" t="n">
         <v>4.531522005685421</v>
@@ -49592,7 +49592,7 @@
         <v>45551</v>
       </c>
       <c r="B2089" t="n">
-        <v>3.740284389162539</v>
+        <v>3.740284389162541</v>
       </c>
       <c r="C2089" t="n">
         <v>4.533523519339526</v>
@@ -49615,7 +49615,7 @@
         <v>45552</v>
       </c>
       <c r="B2090" t="n">
-        <v>3.78248211565238</v>
+        <v>3.782482115652382</v>
       </c>
       <c r="C2090" t="n">
         <v>4.887020633329193</v>
@@ -49638,7 +49638,7 @@
         <v>45553</v>
       </c>
       <c r="B2091" t="n">
-        <v>3.80905590510867</v>
+        <v>3.809055905108672</v>
       </c>
       <c r="C2091" t="n">
         <v>4.891583744896296</v>
@@ -49661,7 +49661,7 @@
         <v>45554</v>
       </c>
       <c r="B2092" t="n">
-        <v>3.835202441103561</v>
+        <v>3.835202441103564</v>
       </c>
       <c r="C2092" t="n">
         <v>4.941413686219824</v>
@@ -49684,7 +49684,7 @@
         <v>45555</v>
       </c>
       <c r="B2093" t="n">
-        <v>3.821827147047742</v>
+        <v>3.821827147047745</v>
       </c>
       <c r="C2093" t="n">
         <v>4.950227656429835</v>
@@ -49707,7 +49707,7 @@
         <v>45556</v>
       </c>
       <c r="B2094" t="n">
-        <v>3.825268416650751</v>
+        <v>3.825268416650755</v>
       </c>
       <c r="C2094" t="n">
         <v>4.945865240469032</v>
@@ -49730,7 +49730,7 @@
         <v>45557</v>
       </c>
       <c r="B2095" t="n">
-        <v>3.845044666135745</v>
+        <v>3.84504466613575</v>
       </c>
       <c r="C2095" t="n">
         <v>4.936789743885312</v>
@@ -49753,7 +49753,7 @@
         <v>45558</v>
       </c>
       <c r="B2096" t="n">
-        <v>3.825931790479219</v>
+        <v>3.825931790479223</v>
       </c>
       <c r="C2096" t="n">
         <v>4.933197411600246</v>
@@ -49776,7 +49776,7 @@
         <v>45559</v>
       </c>
       <c r="B2097" t="n">
-        <v>3.847096478844243</v>
+        <v>3.847096478844245</v>
       </c>
       <c r="C2097" t="n">
         <v>4.942244448291374</v>
@@ -49799,7 +49799,7 @@
         <v>45560</v>
       </c>
       <c r="B2098" t="n">
-        <v>3.832425987790947</v>
+        <v>3.832425987790948</v>
       </c>
       <c r="C2098" t="n">
         <v>4.943101913277496</v>
@@ -49822,7 +49822,7 @@
         <v>45561</v>
       </c>
       <c r="B2099" t="n">
-        <v>3.861579399578993</v>
+        <v>3.861579399578995</v>
       </c>
       <c r="C2099" t="n">
         <v>4.906011330067848</v>
@@ -49845,7 +49845,7 @@
         <v>45562</v>
       </c>
       <c r="B2100" t="n">
-        <v>3.872253907629881</v>
+        <v>3.872253907629883</v>
       </c>
       <c r="C2100" t="n">
         <v>4.909943583625799</v>
@@ -49868,7 +49868,7 @@
         <v>45563</v>
       </c>
       <c r="B2101" t="n">
-        <v>3.868502531686404</v>
+        <v>3.868502531686405</v>
       </c>
       <c r="C2101" t="n">
         <v>4.904842676232835</v>
@@ -49891,22 +49891,22 @@
         <v>45564</v>
       </c>
       <c r="B2102" t="n">
-        <v>3.76694945783331</v>
+        <v>3.766949457833312</v>
       </c>
       <c r="C2102" t="n">
         <v>4.900196585621931</v>
       </c>
       <c r="D2102" t="n">
-        <v>-4.315820520217367</v>
+        <v>-4.317734583626807</v>
       </c>
       <c r="E2102" t="n">
-        <v>3.173511953221236</v>
+        <v>3.17274632785746</v>
       </c>
       <c r="F2102" t="n">
-        <v>1.252122424283177</v>
+        <v>1.250208360873736</v>
       </c>
       <c r="G2102" t="n">
-        <v>5.651470040191837</v>
+        <v>5.650321602146173</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240930.xlsx
+++ b/tame_output/ON/bt/strategyON_20240930.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>54.1%</t>
+          <t>54.8%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.2%</t>
+          <t>66.1%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>65.1%</t>
+          <t>65.0%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>17.8%</t>
+          <t>17.9%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>48.6%</t>
+          <t>51.1%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>113.1%</t>
+          <t>113.7%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>44.0%</t>
+          <t>44.1%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.57</t>
+          <t>2.58</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>47.2%</t>
+          <t>47.3%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>10.8%</t>
+          <t>10.9%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>95.4%</t>
+          <t>95.9%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.9%</t>
+          <t>39.8%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>178.4%</t>
+          <t>180.3%</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-75.3%</t>
+          <t>-75.2%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>422.3%</t>
+          <t>422.6%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-593.3%</t>
+          <t>-592.3%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>44.9%</t>
+          <t>45.4%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>59.9%</t>
+          <t>60.0%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>57.6%</t>
+          <t>57.7%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>14.4%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>39.8%</t>
+          <t>40.3%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>50.1%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-4.7%</t>
+          <t>-4.8%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-58.9%</t>
+          <t>-56.6%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-2.8%</t>
+          <t>-2.7%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>73.3%</t>
+          <t>73.4%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.2%</t>
+          <t>10.3%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>3.9%</t>
+          <t>4.1%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1343,7 +1343,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>42.3%</t>
+          <t>42.2%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-99.0%</t>
+          <t>-97.9%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>125.1%</t>
+          <t>126.0%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>57.8%</t>
+          <t>57.9%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2.17</t>
+          <t>2.18</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>56.7%</t>
+          <t>56.9%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1447,7 +1447,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1481,7 +1481,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>114.2%</t>
+          <t>114.9%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>119.0%</t>
+          <t>121.6%</t>
         </is>
       </c>
     </row>
@@ -49296,19 +49296,19 @@
         <v>3.673978374889191</v>
       </c>
       <c r="C2076" t="n">
-        <v>4.125412636447095</v>
+        <v>4.144444094190696</v>
       </c>
       <c r="D2076" t="n">
         <v>-5.121691981252651</v>
       </c>
       <c r="E2076" t="n">
-        <v>2.076379419632286</v>
+        <v>2.095410877375888</v>
       </c>
       <c r="F2076" t="n">
         <v>0.6767987048708634</v>
       </c>
       <c r="G2076" t="n">
-        <v>4.531491859369613</v>
+        <v>4.550523317113214</v>
       </c>
     </row>
     <row r="2077">
@@ -49319,19 +49319,19 @@
         <v>3.682476099409566</v>
       </c>
       <c r="C2077" t="n">
-        <v>4.1284449751785</v>
+        <v>4.147476432922101</v>
       </c>
       <c r="D2077" t="n">
         <v>-5.192604054994929</v>
       </c>
       <c r="E2077" t="n">
-        <v>2.05104692886678</v>
+        <v>2.070078386610382</v>
       </c>
       <c r="F2077" t="n">
         <v>0.6767987048708634</v>
       </c>
       <c r="G2077" t="n">
-        <v>4.534524198101018</v>
+        <v>4.553555655844619</v>
       </c>
     </row>
     <row r="2078">
@@ -49342,19 +49342,19 @@
         <v>3.67289517745257</v>
       </c>
       <c r="C2078" t="n">
-        <v>4.341349808456558</v>
+        <v>4.360381266200159</v>
       </c>
       <c r="D2078" t="n">
         <v>-5.202920153161281</v>
       </c>
       <c r="E2078" t="n">
-        <v>2.259825322878298</v>
+        <v>2.278856780621899</v>
       </c>
       <c r="F2078" t="n">
         <v>0.6767987048708634</v>
       </c>
       <c r="G2078" t="n">
-        <v>4.747429031379076</v>
+        <v>4.766460489122677</v>
       </c>
     </row>
     <row r="2079">
@@ -49365,19 +49365,19 @@
         <v>3.623960959762287</v>
       </c>
       <c r="C2079" t="n">
-        <v>4.340528475368647</v>
+        <v>4.359559933112249</v>
       </c>
       <c r="D2079" t="n">
         <v>-5.202826185143908</v>
       </c>
       <c r="E2079" t="n">
-        <v>2.259041576997336</v>
+        <v>2.278073034740938</v>
       </c>
       <c r="F2079" t="n">
         <v>0.6771685662181813</v>
       </c>
       <c r="G2079" t="n">
-        <v>4.746829615099556</v>
+        <v>4.765861072843157</v>
       </c>
     </row>
     <row r="2080">
@@ -49388,19 +49388,19 @@
         <v>3.633213467988018</v>
       </c>
       <c r="C2080" t="n">
-        <v>4.334760461313001</v>
+        <v>4.353791919056603</v>
       </c>
       <c r="D2080" t="n">
         <v>-5.351192412800053</v>
       </c>
       <c r="E2080" t="n">
-        <v>2.193927071879232</v>
+        <v>2.212958529622834</v>
       </c>
       <c r="F2080" t="n">
         <v>0.6771685662181813</v>
       </c>
       <c r="G2080" t="n">
-        <v>4.74106160104391</v>
+        <v>4.760093058787511</v>
       </c>
     </row>
     <row r="2081">
@@ -49411,19 +49411,19 @@
         <v>3.647907242740922</v>
       </c>
       <c r="C2081" t="n">
-        <v>4.334760461313001</v>
+        <v>4.353791919056603</v>
       </c>
       <c r="D2081" t="n">
         <v>-5.350243989682014</v>
       </c>
       <c r="E2081" t="n">
-        <v>2.194306441126447</v>
+        <v>2.213337898870049</v>
       </c>
       <c r="F2081" t="n">
         <v>0.6771685662181813</v>
       </c>
       <c r="G2081" t="n">
-        <v>4.74106160104391</v>
+        <v>4.760093058787511</v>
       </c>
     </row>
     <row r="2082">
@@ -49434,19 +49434,19 @@
         <v>3.881065366663625</v>
       </c>
       <c r="C2082" t="n">
-        <v>4.347488069294093</v>
+        <v>4.366519527037695</v>
       </c>
       <c r="D2082" t="n">
         <v>-5.450513807641036</v>
       </c>
       <c r="E2082" t="n">
-        <v>2.166926121923931</v>
+        <v>2.185957579667532</v>
       </c>
       <c r="F2082" t="n">
         <v>0.6771685662181813</v>
       </c>
       <c r="G2082" t="n">
-        <v>4.753789209025002</v>
+        <v>4.772820666768603</v>
       </c>
     </row>
     <row r="2083">
@@ -49457,19 +49457,19 @@
         <v>3.717071158424769</v>
       </c>
       <c r="C2083" t="n">
-        <v>4.349434067718481</v>
+        <v>4.368465525462082</v>
       </c>
       <c r="D2083" t="n">
         <v>-5.444521560852224</v>
       </c>
       <c r="E2083" t="n">
-        <v>2.171269019063844</v>
+        <v>2.190300476807445</v>
       </c>
       <c r="F2083" t="n">
         <v>0.6771685662181813</v>
       </c>
       <c r="G2083" t="n">
-        <v>4.75573520744939</v>
+        <v>4.774766665192991</v>
       </c>
     </row>
     <row r="2084">
@@ -49480,19 +49480,19 @@
         <v>3.741942347149218</v>
       </c>
       <c r="C2084" t="n">
-        <v>4.34308820373625</v>
+        <v>4.362119661479851</v>
       </c>
       <c r="D2084" t="n">
         <v>-5.355963599721457</v>
       </c>
       <c r="E2084" t="n">
-        <v>2.200346339533919</v>
+        <v>2.219377797277521</v>
       </c>
       <c r="F2084" t="n">
         <v>0.6771685662181813</v>
       </c>
       <c r="G2084" t="n">
-        <v>4.749389343467159</v>
+        <v>4.76842080121076</v>
       </c>
     </row>
     <row r="2085">
@@ -49503,19 +49503,19 @@
         <v>3.73530072138309</v>
       </c>
       <c r="C2085" t="n">
-        <v>4.342396881175246</v>
+        <v>4.361428338918847</v>
       </c>
       <c r="D2085" t="n">
         <v>-5.338204522218382</v>
       </c>
       <c r="E2085" t="n">
-        <v>2.206758647974145</v>
+        <v>2.225790105717746</v>
       </c>
       <c r="F2085" t="n">
         <v>0.6771685662181813</v>
       </c>
       <c r="G2085" t="n">
-        <v>4.748698020906154</v>
+        <v>4.767729478649755</v>
       </c>
     </row>
     <row r="2086">
@@ -49526,19 +49526,19 @@
         <v>3.778232147720995</v>
       </c>
       <c r="C2086" t="n">
-        <v>4.355179067083832</v>
+        <v>4.374210524827434</v>
       </c>
       <c r="D2086" t="n">
         <v>-5.238574371169315</v>
       </c>
       <c r="E2086" t="n">
-        <v>2.259392894302358</v>
+        <v>2.27842435204596</v>
       </c>
       <c r="F2086" t="n">
         <v>0.7767987172672488</v>
       </c>
       <c r="G2086" t="n">
-        <v>4.821258297444182</v>
+        <v>4.840289755187783</v>
       </c>
     </row>
     <row r="2087">
@@ -49549,19 +49549,19 @@
         <v>3.77535709745527</v>
       </c>
       <c r="C2087" t="n">
-        <v>4.544333332582559</v>
+        <v>4.56336479032616</v>
       </c>
       <c r="D2087" t="n">
         <v>-5.287973879858326</v>
       </c>
       <c r="E2087" t="n">
-        <v>2.42878735632548</v>
+        <v>2.447818814069082</v>
       </c>
       <c r="F2087" t="n">
         <v>0.7870575506989935</v>
       </c>
       <c r="G2087" t="n">
-        <v>5.016567863001955</v>
+        <v>5.035599320745557</v>
       </c>
     </row>
     <row r="2088">
@@ -49572,19 +49572,19 @@
         <v>3.749078058963131</v>
       </c>
       <c r="C2088" t="n">
-        <v>4.531522005685421</v>
+        <v>4.550553463429022</v>
       </c>
       <c r="D2088" t="n">
         <v>-5.08128940621595</v>
       </c>
       <c r="E2088" t="n">
-        <v>2.498649818885293</v>
+        <v>2.517681276628894</v>
       </c>
       <c r="F2088" t="n">
         <v>0.993742024341369</v>
       </c>
       <c r="G2088" t="n">
-        <v>5.127767220290242</v>
+        <v>5.146798678033844</v>
       </c>
     </row>
     <row r="2089">
@@ -49595,19 +49595,19 @@
         <v>3.740284389162541</v>
       </c>
       <c r="C2089" t="n">
-        <v>4.533523519339526</v>
+        <v>4.552554977083127</v>
       </c>
       <c r="D2089" t="n">
         <v>-5.115446301213476</v>
       </c>
       <c r="E2089" t="n">
-        <v>2.486988574540387</v>
+        <v>2.506020032283989</v>
       </c>
       <c r="F2089" t="n">
         <v>0.9101582548005566</v>
       </c>
       <c r="G2089" t="n">
-        <v>5.07961847221986</v>
+        <v>5.098649929963461</v>
       </c>
     </row>
     <row r="2090">
@@ -49618,19 +49618,19 @@
         <v>3.782482115652382</v>
       </c>
       <c r="C2090" t="n">
-        <v>4.887020633329193</v>
+        <v>4.906052091072794</v>
       </c>
       <c r="D2090" t="n">
         <v>-5.022856822152019</v>
       </c>
       <c r="E2090" t="n">
-        <v>2.877521480154638</v>
+        <v>2.896552937898239</v>
       </c>
       <c r="F2090" t="n">
         <v>0.9101582548005566</v>
       </c>
       <c r="G2090" t="n">
-        <v>5.433115586209527</v>
+        <v>5.452147043953128</v>
       </c>
     </row>
     <row r="2091">
@@ -49641,19 +49641,19 @@
         <v>3.809055905108672</v>
       </c>
       <c r="C2091" t="n">
-        <v>4.891583744896296</v>
+        <v>4.910615202639898</v>
       </c>
       <c r="D2091" t="n">
         <v>-5.096017425925164</v>
       </c>
       <c r="E2091" t="n">
-        <v>2.852820350212483</v>
+        <v>2.871851807956084</v>
       </c>
       <c r="F2091" t="n">
         <v>0.8821370547663134</v>
       </c>
       <c r="G2091" t="n">
-        <v>5.420865977756085</v>
+        <v>5.439897435499686</v>
       </c>
     </row>
     <row r="2092">
@@ -49664,19 +49664,19 @@
         <v>3.835202441103564</v>
       </c>
       <c r="C2092" t="n">
-        <v>4.941413686219824</v>
+        <v>4.960445143963425</v>
       </c>
       <c r="D2092" t="n">
         <v>-5.043801116128822</v>
       </c>
       <c r="E2092" t="n">
-        <v>2.923536815454547</v>
+        <v>2.942568273198148</v>
       </c>
       <c r="F2092" t="n">
         <v>0.8821370547663134</v>
       </c>
       <c r="G2092" t="n">
-        <v>5.470695919079613</v>
+        <v>5.489727376823214</v>
       </c>
     </row>
     <row r="2093">
@@ -49687,19 +49687,19 @@
         <v>3.821827147047745</v>
       </c>
       <c r="C2093" t="n">
-        <v>4.950227656429835</v>
+        <v>4.969259114173436</v>
       </c>
       <c r="D2093" t="n">
         <v>-5.011903599043577</v>
       </c>
       <c r="E2093" t="n">
-        <v>2.945109792498656</v>
+        <v>2.964141250242257</v>
       </c>
       <c r="F2093" t="n">
         <v>0.9140345718515592</v>
       </c>
       <c r="G2093" t="n">
-        <v>5.49864839954077</v>
+        <v>5.517679857284372</v>
       </c>
     </row>
     <row r="2094">
@@ -49710,19 +49710,19 @@
         <v>3.825268416650755</v>
       </c>
       <c r="C2094" t="n">
-        <v>4.945865240469032</v>
+        <v>4.964896698212633</v>
       </c>
       <c r="D2094" t="n">
         <v>-5.026658923243717</v>
       </c>
       <c r="E2094" t="n">
-        <v>2.934845246857797</v>
+        <v>2.953876704601398</v>
       </c>
       <c r="F2094" t="n">
         <v>0.9140345718515592</v>
       </c>
       <c r="G2094" t="n">
-        <v>5.494285983579967</v>
+        <v>5.513317441323569</v>
       </c>
     </row>
     <row r="2095">
@@ -49733,19 +49733,19 @@
         <v>3.84504466613575</v>
       </c>
       <c r="C2095" t="n">
-        <v>4.936789743885312</v>
+        <v>4.955821201628913</v>
       </c>
       <c r="D2095" t="n">
         <v>-4.977194299873806</v>
       </c>
       <c r="E2095" t="n">
-        <v>2.945555599622041</v>
+        <v>2.964587057365643</v>
       </c>
       <c r="F2095" t="n">
         <v>0.9634991952214709</v>
       </c>
       <c r="G2095" t="n">
-        <v>5.514889261018195</v>
+        <v>5.533920718761796</v>
       </c>
     </row>
     <row r="2096">
@@ -49756,19 +49756,19 @@
         <v>3.825931790479223</v>
       </c>
       <c r="C2096" t="n">
-        <v>4.933197411600246</v>
+        <v>4.952228869343847</v>
       </c>
       <c r="D2096" t="n">
         <v>-4.81408630772019</v>
       </c>
       <c r="E2096" t="n">
-        <v>3.007206464198422</v>
+        <v>3.026237921942023</v>
       </c>
       <c r="F2096" t="n">
         <v>1.126607187375086</v>
       </c>
       <c r="G2096" t="n">
-        <v>5.609161724025298</v>
+        <v>5.628193181768899</v>
       </c>
     </row>
     <row r="2097">
@@ -49779,19 +49779,19 @@
         <v>3.847096478844245</v>
       </c>
       <c r="C2097" t="n">
-        <v>4.942244448291374</v>
+        <v>4.961275906034976</v>
       </c>
       <c r="D2097" t="n">
         <v>-4.681278682223024</v>
       </c>
       <c r="E2097" t="n">
-        <v>3.069376551088417</v>
+        <v>3.088408008832018</v>
       </c>
       <c r="F2097" t="n">
         <v>1.126607187375086</v>
       </c>
       <c r="G2097" t="n">
-        <v>5.618208760716426</v>
+        <v>5.637240218460027</v>
       </c>
     </row>
     <row r="2098">
@@ -49802,19 +49802,19 @@
         <v>3.832425987790948</v>
       </c>
       <c r="C2098" t="n">
-        <v>4.943101913277496</v>
+        <v>4.962133371021097</v>
       </c>
       <c r="D2098" t="n">
         <v>-4.743986598697582</v>
       </c>
       <c r="E2098" t="n">
-        <v>3.045150849484715</v>
+        <v>3.064182307228316</v>
       </c>
       <c r="F2098" t="n">
         <v>1.063899270900528</v>
       </c>
       <c r="G2098" t="n">
-        <v>5.581441475817813</v>
+        <v>5.600472933561415</v>
       </c>
     </row>
     <row r="2099">
@@ -49825,19 +49825,19 @@
         <v>3.861579399578995</v>
       </c>
       <c r="C2099" t="n">
-        <v>4.906011330067848</v>
+        <v>4.925042787811449</v>
       </c>
       <c r="D2099" t="n">
         <v>-4.695978474853889</v>
       </c>
       <c r="E2099" t="n">
-        <v>3.027263515812544</v>
+        <v>3.046294973556146</v>
       </c>
       <c r="F2099" t="n">
         <v>1.063899270900528</v>
       </c>
       <c r="G2099" t="n">
-        <v>5.544350892608166</v>
+        <v>5.563382350351767</v>
       </c>
     </row>
     <row r="2100">
@@ -49848,19 +49848,19 @@
         <v>3.872253907629883</v>
       </c>
       <c r="C2100" t="n">
-        <v>4.909943583625799</v>
+        <v>4.9289750413694</v>
       </c>
       <c r="D2100" t="n">
         <v>-4.617152817670299</v>
       </c>
       <c r="E2100" t="n">
-        <v>3.062726032243931</v>
+        <v>3.081757489987532</v>
       </c>
       <c r="F2100" t="n">
         <v>1.142724928084119</v>
       </c>
       <c r="G2100" t="n">
-        <v>5.59557854047627</v>
+        <v>5.614609998219871</v>
       </c>
     </row>
     <row r="2101">
@@ -49871,19 +49871,19 @@
         <v>3.868502531686405</v>
       </c>
       <c r="C2101" t="n">
-        <v>4.904842676232835</v>
+        <v>4.923874133976437</v>
       </c>
       <c r="D2101" t="n">
         <v>-4.425218016416425</v>
       </c>
       <c r="E2101" t="n">
-        <v>3.134399045352517</v>
+        <v>3.153430503096119</v>
       </c>
       <c r="F2101" t="n">
         <v>1.142724928084119</v>
       </c>
       <c r="G2101" t="n">
-        <v>5.590477633083307</v>
+        <v>5.609509090826908</v>
       </c>
     </row>
     <row r="2102">
@@ -49891,22 +49891,22 @@
         <v>45564</v>
       </c>
       <c r="B2102" t="n">
-        <v>3.766949457833312</v>
+        <v>3.792259287839513</v>
       </c>
       <c r="C2102" t="n">
-        <v>4.900196585621931</v>
+        <v>4.919228043365532</v>
       </c>
       <c r="D2102" t="n">
-        <v>-4.317734583626807</v>
+        <v>-4.307044638398498</v>
       </c>
       <c r="E2102" t="n">
-        <v>3.17274632785746</v>
+        <v>3.196053763692385</v>
       </c>
       <c r="F2102" t="n">
-        <v>1.250208360873736</v>
+        <v>1.260898306102046</v>
       </c>
       <c r="G2102" t="n">
-        <v>5.650321602146173</v>
+        <v>5.67576702702676</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240930.xlsx
+++ b/tame_output/ON/bt/strategyON_20240930.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>54.8%</t>
+          <t>57.8%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -610,12 +610,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.2%</t>
+          <t>53.3%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>65.0%</t>
+          <t>64.8%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>17.9%</t>
+          <t>18.2%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>51.1%</t>
+          <t>61.9%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>113.7%</t>
+          <t>113.1%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>44.1%</t>
+          <t>44.0%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.58</t>
+          <t>2.57</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>47.3%</t>
+          <t>47.2%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>10.9%</t>
+          <t>10.8%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>95.9%</t>
+          <t>94.8%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.7</t>
+          <t>2.6</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-8.3%</t>
+          <t>-8.4%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>180.3%</t>
+          <t>178.4%</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-75.2%</t>
+          <t>-75.3%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>107.7%</t>
+          <t>107.8%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -949,7 +949,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>123.0%</t>
+          <t>123.1%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-47.9%</t>
+          <t>-48.0%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-71.3%</t>
+          <t>-71.4%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>422.6%</t>
+          <t>421.8%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-6.0%</t>
+          <t>-7.0%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-592.3%</t>
+          <t>-594.6%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>45.4%</t>
+          <t>44.7%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>59.9%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>57.7%</t>
+          <t>57.6%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1140,7 +1140,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>-8.7%</t>
+          <t>-9.3%</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>14.4%</t>
+          <t>14.3%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>40.3%</t>
+          <t>39.3%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>50.1%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-4.8%</t>
+          <t>-3.9%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14.8%</t>
+          <t>15.4%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-56.6%</t>
+          <t>-59.4%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-2.7%</t>
+          <t>-3.1%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.3%</t>
+          <t>66.4%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1265,7 +1265,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>62.4%</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.3%</t>
+          <t>10.4%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-26.1%</t>
+          <t>-24.7%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>4.1%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.2%</t>
+          <t>55.3%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>42.2%</t>
+          <t>44.9%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-402.3%</t>
+          <t>-392.5%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-97.9%</t>
+          <t>-100.2%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>126.0%</t>
+          <t>124.8%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>57.9%</t>
+          <t>57.8%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2.18</t>
+          <t>2.16</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>59.7%</t>
+          <t>59.8%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>56.9%</t>
+          <t>56.8%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1447,7 +1447,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>14.2%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>114.9%</t>
+          <t>113.0%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>2.4</t>
+          <t>2.3</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-17.3%</t>
+          <t>-17.1%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>36.5%</t>
+          <t>36.6%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>121.6%</t>
+          <t>118.3%</t>
         </is>
       </c>
     </row>
@@ -47706,7 +47706,7 @@
         <v>45469</v>
       </c>
       <c r="B2007" t="n">
-        <v>3.71494119332163</v>
+        <v>3.714941193321629</v>
       </c>
       <c r="C2007" t="n">
         <v>3.209131053508234</v>
@@ -47729,7 +47729,7 @@
         <v>45470</v>
       </c>
       <c r="B2008" t="n">
-        <v>3.727898186347701</v>
+        <v>3.7278981863477</v>
       </c>
       <c r="C2008" t="n">
         <v>3.207242866402009</v>
@@ -47752,7 +47752,7 @@
         <v>45471</v>
       </c>
       <c r="B2009" t="n">
-        <v>3.710654104887746</v>
+        <v>3.710654104887745</v>
       </c>
       <c r="C2009" t="n">
         <v>3.202063096004871</v>
@@ -47775,7 +47775,7 @@
         <v>45472</v>
       </c>
       <c r="B2010" t="n">
-        <v>3.712897612343064</v>
+        <v>3.712897612343062</v>
       </c>
       <c r="C2010" t="n">
         <v>3.200497106215023</v>
@@ -47798,7 +47798,7 @@
         <v>45473</v>
       </c>
       <c r="B2011" t="n">
-        <v>3.754596135389347</v>
+        <v>3.754596135389345</v>
       </c>
       <c r="C2011" t="n">
         <v>3.213570513080942</v>
@@ -47821,7 +47821,7 @@
         <v>45474</v>
       </c>
       <c r="B2012" t="n">
-        <v>3.749882691378389</v>
+        <v>3.749882691378387</v>
       </c>
       <c r="C2012" t="n">
         <v>3.205575709863882</v>
@@ -47844,7 +47844,7 @@
         <v>45475</v>
       </c>
       <c r="B2013" t="n">
-        <v>3.715819895006972</v>
+        <v>3.715819895006971</v>
       </c>
       <c r="C2013" t="n">
         <v>3.204099750990884</v>
@@ -47867,7 +47867,7 @@
         <v>45476</v>
       </c>
       <c r="B2014" t="n">
-        <v>3.684895778787385</v>
+        <v>3.684895778787384</v>
       </c>
       <c r="C2014" t="n">
         <v>3.200864194968083</v>
@@ -47890,7 +47890,7 @@
         <v>45477</v>
       </c>
       <c r="B2015" t="n">
-        <v>3.619348081585935</v>
+        <v>3.619348081585933</v>
       </c>
       <c r="C2015" t="n">
         <v>3.267570154558586</v>
@@ -47913,7 +47913,7 @@
         <v>45478</v>
       </c>
       <c r="B2016" t="n">
-        <v>3.640750087814665</v>
+        <v>3.640750087814663</v>
       </c>
       <c r="C2016" t="n">
         <v>3.407881873560433</v>
@@ -47936,7 +47936,7 @@
         <v>45479</v>
       </c>
       <c r="B2017" t="n">
-        <v>3.668289004237094</v>
+        <v>3.668289004237092</v>
       </c>
       <c r="C2017" t="n">
         <v>3.476862142706073</v>
@@ -47959,7 +47959,7 @@
         <v>45480</v>
       </c>
       <c r="B2018" t="n">
-        <v>3.619923016423387</v>
+        <v>3.619923016423385</v>
       </c>
       <c r="C2018" t="n">
         <v>3.462913344826194</v>
@@ -47982,7 +47982,7 @@
         <v>45481</v>
       </c>
       <c r="B2019" t="n">
-        <v>3.656332733609752</v>
+        <v>3.656332733609751</v>
       </c>
       <c r="C2019" t="n">
         <v>3.474783833881608</v>
@@ -48005,7 +48005,7 @@
         <v>45482</v>
       </c>
       <c r="B2020" t="n">
-        <v>3.674028535973156</v>
+        <v>3.674028535973154</v>
       </c>
       <c r="C2020" t="n">
         <v>3.475994368400552</v>
@@ -48028,7 +48028,7 @@
         <v>45483</v>
       </c>
       <c r="B2021" t="n">
-        <v>3.663509457251943</v>
+        <v>3.663509457251942</v>
       </c>
       <c r="C2021" t="n">
         <v>3.480116110627873</v>
@@ -48051,7 +48051,7 @@
         <v>45484</v>
       </c>
       <c r="B2022" t="n">
-        <v>3.652149152916198</v>
+        <v>3.652149152916196</v>
       </c>
       <c r="C2022" t="n">
         <v>3.475193963364063</v>
@@ -48074,7 +48074,7 @@
         <v>45485</v>
       </c>
       <c r="B2023" t="n">
-        <v>3.667962306830326</v>
+        <v>3.667962306830324</v>
       </c>
       <c r="C2023" t="n">
         <v>3.637398020063107</v>
@@ -48097,7 +48097,7 @@
         <v>45486</v>
       </c>
       <c r="B2024" t="n">
-        <v>3.696539468071548</v>
+        <v>3.696539468071546</v>
       </c>
       <c r="C2024" t="n">
         <v>3.632244658026921</v>
@@ -48120,7 +48120,7 @@
         <v>45487</v>
       </c>
       <c r="B2025" t="n">
-        <v>3.750044015868144</v>
+        <v>3.750044015868141</v>
       </c>
       <c r="C2025" t="n">
         <v>3.642474075595412</v>
@@ -48143,22 +48143,22 @@
         <v>45488</v>
       </c>
       <c r="B2026" t="n">
-        <v>3.783632867332691</v>
+        <v>3.783632867332688</v>
       </c>
       <c r="C2026" t="n">
         <v>3.651399714051315</v>
       </c>
       <c r="D2026" t="n">
-        <v>-5.778940788711521</v>
+        <v>-5.802101772984098</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.339466974252959</v>
+        <v>1.330202580543927</v>
       </c>
       <c r="F2026" t="n">
-        <v>-0.1298787761931792</v>
+        <v>-0.1530397604657562</v>
       </c>
       <c r="G2026" t="n">
-        <v>3.573472448335407</v>
+        <v>3.559575857771861</v>
       </c>
     </row>
     <row r="2027">
@@ -48166,22 +48166,22 @@
         <v>45489</v>
       </c>
       <c r="B2027" t="n">
-        <v>3.798296784231807</v>
+        <v>3.798296784231805</v>
       </c>
       <c r="C2027" t="n">
         <v>3.64355260129549</v>
       </c>
       <c r="D2027" t="n">
-        <v>-5.668934505234299</v>
+        <v>-5.692095489506876</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.375622374888022</v>
+        <v>1.366357981178992</v>
       </c>
       <c r="F2027" t="n">
-        <v>-0.106674204275904</v>
+        <v>-0.129835188548481</v>
       </c>
       <c r="G2027" t="n">
-        <v>3.579548078729948</v>
+        <v>3.565651488166401</v>
       </c>
     </row>
     <row r="2028">
@@ -48189,22 +48189,22 @@
         <v>45490</v>
       </c>
       <c r="B2028" t="n">
-        <v>3.785563924818519</v>
+        <v>3.785563924818517</v>
       </c>
       <c r="C2028" t="n">
         <v>3.647802612017464</v>
       </c>
       <c r="D2028" t="n">
-        <v>-5.525874929493373</v>
+        <v>-5.54903591376595</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.437096215906367</v>
+        <v>1.427831822197336</v>
       </c>
       <c r="F2028" t="n">
-        <v>-0.09866077768592474</v>
+        <v>-0.1218217619585018</v>
       </c>
       <c r="G2028" t="n">
-        <v>3.588606145405909</v>
+        <v>3.574709554842364</v>
       </c>
     </row>
     <row r="2029">
@@ -48212,22 +48212,22 @@
         <v>45491</v>
       </c>
       <c r="B2029" t="n">
-        <v>3.777237412051786</v>
+        <v>3.777237412051783</v>
       </c>
       <c r="C2029" t="n">
         <v>3.6550634949</v>
       </c>
       <c r="D2029" t="n">
-        <v>-5.224428204021535</v>
+        <v>-5.247589188294112</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.564935788977638</v>
+        <v>1.555671395268607</v>
       </c>
       <c r="F2029" t="n">
-        <v>0.2027859477859125</v>
+        <v>0.1796249635133355</v>
       </c>
       <c r="G2029" t="n">
-        <v>3.776735063571548</v>
+        <v>3.762838473008002</v>
       </c>
     </row>
     <row r="2030">
@@ -48235,22 +48235,22 @@
         <v>45492</v>
       </c>
       <c r="B2030" t="n">
-        <v>3.812635940679623</v>
+        <v>3.812635940679621</v>
       </c>
       <c r="C2030" t="n">
         <v>3.656034672652711</v>
       </c>
       <c r="D2030" t="n">
-        <v>-5.249018448256719</v>
+        <v>-5.272179432529296</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.556070869036275</v>
+        <v>1.546806475327244</v>
       </c>
       <c r="F2030" t="n">
-        <v>0.2027859477859125</v>
+        <v>0.1796249635133355</v>
       </c>
       <c r="G2030" t="n">
-        <v>3.777706241324259</v>
+        <v>3.763809650760713</v>
       </c>
     </row>
     <row r="2031">
@@ -48258,22 +48258,22 @@
         <v>45493</v>
       </c>
       <c r="B2031" t="n">
-        <v>3.821184182474158</v>
+        <v>3.821184182474155</v>
       </c>
       <c r="C2031" t="n">
         <v>3.656877577032466</v>
       </c>
       <c r="D2031" t="n">
-        <v>-5.197980072250199</v>
+        <v>-5.221141056522776</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.577329123818639</v>
+        <v>1.568064730109608</v>
       </c>
       <c r="F2031" t="n">
-        <v>0.2027859477859125</v>
+        <v>0.1796249635133355</v>
       </c>
       <c r="G2031" t="n">
-        <v>3.778549145704014</v>
+        <v>3.764652555140468</v>
       </c>
     </row>
     <row r="2032">
@@ -48281,22 +48281,22 @@
         <v>45494</v>
       </c>
       <c r="B2032" t="n">
-        <v>3.831734516969542</v>
+        <v>3.831734516969539</v>
       </c>
       <c r="C2032" t="n">
         <v>3.675915675906612</v>
       </c>
       <c r="D2032" t="n">
-        <v>-5.169131395426739</v>
+        <v>-5.192292379699316</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.607906693422168</v>
+        <v>1.598642299713138</v>
       </c>
       <c r="F2032" t="n">
-        <v>0.2316346246093728</v>
+        <v>0.2084736403367958</v>
       </c>
       <c r="G2032" t="n">
-        <v>3.814896450672236</v>
+        <v>3.80099986010869</v>
       </c>
     </row>
     <row r="2033">
@@ -48304,22 +48304,22 @@
         <v>45495</v>
       </c>
       <c r="B2033" t="n">
-        <v>3.825752932700476</v>
+        <v>3.825752932700473</v>
       </c>
       <c r="C2033" t="n">
         <v>3.492099672030546</v>
       </c>
       <c r="D2033" t="n">
-        <v>-5.072496483408099</v>
+        <v>-5.095657467680676</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.462744654353559</v>
+        <v>1.453480260644528</v>
       </c>
       <c r="F2033" t="n">
-        <v>0.3282695366280127</v>
+        <v>0.3051085523554357</v>
       </c>
       <c r="G2033" t="n">
-        <v>3.689061394007354</v>
+        <v>3.675164803443808</v>
       </c>
     </row>
     <row r="2034">
@@ -48327,22 +48327,22 @@
         <v>45496</v>
       </c>
       <c r="B2034" t="n">
-        <v>3.804688961077638</v>
+        <v>3.804688961077636</v>
       </c>
       <c r="C2034" t="n">
         <v>3.495601716104511</v>
       </c>
       <c r="D2034" t="n">
-        <v>-5.003458472459631</v>
+        <v>-5.026619456732208</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.49386190280691</v>
+        <v>1.484597509097879</v>
       </c>
       <c r="F2034" t="n">
-        <v>0.3973075475764808</v>
+        <v>0.3741465633039038</v>
       </c>
       <c r="G2034" t="n">
-        <v>3.733986244650399</v>
+        <v>3.720089654086853</v>
       </c>
     </row>
     <row r="2035">
@@ -48350,22 +48350,22 @@
         <v>45497</v>
       </c>
       <c r="B2035" t="n">
-        <v>3.775028860833457</v>
+        <v>3.775028860833455</v>
       </c>
       <c r="C2035" t="n">
         <v>3.480028535180593</v>
       </c>
       <c r="D2035" t="n">
-        <v>-4.984671372090692</v>
+        <v>-5.007832356363269</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.485803562030568</v>
+        <v>1.476539168321537</v>
       </c>
       <c r="F2035" t="n">
-        <v>0.4160946479454193</v>
+        <v>0.3929336636728423</v>
       </c>
       <c r="G2035" t="n">
-        <v>3.729685323947845</v>
+        <v>3.715788733384298</v>
       </c>
     </row>
     <row r="2036">
@@ -48373,22 +48373,22 @@
         <v>45498</v>
       </c>
       <c r="B2036" t="n">
-        <v>3.821030660077626</v>
+        <v>3.821030660077624</v>
       </c>
       <c r="C2036" t="n">
         <v>3.479216245617023</v>
       </c>
       <c r="D2036" t="n">
-        <v>-4.907572770548819</v>
+        <v>-4.930733754821397</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.515830713083747</v>
+        <v>1.506566319374716</v>
       </c>
       <c r="F2036" t="n">
-        <v>0.4160946479454193</v>
+        <v>0.3929336636728423</v>
       </c>
       <c r="G2036" t="n">
-        <v>3.728873034384275</v>
+        <v>3.714976443820728</v>
       </c>
     </row>
     <row r="2037">
@@ -48396,22 +48396,22 @@
         <v>45499</v>
       </c>
       <c r="B2037" t="n">
-        <v>3.832307024147908</v>
+        <v>3.832307024147906</v>
       </c>
       <c r="C2037" t="n">
         <v>3.489085024742095</v>
       </c>
       <c r="D2037" t="n">
-        <v>-4.917957965438709</v>
+        <v>-4.941118949711286</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.521545414252864</v>
+        <v>1.512281020543833</v>
       </c>
       <c r="F2037" t="n">
-        <v>0.40570945305553</v>
+        <v>0.382548468782953</v>
       </c>
       <c r="G2037" t="n">
-        <v>3.732510696575413</v>
+        <v>3.718614106011867</v>
       </c>
     </row>
     <row r="2038">
@@ -48419,22 +48419,22 @@
         <v>45500</v>
       </c>
       <c r="B2038" t="n">
-        <v>3.834415493735278</v>
+        <v>3.834415493735277</v>
       </c>
       <c r="C2038" t="n">
         <v>3.55992203051852</v>
       </c>
       <c r="D2038" t="n">
-        <v>-4.936546124160934</v>
+        <v>-4.959707108433511</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.584947156540399</v>
+        <v>1.575682762831368</v>
       </c>
       <c r="F2038" t="n">
-        <v>0.3871212943333046</v>
+        <v>0.3639603100607276</v>
       </c>
       <c r="G2038" t="n">
-        <v>3.792194807118503</v>
+        <v>3.778298216554957</v>
       </c>
     </row>
     <row r="2039">
@@ -48442,22 +48442,22 @@
         <v>45501</v>
       </c>
       <c r="B2039" t="n">
-        <v>3.855120535496552</v>
+        <v>3.855120535496551</v>
       </c>
       <c r="C2039" t="n">
         <v>3.556791041336819</v>
       </c>
       <c r="D2039" t="n">
-        <v>-4.93684467085697</v>
+        <v>-4.960005655129547</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.581696748680283</v>
+        <v>1.572432354971252</v>
       </c>
       <c r="F2039" t="n">
-        <v>0.3868227476372687</v>
+        <v>0.3636617633646917</v>
       </c>
       <c r="G2039" t="n">
-        <v>3.78888468991918</v>
+        <v>3.774988099355634</v>
       </c>
     </row>
     <row r="2040">
@@ -48465,22 +48465,22 @@
         <v>45502</v>
       </c>
       <c r="B2040" t="n">
-        <v>3.815643212108855</v>
+        <v>3.815643212108852</v>
       </c>
       <c r="C2040" t="n">
         <v>3.56132193627621</v>
       </c>
       <c r="D2040" t="n">
-        <v>-4.836021537166542</v>
+        <v>-4.859182521439119</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.626556897095845</v>
+        <v>1.617292503386815</v>
       </c>
       <c r="F2040" t="n">
-        <v>0.3992869631216225</v>
+        <v>0.3761259788490455</v>
       </c>
       <c r="G2040" t="n">
-        <v>3.800894114149184</v>
+        <v>3.786997523585638</v>
       </c>
     </row>
     <row r="2041">
@@ -48488,22 +48488,22 @@
         <v>45503</v>
       </c>
       <c r="B2041" t="n">
-        <v>3.807356168121466</v>
+        <v>3.807356168121463</v>
       </c>
       <c r="C2041" t="n">
         <v>3.561451189754754</v>
       </c>
       <c r="D2041" t="n">
-        <v>-4.645240176414134</v>
+        <v>-4.668401160686711</v>
       </c>
       <c r="E2041" t="n">
-        <v>1.702998694875352</v>
+        <v>1.693734301166321</v>
       </c>
       <c r="F2041" t="n">
-        <v>0.5900683238740299</v>
+        <v>0.5669073396014529</v>
       </c>
       <c r="G2041" t="n">
-        <v>3.915492184079172</v>
+        <v>3.901595593515625</v>
       </c>
     </row>
     <row r="2042">
@@ -48511,22 +48511,22 @@
         <v>45504</v>
       </c>
       <c r="B2042" t="n">
-        <v>3.775233033906079</v>
+        <v>3.775233033906076</v>
       </c>
       <c r="C2042" t="n">
         <v>3.54128803549235</v>
       </c>
       <c r="D2042" t="n">
-        <v>-4.538276818564713</v>
+        <v>-4.56143780283729</v>
       </c>
       <c r="E2042" t="n">
-        <v>1.725620883752717</v>
+        <v>1.716356490043686</v>
       </c>
       <c r="F2042" t="n">
-        <v>0.6485329318338313</v>
+        <v>0.6253719475612544</v>
       </c>
       <c r="G2042" t="n">
-        <v>3.930407794592649</v>
+        <v>3.916511204029103</v>
       </c>
     </row>
     <row r="2043">
@@ -48534,22 +48534,22 @@
         <v>45505</v>
       </c>
       <c r="B2043" t="n">
-        <v>3.785761685912983</v>
+        <v>3.785761685912981</v>
       </c>
       <c r="C2043" t="n">
         <v>3.576254972104409</v>
       </c>
       <c r="D2043" t="n">
-        <v>-4.48294623066295</v>
+        <v>-4.506107214935527</v>
       </c>
       <c r="E2043" t="n">
-        <v>1.782720055525481</v>
+        <v>1.77345566181645</v>
       </c>
       <c r="F2043" t="n">
-        <v>0.7038635197355935</v>
+        <v>0.6807025354630165</v>
       </c>
       <c r="G2043" t="n">
-        <v>3.998573083945764</v>
+        <v>3.984676493382219</v>
       </c>
     </row>
     <row r="2044">
@@ -48557,22 +48557,22 @@
         <v>45506</v>
       </c>
       <c r="B2044" t="n">
-        <v>3.743767956539893</v>
+        <v>3.74376795653989</v>
       </c>
       <c r="C2044" t="n">
         <v>3.569941540005846</v>
       </c>
       <c r="D2044" t="n">
-        <v>-4.470892103749987</v>
+        <v>-4.494053088022564</v>
       </c>
       <c r="E2044" t="n">
-        <v>1.781228274192103</v>
+        <v>1.771963880483073</v>
       </c>
       <c r="F2044" t="n">
-        <v>0.7159176466485563</v>
+        <v>0.6927566623759793</v>
       </c>
       <c r="G2044" t="n">
-        <v>3.99949212799498</v>
+        <v>3.985595537431434</v>
       </c>
     </row>
     <row r="2045">
@@ -48580,22 +48580,22 @@
         <v>45507</v>
       </c>
       <c r="B2045" t="n">
-        <v>3.725010844811008</v>
+        <v>3.725010844811005</v>
       </c>
       <c r="C2045" t="n">
         <v>3.571822170189982</v>
       </c>
       <c r="D2045" t="n">
-        <v>-4.512047223318208</v>
+        <v>-4.535208207590785</v>
       </c>
       <c r="E2045" t="n">
-        <v>1.766646856548951</v>
+        <v>1.75738246283992</v>
       </c>
       <c r="F2045" t="n">
-        <v>0.6747625270803354</v>
+        <v>0.6516015428077584</v>
       </c>
       <c r="G2045" t="n">
-        <v>3.976679686438183</v>
+        <v>3.962783095874637</v>
       </c>
     </row>
     <row r="2046">
@@ -48603,22 +48603,22 @@
         <v>45508</v>
       </c>
       <c r="B2046" t="n">
-        <v>3.612322444382919</v>
+        <v>3.612322444382916</v>
       </c>
       <c r="C2046" t="n">
         <v>3.584673196067865</v>
       </c>
       <c r="D2046" t="n">
-        <v>-4.443998660626678</v>
+        <v>-4.467159644899255</v>
       </c>
       <c r="E2046" t="n">
-        <v>1.806717307503445</v>
+        <v>1.797452913794414</v>
       </c>
       <c r="F2046" t="n">
-        <v>0.7428110897718652</v>
+        <v>0.7196501054992882</v>
       </c>
       <c r="G2046" t="n">
-        <v>4.030359849930984</v>
+        <v>4.016463259367438</v>
       </c>
     </row>
     <row r="2047">
@@ -48626,22 +48626,22 @@
         <v>45509</v>
       </c>
       <c r="B2047" t="n">
-        <v>3.645256780013425</v>
+        <v>3.645256780013423</v>
       </c>
       <c r="C2047" t="n">
         <v>3.604875866241459</v>
       </c>
       <c r="D2047" t="n">
-        <v>-4.675599053796179</v>
+        <v>-4.698760038068756</v>
       </c>
       <c r="E2047" t="n">
-        <v>1.734279820409239</v>
+        <v>1.725015426700208</v>
       </c>
       <c r="F2047" t="n">
-        <v>0.7428110897718652</v>
+        <v>0.7196501054992882</v>
       </c>
       <c r="G2047" t="n">
-        <v>4.050562520104578</v>
+        <v>4.036665929541032</v>
       </c>
     </row>
     <row r="2048">
@@ -48649,22 +48649,22 @@
         <v>45510</v>
       </c>
       <c r="B2048" t="n">
-        <v>3.666747201498968</v>
+        <v>3.666747201498965</v>
       </c>
       <c r="C2048" t="n">
         <v>3.588482102308341</v>
       </c>
       <c r="D2048" t="n">
-        <v>-4.725650599325398</v>
+        <v>-4.748811583597975</v>
       </c>
       <c r="E2048" t="n">
-        <v>1.697865438264434</v>
+        <v>1.688601044555403</v>
       </c>
       <c r="F2048" t="n">
-        <v>0.7428110897718652</v>
+        <v>0.7196501054992882</v>
       </c>
       <c r="G2048" t="n">
-        <v>4.03416875617146</v>
+        <v>4.020272165607914</v>
       </c>
     </row>
     <row r="2049">
@@ -48672,22 +48672,22 @@
         <v>45511</v>
       </c>
       <c r="B2049" t="n">
-        <v>3.670048702800097</v>
+        <v>3.670048702800094</v>
       </c>
       <c r="C2049" t="n">
         <v>3.548734015901807</v>
       </c>
       <c r="D2049" t="n">
-        <v>-4.900757431901843</v>
+        <v>-4.92391841617442</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.588074618827322</v>
+        <v>1.578810225118292</v>
       </c>
       <c r="F2049" t="n">
-        <v>0.7428110897718652</v>
+        <v>0.7196501054992882</v>
       </c>
       <c r="G2049" t="n">
-        <v>3.994420669764927</v>
+        <v>3.980524079201381</v>
       </c>
     </row>
     <row r="2050">
@@ -48695,22 +48695,22 @@
         <v>45512</v>
       </c>
       <c r="B2050" t="n">
-        <v>3.745573148660849</v>
+        <v>3.745573148660847</v>
       </c>
       <c r="C2050" t="n">
         <v>3.555756634898747</v>
       </c>
       <c r="D2050" t="n">
-        <v>-4.70465727847132</v>
+        <v>-4.727818262743897</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.673537299196472</v>
+        <v>1.664272905487441</v>
       </c>
       <c r="F2050" t="n">
-        <v>0.9389112432023881</v>
+        <v>0.9157502589298111</v>
       </c>
       <c r="G2050" t="n">
-        <v>4.119103380820181</v>
+        <v>4.105206790256634</v>
       </c>
     </row>
     <row r="2051">
@@ -48718,22 +48718,22 @@
         <v>45513</v>
       </c>
       <c r="B2051" t="n">
-        <v>3.730570473395087</v>
+        <v>3.730570473395083</v>
       </c>
       <c r="C2051" t="n">
         <v>3.654927634471652</v>
       </c>
       <c r="D2051" t="n">
-        <v>-4.551631886358035</v>
+        <v>-4.574792870630612</v>
       </c>
       <c r="E2051" t="n">
-        <v>1.83391845561469</v>
+        <v>1.824654061905659</v>
       </c>
       <c r="F2051" t="n">
-        <v>1.091936635315672</v>
+        <v>1.068775651043095</v>
       </c>
       <c r="G2051" t="n">
-        <v>4.310089615661055</v>
+        <v>4.29619302509751</v>
       </c>
     </row>
     <row r="2052">
@@ -48741,22 +48741,22 @@
         <v>45514</v>
       </c>
       <c r="B2052" t="n">
-        <v>3.741278332791149</v>
+        <v>3.741278332791145</v>
       </c>
       <c r="C2052" t="n">
         <v>3.842393859379944</v>
       </c>
       <c r="D2052" t="n">
-        <v>-4.579939200231306</v>
+        <v>-4.603100184503883</v>
       </c>
       <c r="E2052" t="n">
-        <v>2.010061754973674</v>
+        <v>2.000797361264643</v>
       </c>
       <c r="F2052" t="n">
-        <v>1.091936635315672</v>
+        <v>1.068775651043095</v>
       </c>
       <c r="G2052" t="n">
-        <v>4.497555840569348</v>
+        <v>4.483659250005802</v>
       </c>
     </row>
     <row r="2053">
@@ -48764,22 +48764,22 @@
         <v>45515</v>
       </c>
       <c r="B2053" t="n">
-        <v>3.699115615620435</v>
+        <v>3.699115615620431</v>
       </c>
       <c r="C2053" t="n">
         <v>3.811796810734027</v>
       </c>
       <c r="D2053" t="n">
-        <v>-4.746532425344828</v>
+        <v>-4.769693409617405</v>
       </c>
       <c r="E2053" t="n">
-        <v>1.912827416282348</v>
+        <v>1.903563022573317</v>
       </c>
       <c r="F2053" t="n">
-        <v>0.9253434102021496</v>
+        <v>0.9021824259295728</v>
       </c>
       <c r="G2053" t="n">
-        <v>4.367002856855317</v>
+        <v>4.353106266291771</v>
       </c>
     </row>
     <row r="2054">
@@ -48787,22 +48787,22 @@
         <v>45516</v>
       </c>
       <c r="B2054" t="n">
-        <v>3.708182519285647</v>
+        <v>3.708182519285644</v>
       </c>
       <c r="C2054" t="n">
         <v>3.815473213395745</v>
       </c>
       <c r="D2054" t="n">
-        <v>-4.723496631983262</v>
+        <v>-4.746657616255839</v>
       </c>
       <c r="E2054" t="n">
-        <v>1.925718136288692</v>
+        <v>1.916453742579662</v>
       </c>
       <c r="F2054" t="n">
-        <v>0.9253434102021496</v>
+        <v>0.9021824259295728</v>
       </c>
       <c r="G2054" t="n">
-        <v>4.370679259517035</v>
+        <v>4.356782668953489</v>
       </c>
     </row>
     <row r="2055">
@@ -48810,22 +48810,22 @@
         <v>45517</v>
       </c>
       <c r="B2055" t="n">
-        <v>3.740581401399469</v>
+        <v>3.740581401399465</v>
       </c>
       <c r="C2055" t="n">
         <v>3.81309126851924</v>
       </c>
       <c r="D2055" t="n">
-        <v>-4.694250651527565</v>
+        <v>-4.717411635800143</v>
       </c>
       <c r="E2055" t="n">
-        <v>1.935034583594466</v>
+        <v>1.925770189885435</v>
       </c>
       <c r="F2055" t="n">
-        <v>0.9253434102021496</v>
+        <v>0.9021824259295728</v>
       </c>
       <c r="G2055" t="n">
-        <v>4.368297314640531</v>
+        <v>4.354400724076984</v>
       </c>
     </row>
     <row r="2056">
@@ -48833,22 +48833,22 @@
         <v>45518</v>
       </c>
       <c r="B2056" t="n">
-        <v>3.69940464225637</v>
+        <v>3.699404642256367</v>
       </c>
       <c r="C2056" t="n">
         <v>3.810384507676875</v>
       </c>
       <c r="D2056" t="n">
-        <v>-4.801176199405417</v>
+        <v>-4.824337183677994</v>
       </c>
       <c r="E2056" t="n">
-        <v>1.889557603600961</v>
+        <v>1.88029320989193</v>
       </c>
       <c r="F2056" t="n">
-        <v>0.8184178623242983</v>
+        <v>0.7952568780517214</v>
       </c>
       <c r="G2056" t="n">
-        <v>4.301435225071454</v>
+        <v>4.287538634507908</v>
       </c>
     </row>
     <row r="2057">
@@ -48856,22 +48856,22 @@
         <v>45519</v>
       </c>
       <c r="B2057" t="n">
-        <v>3.689942600700999</v>
+        <v>3.689942600700996</v>
       </c>
       <c r="C2057" t="n">
         <v>3.811813309820109</v>
       </c>
       <c r="D2057" t="n">
-        <v>-4.946194757912665</v>
+        <v>-4.969355742185242</v>
       </c>
       <c r="E2057" t="n">
-        <v>1.832978982341295</v>
+        <v>1.823714588632265</v>
       </c>
       <c r="F2057" t="n">
-        <v>0.6733993038170497</v>
+        <v>0.6502383195444729</v>
       </c>
       <c r="G2057" t="n">
-        <v>4.215852892110339</v>
+        <v>4.201956301546794</v>
       </c>
     </row>
     <row r="2058">
@@ -48879,22 +48879,22 @@
         <v>45520</v>
       </c>
       <c r="B2058" t="n">
-        <v>3.711852429687012</v>
+        <v>3.711852429687008</v>
       </c>
       <c r="C2058" t="n">
         <v>3.911744549077862</v>
       </c>
       <c r="D2058" t="n">
-        <v>-5.064536523697383</v>
+        <v>-5.08769750796996</v>
       </c>
       <c r="E2058" t="n">
-        <v>1.885573515285161</v>
+        <v>1.876309121576131</v>
       </c>
       <c r="F2058" t="n">
-        <v>0.6840853423799398</v>
+        <v>0.6609243581073629</v>
       </c>
       <c r="G2058" t="n">
-        <v>4.322195754505826</v>
+        <v>4.30829916394228</v>
       </c>
     </row>
     <row r="2059">
@@ -48902,22 +48902,22 @@
         <v>45521</v>
       </c>
       <c r="B2059" t="n">
-        <v>3.714879051790802</v>
+        <v>3.714879051790798</v>
       </c>
       <c r="C2059" t="n">
         <v>3.909530246203802</v>
       </c>
       <c r="D2059" t="n">
-        <v>-5.115946946018091</v>
+        <v>-5.139107930290668</v>
       </c>
       <c r="E2059" t="n">
-        <v>1.862795043482817</v>
+        <v>1.853530649773786</v>
       </c>
       <c r="F2059" t="n">
-        <v>0.6840853423799398</v>
+        <v>0.6609243581073629</v>
       </c>
       <c r="G2059" t="n">
-        <v>4.319981451631766</v>
+        <v>4.30608486106822</v>
       </c>
     </row>
     <row r="2060">
@@ -48925,22 +48925,22 @@
         <v>45522</v>
       </c>
       <c r="B2060" t="n">
-        <v>3.70475794943733</v>
+        <v>3.704757949437326</v>
       </c>
       <c r="C2060" t="n">
         <v>3.909433374278091</v>
       </c>
       <c r="D2060" t="n">
-        <v>-5.195366397225842</v>
+        <v>-5.218527381498419</v>
       </c>
       <c r="E2060" t="n">
-        <v>1.830930391074006</v>
+        <v>1.821665997364975</v>
       </c>
       <c r="F2060" t="n">
-        <v>0.6840853423799398</v>
+        <v>0.6609243581073629</v>
       </c>
       <c r="G2060" t="n">
-        <v>4.319884579706055</v>
+        <v>4.305987989142508</v>
       </c>
     </row>
     <row r="2061">
@@ -48948,22 +48948,22 @@
         <v>45523</v>
       </c>
       <c r="B2061" t="n">
-        <v>3.736804952298398</v>
+        <v>3.736804952298394</v>
       </c>
       <c r="C2061" t="n">
         <v>3.909427267836134</v>
       </c>
       <c r="D2061" t="n">
-        <v>-5.29082939514306</v>
+        <v>-5.313990379415637</v>
       </c>
       <c r="E2061" t="n">
-        <v>1.792739085465162</v>
+        <v>1.783474691756131</v>
       </c>
       <c r="F2061" t="n">
-        <v>0.6840853423799398</v>
+        <v>0.6609243581073629</v>
       </c>
       <c r="G2061" t="n">
-        <v>4.319878473264098</v>
+        <v>4.305981882700552</v>
       </c>
     </row>
     <row r="2062">
@@ -48971,22 +48971,22 @@
         <v>45524</v>
       </c>
       <c r="B2062" t="n">
-        <v>3.715372960218</v>
+        <v>3.715372960217996</v>
       </c>
       <c r="C2062" t="n">
         <v>3.907523664398744</v>
       </c>
       <c r="D2062" t="n">
-        <v>-5.226453484292345</v>
+        <v>-5.249614468564922</v>
       </c>
       <c r="E2062" t="n">
-        <v>1.816585846368058</v>
+        <v>1.807321452659028</v>
       </c>
       <c r="F2062" t="n">
-        <v>0.7484612532306549</v>
+        <v>0.7253002689580781</v>
       </c>
       <c r="G2062" t="n">
-        <v>4.356600416337137</v>
+        <v>4.342703825773591</v>
       </c>
     </row>
     <row r="2063">
@@ -48994,22 +48994,22 @@
         <v>45525</v>
       </c>
       <c r="B2063" t="n">
-        <v>3.736089413353535</v>
+        <v>3.736089413353532</v>
       </c>
       <c r="C2063" t="n">
         <v>3.913257482146471</v>
       </c>
       <c r="D2063" t="n">
-        <v>-5.281822646424539</v>
+        <v>-5.304983630697116</v>
       </c>
       <c r="E2063" t="n">
-        <v>1.800171999262907</v>
+        <v>1.790907605553877</v>
       </c>
       <c r="F2063" t="n">
-        <v>0.7484612532306549</v>
+        <v>0.7253002689580781</v>
       </c>
       <c r="G2063" t="n">
-        <v>4.362334234084864</v>
+        <v>4.348437643521318</v>
       </c>
     </row>
     <row r="2064">
@@ -49017,22 +49017,22 @@
         <v>45526</v>
       </c>
       <c r="B2064" t="n">
-        <v>3.736822870113278</v>
+        <v>3.736822870113275</v>
       </c>
       <c r="C2064" t="n">
         <v>3.912795845489403</v>
       </c>
       <c r="D2064" t="n">
-        <v>-5.300041113422147</v>
+        <v>-5.323202097694725</v>
       </c>
       <c r="E2064" t="n">
-        <v>1.792422975806796</v>
+        <v>1.783158582097766</v>
       </c>
       <c r="F2064" t="n">
-        <v>0.7233548159748128</v>
+        <v>0.7001938317022359</v>
       </c>
       <c r="G2064" t="n">
-        <v>4.346808735074291</v>
+        <v>4.332912144510745</v>
       </c>
     </row>
     <row r="2065">
@@ -49040,22 +49040,22 @@
         <v>45527</v>
       </c>
       <c r="B2065" t="n">
-        <v>3.790272500113687</v>
+        <v>3.790272500113684</v>
       </c>
       <c r="C2065" t="n">
         <v>3.932670238339722</v>
       </c>
       <c r="D2065" t="n">
-        <v>-5.211834279274569</v>
+        <v>-5.234995263547146</v>
       </c>
       <c r="E2065" t="n">
-        <v>1.847580102316146</v>
+        <v>1.838315708607115</v>
       </c>
       <c r="F2065" t="n">
-        <v>0.7233548159748128</v>
+        <v>0.7001938317022359</v>
       </c>
       <c r="G2065" t="n">
-        <v>4.36668312792461</v>
+        <v>4.352786537361064</v>
       </c>
     </row>
     <row r="2066">
@@ -49063,22 +49063,22 @@
         <v>45528</v>
       </c>
       <c r="B2066" t="n">
-        <v>3.794486844016438</v>
+        <v>3.794486844016435</v>
       </c>
       <c r="C2066" t="n">
         <v>3.91637093886445</v>
       </c>
       <c r="D2066" t="n">
-        <v>-5.10579928406926</v>
+        <v>-5.128960268341837</v>
       </c>
       <c r="E2066" t="n">
-        <v>1.873694800922998</v>
+        <v>1.864430407213967</v>
       </c>
       <c r="F2066" t="n">
-        <v>0.7233548159748128</v>
+        <v>0.7001938317022359</v>
       </c>
       <c r="G2066" t="n">
-        <v>4.350383828449337</v>
+        <v>4.336487237885792</v>
       </c>
     </row>
     <row r="2067">
@@ -49086,22 +49086,22 @@
         <v>45529</v>
       </c>
       <c r="B2067" t="n">
-        <v>3.79470509330767</v>
+        <v>3.794705093307666</v>
       </c>
       <c r="C2067" t="n">
         <v>3.918801888328495</v>
       </c>
       <c r="D2067" t="n">
-        <v>-4.922587620936165</v>
+        <v>-4.945748605208742</v>
       </c>
       <c r="E2067" t="n">
-        <v>1.949410415640282</v>
+        <v>1.940146021931251</v>
       </c>
       <c r="F2067" t="n">
-        <v>0.7233548159748128</v>
+        <v>0.7001938317022359</v>
       </c>
       <c r="G2067" t="n">
-        <v>4.352814777913383</v>
+        <v>4.338918187349837</v>
       </c>
     </row>
     <row r="2068">
@@ -49109,22 +49109,22 @@
         <v>45530</v>
       </c>
       <c r="B2068" t="n">
-        <v>3.776846557863551</v>
+        <v>3.776846557863547</v>
       </c>
       <c r="C2068" t="n">
         <v>3.901746294407872</v>
       </c>
       <c r="D2068" t="n">
-        <v>-4.850866173922314</v>
+        <v>-4.874027158194891</v>
       </c>
       <c r="E2068" t="n">
-        <v>1.961043400525199</v>
+        <v>1.951779006816168</v>
       </c>
       <c r="F2068" t="n">
-        <v>0.7950762629886634</v>
+        <v>0.7719152787160866</v>
       </c>
       <c r="G2068" t="n">
-        <v>4.378792052201071</v>
+        <v>4.364895461637524</v>
       </c>
     </row>
     <row r="2069">
@@ -49132,22 +49132,22 @@
         <v>45531</v>
       </c>
       <c r="B2069" t="n">
-        <v>3.723789705394111</v>
+        <v>3.723789705394108</v>
       </c>
       <c r="C2069" t="n">
         <v>3.848662040329044</v>
       </c>
       <c r="D2069" t="n">
-        <v>-4.828493148314608</v>
+        <v>-4.851654132587185</v>
       </c>
       <c r="E2069" t="n">
-        <v>1.916908356689453</v>
+        <v>1.907643962980422</v>
       </c>
       <c r="F2069" t="n">
-        <v>0.806332014101565</v>
+        <v>0.7831710298289881</v>
       </c>
       <c r="G2069" t="n">
-        <v>4.332461248789984</v>
+        <v>4.318564658226437</v>
       </c>
     </row>
     <row r="2070">
@@ -49155,22 +49155,22 @@
         <v>45532</v>
       </c>
       <c r="B2070" t="n">
-        <v>3.715607446456728</v>
+        <v>3.715607446456724</v>
       </c>
       <c r="C2070" t="n">
         <v>4.0338602452144</v>
       </c>
       <c r="D2070" t="n">
-        <v>-4.861509444225352</v>
+        <v>-4.884670428497929</v>
       </c>
       <c r="E2070" t="n">
-        <v>2.08890004321051</v>
+        <v>2.07963564950148</v>
       </c>
       <c r="F2070" t="n">
-        <v>0.7368946374348133</v>
+        <v>0.7137336531622365</v>
       </c>
       <c r="G2070" t="n">
-        <v>4.475997027675288</v>
+        <v>4.462100437111742</v>
       </c>
     </row>
     <row r="2071">
@@ -49178,22 +49178,22 @@
         <v>45533</v>
       </c>
       <c r="B2071" t="n">
-        <v>3.713762536883677</v>
+        <v>3.713762536883673</v>
       </c>
       <c r="C2071" t="n">
         <v>4.025781471042649</v>
       </c>
       <c r="D2071" t="n">
-        <v>-4.849981808575744</v>
+        <v>-4.873142792848321</v>
       </c>
       <c r="E2071" t="n">
-        <v>2.085432323298603</v>
+        <v>2.076167929589572</v>
       </c>
       <c r="F2071" t="n">
-        <v>0.7958952956361758</v>
+        <v>0.7727343113635989</v>
       </c>
       <c r="G2071" t="n">
-        <v>4.503318648424354</v>
+        <v>4.489422057860808</v>
       </c>
     </row>
     <row r="2072">
@@ -49201,22 +49201,22 @@
         <v>45534</v>
       </c>
       <c r="B2072" t="n">
-        <v>3.717150699236297</v>
+        <v>3.717150699236293</v>
       </c>
       <c r="C2072" t="n">
         <v>4.029449583564437</v>
       </c>
       <c r="D2072" t="n">
-        <v>-4.947323309918112</v>
+        <v>-4.970484294190689</v>
       </c>
       <c r="E2072" t="n">
-        <v>2.050163835283445</v>
+        <v>2.040899441574413</v>
       </c>
       <c r="F2072" t="n">
-        <v>0.7514751134706874</v>
+        <v>0.7283141291981106</v>
       </c>
       <c r="G2072" t="n">
-        <v>4.48033465164685</v>
+        <v>4.466438061083304</v>
       </c>
     </row>
     <row r="2073">
@@ -49224,22 +49224,22 @@
         <v>45535</v>
       </c>
       <c r="B2073" t="n">
-        <v>3.705201079427684</v>
+        <v>3.705201079427679</v>
       </c>
       <c r="C2073" t="n">
         <v>4.030700665757275</v>
       </c>
       <c r="D2073" t="n">
-        <v>-5.033179339258079</v>
+        <v>-5.056340323530656</v>
       </c>
       <c r="E2073" t="n">
-        <v>2.017072505740296</v>
+        <v>2.007808112031265</v>
       </c>
       <c r="F2073" t="n">
-        <v>0.7090990442445524</v>
+        <v>0.6859380599719755</v>
       </c>
       <c r="G2073" t="n">
-        <v>4.456160092304007</v>
+        <v>4.442263501740461</v>
       </c>
     </row>
     <row r="2074">
@@ -49247,22 +49247,22 @@
         <v>45536</v>
       </c>
       <c r="B2074" t="n">
-        <v>3.69183549961038</v>
+        <v>3.691835499610376</v>
       </c>
       <c r="C2074" t="n">
         <v>4.013119867577777</v>
       </c>
       <c r="D2074" t="n">
-        <v>-5.042016136674198</v>
+        <v>-5.065177120946776</v>
       </c>
       <c r="E2074" t="n">
-        <v>1.99595698859435</v>
+        <v>1.986692594885319</v>
       </c>
       <c r="F2074" t="n">
-        <v>0.7016568716032017</v>
+        <v>0.6784958873306248</v>
       </c>
       <c r="G2074" t="n">
-        <v>4.434113990539698</v>
+        <v>4.420217399976153</v>
       </c>
     </row>
     <row r="2075">
@@ -49270,22 +49270,22 @@
         <v>45537</v>
       </c>
       <c r="B2075" t="n">
-        <v>3.715544411667453</v>
+        <v>3.715544411667449</v>
       </c>
       <c r="C2075" t="n">
         <v>4.023284378622827</v>
       </c>
       <c r="D2075" t="n">
-        <v>-5.133398699239657</v>
+        <v>-5.156559683512234</v>
       </c>
       <c r="E2075" t="n">
-        <v>1.969568474613216</v>
+        <v>1.960304080904185</v>
       </c>
       <c r="F2075" t="n">
-        <v>0.665091986883857</v>
+        <v>0.6419310026112801</v>
       </c>
       <c r="G2075" t="n">
-        <v>4.422339570753141</v>
+        <v>4.408442980189595</v>
       </c>
     </row>
     <row r="2076">
@@ -49293,22 +49293,22 @@
         <v>45538</v>
       </c>
       <c r="B2076" t="n">
-        <v>3.673978374889191</v>
+        <v>3.673978374889186</v>
       </c>
       <c r="C2076" t="n">
-        <v>4.144444094190696</v>
+        <v>4.125412636447095</v>
       </c>
       <c r="D2076" t="n">
-        <v>-5.121691981252651</v>
+        <v>-5.144852965525228</v>
       </c>
       <c r="E2076" t="n">
-        <v>2.095410877375888</v>
+        <v>2.067115025923256</v>
       </c>
       <c r="F2076" t="n">
-        <v>0.6767987048708634</v>
+        <v>0.6536377205982865</v>
       </c>
       <c r="G2076" t="n">
-        <v>4.550523317113214</v>
+        <v>4.517595268806067</v>
       </c>
     </row>
     <row r="2077">
@@ -49316,22 +49316,22 @@
         <v>45539</v>
       </c>
       <c r="B2077" t="n">
-        <v>3.682476099409566</v>
+        <v>3.682476099409562</v>
       </c>
       <c r="C2077" t="n">
-        <v>4.147476432922101</v>
+        <v>4.1284449751785</v>
       </c>
       <c r="D2077" t="n">
-        <v>-5.192604054994929</v>
+        <v>-5.215765039267506</v>
       </c>
       <c r="E2077" t="n">
-        <v>2.070078386610382</v>
+        <v>2.041782535157749</v>
       </c>
       <c r="F2077" t="n">
-        <v>0.6767987048708634</v>
+        <v>0.6536377205982865</v>
       </c>
       <c r="G2077" t="n">
-        <v>4.553555655844619</v>
+        <v>4.520627607537472</v>
       </c>
     </row>
     <row r="2078">
@@ -49339,22 +49339,22 @@
         <v>45540</v>
       </c>
       <c r="B2078" t="n">
-        <v>3.67289517745257</v>
+        <v>3.672895177452566</v>
       </c>
       <c r="C2078" t="n">
-        <v>4.360381266200159</v>
+        <v>4.341349808456558</v>
       </c>
       <c r="D2078" t="n">
-        <v>-5.202920153161281</v>
+        <v>-5.226081137433858</v>
       </c>
       <c r="E2078" t="n">
-        <v>2.278856780621899</v>
+        <v>2.250560929169267</v>
       </c>
       <c r="F2078" t="n">
-        <v>0.6767987048708634</v>
+        <v>0.6536377205982865</v>
       </c>
       <c r="G2078" t="n">
-        <v>4.766460489122677</v>
+        <v>4.73353244081553</v>
       </c>
     </row>
     <row r="2079">
@@ -49362,22 +49362,22 @@
         <v>45541</v>
       </c>
       <c r="B2079" t="n">
-        <v>3.623960959762287</v>
+        <v>3.623960959762282</v>
       </c>
       <c r="C2079" t="n">
-        <v>4.359559933112249</v>
+        <v>4.340528475368647</v>
       </c>
       <c r="D2079" t="n">
-        <v>-5.202826185143908</v>
+        <v>-5.225987169416485</v>
       </c>
       <c r="E2079" t="n">
-        <v>2.278073034740938</v>
+        <v>2.249777183288305</v>
       </c>
       <c r="F2079" t="n">
-        <v>0.6771685662181813</v>
+        <v>0.6540075819456045</v>
       </c>
       <c r="G2079" t="n">
-        <v>4.765861072843157</v>
+        <v>4.732933024536011</v>
       </c>
     </row>
     <row r="2080">
@@ -49385,22 +49385,22 @@
         <v>45542</v>
       </c>
       <c r="B2080" t="n">
-        <v>3.633213467988018</v>
+        <v>3.633213467988013</v>
       </c>
       <c r="C2080" t="n">
-        <v>4.353791919056603</v>
+        <v>4.334760461313001</v>
       </c>
       <c r="D2080" t="n">
-        <v>-5.351192412800053</v>
+        <v>-5.37435339707263</v>
       </c>
       <c r="E2080" t="n">
-        <v>2.212958529622834</v>
+        <v>2.184662678170201</v>
       </c>
       <c r="F2080" t="n">
-        <v>0.6771685662181813</v>
+        <v>0.6540075819456045</v>
       </c>
       <c r="G2080" t="n">
-        <v>4.760093058787511</v>
+        <v>4.727165010480364</v>
       </c>
     </row>
     <row r="2081">
@@ -49408,22 +49408,22 @@
         <v>45543</v>
       </c>
       <c r="B2081" t="n">
-        <v>3.647907242740922</v>
+        <v>3.647907242740917</v>
       </c>
       <c r="C2081" t="n">
-        <v>4.353791919056603</v>
+        <v>4.334760461313001</v>
       </c>
       <c r="D2081" t="n">
-        <v>-5.350243989682014</v>
+        <v>-5.373404973954591</v>
       </c>
       <c r="E2081" t="n">
-        <v>2.213337898870049</v>
+        <v>2.185042047417417</v>
       </c>
       <c r="F2081" t="n">
-        <v>0.6771685662181813</v>
+        <v>0.6540075819456045</v>
       </c>
       <c r="G2081" t="n">
-        <v>4.760093058787511</v>
+        <v>4.727165010480364</v>
       </c>
     </row>
     <row r="2082">
@@ -49431,22 +49431,22 @@
         <v>45544</v>
       </c>
       <c r="B2082" t="n">
-        <v>3.881065366663625</v>
+        <v>3.88106536666362</v>
       </c>
       <c r="C2082" t="n">
-        <v>4.366519527037695</v>
+        <v>4.347488069294093</v>
       </c>
       <c r="D2082" t="n">
-        <v>-5.450513807641036</v>
+        <v>-5.473674791913613</v>
       </c>
       <c r="E2082" t="n">
-        <v>2.185957579667532</v>
+        <v>2.1576617282149</v>
       </c>
       <c r="F2082" t="n">
-        <v>0.6771685662181813</v>
+        <v>0.6540075819456045</v>
       </c>
       <c r="G2082" t="n">
-        <v>4.772820666768603</v>
+        <v>4.739892618461456</v>
       </c>
     </row>
     <row r="2083">
@@ -49454,22 +49454,22 @@
         <v>45545</v>
       </c>
       <c r="B2083" t="n">
-        <v>3.717071158424769</v>
+        <v>3.717071158424764</v>
       </c>
       <c r="C2083" t="n">
-        <v>4.368465525462082</v>
+        <v>4.349434067718481</v>
       </c>
       <c r="D2083" t="n">
-        <v>-5.444521560852224</v>
+        <v>-5.467682545124801</v>
       </c>
       <c r="E2083" t="n">
-        <v>2.190300476807445</v>
+        <v>2.162004625354812</v>
       </c>
       <c r="F2083" t="n">
-        <v>0.6771685662181813</v>
+        <v>0.6540075819456045</v>
       </c>
       <c r="G2083" t="n">
-        <v>4.774766665192991</v>
+        <v>4.741838616885844</v>
       </c>
     </row>
     <row r="2084">
@@ -49477,22 +49477,22 @@
         <v>45546</v>
       </c>
       <c r="B2084" t="n">
-        <v>3.741942347149218</v>
+        <v>3.741942347149212</v>
       </c>
       <c r="C2084" t="n">
-        <v>4.362119661479851</v>
+        <v>4.34308820373625</v>
       </c>
       <c r="D2084" t="n">
-        <v>-5.355963599721457</v>
+        <v>-5.379124583994034</v>
       </c>
       <c r="E2084" t="n">
-        <v>2.219377797277521</v>
+        <v>2.191081945824889</v>
       </c>
       <c r="F2084" t="n">
-        <v>0.6771685662181813</v>
+        <v>0.6540075819456045</v>
       </c>
       <c r="G2084" t="n">
-        <v>4.76842080121076</v>
+        <v>4.735492752903613</v>
       </c>
     </row>
     <row r="2085">
@@ -49500,22 +49500,22 @@
         <v>45547</v>
       </c>
       <c r="B2085" t="n">
-        <v>3.73530072138309</v>
+        <v>3.735300721383084</v>
       </c>
       <c r="C2085" t="n">
-        <v>4.361428338918847</v>
+        <v>4.342396881175246</v>
       </c>
       <c r="D2085" t="n">
-        <v>-5.338204522218382</v>
+        <v>-5.36136550649096</v>
       </c>
       <c r="E2085" t="n">
-        <v>2.225790105717746</v>
+        <v>2.197494254265114</v>
       </c>
       <c r="F2085" t="n">
-        <v>0.6771685662181813</v>
+        <v>0.6540075819456045</v>
       </c>
       <c r="G2085" t="n">
-        <v>4.767729478649755</v>
+        <v>4.734801430342609</v>
       </c>
     </row>
     <row r="2086">
@@ -49523,22 +49523,22 @@
         <v>45548</v>
       </c>
       <c r="B2086" t="n">
-        <v>3.778232147720995</v>
+        <v>3.77823214772099</v>
       </c>
       <c r="C2086" t="n">
-        <v>4.374210524827434</v>
+        <v>4.355179067083832</v>
       </c>
       <c r="D2086" t="n">
-        <v>-5.238574371169315</v>
+        <v>-5.261735355441892</v>
       </c>
       <c r="E2086" t="n">
-        <v>2.27842435204596</v>
+        <v>2.250128500593328</v>
       </c>
       <c r="F2086" t="n">
-        <v>0.7767987172672488</v>
+        <v>0.753637732994672</v>
       </c>
       <c r="G2086" t="n">
-        <v>4.840289755187783</v>
+        <v>4.807361706880636</v>
       </c>
     </row>
     <row r="2087">
@@ -49546,22 +49546,22 @@
         <v>45549</v>
       </c>
       <c r="B2087" t="n">
-        <v>3.77535709745527</v>
+        <v>3.775357097455265</v>
       </c>
       <c r="C2087" t="n">
-        <v>4.56336479032616</v>
+        <v>4.544333332582559</v>
       </c>
       <c r="D2087" t="n">
-        <v>-5.287973879858326</v>
+        <v>-5.311134864130903</v>
       </c>
       <c r="E2087" t="n">
-        <v>2.447818814069082</v>
+        <v>2.41952296261645</v>
       </c>
       <c r="F2087" t="n">
-        <v>0.7870575506989935</v>
+        <v>0.7638965664264167</v>
       </c>
       <c r="G2087" t="n">
-        <v>5.035599320745557</v>
+        <v>5.002671272438409</v>
       </c>
     </row>
     <row r="2088">
@@ -49569,22 +49569,22 @@
         <v>45550</v>
       </c>
       <c r="B2088" t="n">
-        <v>3.749078058963131</v>
+        <v>3.749078058963126</v>
       </c>
       <c r="C2088" t="n">
-        <v>4.550553463429022</v>
+        <v>4.531522005685421</v>
       </c>
       <c r="D2088" t="n">
-        <v>-5.08128940621595</v>
+        <v>-5.104450390488527</v>
       </c>
       <c r="E2088" t="n">
-        <v>2.517681276628894</v>
+        <v>2.489385425176262</v>
       </c>
       <c r="F2088" t="n">
-        <v>0.993742024341369</v>
+        <v>0.9705810400687923</v>
       </c>
       <c r="G2088" t="n">
-        <v>5.146798678033844</v>
+        <v>5.113870629726696</v>
       </c>
     </row>
     <row r="2089">
@@ -49592,22 +49592,22 @@
         <v>45551</v>
       </c>
       <c r="B2089" t="n">
-        <v>3.740284389162541</v>
+        <v>3.740284389162536</v>
       </c>
       <c r="C2089" t="n">
-        <v>4.552554977083127</v>
+        <v>4.533523519339526</v>
       </c>
       <c r="D2089" t="n">
-        <v>-5.115446301213476</v>
+        <v>-5.138607285486053</v>
       </c>
       <c r="E2089" t="n">
-        <v>2.506020032283989</v>
+        <v>2.477724180831357</v>
       </c>
       <c r="F2089" t="n">
-        <v>0.9101582548005566</v>
+        <v>0.8869972705279798</v>
       </c>
       <c r="G2089" t="n">
-        <v>5.098649929963461</v>
+        <v>5.065721881656314</v>
       </c>
     </row>
     <row r="2090">
@@ -49615,22 +49615,22 @@
         <v>45552</v>
       </c>
       <c r="B2090" t="n">
-        <v>3.782482115652382</v>
+        <v>3.782482115652376</v>
       </c>
       <c r="C2090" t="n">
-        <v>4.906052091072794</v>
+        <v>4.887020633329193</v>
       </c>
       <c r="D2090" t="n">
-        <v>-5.022856822152019</v>
+        <v>-5.046017806424596</v>
       </c>
       <c r="E2090" t="n">
-        <v>2.896552937898239</v>
+        <v>2.868257086445607</v>
       </c>
       <c r="F2090" t="n">
-        <v>0.9101582548005566</v>
+        <v>0.8869972705279798</v>
       </c>
       <c r="G2090" t="n">
-        <v>5.452147043953128</v>
+        <v>5.419218995645982</v>
       </c>
     </row>
     <row r="2091">
@@ -49638,22 +49638,22 @@
         <v>45553</v>
       </c>
       <c r="B2091" t="n">
-        <v>3.809055905108672</v>
+        <v>3.809055905108666</v>
       </c>
       <c r="C2091" t="n">
-        <v>4.910615202639898</v>
+        <v>4.891583744896296</v>
       </c>
       <c r="D2091" t="n">
-        <v>-5.096017425925164</v>
+        <v>-5.119178410197741</v>
       </c>
       <c r="E2091" t="n">
-        <v>2.871851807956084</v>
+        <v>2.843555956503452</v>
       </c>
       <c r="F2091" t="n">
-        <v>0.8821370547663134</v>
+        <v>0.8589760704937368</v>
       </c>
       <c r="G2091" t="n">
-        <v>5.439897435499686</v>
+        <v>5.406969387192539</v>
       </c>
     </row>
     <row r="2092">
@@ -49661,22 +49661,22 @@
         <v>45554</v>
       </c>
       <c r="B2092" t="n">
-        <v>3.835202441103564</v>
+        <v>3.835202441103558</v>
       </c>
       <c r="C2092" t="n">
-        <v>4.960445143963425</v>
+        <v>4.941413686219824</v>
       </c>
       <c r="D2092" t="n">
-        <v>-5.043801116128822</v>
+        <v>-5.066962100401399</v>
       </c>
       <c r="E2092" t="n">
-        <v>2.942568273198148</v>
+        <v>2.914272421745516</v>
       </c>
       <c r="F2092" t="n">
-        <v>0.8821370547663134</v>
+        <v>0.8589760704937368</v>
       </c>
       <c r="G2092" t="n">
-        <v>5.489727376823214</v>
+        <v>5.456799328516066</v>
       </c>
     </row>
     <row r="2093">
@@ -49684,22 +49684,22 @@
         <v>45555</v>
       </c>
       <c r="B2093" t="n">
-        <v>3.821827147047745</v>
+        <v>3.821827147047739</v>
       </c>
       <c r="C2093" t="n">
-        <v>4.969259114173436</v>
+        <v>4.950227656429835</v>
       </c>
       <c r="D2093" t="n">
-        <v>-5.011903599043577</v>
+        <v>-5.035064583316154</v>
       </c>
       <c r="E2093" t="n">
-        <v>2.964141250242257</v>
+        <v>2.935845398789625</v>
       </c>
       <c r="F2093" t="n">
-        <v>0.9140345718515592</v>
+        <v>0.8908735875789826</v>
       </c>
       <c r="G2093" t="n">
-        <v>5.517679857284372</v>
+        <v>5.484751808977225</v>
       </c>
     </row>
     <row r="2094">
@@ -49707,22 +49707,22 @@
         <v>45556</v>
       </c>
       <c r="B2094" t="n">
-        <v>3.825268416650755</v>
+        <v>3.825268416650749</v>
       </c>
       <c r="C2094" t="n">
-        <v>4.964896698212633</v>
+        <v>4.945865240469032</v>
       </c>
       <c r="D2094" t="n">
-        <v>-5.026658923243717</v>
+        <v>-5.049819907516294</v>
       </c>
       <c r="E2094" t="n">
-        <v>2.953876704601398</v>
+        <v>2.925580853148766</v>
       </c>
       <c r="F2094" t="n">
-        <v>0.9140345718515592</v>
+        <v>0.8908735875789826</v>
       </c>
       <c r="G2094" t="n">
-        <v>5.513317441323569</v>
+        <v>5.480389393016422</v>
       </c>
     </row>
     <row r="2095">
@@ -49730,22 +49730,22 @@
         <v>45557</v>
       </c>
       <c r="B2095" t="n">
-        <v>3.84504466613575</v>
+        <v>3.845044666135744</v>
       </c>
       <c r="C2095" t="n">
-        <v>4.955821201628913</v>
+        <v>4.936789743885312</v>
       </c>
       <c r="D2095" t="n">
-        <v>-4.977194299873806</v>
+        <v>-5.000355284146383</v>
       </c>
       <c r="E2095" t="n">
-        <v>2.964587057365643</v>
+        <v>2.936291205913011</v>
       </c>
       <c r="F2095" t="n">
-        <v>0.9634991952214709</v>
+        <v>0.9403382109488942</v>
       </c>
       <c r="G2095" t="n">
-        <v>5.533920718761796</v>
+        <v>5.500992670454648</v>
       </c>
     </row>
     <row r="2096">
@@ -49753,22 +49753,22 @@
         <v>45558</v>
       </c>
       <c r="B2096" t="n">
-        <v>3.825931790479223</v>
+        <v>3.825931790479217</v>
       </c>
       <c r="C2096" t="n">
-        <v>4.952228869343847</v>
+        <v>4.933197411600246</v>
       </c>
       <c r="D2096" t="n">
-        <v>-4.81408630772019</v>
+        <v>-4.837247291992767</v>
       </c>
       <c r="E2096" t="n">
-        <v>3.026237921942023</v>
+        <v>2.997942070489391</v>
       </c>
       <c r="F2096" t="n">
-        <v>1.126607187375086</v>
+        <v>1.103446203102509</v>
       </c>
       <c r="G2096" t="n">
-        <v>5.628193181768899</v>
+        <v>5.595265133461752</v>
       </c>
     </row>
     <row r="2097">
@@ -49776,22 +49776,22 @@
         <v>45559</v>
       </c>
       <c r="B2097" t="n">
-        <v>3.847096478844245</v>
+        <v>3.847096478844239</v>
       </c>
       <c r="C2097" t="n">
-        <v>4.961275906034976</v>
+        <v>4.942244448291374</v>
       </c>
       <c r="D2097" t="n">
-        <v>-4.681278682223024</v>
+        <v>-4.704439666495601</v>
       </c>
       <c r="E2097" t="n">
-        <v>3.088408008832018</v>
+        <v>3.060112157379386</v>
       </c>
       <c r="F2097" t="n">
-        <v>1.126607187375086</v>
+        <v>1.103446203102509</v>
       </c>
       <c r="G2097" t="n">
-        <v>5.637240218460027</v>
+        <v>5.60431217015288</v>
       </c>
     </row>
     <row r="2098">
@@ -49799,22 +49799,22 @@
         <v>45560</v>
       </c>
       <c r="B2098" t="n">
-        <v>3.832425987790948</v>
+        <v>3.832425987790942</v>
       </c>
       <c r="C2098" t="n">
-        <v>4.962133371021097</v>
+        <v>4.943101913277496</v>
       </c>
       <c r="D2098" t="n">
-        <v>-4.743986598697582</v>
+        <v>-4.767147582970159</v>
       </c>
       <c r="E2098" t="n">
-        <v>3.064182307228316</v>
+        <v>3.035886455775684</v>
       </c>
       <c r="F2098" t="n">
-        <v>1.063899270900528</v>
+        <v>1.040738286627952</v>
       </c>
       <c r="G2098" t="n">
-        <v>5.600472933561415</v>
+        <v>5.567544885254267</v>
       </c>
     </row>
     <row r="2099">
@@ -49822,22 +49822,22 @@
         <v>45561</v>
       </c>
       <c r="B2099" t="n">
-        <v>3.861579399578995</v>
+        <v>3.861579399578989</v>
       </c>
       <c r="C2099" t="n">
-        <v>4.925042787811449</v>
+        <v>4.906011330067848</v>
       </c>
       <c r="D2099" t="n">
-        <v>-4.695978474853889</v>
+        <v>-4.719139459126466</v>
       </c>
       <c r="E2099" t="n">
-        <v>3.046294973556146</v>
+        <v>3.017999122103514</v>
       </c>
       <c r="F2099" t="n">
-        <v>1.063899270900528</v>
+        <v>1.040738286627952</v>
       </c>
       <c r="G2099" t="n">
-        <v>5.563382350351767</v>
+        <v>5.530454302044619</v>
       </c>
     </row>
     <row r="2100">
@@ -49845,22 +49845,22 @@
         <v>45562</v>
       </c>
       <c r="B2100" t="n">
-        <v>3.872253907629883</v>
+        <v>3.872253907629878</v>
       </c>
       <c r="C2100" t="n">
-        <v>4.9289750413694</v>
+        <v>4.909943583625799</v>
       </c>
       <c r="D2100" t="n">
-        <v>-4.617152817670299</v>
+        <v>-4.640313801942876</v>
       </c>
       <c r="E2100" t="n">
-        <v>3.081757489987532</v>
+        <v>3.0534616385349</v>
       </c>
       <c r="F2100" t="n">
-        <v>1.142724928084119</v>
+        <v>1.119563943811542</v>
       </c>
       <c r="G2100" t="n">
-        <v>5.614609998219871</v>
+        <v>5.581681949912724</v>
       </c>
     </row>
     <row r="2101">
@@ -49868,22 +49868,22 @@
         <v>45563</v>
       </c>
       <c r="B2101" t="n">
-        <v>3.868502531686405</v>
+        <v>3.8685025316864</v>
       </c>
       <c r="C2101" t="n">
-        <v>4.923874133976437</v>
+        <v>4.904842676232835</v>
       </c>
       <c r="D2101" t="n">
-        <v>-4.425218016416425</v>
+        <v>-4.448379000689002</v>
       </c>
       <c r="E2101" t="n">
-        <v>3.153430503096119</v>
+        <v>3.125134651643487</v>
       </c>
       <c r="F2101" t="n">
-        <v>1.142724928084119</v>
+        <v>1.119563943811542</v>
       </c>
       <c r="G2101" t="n">
-        <v>5.609509090826908</v>
+        <v>5.576581042519761</v>
       </c>
     </row>
     <row r="2102">
@@ -49891,22 +49891,22 @@
         <v>45564</v>
       </c>
       <c r="B2102" t="n">
-        <v>3.792259287839513</v>
+        <v>3.900114331443694</v>
       </c>
       <c r="C2102" t="n">
-        <v>4.919228043365532</v>
+        <v>4.900196585621931</v>
       </c>
       <c r="D2102" t="n">
-        <v>-4.307044638398498</v>
+        <v>-4.330205622671075</v>
       </c>
       <c r="E2102" t="n">
-        <v>3.196053763692385</v>
+        <v>3.167757912239753</v>
       </c>
       <c r="F2102" t="n">
-        <v>1.260898306102046</v>
+        <v>1.237737321829469</v>
       </c>
       <c r="G2102" t="n">
-        <v>5.67576702702676</v>
+        <v>5.642838978719612</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240930.xlsx
+++ b/tame_output/ON/bt/strategyON_20240930.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>57.8%</t>
+          <t>54.0%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -610,16 +610,16 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.3%</t>
+          <t>53.2%</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2099</v>
+        <v>2100</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -628,12 +628,12 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2024-09-29</t>
+          <t>2024-09-30</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>64.8%</t>
+          <t>65.0%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.2%</t>
+          <t>17.8%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>61.9%</t>
+          <t>48.5%</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>113.1%</t>
+          <t>111.0%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -768,7 +768,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.57</t>
+          <t>2.52</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -777,7 +777,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2099</v>
+        <v>2100</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -786,12 +786,12 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2024-09-29</t>
+          <t>2024-09-30</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>39.6%</t>
+          <t>39.7%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>10.8%</t>
+          <t>10.7%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>94.8%</t>
+          <t>93.3%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-8.4%</t>
+          <t>-8.2%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>178.4%</t>
+          <t>172.9%</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-75.3%</t>
+          <t>-75.6%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>107.8%</t>
+          <t>107.6%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2099</v>
+        <v>2100</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -944,17 +944,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2024-09-29</t>
+          <t>2024-09-30</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>123.1%</t>
+          <t>123.0%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>91.6%</t>
+          <t>91.4%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>21.9%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-48.0%</t>
+          <t>-47.9%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-71.4%</t>
+          <t>-71.8%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>89.4%</t>
+          <t>89.3%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>421.8%</t>
+          <t>420.8%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-7.0%</t>
+          <t>-6.9%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-594.6%</t>
+          <t>-603.1%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>44.7%</t>
+          <t>43.9%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1093,7 +1093,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2099</v>
+        <v>2100</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2024-09-29</t>
+          <t>2024-09-30</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1140,7 +1140,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>-9.3%</t>
+          <t>-8.7%</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>14.2%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>39.3%</t>
+          <t>38.7%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1190,7 +1190,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15.4%</t>
+          <t>15.3%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-59.4%</t>
+          <t>-62.8%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-3.1%</t>
+          <t>-4.4%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.4%</t>
+          <t>66.1%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1251,7 +1251,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2099</v>
+        <v>2100</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1260,17 +1260,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2024-09-29</t>
+          <t>2024-09-30</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>62.3%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>73.4%</t>
+          <t>72.9%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.4%</t>
+          <t>10.1%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-24.7%</t>
+          <t>-26.1%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>2.0%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.3%</t>
+          <t>55.1%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>44.9%</t>
+          <t>45.4%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-392.5%</t>
+          <t>-400.8%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-100.2%</t>
+          <t>-108.7%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>124.8%</t>
+          <t>74.7%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>57.8%</t>
+          <t>65.7%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2.16</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1409,7 +1409,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2099</v>
+        <v>2100</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1418,17 +1418,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2024-09-29</t>
+          <t>2024-09-30</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>59.8%</t>
+          <t>76.9%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>56.8%</t>
+          <t>56.7%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>14.2%</t>
+          <t>12.8%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>113.0%</t>
+          <t>64.0%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>48.2%</t>
+          <t>54.6%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>2.3</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-17.1%</t>
+          <t>-15.6%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>118.3%</t>
+          <t>37.8%</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2102"/>
+  <dimension ref="A1:G2103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -47821,7 +47821,7 @@
         <v>45474</v>
       </c>
       <c r="B2012" t="n">
-        <v>3.749882691378387</v>
+        <v>3.749882691378388</v>
       </c>
       <c r="C2012" t="n">
         <v>3.205575709863882</v>
@@ -47890,7 +47890,7 @@
         <v>45477</v>
       </c>
       <c r="B2015" t="n">
-        <v>3.619348081585933</v>
+        <v>3.619348081585934</v>
       </c>
       <c r="C2015" t="n">
         <v>3.267570154558586</v>
@@ -47913,7 +47913,7 @@
         <v>45478</v>
       </c>
       <c r="B2016" t="n">
-        <v>3.640750087814663</v>
+        <v>3.640750087814664</v>
       </c>
       <c r="C2016" t="n">
         <v>3.407881873560433</v>
@@ -47936,7 +47936,7 @@
         <v>45479</v>
       </c>
       <c r="B2017" t="n">
-        <v>3.668289004237092</v>
+        <v>3.668289004237093</v>
       </c>
       <c r="C2017" t="n">
         <v>3.476862142706073</v>
@@ -47959,7 +47959,7 @@
         <v>45480</v>
       </c>
       <c r="B2018" t="n">
-        <v>3.619923016423385</v>
+        <v>3.619923016423386</v>
       </c>
       <c r="C2018" t="n">
         <v>3.462913344826194</v>
@@ -47982,7 +47982,7 @@
         <v>45481</v>
       </c>
       <c r="B2019" t="n">
-        <v>3.656332733609751</v>
+        <v>3.656332733609752</v>
       </c>
       <c r="C2019" t="n">
         <v>3.474783833881608</v>
@@ -48005,7 +48005,7 @@
         <v>45482</v>
       </c>
       <c r="B2020" t="n">
-        <v>3.674028535973154</v>
+        <v>3.674028535973155</v>
       </c>
       <c r="C2020" t="n">
         <v>3.475994368400552</v>
@@ -48051,7 +48051,7 @@
         <v>45484</v>
       </c>
       <c r="B2022" t="n">
-        <v>3.652149152916196</v>
+        <v>3.652149152916197</v>
       </c>
       <c r="C2022" t="n">
         <v>3.475193963364063</v>
@@ -48074,7 +48074,7 @@
         <v>45485</v>
       </c>
       <c r="B2023" t="n">
-        <v>3.667962306830324</v>
+        <v>3.667962306830325</v>
       </c>
       <c r="C2023" t="n">
         <v>3.637398020063107</v>
@@ -48097,7 +48097,7 @@
         <v>45486</v>
       </c>
       <c r="B2024" t="n">
-        <v>3.696539468071546</v>
+        <v>3.696539468071547</v>
       </c>
       <c r="C2024" t="n">
         <v>3.632244658026921</v>
@@ -48120,7 +48120,7 @@
         <v>45487</v>
       </c>
       <c r="B2025" t="n">
-        <v>3.750044015868141</v>
+        <v>3.750044015868143</v>
       </c>
       <c r="C2025" t="n">
         <v>3.642474075595412</v>
@@ -48143,22 +48143,22 @@
         <v>45488</v>
       </c>
       <c r="B2026" t="n">
-        <v>3.783632867332688</v>
+        <v>3.783632867332689</v>
       </c>
       <c r="C2026" t="n">
         <v>3.651399714051315</v>
       </c>
       <c r="D2026" t="n">
-        <v>-5.802101772984098</v>
+        <v>-5.778940788711521</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.330202580543927</v>
+        <v>1.339466974252959</v>
       </c>
       <c r="F2026" t="n">
-        <v>-0.1530397604657562</v>
+        <v>-0.1298787761931792</v>
       </c>
       <c r="G2026" t="n">
-        <v>3.559575857771861</v>
+        <v>3.573472448335407</v>
       </c>
     </row>
     <row r="2027">
@@ -48172,16 +48172,16 @@
         <v>3.64355260129549</v>
       </c>
       <c r="D2027" t="n">
-        <v>-5.692095489506876</v>
+        <v>-5.668934505234299</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.366357981178992</v>
+        <v>1.375622374888022</v>
       </c>
       <c r="F2027" t="n">
-        <v>-0.129835188548481</v>
+        <v>-0.106674204275904</v>
       </c>
       <c r="G2027" t="n">
-        <v>3.565651488166401</v>
+        <v>3.579548078729948</v>
       </c>
     </row>
     <row r="2028">
@@ -48189,22 +48189,22 @@
         <v>45490</v>
       </c>
       <c r="B2028" t="n">
-        <v>3.785563924818517</v>
+        <v>3.785563924818519</v>
       </c>
       <c r="C2028" t="n">
         <v>3.647802612017464</v>
       </c>
       <c r="D2028" t="n">
-        <v>-5.54903591376595</v>
+        <v>-5.525874929493373</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.427831822197336</v>
+        <v>1.437096215906367</v>
       </c>
       <c r="F2028" t="n">
-        <v>-0.1218217619585018</v>
+        <v>-0.09866077768592474</v>
       </c>
       <c r="G2028" t="n">
-        <v>3.574709554842364</v>
+        <v>3.588606145405909</v>
       </c>
     </row>
     <row r="2029">
@@ -48212,22 +48212,22 @@
         <v>45491</v>
       </c>
       <c r="B2029" t="n">
-        <v>3.777237412051783</v>
+        <v>3.777237412051786</v>
       </c>
       <c r="C2029" t="n">
         <v>3.6550634949</v>
       </c>
       <c r="D2029" t="n">
-        <v>-5.247589188294112</v>
+        <v>-5.224428204021535</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.555671395268607</v>
+        <v>1.564935788977638</v>
       </c>
       <c r="F2029" t="n">
-        <v>0.1796249635133355</v>
+        <v>0.2027859477859125</v>
       </c>
       <c r="G2029" t="n">
-        <v>3.762838473008002</v>
+        <v>3.776735063571548</v>
       </c>
     </row>
     <row r="2030">
@@ -48235,22 +48235,22 @@
         <v>45492</v>
       </c>
       <c r="B2030" t="n">
-        <v>3.812635940679621</v>
+        <v>3.812635940679623</v>
       </c>
       <c r="C2030" t="n">
         <v>3.656034672652711</v>
       </c>
       <c r="D2030" t="n">
-        <v>-5.272179432529296</v>
+        <v>-5.249018448256719</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.546806475327244</v>
+        <v>1.556070869036275</v>
       </c>
       <c r="F2030" t="n">
-        <v>0.1796249635133355</v>
+        <v>0.2027859477859125</v>
       </c>
       <c r="G2030" t="n">
-        <v>3.763809650760713</v>
+        <v>3.777706241324259</v>
       </c>
     </row>
     <row r="2031">
@@ -48258,22 +48258,22 @@
         <v>45493</v>
       </c>
       <c r="B2031" t="n">
-        <v>3.821184182474155</v>
+        <v>3.821184182474158</v>
       </c>
       <c r="C2031" t="n">
         <v>3.656877577032466</v>
       </c>
       <c r="D2031" t="n">
-        <v>-5.221141056522776</v>
+        <v>-5.197980072250199</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.568064730109608</v>
+        <v>1.577329123818639</v>
       </c>
       <c r="F2031" t="n">
-        <v>0.1796249635133355</v>
+        <v>0.2027859477859125</v>
       </c>
       <c r="G2031" t="n">
-        <v>3.764652555140468</v>
+        <v>3.778549145704014</v>
       </c>
     </row>
     <row r="2032">
@@ -48281,22 +48281,22 @@
         <v>45494</v>
       </c>
       <c r="B2032" t="n">
-        <v>3.831734516969539</v>
+        <v>3.831734516969542</v>
       </c>
       <c r="C2032" t="n">
         <v>3.675915675906612</v>
       </c>
       <c r="D2032" t="n">
-        <v>-5.192292379699316</v>
+        <v>-5.169131395426739</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.598642299713138</v>
+        <v>1.607906693422168</v>
       </c>
       <c r="F2032" t="n">
-        <v>0.2084736403367958</v>
+        <v>0.2316346246093728</v>
       </c>
       <c r="G2032" t="n">
-        <v>3.80099986010869</v>
+        <v>3.814896450672236</v>
       </c>
     </row>
     <row r="2033">
@@ -48304,22 +48304,22 @@
         <v>45495</v>
       </c>
       <c r="B2033" t="n">
-        <v>3.825752932700473</v>
+        <v>3.825752932700476</v>
       </c>
       <c r="C2033" t="n">
         <v>3.492099672030546</v>
       </c>
       <c r="D2033" t="n">
-        <v>-5.095657467680676</v>
+        <v>-5.072496483408099</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.453480260644528</v>
+        <v>1.462744654353559</v>
       </c>
       <c r="F2033" t="n">
-        <v>0.3051085523554357</v>
+        <v>0.3282695366280127</v>
       </c>
       <c r="G2033" t="n">
-        <v>3.675164803443808</v>
+        <v>3.689061394007354</v>
       </c>
     </row>
     <row r="2034">
@@ -48327,22 +48327,22 @@
         <v>45496</v>
       </c>
       <c r="B2034" t="n">
-        <v>3.804688961077636</v>
+        <v>3.804688961077638</v>
       </c>
       <c r="C2034" t="n">
         <v>3.495601716104511</v>
       </c>
       <c r="D2034" t="n">
-        <v>-5.026619456732208</v>
+        <v>-5.003458472459631</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.484597509097879</v>
+        <v>1.49386190280691</v>
       </c>
       <c r="F2034" t="n">
-        <v>0.3741465633039038</v>
+        <v>0.3973075475764808</v>
       </c>
       <c r="G2034" t="n">
-        <v>3.720089654086853</v>
+        <v>3.733986244650399</v>
       </c>
     </row>
     <row r="2035">
@@ -48350,22 +48350,22 @@
         <v>45497</v>
       </c>
       <c r="B2035" t="n">
-        <v>3.775028860833455</v>
+        <v>3.775028860833456</v>
       </c>
       <c r="C2035" t="n">
         <v>3.480028535180593</v>
       </c>
       <c r="D2035" t="n">
-        <v>-5.007832356363269</v>
+        <v>-4.984671372090692</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.476539168321537</v>
+        <v>1.485803562030568</v>
       </c>
       <c r="F2035" t="n">
-        <v>0.3929336636728423</v>
+        <v>0.4160946479454193</v>
       </c>
       <c r="G2035" t="n">
-        <v>3.715788733384298</v>
+        <v>3.729685323947845</v>
       </c>
     </row>
     <row r="2036">
@@ -48373,22 +48373,22 @@
         <v>45498</v>
       </c>
       <c r="B2036" t="n">
-        <v>3.821030660077624</v>
+        <v>3.821030660077626</v>
       </c>
       <c r="C2036" t="n">
         <v>3.479216245617023</v>
       </c>
       <c r="D2036" t="n">
-        <v>-4.930733754821397</v>
+        <v>-4.907572770548819</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.506566319374716</v>
+        <v>1.515830713083747</v>
       </c>
       <c r="F2036" t="n">
-        <v>0.3929336636728423</v>
+        <v>0.4160946479454193</v>
       </c>
       <c r="G2036" t="n">
-        <v>3.714976443820728</v>
+        <v>3.728873034384275</v>
       </c>
     </row>
     <row r="2037">
@@ -48396,22 +48396,22 @@
         <v>45499</v>
       </c>
       <c r="B2037" t="n">
-        <v>3.832307024147906</v>
+        <v>3.832307024147908</v>
       </c>
       <c r="C2037" t="n">
         <v>3.489085024742095</v>
       </c>
       <c r="D2037" t="n">
-        <v>-4.941118949711286</v>
+        <v>-4.917957965438709</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.512281020543833</v>
+        <v>1.521545414252864</v>
       </c>
       <c r="F2037" t="n">
-        <v>0.382548468782953</v>
+        <v>0.40570945305553</v>
       </c>
       <c r="G2037" t="n">
-        <v>3.718614106011867</v>
+        <v>3.732510696575413</v>
       </c>
     </row>
     <row r="2038">
@@ -48419,22 +48419,22 @@
         <v>45500</v>
       </c>
       <c r="B2038" t="n">
-        <v>3.834415493735277</v>
+        <v>3.834415493735278</v>
       </c>
       <c r="C2038" t="n">
         <v>3.55992203051852</v>
       </c>
       <c r="D2038" t="n">
-        <v>-4.959707108433511</v>
+        <v>-4.936546124160934</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.575682762831368</v>
+        <v>1.584947156540399</v>
       </c>
       <c r="F2038" t="n">
-        <v>0.3639603100607276</v>
+        <v>0.3871212943333046</v>
       </c>
       <c r="G2038" t="n">
-        <v>3.778298216554957</v>
+        <v>3.792194807118503</v>
       </c>
     </row>
     <row r="2039">
@@ -48442,22 +48442,22 @@
         <v>45501</v>
       </c>
       <c r="B2039" t="n">
-        <v>3.855120535496551</v>
+        <v>3.855120535496552</v>
       </c>
       <c r="C2039" t="n">
         <v>3.556791041336819</v>
       </c>
       <c r="D2039" t="n">
-        <v>-4.960005655129547</v>
+        <v>-4.93684467085697</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.572432354971252</v>
+        <v>1.581696748680283</v>
       </c>
       <c r="F2039" t="n">
-        <v>0.3636617633646917</v>
+        <v>0.3868227476372687</v>
       </c>
       <c r="G2039" t="n">
-        <v>3.774988099355634</v>
+        <v>3.78888468991918</v>
       </c>
     </row>
     <row r="2040">
@@ -48465,22 +48465,22 @@
         <v>45502</v>
       </c>
       <c r="B2040" t="n">
-        <v>3.815643212108852</v>
+        <v>3.815643212108854</v>
       </c>
       <c r="C2040" t="n">
         <v>3.56132193627621</v>
       </c>
       <c r="D2040" t="n">
-        <v>-4.859182521439119</v>
+        <v>-4.836021537166542</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.617292503386815</v>
+        <v>1.626556897095845</v>
       </c>
       <c r="F2040" t="n">
-        <v>0.3761259788490455</v>
+        <v>0.3992869631216225</v>
       </c>
       <c r="G2040" t="n">
-        <v>3.786997523585638</v>
+        <v>3.800894114149184</v>
       </c>
     </row>
     <row r="2041">
@@ -48494,16 +48494,16 @@
         <v>3.561451189754754</v>
       </c>
       <c r="D2041" t="n">
-        <v>-4.668401160686711</v>
+        <v>-4.645240176414134</v>
       </c>
       <c r="E2041" t="n">
-        <v>1.693734301166321</v>
+        <v>1.702998694875352</v>
       </c>
       <c r="F2041" t="n">
-        <v>0.5669073396014529</v>
+        <v>0.5900683238740299</v>
       </c>
       <c r="G2041" t="n">
-        <v>3.901595593515625</v>
+        <v>3.915492184079172</v>
       </c>
     </row>
     <row r="2042">
@@ -48517,16 +48517,16 @@
         <v>3.54128803549235</v>
       </c>
       <c r="D2042" t="n">
-        <v>-4.56143780283729</v>
+        <v>-4.538276818564713</v>
       </c>
       <c r="E2042" t="n">
-        <v>1.716356490043686</v>
+        <v>1.725620883752717</v>
       </c>
       <c r="F2042" t="n">
-        <v>0.6253719475612544</v>
+        <v>0.6485329318338313</v>
       </c>
       <c r="G2042" t="n">
-        <v>3.916511204029103</v>
+        <v>3.930407794592649</v>
       </c>
     </row>
     <row r="2043">
@@ -48540,16 +48540,16 @@
         <v>3.576254972104409</v>
       </c>
       <c r="D2043" t="n">
-        <v>-4.506107214935527</v>
+        <v>-4.48294623066295</v>
       </c>
       <c r="E2043" t="n">
-        <v>1.77345566181645</v>
+        <v>1.782720055525481</v>
       </c>
       <c r="F2043" t="n">
-        <v>0.6807025354630165</v>
+        <v>0.7038635197355935</v>
       </c>
       <c r="G2043" t="n">
-        <v>3.984676493382219</v>
+        <v>3.998573083945764</v>
       </c>
     </row>
     <row r="2044">
@@ -48563,16 +48563,16 @@
         <v>3.569941540005846</v>
       </c>
       <c r="D2044" t="n">
-        <v>-4.494053088022564</v>
+        <v>-4.470892103749987</v>
       </c>
       <c r="E2044" t="n">
-        <v>1.771963880483073</v>
+        <v>1.781228274192103</v>
       </c>
       <c r="F2044" t="n">
-        <v>0.6927566623759793</v>
+        <v>0.7159176466485563</v>
       </c>
       <c r="G2044" t="n">
-        <v>3.985595537431434</v>
+        <v>3.99949212799498</v>
       </c>
     </row>
     <row r="2045">
@@ -48580,22 +48580,22 @@
         <v>45507</v>
       </c>
       <c r="B2045" t="n">
-        <v>3.725010844811005</v>
+        <v>3.725010844811004</v>
       </c>
       <c r="C2045" t="n">
         <v>3.571822170189982</v>
       </c>
       <c r="D2045" t="n">
-        <v>-4.535208207590785</v>
+        <v>-4.512047223318208</v>
       </c>
       <c r="E2045" t="n">
-        <v>1.75738246283992</v>
+        <v>1.766646856548951</v>
       </c>
       <c r="F2045" t="n">
-        <v>0.6516015428077584</v>
+        <v>0.6747625270803354</v>
       </c>
       <c r="G2045" t="n">
-        <v>3.962783095874637</v>
+        <v>3.976679686438183</v>
       </c>
     </row>
     <row r="2046">
@@ -48603,22 +48603,22 @@
         <v>45508</v>
       </c>
       <c r="B2046" t="n">
-        <v>3.612322444382916</v>
+        <v>3.612322444382915</v>
       </c>
       <c r="C2046" t="n">
         <v>3.584673196067865</v>
       </c>
       <c r="D2046" t="n">
-        <v>-4.467159644899255</v>
+        <v>-4.443998660626678</v>
       </c>
       <c r="E2046" t="n">
-        <v>1.797452913794414</v>
+        <v>1.806717307503445</v>
       </c>
       <c r="F2046" t="n">
-        <v>0.7196501054992882</v>
+        <v>0.7428110897718652</v>
       </c>
       <c r="G2046" t="n">
-        <v>4.016463259367438</v>
+        <v>4.030359849930984</v>
       </c>
     </row>
     <row r="2047">
@@ -48626,22 +48626,22 @@
         <v>45509</v>
       </c>
       <c r="B2047" t="n">
-        <v>3.645256780013423</v>
+        <v>3.645256780013422</v>
       </c>
       <c r="C2047" t="n">
         <v>3.604875866241459</v>
       </c>
       <c r="D2047" t="n">
-        <v>-4.698760038068756</v>
+        <v>-4.675599053796179</v>
       </c>
       <c r="E2047" t="n">
-        <v>1.725015426700208</v>
+        <v>1.734279820409239</v>
       </c>
       <c r="F2047" t="n">
-        <v>0.7196501054992882</v>
+        <v>0.7428110897718652</v>
       </c>
       <c r="G2047" t="n">
-        <v>4.036665929541032</v>
+        <v>4.050562520104578</v>
       </c>
     </row>
     <row r="2048">
@@ -48649,22 +48649,22 @@
         <v>45510</v>
       </c>
       <c r="B2048" t="n">
-        <v>3.666747201498965</v>
+        <v>3.666747201498967</v>
       </c>
       <c r="C2048" t="n">
         <v>3.588482102308341</v>
       </c>
       <c r="D2048" t="n">
-        <v>-4.748811583597975</v>
+        <v>-4.725650599325398</v>
       </c>
       <c r="E2048" t="n">
-        <v>1.688601044555403</v>
+        <v>1.697865438264434</v>
       </c>
       <c r="F2048" t="n">
-        <v>0.7196501054992882</v>
+        <v>0.7428110897718652</v>
       </c>
       <c r="G2048" t="n">
-        <v>4.020272165607914</v>
+        <v>4.03416875617146</v>
       </c>
     </row>
     <row r="2049">
@@ -48672,22 +48672,22 @@
         <v>45511</v>
       </c>
       <c r="B2049" t="n">
-        <v>3.670048702800094</v>
+        <v>3.670048702800096</v>
       </c>
       <c r="C2049" t="n">
         <v>3.548734015901807</v>
       </c>
       <c r="D2049" t="n">
-        <v>-4.92391841617442</v>
+        <v>-4.900757431901843</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.578810225118292</v>
+        <v>1.588074618827322</v>
       </c>
       <c r="F2049" t="n">
-        <v>0.7196501054992882</v>
+        <v>0.7428110897718652</v>
       </c>
       <c r="G2049" t="n">
-        <v>3.980524079201381</v>
+        <v>3.994420669764927</v>
       </c>
     </row>
     <row r="2050">
@@ -48695,22 +48695,22 @@
         <v>45512</v>
       </c>
       <c r="B2050" t="n">
-        <v>3.745573148660847</v>
+        <v>3.745573148660848</v>
       </c>
       <c r="C2050" t="n">
         <v>3.555756634898747</v>
       </c>
       <c r="D2050" t="n">
-        <v>-4.727818262743897</v>
+        <v>-4.70465727847132</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.664272905487441</v>
+        <v>1.673537299196472</v>
       </c>
       <c r="F2050" t="n">
-        <v>0.9157502589298111</v>
+        <v>0.9389112432023881</v>
       </c>
       <c r="G2050" t="n">
-        <v>4.105206790256634</v>
+        <v>4.119103380820181</v>
       </c>
     </row>
     <row r="2051">
@@ -48718,22 +48718,22 @@
         <v>45513</v>
       </c>
       <c r="B2051" t="n">
-        <v>3.730570473395083</v>
+        <v>3.730570473395085</v>
       </c>
       <c r="C2051" t="n">
         <v>3.654927634471652</v>
       </c>
       <c r="D2051" t="n">
-        <v>-4.574792870630612</v>
+        <v>-4.551631886358035</v>
       </c>
       <c r="E2051" t="n">
-        <v>1.824654061905659</v>
+        <v>1.83391845561469</v>
       </c>
       <c r="F2051" t="n">
-        <v>1.068775651043095</v>
+        <v>1.091936635315672</v>
       </c>
       <c r="G2051" t="n">
-        <v>4.29619302509751</v>
+        <v>4.310089615661055</v>
       </c>
     </row>
     <row r="2052">
@@ -48741,22 +48741,22 @@
         <v>45514</v>
       </c>
       <c r="B2052" t="n">
-        <v>3.741278332791145</v>
+        <v>3.741278332791147</v>
       </c>
       <c r="C2052" t="n">
         <v>3.842393859379944</v>
       </c>
       <c r="D2052" t="n">
-        <v>-4.603100184503883</v>
+        <v>-4.579939200231306</v>
       </c>
       <c r="E2052" t="n">
-        <v>2.000797361264643</v>
+        <v>2.010061754973674</v>
       </c>
       <c r="F2052" t="n">
-        <v>1.068775651043095</v>
+        <v>1.091936635315672</v>
       </c>
       <c r="G2052" t="n">
-        <v>4.483659250005802</v>
+        <v>4.497555840569348</v>
       </c>
     </row>
     <row r="2053">
@@ -48764,22 +48764,22 @@
         <v>45515</v>
       </c>
       <c r="B2053" t="n">
-        <v>3.699115615620431</v>
+        <v>3.699115615620433</v>
       </c>
       <c r="C2053" t="n">
         <v>3.811796810734027</v>
       </c>
       <c r="D2053" t="n">
-        <v>-4.769693409617405</v>
+        <v>-4.746532425344828</v>
       </c>
       <c r="E2053" t="n">
-        <v>1.903563022573317</v>
+        <v>1.912827416282348</v>
       </c>
       <c r="F2053" t="n">
-        <v>0.9021824259295728</v>
+        <v>0.9253434102021496</v>
       </c>
       <c r="G2053" t="n">
-        <v>4.353106266291771</v>
+        <v>4.367002856855317</v>
       </c>
     </row>
     <row r="2054">
@@ -48787,22 +48787,22 @@
         <v>45516</v>
       </c>
       <c r="B2054" t="n">
-        <v>3.708182519285644</v>
+        <v>3.708182519285645</v>
       </c>
       <c r="C2054" t="n">
         <v>3.815473213395745</v>
       </c>
       <c r="D2054" t="n">
-        <v>-4.746657616255839</v>
+        <v>-4.723496631983262</v>
       </c>
       <c r="E2054" t="n">
-        <v>1.916453742579662</v>
+        <v>1.925718136288692</v>
       </c>
       <c r="F2054" t="n">
-        <v>0.9021824259295728</v>
+        <v>0.9253434102021496</v>
       </c>
       <c r="G2054" t="n">
-        <v>4.356782668953489</v>
+        <v>4.370679259517035</v>
       </c>
     </row>
     <row r="2055">
@@ -48810,22 +48810,22 @@
         <v>45517</v>
       </c>
       <c r="B2055" t="n">
-        <v>3.740581401399465</v>
+        <v>3.740581401399467</v>
       </c>
       <c r="C2055" t="n">
         <v>3.81309126851924</v>
       </c>
       <c r="D2055" t="n">
-        <v>-4.717411635800143</v>
+        <v>-4.694250651527565</v>
       </c>
       <c r="E2055" t="n">
-        <v>1.925770189885435</v>
+        <v>1.935034583594466</v>
       </c>
       <c r="F2055" t="n">
-        <v>0.9021824259295728</v>
+        <v>0.9253434102021496</v>
       </c>
       <c r="G2055" t="n">
-        <v>4.354400724076984</v>
+        <v>4.368297314640531</v>
       </c>
     </row>
     <row r="2056">
@@ -48833,22 +48833,22 @@
         <v>45518</v>
       </c>
       <c r="B2056" t="n">
-        <v>3.699404642256367</v>
+        <v>3.699404642256368</v>
       </c>
       <c r="C2056" t="n">
         <v>3.810384507676875</v>
       </c>
       <c r="D2056" t="n">
-        <v>-4.824337183677994</v>
+        <v>-4.801176199405417</v>
       </c>
       <c r="E2056" t="n">
-        <v>1.88029320989193</v>
+        <v>1.889557603600961</v>
       </c>
       <c r="F2056" t="n">
-        <v>0.7952568780517214</v>
+        <v>0.8184178623242983</v>
       </c>
       <c r="G2056" t="n">
-        <v>4.287538634507908</v>
+        <v>4.301435225071454</v>
       </c>
     </row>
     <row r="2057">
@@ -48856,22 +48856,22 @@
         <v>45519</v>
       </c>
       <c r="B2057" t="n">
-        <v>3.689942600700996</v>
+        <v>3.689942600700998</v>
       </c>
       <c r="C2057" t="n">
         <v>3.811813309820109</v>
       </c>
       <c r="D2057" t="n">
-        <v>-4.969355742185242</v>
+        <v>-4.946194757912665</v>
       </c>
       <c r="E2057" t="n">
-        <v>1.823714588632265</v>
+        <v>1.832978982341295</v>
       </c>
       <c r="F2057" t="n">
-        <v>0.6502383195444729</v>
+        <v>0.6733993038170497</v>
       </c>
       <c r="G2057" t="n">
-        <v>4.201956301546794</v>
+        <v>4.215852892110339</v>
       </c>
     </row>
     <row r="2058">
@@ -48879,22 +48879,22 @@
         <v>45520</v>
       </c>
       <c r="B2058" t="n">
-        <v>3.711852429687008</v>
+        <v>3.71185242968701</v>
       </c>
       <c r="C2058" t="n">
         <v>3.911744549077862</v>
       </c>
       <c r="D2058" t="n">
-        <v>-5.08769750796996</v>
+        <v>-5.064536523697383</v>
       </c>
       <c r="E2058" t="n">
-        <v>1.876309121576131</v>
+        <v>1.885573515285161</v>
       </c>
       <c r="F2058" t="n">
-        <v>0.6609243581073629</v>
+        <v>0.6840853423799398</v>
       </c>
       <c r="G2058" t="n">
-        <v>4.30829916394228</v>
+        <v>4.322195754505826</v>
       </c>
     </row>
     <row r="2059">
@@ -48902,22 +48902,22 @@
         <v>45521</v>
       </c>
       <c r="B2059" t="n">
-        <v>3.714879051790798</v>
+        <v>3.7148790517908</v>
       </c>
       <c r="C2059" t="n">
         <v>3.909530246203802</v>
       </c>
       <c r="D2059" t="n">
-        <v>-5.139107930290668</v>
+        <v>-5.115946946018091</v>
       </c>
       <c r="E2059" t="n">
-        <v>1.853530649773786</v>
+        <v>1.862795043482817</v>
       </c>
       <c r="F2059" t="n">
-        <v>0.6609243581073629</v>
+        <v>0.6840853423799398</v>
       </c>
       <c r="G2059" t="n">
-        <v>4.30608486106822</v>
+        <v>4.319981451631766</v>
       </c>
     </row>
     <row r="2060">
@@ -48925,22 +48925,22 @@
         <v>45522</v>
       </c>
       <c r="B2060" t="n">
-        <v>3.704757949437326</v>
+        <v>3.704757949437328</v>
       </c>
       <c r="C2060" t="n">
         <v>3.909433374278091</v>
       </c>
       <c r="D2060" t="n">
-        <v>-5.218527381498419</v>
+        <v>-5.195366397225842</v>
       </c>
       <c r="E2060" t="n">
-        <v>1.821665997364975</v>
+        <v>1.830930391074006</v>
       </c>
       <c r="F2060" t="n">
-        <v>0.6609243581073629</v>
+        <v>0.6840853423799398</v>
       </c>
       <c r="G2060" t="n">
-        <v>4.305987989142508</v>
+        <v>4.319884579706055</v>
       </c>
     </row>
     <row r="2061">
@@ -48954,16 +48954,16 @@
         <v>3.909427267836134</v>
       </c>
       <c r="D2061" t="n">
-        <v>-5.313990379415637</v>
+        <v>-5.29082939514306</v>
       </c>
       <c r="E2061" t="n">
-        <v>1.783474691756131</v>
+        <v>1.792739085465162</v>
       </c>
       <c r="F2061" t="n">
-        <v>0.6609243581073629</v>
+        <v>0.6840853423799398</v>
       </c>
       <c r="G2061" t="n">
-        <v>4.305981882700552</v>
+        <v>4.319878473264098</v>
       </c>
     </row>
     <row r="2062">
@@ -48977,16 +48977,16 @@
         <v>3.907523664398744</v>
       </c>
       <c r="D2062" t="n">
-        <v>-5.249614468564922</v>
+        <v>-5.226453484292345</v>
       </c>
       <c r="E2062" t="n">
-        <v>1.807321452659028</v>
+        <v>1.816585846368058</v>
       </c>
       <c r="F2062" t="n">
-        <v>0.7253002689580781</v>
+        <v>0.7484612532306549</v>
       </c>
       <c r="G2062" t="n">
-        <v>4.342703825773591</v>
+        <v>4.356600416337137</v>
       </c>
     </row>
     <row r="2063">
@@ -49000,16 +49000,16 @@
         <v>3.913257482146471</v>
       </c>
       <c r="D2063" t="n">
-        <v>-5.304983630697116</v>
+        <v>-5.281822646424539</v>
       </c>
       <c r="E2063" t="n">
-        <v>1.790907605553877</v>
+        <v>1.800171999262907</v>
       </c>
       <c r="F2063" t="n">
-        <v>0.7253002689580781</v>
+        <v>0.7484612532306549</v>
       </c>
       <c r="G2063" t="n">
-        <v>4.348437643521318</v>
+        <v>4.362334234084864</v>
       </c>
     </row>
     <row r="2064">
@@ -49023,16 +49023,16 @@
         <v>3.912795845489403</v>
       </c>
       <c r="D2064" t="n">
-        <v>-5.323202097694725</v>
+        <v>-5.300041113422147</v>
       </c>
       <c r="E2064" t="n">
-        <v>1.783158582097766</v>
+        <v>1.792422975806796</v>
       </c>
       <c r="F2064" t="n">
-        <v>0.7001938317022359</v>
+        <v>0.7233548159748128</v>
       </c>
       <c r="G2064" t="n">
-        <v>4.332912144510745</v>
+        <v>4.346808735074291</v>
       </c>
     </row>
     <row r="2065">
@@ -49046,16 +49046,16 @@
         <v>3.932670238339722</v>
       </c>
       <c r="D2065" t="n">
-        <v>-5.234995263547146</v>
+        <v>-5.211834279274569</v>
       </c>
       <c r="E2065" t="n">
-        <v>1.838315708607115</v>
+        <v>1.847580102316146</v>
       </c>
       <c r="F2065" t="n">
-        <v>0.7001938317022359</v>
+        <v>0.7233548159748128</v>
       </c>
       <c r="G2065" t="n">
-        <v>4.352786537361064</v>
+        <v>4.36668312792461</v>
       </c>
     </row>
     <row r="2066">
@@ -49063,22 +49063,22 @@
         <v>45528</v>
       </c>
       <c r="B2066" t="n">
-        <v>3.794486844016435</v>
+        <v>3.794486844016437</v>
       </c>
       <c r="C2066" t="n">
         <v>3.91637093886445</v>
       </c>
       <c r="D2066" t="n">
-        <v>-5.128960268341837</v>
+        <v>-5.10579928406926</v>
       </c>
       <c r="E2066" t="n">
-        <v>1.864430407213967</v>
+        <v>1.873694800922998</v>
       </c>
       <c r="F2066" t="n">
-        <v>0.7001938317022359</v>
+        <v>0.7233548159748128</v>
       </c>
       <c r="G2066" t="n">
-        <v>4.336487237885792</v>
+        <v>4.350383828449337</v>
       </c>
     </row>
     <row r="2067">
@@ -49086,22 +49086,22 @@
         <v>45529</v>
       </c>
       <c r="B2067" t="n">
-        <v>3.794705093307666</v>
+        <v>3.794705093307669</v>
       </c>
       <c r="C2067" t="n">
         <v>3.918801888328495</v>
       </c>
       <c r="D2067" t="n">
-        <v>-4.945748605208742</v>
+        <v>-4.922587620936165</v>
       </c>
       <c r="E2067" t="n">
-        <v>1.940146021931251</v>
+        <v>1.949410415640282</v>
       </c>
       <c r="F2067" t="n">
-        <v>0.7001938317022359</v>
+        <v>0.7233548159748128</v>
       </c>
       <c r="G2067" t="n">
-        <v>4.338918187349837</v>
+        <v>4.352814777913383</v>
       </c>
     </row>
     <row r="2068">
@@ -49109,22 +49109,22 @@
         <v>45530</v>
       </c>
       <c r="B2068" t="n">
-        <v>3.776846557863547</v>
+        <v>3.77684655786355</v>
       </c>
       <c r="C2068" t="n">
         <v>3.901746294407872</v>
       </c>
       <c r="D2068" t="n">
-        <v>-4.874027158194891</v>
+        <v>-4.850866173922314</v>
       </c>
       <c r="E2068" t="n">
-        <v>1.951779006816168</v>
+        <v>1.961043400525199</v>
       </c>
       <c r="F2068" t="n">
-        <v>0.7719152787160866</v>
+        <v>0.7950762629886634</v>
       </c>
       <c r="G2068" t="n">
-        <v>4.364895461637524</v>
+        <v>4.378792052201071</v>
       </c>
     </row>
     <row r="2069">
@@ -49132,22 +49132,22 @@
         <v>45531</v>
       </c>
       <c r="B2069" t="n">
-        <v>3.723789705394108</v>
+        <v>3.72378970539411</v>
       </c>
       <c r="C2069" t="n">
         <v>3.848662040329044</v>
       </c>
       <c r="D2069" t="n">
-        <v>-4.851654132587185</v>
+        <v>-4.828493148314608</v>
       </c>
       <c r="E2069" t="n">
-        <v>1.907643962980422</v>
+        <v>1.916908356689453</v>
       </c>
       <c r="F2069" t="n">
-        <v>0.7831710298289881</v>
+        <v>0.806332014101565</v>
       </c>
       <c r="G2069" t="n">
-        <v>4.318564658226437</v>
+        <v>4.332461248789984</v>
       </c>
     </row>
     <row r="2070">
@@ -49155,22 +49155,22 @@
         <v>45532</v>
       </c>
       <c r="B2070" t="n">
-        <v>3.715607446456724</v>
+        <v>3.715607446456727</v>
       </c>
       <c r="C2070" t="n">
         <v>4.0338602452144</v>
       </c>
       <c r="D2070" t="n">
-        <v>-4.884670428497929</v>
+        <v>-4.861509444225352</v>
       </c>
       <c r="E2070" t="n">
-        <v>2.07963564950148</v>
+        <v>2.08890004321051</v>
       </c>
       <c r="F2070" t="n">
-        <v>0.7137336531622365</v>
+        <v>0.7368946374348133</v>
       </c>
       <c r="G2070" t="n">
-        <v>4.462100437111742</v>
+        <v>4.475997027675288</v>
       </c>
     </row>
     <row r="2071">
@@ -49178,22 +49178,22 @@
         <v>45533</v>
       </c>
       <c r="B2071" t="n">
-        <v>3.713762536883673</v>
+        <v>3.713762536883674</v>
       </c>
       <c r="C2071" t="n">
         <v>4.025781471042649</v>
       </c>
       <c r="D2071" t="n">
-        <v>-4.873142792848321</v>
+        <v>-4.849981808575744</v>
       </c>
       <c r="E2071" t="n">
-        <v>2.076167929589572</v>
+        <v>2.085432323298603</v>
       </c>
       <c r="F2071" t="n">
-        <v>0.7727343113635989</v>
+        <v>0.7958952956361758</v>
       </c>
       <c r="G2071" t="n">
-        <v>4.489422057860808</v>
+        <v>4.503318648424354</v>
       </c>
     </row>
     <row r="2072">
@@ -49201,22 +49201,22 @@
         <v>45534</v>
       </c>
       <c r="B2072" t="n">
-        <v>3.717150699236293</v>
+        <v>3.717150699236294</v>
       </c>
       <c r="C2072" t="n">
         <v>4.029449583564437</v>
       </c>
       <c r="D2072" t="n">
-        <v>-4.970484294190689</v>
+        <v>-4.947323309918112</v>
       </c>
       <c r="E2072" t="n">
-        <v>2.040899441574413</v>
+        <v>2.050163835283445</v>
       </c>
       <c r="F2072" t="n">
-        <v>0.7283141291981106</v>
+        <v>0.7514751134706874</v>
       </c>
       <c r="G2072" t="n">
-        <v>4.466438061083304</v>
+        <v>4.48033465164685</v>
       </c>
     </row>
     <row r="2073">
@@ -49224,22 +49224,22 @@
         <v>45535</v>
       </c>
       <c r="B2073" t="n">
-        <v>3.705201079427679</v>
+        <v>3.70520107942768</v>
       </c>
       <c r="C2073" t="n">
         <v>4.030700665757275</v>
       </c>
       <c r="D2073" t="n">
-        <v>-5.056340323530656</v>
+        <v>-5.033179339258079</v>
       </c>
       <c r="E2073" t="n">
-        <v>2.007808112031265</v>
+        <v>2.017072505740296</v>
       </c>
       <c r="F2073" t="n">
-        <v>0.6859380599719755</v>
+        <v>0.7090990442445524</v>
       </c>
       <c r="G2073" t="n">
-        <v>4.442263501740461</v>
+        <v>4.456160092304007</v>
       </c>
     </row>
     <row r="2074">
@@ -49247,22 +49247,22 @@
         <v>45536</v>
       </c>
       <c r="B2074" t="n">
-        <v>3.691835499610376</v>
+        <v>3.691835499610379</v>
       </c>
       <c r="C2074" t="n">
         <v>4.013119867577777</v>
       </c>
       <c r="D2074" t="n">
-        <v>-5.065177120946776</v>
+        <v>-5.042016136674198</v>
       </c>
       <c r="E2074" t="n">
-        <v>1.986692594885319</v>
+        <v>1.99595698859435</v>
       </c>
       <c r="F2074" t="n">
-        <v>0.6784958873306248</v>
+        <v>0.7016568716032017</v>
       </c>
       <c r="G2074" t="n">
-        <v>4.420217399976153</v>
+        <v>4.434113990539698</v>
       </c>
     </row>
     <row r="2075">
@@ -49270,22 +49270,22 @@
         <v>45537</v>
       </c>
       <c r="B2075" t="n">
-        <v>3.715544411667449</v>
+        <v>3.715544411667452</v>
       </c>
       <c r="C2075" t="n">
         <v>4.023284378622827</v>
       </c>
       <c r="D2075" t="n">
-        <v>-5.156559683512234</v>
+        <v>-5.133398699239657</v>
       </c>
       <c r="E2075" t="n">
-        <v>1.960304080904185</v>
+        <v>1.969568474613216</v>
       </c>
       <c r="F2075" t="n">
-        <v>0.6419310026112801</v>
+        <v>0.665091986883857</v>
       </c>
       <c r="G2075" t="n">
-        <v>4.408442980189595</v>
+        <v>4.422339570753141</v>
       </c>
     </row>
     <row r="2076">
@@ -49293,22 +49293,22 @@
         <v>45538</v>
       </c>
       <c r="B2076" t="n">
-        <v>3.673978374889186</v>
+        <v>3.673978374889187</v>
       </c>
       <c r="C2076" t="n">
         <v>4.125412636447095</v>
       </c>
       <c r="D2076" t="n">
-        <v>-5.144852965525228</v>
+        <v>-5.121691981252651</v>
       </c>
       <c r="E2076" t="n">
-        <v>2.067115025923256</v>
+        <v>2.076379419632286</v>
       </c>
       <c r="F2076" t="n">
-        <v>0.6536377205982865</v>
+        <v>0.6767987048708634</v>
       </c>
       <c r="G2076" t="n">
-        <v>4.517595268806067</v>
+        <v>4.531491859369613</v>
       </c>
     </row>
     <row r="2077">
@@ -49316,22 +49316,22 @@
         <v>45539</v>
       </c>
       <c r="B2077" t="n">
-        <v>3.682476099409562</v>
+        <v>3.682476099409563</v>
       </c>
       <c r="C2077" t="n">
         <v>4.1284449751785</v>
       </c>
       <c r="D2077" t="n">
-        <v>-5.215765039267506</v>
+        <v>-5.192604054994929</v>
       </c>
       <c r="E2077" t="n">
-        <v>2.041782535157749</v>
+        <v>2.05104692886678</v>
       </c>
       <c r="F2077" t="n">
-        <v>0.6536377205982865</v>
+        <v>0.6767987048708634</v>
       </c>
       <c r="G2077" t="n">
-        <v>4.520627607537472</v>
+        <v>4.534524198101018</v>
       </c>
     </row>
     <row r="2078">
@@ -49339,22 +49339,22 @@
         <v>45540</v>
       </c>
       <c r="B2078" t="n">
-        <v>3.672895177452566</v>
+        <v>3.672895177452569</v>
       </c>
       <c r="C2078" t="n">
         <v>4.341349808456558</v>
       </c>
       <c r="D2078" t="n">
-        <v>-5.226081137433858</v>
+        <v>-5.202920153161281</v>
       </c>
       <c r="E2078" t="n">
-        <v>2.250560929169267</v>
+        <v>2.259825322878298</v>
       </c>
       <c r="F2078" t="n">
-        <v>0.6536377205982865</v>
+        <v>0.6767987048708634</v>
       </c>
       <c r="G2078" t="n">
-        <v>4.73353244081553</v>
+        <v>4.747429031379076</v>
       </c>
     </row>
     <row r="2079">
@@ -49368,16 +49368,16 @@
         <v>4.340528475368647</v>
       </c>
       <c r="D2079" t="n">
-        <v>-5.225987169416485</v>
+        <v>-5.202826185143908</v>
       </c>
       <c r="E2079" t="n">
-        <v>2.249777183288305</v>
+        <v>2.259041576997336</v>
       </c>
       <c r="F2079" t="n">
-        <v>0.6540075819456045</v>
+        <v>0.6771685662181813</v>
       </c>
       <c r="G2079" t="n">
-        <v>4.732933024536011</v>
+        <v>4.746829615099556</v>
       </c>
     </row>
     <row r="2080">
@@ -49391,16 +49391,16 @@
         <v>4.334760461313001</v>
       </c>
       <c r="D2080" t="n">
-        <v>-5.37435339707263</v>
+        <v>-5.351192412800053</v>
       </c>
       <c r="E2080" t="n">
-        <v>2.184662678170201</v>
+        <v>2.193927071879232</v>
       </c>
       <c r="F2080" t="n">
-        <v>0.6540075819456045</v>
+        <v>0.6771685662181813</v>
       </c>
       <c r="G2080" t="n">
-        <v>4.727165010480364</v>
+        <v>4.74106160104391</v>
       </c>
     </row>
     <row r="2081">
@@ -49408,22 +49408,22 @@
         <v>45543</v>
       </c>
       <c r="B2081" t="n">
-        <v>3.647907242740917</v>
+        <v>3.64790724274092</v>
       </c>
       <c r="C2081" t="n">
         <v>4.334760461313001</v>
       </c>
       <c r="D2081" t="n">
-        <v>-5.373404973954591</v>
+        <v>-5.350243989682014</v>
       </c>
       <c r="E2081" t="n">
-        <v>2.185042047417417</v>
+        <v>2.194306441126447</v>
       </c>
       <c r="F2081" t="n">
-        <v>0.6540075819456045</v>
+        <v>0.6771685662181813</v>
       </c>
       <c r="G2081" t="n">
-        <v>4.727165010480364</v>
+        <v>4.74106160104391</v>
       </c>
     </row>
     <row r="2082">
@@ -49431,22 +49431,22 @@
         <v>45544</v>
       </c>
       <c r="B2082" t="n">
-        <v>3.88106536666362</v>
+        <v>3.881065366663623</v>
       </c>
       <c r="C2082" t="n">
         <v>4.347488069294093</v>
       </c>
       <c r="D2082" t="n">
-        <v>-5.473674791913613</v>
+        <v>-5.450513807641036</v>
       </c>
       <c r="E2082" t="n">
-        <v>2.1576617282149</v>
+        <v>2.166926121923931</v>
       </c>
       <c r="F2082" t="n">
-        <v>0.6540075819456045</v>
+        <v>0.6771685662181813</v>
       </c>
       <c r="G2082" t="n">
-        <v>4.739892618461456</v>
+        <v>4.753789209025002</v>
       </c>
     </row>
     <row r="2083">
@@ -49454,22 +49454,22 @@
         <v>45545</v>
       </c>
       <c r="B2083" t="n">
-        <v>3.717071158424764</v>
+        <v>3.717071158424767</v>
       </c>
       <c r="C2083" t="n">
         <v>4.349434067718481</v>
       </c>
       <c r="D2083" t="n">
-        <v>-5.467682545124801</v>
+        <v>-5.444521560852224</v>
       </c>
       <c r="E2083" t="n">
-        <v>2.162004625354812</v>
+        <v>2.171269019063844</v>
       </c>
       <c r="F2083" t="n">
-        <v>0.6540075819456045</v>
+        <v>0.6771685662181813</v>
       </c>
       <c r="G2083" t="n">
-        <v>4.741838616885844</v>
+        <v>4.75573520744939</v>
       </c>
     </row>
     <row r="2084">
@@ -49477,22 +49477,22 @@
         <v>45546</v>
       </c>
       <c r="B2084" t="n">
-        <v>3.741942347149212</v>
+        <v>3.741942347149216</v>
       </c>
       <c r="C2084" t="n">
         <v>4.34308820373625</v>
       </c>
       <c r="D2084" t="n">
-        <v>-5.379124583994034</v>
+        <v>-5.355963599721457</v>
       </c>
       <c r="E2084" t="n">
-        <v>2.191081945824889</v>
+        <v>2.200346339533919</v>
       </c>
       <c r="F2084" t="n">
-        <v>0.6540075819456045</v>
+        <v>0.6771685662181813</v>
       </c>
       <c r="G2084" t="n">
-        <v>4.735492752903613</v>
+        <v>4.749389343467159</v>
       </c>
     </row>
     <row r="2085">
@@ -49500,22 +49500,22 @@
         <v>45547</v>
       </c>
       <c r="B2085" t="n">
-        <v>3.735300721383084</v>
+        <v>3.735300721383088</v>
       </c>
       <c r="C2085" t="n">
         <v>4.342396881175246</v>
       </c>
       <c r="D2085" t="n">
-        <v>-5.36136550649096</v>
+        <v>-5.338204522218382</v>
       </c>
       <c r="E2085" t="n">
-        <v>2.197494254265114</v>
+        <v>2.206758647974145</v>
       </c>
       <c r="F2085" t="n">
-        <v>0.6540075819456045</v>
+        <v>0.6771685662181813</v>
       </c>
       <c r="G2085" t="n">
-        <v>4.734801430342609</v>
+        <v>4.748698020906154</v>
       </c>
     </row>
     <row r="2086">
@@ -49523,22 +49523,22 @@
         <v>45548</v>
       </c>
       <c r="B2086" t="n">
-        <v>3.77823214772099</v>
+        <v>3.778232147720994</v>
       </c>
       <c r="C2086" t="n">
         <v>4.355179067083832</v>
       </c>
       <c r="D2086" t="n">
-        <v>-5.261735355441892</v>
+        <v>-5.238574371169315</v>
       </c>
       <c r="E2086" t="n">
-        <v>2.250128500593328</v>
+        <v>2.259392894302358</v>
       </c>
       <c r="F2086" t="n">
-        <v>0.753637732994672</v>
+        <v>0.7767987172672488</v>
       </c>
       <c r="G2086" t="n">
-        <v>4.807361706880636</v>
+        <v>4.821258297444182</v>
       </c>
     </row>
     <row r="2087">
@@ -49546,22 +49546,22 @@
         <v>45549</v>
       </c>
       <c r="B2087" t="n">
-        <v>3.775357097455265</v>
+        <v>3.775357097455268</v>
       </c>
       <c r="C2087" t="n">
         <v>4.544333332582559</v>
       </c>
       <c r="D2087" t="n">
-        <v>-5.311134864130903</v>
+        <v>-5.287973879858326</v>
       </c>
       <c r="E2087" t="n">
-        <v>2.41952296261645</v>
+        <v>2.42878735632548</v>
       </c>
       <c r="F2087" t="n">
-        <v>0.7638965664264167</v>
+        <v>0.7870575506989935</v>
       </c>
       <c r="G2087" t="n">
-        <v>5.002671272438409</v>
+        <v>5.016567863001955</v>
       </c>
     </row>
     <row r="2088">
@@ -49569,22 +49569,22 @@
         <v>45550</v>
       </c>
       <c r="B2088" t="n">
-        <v>3.749078058963126</v>
+        <v>3.749078058963129</v>
       </c>
       <c r="C2088" t="n">
         <v>4.531522005685421</v>
       </c>
       <c r="D2088" t="n">
-        <v>-5.104450390488527</v>
+        <v>-5.08128940621595</v>
       </c>
       <c r="E2088" t="n">
-        <v>2.489385425176262</v>
+        <v>2.498649818885293</v>
       </c>
       <c r="F2088" t="n">
-        <v>0.9705810400687923</v>
+        <v>0.993742024341369</v>
       </c>
       <c r="G2088" t="n">
-        <v>5.113870629726696</v>
+        <v>5.127767220290242</v>
       </c>
     </row>
     <row r="2089">
@@ -49592,22 +49592,22 @@
         <v>45551</v>
       </c>
       <c r="B2089" t="n">
-        <v>3.740284389162536</v>
+        <v>3.740284389162539</v>
       </c>
       <c r="C2089" t="n">
         <v>4.533523519339526</v>
       </c>
       <c r="D2089" t="n">
-        <v>-5.138607285486053</v>
+        <v>-5.115446301213476</v>
       </c>
       <c r="E2089" t="n">
-        <v>2.477724180831357</v>
+        <v>2.486988574540387</v>
       </c>
       <c r="F2089" t="n">
-        <v>0.8869972705279798</v>
+        <v>0.9101582548005566</v>
       </c>
       <c r="G2089" t="n">
-        <v>5.065721881656314</v>
+        <v>5.07961847221986</v>
       </c>
     </row>
     <row r="2090">
@@ -49615,22 +49615,22 @@
         <v>45552</v>
       </c>
       <c r="B2090" t="n">
-        <v>3.782482115652376</v>
+        <v>3.78248211565238</v>
       </c>
       <c r="C2090" t="n">
         <v>4.887020633329193</v>
       </c>
       <c r="D2090" t="n">
-        <v>-5.046017806424596</v>
+        <v>-5.022856822152019</v>
       </c>
       <c r="E2090" t="n">
-        <v>2.868257086445607</v>
+        <v>2.877521480154638</v>
       </c>
       <c r="F2090" t="n">
-        <v>0.8869972705279798</v>
+        <v>0.9101582548005566</v>
       </c>
       <c r="G2090" t="n">
-        <v>5.419218995645982</v>
+        <v>5.433115586209527</v>
       </c>
     </row>
     <row r="2091">
@@ -49638,22 +49638,22 @@
         <v>45553</v>
       </c>
       <c r="B2091" t="n">
-        <v>3.809055905108666</v>
+        <v>3.80905590510867</v>
       </c>
       <c r="C2091" t="n">
         <v>4.891583744896296</v>
       </c>
       <c r="D2091" t="n">
-        <v>-5.119178410197741</v>
+        <v>-5.096017425925164</v>
       </c>
       <c r="E2091" t="n">
-        <v>2.843555956503452</v>
+        <v>2.852820350212483</v>
       </c>
       <c r="F2091" t="n">
-        <v>0.8589760704937368</v>
+        <v>0.8821370547663134</v>
       </c>
       <c r="G2091" t="n">
-        <v>5.406969387192539</v>
+        <v>5.420865977756085</v>
       </c>
     </row>
     <row r="2092">
@@ -49661,22 +49661,22 @@
         <v>45554</v>
       </c>
       <c r="B2092" t="n">
-        <v>3.835202441103558</v>
+        <v>3.835202441103561</v>
       </c>
       <c r="C2092" t="n">
         <v>4.941413686219824</v>
       </c>
       <c r="D2092" t="n">
-        <v>-5.066962100401399</v>
+        <v>-5.043801116128822</v>
       </c>
       <c r="E2092" t="n">
-        <v>2.914272421745516</v>
+        <v>2.923536815454547</v>
       </c>
       <c r="F2092" t="n">
-        <v>0.8589760704937368</v>
+        <v>0.8821370547663134</v>
       </c>
       <c r="G2092" t="n">
-        <v>5.456799328516066</v>
+        <v>5.470695919079613</v>
       </c>
     </row>
     <row r="2093">
@@ -49684,22 +49684,22 @@
         <v>45555</v>
       </c>
       <c r="B2093" t="n">
-        <v>3.821827147047739</v>
+        <v>3.821827147047742</v>
       </c>
       <c r="C2093" t="n">
         <v>4.950227656429835</v>
       </c>
       <c r="D2093" t="n">
-        <v>-5.035064583316154</v>
+        <v>-5.011903599043577</v>
       </c>
       <c r="E2093" t="n">
-        <v>2.935845398789625</v>
+        <v>2.945109792498656</v>
       </c>
       <c r="F2093" t="n">
-        <v>0.8908735875789826</v>
+        <v>0.9140345718515592</v>
       </c>
       <c r="G2093" t="n">
-        <v>5.484751808977225</v>
+        <v>5.49864839954077</v>
       </c>
     </row>
     <row r="2094">
@@ -49707,22 +49707,22 @@
         <v>45556</v>
       </c>
       <c r="B2094" t="n">
-        <v>3.825268416650749</v>
+        <v>3.825268416650751</v>
       </c>
       <c r="C2094" t="n">
         <v>4.945865240469032</v>
       </c>
       <c r="D2094" t="n">
-        <v>-5.049819907516294</v>
+        <v>-5.026658923243717</v>
       </c>
       <c r="E2094" t="n">
-        <v>2.925580853148766</v>
+        <v>2.934845246857797</v>
       </c>
       <c r="F2094" t="n">
-        <v>0.8908735875789826</v>
+        <v>0.9140345718515592</v>
       </c>
       <c r="G2094" t="n">
-        <v>5.480389393016422</v>
+        <v>5.494285983579967</v>
       </c>
     </row>
     <row r="2095">
@@ -49730,22 +49730,22 @@
         <v>45557</v>
       </c>
       <c r="B2095" t="n">
-        <v>3.845044666135744</v>
+        <v>3.845044666135745</v>
       </c>
       <c r="C2095" t="n">
         <v>4.936789743885312</v>
       </c>
       <c r="D2095" t="n">
-        <v>-5.000355284146383</v>
+        <v>-4.977194299873806</v>
       </c>
       <c r="E2095" t="n">
-        <v>2.936291205913011</v>
+        <v>2.945555599622041</v>
       </c>
       <c r="F2095" t="n">
-        <v>0.9403382109488942</v>
+        <v>0.9634991952214709</v>
       </c>
       <c r="G2095" t="n">
-        <v>5.500992670454648</v>
+        <v>5.514889261018195</v>
       </c>
     </row>
     <row r="2096">
@@ -49753,22 +49753,22 @@
         <v>45558</v>
       </c>
       <c r="B2096" t="n">
-        <v>3.825931790479217</v>
+        <v>3.825931790479219</v>
       </c>
       <c r="C2096" t="n">
         <v>4.933197411600246</v>
       </c>
       <c r="D2096" t="n">
-        <v>-4.837247291992767</v>
+        <v>-4.81408630772019</v>
       </c>
       <c r="E2096" t="n">
-        <v>2.997942070489391</v>
+        <v>3.007206464198422</v>
       </c>
       <c r="F2096" t="n">
-        <v>1.103446203102509</v>
+        <v>1.126607187375086</v>
       </c>
       <c r="G2096" t="n">
-        <v>5.595265133461752</v>
+        <v>5.609161724025298</v>
       </c>
     </row>
     <row r="2097">
@@ -49776,22 +49776,22 @@
         <v>45559</v>
       </c>
       <c r="B2097" t="n">
-        <v>3.847096478844239</v>
+        <v>3.847096478844243</v>
       </c>
       <c r="C2097" t="n">
         <v>4.942244448291374</v>
       </c>
       <c r="D2097" t="n">
-        <v>-4.704439666495601</v>
+        <v>-4.681278682223024</v>
       </c>
       <c r="E2097" t="n">
-        <v>3.060112157379386</v>
+        <v>3.069376551088417</v>
       </c>
       <c r="F2097" t="n">
-        <v>1.103446203102509</v>
+        <v>1.126607187375086</v>
       </c>
       <c r="G2097" t="n">
-        <v>5.60431217015288</v>
+        <v>5.618208760716426</v>
       </c>
     </row>
     <row r="2098">
@@ -49799,22 +49799,22 @@
         <v>45560</v>
       </c>
       <c r="B2098" t="n">
-        <v>3.832425987790942</v>
+        <v>3.832425987790947</v>
       </c>
       <c r="C2098" t="n">
         <v>4.943101913277496</v>
       </c>
       <c r="D2098" t="n">
-        <v>-4.767147582970159</v>
+        <v>-4.743986598697582</v>
       </c>
       <c r="E2098" t="n">
-        <v>3.035886455775684</v>
+        <v>3.045150849484715</v>
       </c>
       <c r="F2098" t="n">
-        <v>1.040738286627952</v>
+        <v>1.063899270900528</v>
       </c>
       <c r="G2098" t="n">
-        <v>5.567544885254267</v>
+        <v>5.581441475817813</v>
       </c>
     </row>
     <row r="2099">
@@ -49822,22 +49822,22 @@
         <v>45561</v>
       </c>
       <c r="B2099" t="n">
-        <v>3.861579399578989</v>
+        <v>3.861579399578993</v>
       </c>
       <c r="C2099" t="n">
         <v>4.906011330067848</v>
       </c>
       <c r="D2099" t="n">
-        <v>-4.719139459126466</v>
+        <v>-4.695978474853889</v>
       </c>
       <c r="E2099" t="n">
-        <v>3.017999122103514</v>
+        <v>3.027263515812544</v>
       </c>
       <c r="F2099" t="n">
-        <v>1.040738286627952</v>
+        <v>1.063899270900528</v>
       </c>
       <c r="G2099" t="n">
-        <v>5.530454302044619</v>
+        <v>5.544350892608166</v>
       </c>
     </row>
     <row r="2100">
@@ -49845,22 +49845,22 @@
         <v>45562</v>
       </c>
       <c r="B2100" t="n">
-        <v>3.872253907629878</v>
+        <v>3.872253907629881</v>
       </c>
       <c r="C2100" t="n">
         <v>4.909943583625799</v>
       </c>
       <c r="D2100" t="n">
-        <v>-4.640313801942876</v>
+        <v>-4.617152817670299</v>
       </c>
       <c r="E2100" t="n">
-        <v>3.0534616385349</v>
+        <v>3.062726032243931</v>
       </c>
       <c r="F2100" t="n">
-        <v>1.119563943811542</v>
+        <v>1.142724928084119</v>
       </c>
       <c r="G2100" t="n">
-        <v>5.581681949912724</v>
+        <v>5.59557854047627</v>
       </c>
     </row>
     <row r="2101">
@@ -49868,22 +49868,22 @@
         <v>45563</v>
       </c>
       <c r="B2101" t="n">
-        <v>3.8685025316864</v>
+        <v>3.868502531686404</v>
       </c>
       <c r="C2101" t="n">
         <v>4.904842676232835</v>
       </c>
       <c r="D2101" t="n">
-        <v>-4.448379000689002</v>
+        <v>-4.425218016416425</v>
       </c>
       <c r="E2101" t="n">
-        <v>3.125134651643487</v>
+        <v>3.134399045352517</v>
       </c>
       <c r="F2101" t="n">
-        <v>1.119563943811542</v>
+        <v>1.142724928084119</v>
       </c>
       <c r="G2101" t="n">
-        <v>5.576581042519761</v>
+        <v>5.590477633083307</v>
       </c>
     </row>
     <row r="2102">
@@ -49891,22 +49891,45 @@
         <v>45564</v>
       </c>
       <c r="B2102" t="n">
-        <v>3.900114331443694</v>
+        <v>3.849324044046709</v>
       </c>
       <c r="C2102" t="n">
         <v>4.900196585621931</v>
       </c>
       <c r="D2102" t="n">
-        <v>-4.330205622671075</v>
+        <v>-4.415001042633214</v>
       </c>
       <c r="E2102" t="n">
-        <v>3.167757912239753</v>
+        <v>3.133839744254897</v>
       </c>
       <c r="F2102" t="n">
-        <v>1.237737321829469</v>
+        <v>1.152941901867329</v>
       </c>
       <c r="G2102" t="n">
-        <v>5.642838978719612</v>
+        <v>5.591961726742329</v>
+      </c>
+    </row>
+    <row r="2103">
+      <c r="A2103" s="2" t="n">
+        <v>45565</v>
+      </c>
+      <c r="B2103" t="n">
+        <v>3.765338746849089</v>
+      </c>
+      <c r="C2103" t="n">
+        <v>4.845407776679131</v>
+      </c>
+      <c r="D2103" t="n">
+        <v>-4.415001042633214</v>
+      </c>
+      <c r="E2103" t="n">
+        <v>3.133839744254897</v>
+      </c>
+      <c r="F2103" t="n">
+        <v>1.152941901867329</v>
+      </c>
+      <c r="G2103" t="n">
+        <v>4.838471573665499</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240930.xlsx
+++ b/tame_output/ON/bt/strategyON_20240930.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>54.0%</t>
+          <t>57.8%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -610,7 +610,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>65.0%</t>
+          <t>64.8%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>17.8%</t>
+          <t>18.2%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>48.5%</t>
+          <t>62.0%</t>
         </is>
       </c>
     </row>
@@ -758,22 +758,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>111.0%</t>
+          <t>118.5%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>44.0%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.52</t>
+          <t>2.67</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>58.5%</t>
+          <t>58.6%</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -791,12 +791,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>39.7%</t>
+          <t>39.6%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>47.2%</t>
+          <t>47.9%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>10.7%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>93.3%</t>
+          <t>99.4%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>36.0%</t>
+          <t>36.3%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.6</t>
+          <t>2.7</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-8.2%</t>
+          <t>-8.4%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.8%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>172.9%</t>
+          <t>194.1%</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-75.6%</t>
+          <t>-75.1%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>107.6%</t>
+          <t>107.7%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>123.0%</t>
+          <t>122.9%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>91.4%</t>
+          <t>91.6%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>21.9%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-71.8%</t>
+          <t>-71.1%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>89.3%</t>
+          <t>89.4%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>420.8%</t>
+          <t>421.8%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-6.9%</t>
+          <t>-7.1%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-603.1%</t>
+          <t>-591.1%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>43.9%</t>
+          <t>45.5%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>59.9%</t>
+          <t>60.0%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>57.6%</t>
+          <t>57.7%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1140,7 +1140,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>-8.7%</t>
+          <t>-8.5%</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>14.2%</t>
+          <t>14.4%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-33.6%</t>
+          <t>-33.5%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>38.7%</t>
+          <t>40.1%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>50.1%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-3.9%</t>
+          <t>-4.0%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15.3%</t>
+          <t>15.4%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-62.8%</t>
+          <t>-56.2%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-4.4%</t>
+          <t>-2.4%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.1%</t>
+          <t>66.3%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>72.9%</t>
+          <t>73.4%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.1%</t>
+          <t>10.3%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>2.0%</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.1%</t>
+          <t>55.2%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>45.4%</t>
+          <t>45.8%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-400.8%</t>
+          <t>-403.0%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-108.7%</t>
+          <t>-96.8%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>74.7%</t>
+          <t>90.1%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>65.7%</t>
+          <t>63.5%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.14</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>76.9%</t>
+          <t>72.3%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>56.7%</t>
+          <t>56.9%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1447,7 +1447,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.8%</t>
+          <t>13.2%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>64.0%</t>
+          <t>81.6%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>54.6%</t>
+          <t>53.0%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-15.6%</t>
+          <t>-17.1%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>36.6%</t>
+          <t>35.8%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>37.8%</t>
+          <t>59.0%</t>
         </is>
       </c>
     </row>
@@ -47729,7 +47729,7 @@
         <v>45470</v>
       </c>
       <c r="B2008" t="n">
-        <v>3.7278981863477</v>
+        <v>3.727898186347699</v>
       </c>
       <c r="C2008" t="n">
         <v>3.207242866402009</v>
@@ -47752,7 +47752,7 @@
         <v>45471</v>
       </c>
       <c r="B2009" t="n">
-        <v>3.710654104887745</v>
+        <v>3.710654104887744</v>
       </c>
       <c r="C2009" t="n">
         <v>3.202063096004871</v>
@@ -47775,7 +47775,7 @@
         <v>45472</v>
       </c>
       <c r="B2010" t="n">
-        <v>3.712897612343062</v>
+        <v>3.712897612343061</v>
       </c>
       <c r="C2010" t="n">
         <v>3.200497106215023</v>
@@ -47798,7 +47798,7 @@
         <v>45473</v>
       </c>
       <c r="B2011" t="n">
-        <v>3.754596135389345</v>
+        <v>3.754596135389344</v>
       </c>
       <c r="C2011" t="n">
         <v>3.213570513080942</v>
@@ -48120,7 +48120,7 @@
         <v>45487</v>
       </c>
       <c r="B2025" t="n">
-        <v>3.750044015868143</v>
+        <v>3.750044015868142</v>
       </c>
       <c r="C2025" t="n">
         <v>3.642474075595412</v>
@@ -48143,22 +48143,22 @@
         <v>45488</v>
       </c>
       <c r="B2026" t="n">
-        <v>3.783632867332689</v>
+        <v>3.783632867332688</v>
       </c>
       <c r="C2026" t="n">
         <v>3.651399714051315</v>
       </c>
       <c r="D2026" t="n">
-        <v>-5.778940788711521</v>
+        <v>-5.767420677701326</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.339466974252959</v>
+        <v>1.344075018657036</v>
       </c>
       <c r="F2026" t="n">
-        <v>-0.1298787761931792</v>
+        <v>-0.118358665182984</v>
       </c>
       <c r="G2026" t="n">
-        <v>3.573472448335407</v>
+        <v>3.580384514941525</v>
       </c>
     </row>
     <row r="2027">
@@ -48172,16 +48172,16 @@
         <v>3.64355260129549</v>
       </c>
       <c r="D2027" t="n">
-        <v>-5.668934505234299</v>
+        <v>-5.657414394224104</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.375622374888022</v>
+        <v>1.3802304192921</v>
       </c>
       <c r="F2027" t="n">
-        <v>-0.106674204275904</v>
+        <v>-0.09515409326570884</v>
       </c>
       <c r="G2027" t="n">
-        <v>3.579548078729948</v>
+        <v>3.586460145336065</v>
       </c>
     </row>
     <row r="2028">
@@ -48189,22 +48189,22 @@
         <v>45490</v>
       </c>
       <c r="B2028" t="n">
-        <v>3.785563924818519</v>
+        <v>3.785563924818518</v>
       </c>
       <c r="C2028" t="n">
         <v>3.647802612017464</v>
       </c>
       <c r="D2028" t="n">
-        <v>-5.525874929493373</v>
+        <v>-5.514354818483179</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.437096215906367</v>
+        <v>1.441704260310445</v>
       </c>
       <c r="F2028" t="n">
-        <v>-0.09866077768592474</v>
+        <v>-0.08714066667572956</v>
       </c>
       <c r="G2028" t="n">
-        <v>3.588606145405909</v>
+        <v>3.595518212012027</v>
       </c>
     </row>
     <row r="2029">
@@ -48212,22 +48212,22 @@
         <v>45491</v>
       </c>
       <c r="B2029" t="n">
-        <v>3.777237412051786</v>
+        <v>3.777237412051785</v>
       </c>
       <c r="C2029" t="n">
         <v>3.6550634949</v>
       </c>
       <c r="D2029" t="n">
-        <v>-5.224428204021535</v>
+        <v>-5.212908093011341</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.564935788977638</v>
+        <v>1.569543833381716</v>
       </c>
       <c r="F2029" t="n">
-        <v>0.2027859477859125</v>
+        <v>0.2143060587961077</v>
       </c>
       <c r="G2029" t="n">
-        <v>3.776735063571548</v>
+        <v>3.783647130177665</v>
       </c>
     </row>
     <row r="2030">
@@ -48235,22 +48235,22 @@
         <v>45492</v>
       </c>
       <c r="B2030" t="n">
-        <v>3.812635940679623</v>
+        <v>3.812635940679622</v>
       </c>
       <c r="C2030" t="n">
         <v>3.656034672652711</v>
       </c>
       <c r="D2030" t="n">
-        <v>-5.249018448256719</v>
+        <v>-5.237498337246525</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.556070869036275</v>
+        <v>1.560678913440353</v>
       </c>
       <c r="F2030" t="n">
-        <v>0.2027859477859125</v>
+        <v>0.2143060587961077</v>
       </c>
       <c r="G2030" t="n">
-        <v>3.777706241324259</v>
+        <v>3.784618307930376</v>
       </c>
     </row>
     <row r="2031">
@@ -48258,22 +48258,22 @@
         <v>45493</v>
       </c>
       <c r="B2031" t="n">
-        <v>3.821184182474158</v>
+        <v>3.821184182474157</v>
       </c>
       <c r="C2031" t="n">
         <v>3.656877577032466</v>
       </c>
       <c r="D2031" t="n">
-        <v>-5.197980072250199</v>
+        <v>-5.186459961240005</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.577329123818639</v>
+        <v>1.581937168222717</v>
       </c>
       <c r="F2031" t="n">
-        <v>0.2027859477859125</v>
+        <v>0.2143060587961077</v>
       </c>
       <c r="G2031" t="n">
-        <v>3.778549145704014</v>
+        <v>3.785461212310131</v>
       </c>
     </row>
     <row r="2032">
@@ -48281,22 +48281,22 @@
         <v>45494</v>
       </c>
       <c r="B2032" t="n">
-        <v>3.831734516969542</v>
+        <v>3.831734516969541</v>
       </c>
       <c r="C2032" t="n">
         <v>3.675915675906612</v>
       </c>
       <c r="D2032" t="n">
-        <v>-5.169131395426739</v>
+        <v>-5.157611284416545</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.607906693422168</v>
+        <v>1.612514737826246</v>
       </c>
       <c r="F2032" t="n">
-        <v>0.2316346246093728</v>
+        <v>0.243154735619568</v>
       </c>
       <c r="G2032" t="n">
-        <v>3.814896450672236</v>
+        <v>3.821808517278353</v>
       </c>
     </row>
     <row r="2033">
@@ -48304,22 +48304,22 @@
         <v>45495</v>
       </c>
       <c r="B2033" t="n">
-        <v>3.825752932700476</v>
+        <v>3.825752932700475</v>
       </c>
       <c r="C2033" t="n">
         <v>3.492099672030546</v>
       </c>
       <c r="D2033" t="n">
-        <v>-5.072496483408099</v>
+        <v>-5.060976372397905</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.462744654353559</v>
+        <v>1.467352698757637</v>
       </c>
       <c r="F2033" t="n">
-        <v>0.3282695366280127</v>
+        <v>0.3397896476382079</v>
       </c>
       <c r="G2033" t="n">
-        <v>3.689061394007354</v>
+        <v>3.695973460613471</v>
       </c>
     </row>
     <row r="2034">
@@ -48333,16 +48333,16 @@
         <v>3.495601716104511</v>
       </c>
       <c r="D2034" t="n">
-        <v>-5.003458472459631</v>
+        <v>-4.991938361449437</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.49386190280691</v>
+        <v>1.498469947210988</v>
       </c>
       <c r="F2034" t="n">
-        <v>0.3973075475764808</v>
+        <v>0.408827658586676</v>
       </c>
       <c r="G2034" t="n">
-        <v>3.733986244650399</v>
+        <v>3.740898311256516</v>
       </c>
     </row>
     <row r="2035">
@@ -48350,22 +48350,22 @@
         <v>45497</v>
       </c>
       <c r="B2035" t="n">
-        <v>3.775028860833456</v>
+        <v>3.775028860833455</v>
       </c>
       <c r="C2035" t="n">
         <v>3.480028535180593</v>
       </c>
       <c r="D2035" t="n">
-        <v>-4.984671372090692</v>
+        <v>-4.973151261080498</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.485803562030568</v>
+        <v>1.490411606434646</v>
       </c>
       <c r="F2035" t="n">
-        <v>0.4160946479454193</v>
+        <v>0.4276147589556145</v>
       </c>
       <c r="G2035" t="n">
-        <v>3.729685323947845</v>
+        <v>3.736597390553962</v>
       </c>
     </row>
     <row r="2036">
@@ -48379,16 +48379,16 @@
         <v>3.479216245617023</v>
       </c>
       <c r="D2036" t="n">
-        <v>-4.907572770548819</v>
+        <v>-4.896052659538626</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.515830713083747</v>
+        <v>1.520438757487825</v>
       </c>
       <c r="F2036" t="n">
-        <v>0.4160946479454193</v>
+        <v>0.4276147589556145</v>
       </c>
       <c r="G2036" t="n">
-        <v>3.728873034384275</v>
+        <v>3.735785100990392</v>
       </c>
     </row>
     <row r="2037">
@@ -48402,16 +48402,16 @@
         <v>3.489085024742095</v>
       </c>
       <c r="D2037" t="n">
-        <v>-4.917957965438709</v>
+        <v>-4.906437854428515</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.521545414252864</v>
+        <v>1.526153458656941</v>
       </c>
       <c r="F2037" t="n">
-        <v>0.40570945305553</v>
+        <v>0.4172295640657251</v>
       </c>
       <c r="G2037" t="n">
-        <v>3.732510696575413</v>
+        <v>3.739422763181531</v>
       </c>
     </row>
     <row r="2038">
@@ -48419,22 +48419,22 @@
         <v>45500</v>
       </c>
       <c r="B2038" t="n">
-        <v>3.834415493735278</v>
+        <v>3.834415493735277</v>
       </c>
       <c r="C2038" t="n">
         <v>3.55992203051852</v>
       </c>
       <c r="D2038" t="n">
-        <v>-4.936546124160934</v>
+        <v>-4.92502601315074</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.584947156540399</v>
+        <v>1.589555200944476</v>
       </c>
       <c r="F2038" t="n">
-        <v>0.3871212943333046</v>
+        <v>0.3986414053434998</v>
       </c>
       <c r="G2038" t="n">
-        <v>3.792194807118503</v>
+        <v>3.799106873724621</v>
       </c>
     </row>
     <row r="2039">
@@ -48448,16 +48448,16 @@
         <v>3.556791041336819</v>
       </c>
       <c r="D2039" t="n">
-        <v>-4.93684467085697</v>
+        <v>-4.925324559846776</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.581696748680283</v>
+        <v>1.586304793084361</v>
       </c>
       <c r="F2039" t="n">
-        <v>0.3868227476372687</v>
+        <v>0.3983428586474639</v>
       </c>
       <c r="G2039" t="n">
-        <v>3.78888468991918</v>
+        <v>3.795796756525298</v>
       </c>
     </row>
     <row r="2040">
@@ -48465,22 +48465,22 @@
         <v>45502</v>
       </c>
       <c r="B2040" t="n">
-        <v>3.815643212108854</v>
+        <v>3.815643212108853</v>
       </c>
       <c r="C2040" t="n">
         <v>3.56132193627621</v>
       </c>
       <c r="D2040" t="n">
-        <v>-4.836021537166542</v>
+        <v>-4.824501426156348</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.626556897095845</v>
+        <v>1.631164941499923</v>
       </c>
       <c r="F2040" t="n">
-        <v>0.3992869631216225</v>
+        <v>0.4108070741318177</v>
       </c>
       <c r="G2040" t="n">
-        <v>3.800894114149184</v>
+        <v>3.807806180755301</v>
       </c>
     </row>
     <row r="2041">
@@ -48488,22 +48488,22 @@
         <v>45503</v>
       </c>
       <c r="B2041" t="n">
-        <v>3.807356168121463</v>
+        <v>3.807356168121462</v>
       </c>
       <c r="C2041" t="n">
         <v>3.561451189754754</v>
       </c>
       <c r="D2041" t="n">
-        <v>-4.645240176414134</v>
+        <v>-4.63372006540394</v>
       </c>
       <c r="E2041" t="n">
-        <v>1.702998694875352</v>
+        <v>1.707606739279429</v>
       </c>
       <c r="F2041" t="n">
-        <v>0.5900683238740299</v>
+        <v>0.6015884348842251</v>
       </c>
       <c r="G2041" t="n">
-        <v>3.915492184079172</v>
+        <v>3.922404250685289</v>
       </c>
     </row>
     <row r="2042">
@@ -48511,22 +48511,22 @@
         <v>45504</v>
       </c>
       <c r="B2042" t="n">
-        <v>3.775233033906076</v>
+        <v>3.775233033906075</v>
       </c>
       <c r="C2042" t="n">
         <v>3.54128803549235</v>
       </c>
       <c r="D2042" t="n">
-        <v>-4.538276818564713</v>
+        <v>-4.526756707554519</v>
       </c>
       <c r="E2042" t="n">
-        <v>1.725620883752717</v>
+        <v>1.730228928156795</v>
       </c>
       <c r="F2042" t="n">
-        <v>0.6485329318338313</v>
+        <v>0.6600530428440265</v>
       </c>
       <c r="G2042" t="n">
-        <v>3.930407794592649</v>
+        <v>3.937319861198766</v>
       </c>
     </row>
     <row r="2043">
@@ -48540,16 +48540,16 @@
         <v>3.576254972104409</v>
       </c>
       <c r="D2043" t="n">
-        <v>-4.48294623066295</v>
+        <v>-4.471426119652756</v>
       </c>
       <c r="E2043" t="n">
-        <v>1.782720055525481</v>
+        <v>1.787328099929558</v>
       </c>
       <c r="F2043" t="n">
-        <v>0.7038635197355935</v>
+        <v>0.7153836307457887</v>
       </c>
       <c r="G2043" t="n">
-        <v>3.998573083945764</v>
+        <v>4.005485150551882</v>
       </c>
     </row>
     <row r="2044">
@@ -48563,16 +48563,16 @@
         <v>3.569941540005846</v>
       </c>
       <c r="D2044" t="n">
-        <v>-4.470892103749987</v>
+        <v>-4.459371992739793</v>
       </c>
       <c r="E2044" t="n">
-        <v>1.781228274192103</v>
+        <v>1.785836318596181</v>
       </c>
       <c r="F2044" t="n">
-        <v>0.7159176466485563</v>
+        <v>0.7274377576587515</v>
       </c>
       <c r="G2044" t="n">
-        <v>3.99949212799498</v>
+        <v>4.006404194601098</v>
       </c>
     </row>
     <row r="2045">
@@ -48586,16 +48586,16 @@
         <v>3.571822170189982</v>
       </c>
       <c r="D2045" t="n">
-        <v>-4.512047223318208</v>
+        <v>-4.500527112308014</v>
       </c>
       <c r="E2045" t="n">
-        <v>1.766646856548951</v>
+        <v>1.771254900953029</v>
       </c>
       <c r="F2045" t="n">
-        <v>0.6747625270803354</v>
+        <v>0.6862826380905306</v>
       </c>
       <c r="G2045" t="n">
-        <v>3.976679686438183</v>
+        <v>3.9835917530443</v>
       </c>
     </row>
     <row r="2046">
@@ -48609,16 +48609,16 @@
         <v>3.584673196067865</v>
       </c>
       <c r="D2046" t="n">
-        <v>-4.443998660626678</v>
+        <v>-4.432478549616484</v>
       </c>
       <c r="E2046" t="n">
-        <v>1.806717307503445</v>
+        <v>1.811325351907523</v>
       </c>
       <c r="F2046" t="n">
-        <v>0.7428110897718652</v>
+        <v>0.7543312007820604</v>
       </c>
       <c r="G2046" t="n">
-        <v>4.030359849930984</v>
+        <v>4.037271916537101</v>
       </c>
     </row>
     <row r="2047">
@@ -48632,16 +48632,16 @@
         <v>3.604875866241459</v>
       </c>
       <c r="D2047" t="n">
-        <v>-4.675599053796179</v>
+        <v>-4.664078942785985</v>
       </c>
       <c r="E2047" t="n">
-        <v>1.734279820409239</v>
+        <v>1.738887864813317</v>
       </c>
       <c r="F2047" t="n">
-        <v>0.7428110897718652</v>
+        <v>0.7543312007820604</v>
       </c>
       <c r="G2047" t="n">
-        <v>4.050562520104578</v>
+        <v>4.057474586710695</v>
       </c>
     </row>
     <row r="2048">
@@ -48655,16 +48655,16 @@
         <v>3.588482102308341</v>
       </c>
       <c r="D2048" t="n">
-        <v>-4.725650599325398</v>
+        <v>-4.714130488315204</v>
       </c>
       <c r="E2048" t="n">
-        <v>1.697865438264434</v>
+        <v>1.702473482668511</v>
       </c>
       <c r="F2048" t="n">
-        <v>0.7428110897718652</v>
+        <v>0.7543312007820604</v>
       </c>
       <c r="G2048" t="n">
-        <v>4.03416875617146</v>
+        <v>4.041080822777578</v>
       </c>
     </row>
     <row r="2049">
@@ -48678,16 +48678,16 @@
         <v>3.548734015901807</v>
       </c>
       <c r="D2049" t="n">
-        <v>-4.900757431901843</v>
+        <v>-4.889237320891649</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.588074618827322</v>
+        <v>1.5926826632314</v>
       </c>
       <c r="F2049" t="n">
-        <v>0.7428110897718652</v>
+        <v>0.7543312007820604</v>
       </c>
       <c r="G2049" t="n">
-        <v>3.994420669764927</v>
+        <v>4.001332736371044</v>
       </c>
     </row>
     <row r="2050">
@@ -48701,16 +48701,16 @@
         <v>3.555756634898747</v>
       </c>
       <c r="D2050" t="n">
-        <v>-4.70465727847132</v>
+        <v>-4.693137167461126</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.673537299196472</v>
+        <v>1.678145343600549</v>
       </c>
       <c r="F2050" t="n">
-        <v>0.9389112432023881</v>
+        <v>0.9504313542125833</v>
       </c>
       <c r="G2050" t="n">
-        <v>4.119103380820181</v>
+        <v>4.126015447426298</v>
       </c>
     </row>
     <row r="2051">
@@ -48724,16 +48724,16 @@
         <v>3.654927634471652</v>
       </c>
       <c r="D2051" t="n">
-        <v>-4.551631886358035</v>
+        <v>-4.540111775347841</v>
       </c>
       <c r="E2051" t="n">
-        <v>1.83391845561469</v>
+        <v>1.838526500018767</v>
       </c>
       <c r="F2051" t="n">
-        <v>1.091936635315672</v>
+        <v>1.103456746325867</v>
       </c>
       <c r="G2051" t="n">
-        <v>4.310089615661055</v>
+        <v>4.317001682267173</v>
       </c>
     </row>
     <row r="2052">
@@ -48747,16 +48747,16 @@
         <v>3.842393859379944</v>
       </c>
       <c r="D2052" t="n">
-        <v>-4.579939200231306</v>
+        <v>-4.568419089221112</v>
       </c>
       <c r="E2052" t="n">
-        <v>2.010061754973674</v>
+        <v>2.014669799377752</v>
       </c>
       <c r="F2052" t="n">
-        <v>1.091936635315672</v>
+        <v>1.103456746325867</v>
       </c>
       <c r="G2052" t="n">
-        <v>4.497555840569348</v>
+        <v>4.504467907175465</v>
       </c>
     </row>
     <row r="2053">
@@ -48770,16 +48770,16 @@
         <v>3.811796810734027</v>
       </c>
       <c r="D2053" t="n">
-        <v>-4.746532425344828</v>
+        <v>-4.735012314334634</v>
       </c>
       <c r="E2053" t="n">
-        <v>1.912827416282348</v>
+        <v>1.917435460686426</v>
       </c>
       <c r="F2053" t="n">
-        <v>0.9253434102021496</v>
+        <v>0.9368635212123448</v>
       </c>
       <c r="G2053" t="n">
-        <v>4.367002856855317</v>
+        <v>4.373914923461435</v>
       </c>
     </row>
     <row r="2054">
@@ -48793,16 +48793,16 @@
         <v>3.815473213395745</v>
       </c>
       <c r="D2054" t="n">
-        <v>-4.723496631983262</v>
+        <v>-4.711976520973068</v>
       </c>
       <c r="E2054" t="n">
-        <v>1.925718136288692</v>
+        <v>1.93032618069277</v>
       </c>
       <c r="F2054" t="n">
-        <v>0.9253434102021496</v>
+        <v>0.9368635212123448</v>
       </c>
       <c r="G2054" t="n">
-        <v>4.370679259517035</v>
+        <v>4.377591326123152</v>
       </c>
     </row>
     <row r="2055">
@@ -48816,16 +48816,16 @@
         <v>3.81309126851924</v>
       </c>
       <c r="D2055" t="n">
-        <v>-4.694250651527565</v>
+        <v>-4.682730540517372</v>
       </c>
       <c r="E2055" t="n">
-        <v>1.935034583594466</v>
+        <v>1.939642627998543</v>
       </c>
       <c r="F2055" t="n">
-        <v>0.9253434102021496</v>
+        <v>0.9368635212123448</v>
       </c>
       <c r="G2055" t="n">
-        <v>4.368297314640531</v>
+        <v>4.375209381246647</v>
       </c>
     </row>
     <row r="2056">
@@ -48839,16 +48839,16 @@
         <v>3.810384507676875</v>
       </c>
       <c r="D2056" t="n">
-        <v>-4.801176199405417</v>
+        <v>-4.789656088395223</v>
       </c>
       <c r="E2056" t="n">
-        <v>1.889557603600961</v>
+        <v>1.894165648005038</v>
       </c>
       <c r="F2056" t="n">
-        <v>0.8184178623242983</v>
+        <v>0.8299379733344935</v>
       </c>
       <c r="G2056" t="n">
-        <v>4.301435225071454</v>
+        <v>4.308347291677571</v>
       </c>
     </row>
     <row r="2057">
@@ -48862,16 +48862,16 @@
         <v>3.811813309820109</v>
       </c>
       <c r="D2057" t="n">
-        <v>-4.946194757912665</v>
+        <v>-4.934674646902471</v>
       </c>
       <c r="E2057" t="n">
-        <v>1.832978982341295</v>
+        <v>1.837587026745373</v>
       </c>
       <c r="F2057" t="n">
-        <v>0.6733993038170497</v>
+        <v>0.6849194148272449</v>
       </c>
       <c r="G2057" t="n">
-        <v>4.215852892110339</v>
+        <v>4.222764958716457</v>
       </c>
     </row>
     <row r="2058">
@@ -48885,16 +48885,16 @@
         <v>3.911744549077862</v>
       </c>
       <c r="D2058" t="n">
-        <v>-5.064536523697383</v>
+        <v>-5.053016412687189</v>
       </c>
       <c r="E2058" t="n">
-        <v>1.885573515285161</v>
+        <v>1.890181559689239</v>
       </c>
       <c r="F2058" t="n">
-        <v>0.6840853423799398</v>
+        <v>0.695605453390135</v>
       </c>
       <c r="G2058" t="n">
-        <v>4.322195754505826</v>
+        <v>4.329107821111943</v>
       </c>
     </row>
     <row r="2059">
@@ -48908,16 +48908,16 @@
         <v>3.909530246203802</v>
       </c>
       <c r="D2059" t="n">
-        <v>-5.115946946018091</v>
+        <v>-5.104426835007897</v>
       </c>
       <c r="E2059" t="n">
-        <v>1.862795043482817</v>
+        <v>1.867403087886895</v>
       </c>
       <c r="F2059" t="n">
-        <v>0.6840853423799398</v>
+        <v>0.695605453390135</v>
       </c>
       <c r="G2059" t="n">
-        <v>4.319981451631766</v>
+        <v>4.326893518237883</v>
       </c>
     </row>
     <row r="2060">
@@ -48925,22 +48925,22 @@
         <v>45522</v>
       </c>
       <c r="B2060" t="n">
-        <v>3.704757949437328</v>
+        <v>3.704757949437327</v>
       </c>
       <c r="C2060" t="n">
         <v>3.909433374278091</v>
       </c>
       <c r="D2060" t="n">
-        <v>-5.195366397225842</v>
+        <v>-5.183846286215648</v>
       </c>
       <c r="E2060" t="n">
-        <v>1.830930391074006</v>
+        <v>1.835538435478083</v>
       </c>
       <c r="F2060" t="n">
-        <v>0.6840853423799398</v>
+        <v>0.695605453390135</v>
       </c>
       <c r="G2060" t="n">
-        <v>4.319884579706055</v>
+        <v>4.326796646312172</v>
       </c>
     </row>
     <row r="2061">
@@ -48954,16 +48954,16 @@
         <v>3.909427267836134</v>
       </c>
       <c r="D2061" t="n">
-        <v>-5.29082939514306</v>
+        <v>-5.279309284132866</v>
       </c>
       <c r="E2061" t="n">
-        <v>1.792739085465162</v>
+        <v>1.797347129869239</v>
       </c>
       <c r="F2061" t="n">
-        <v>0.6840853423799398</v>
+        <v>0.695605453390135</v>
       </c>
       <c r="G2061" t="n">
-        <v>4.319878473264098</v>
+        <v>4.326790539870215</v>
       </c>
     </row>
     <row r="2062">
@@ -48977,16 +48977,16 @@
         <v>3.907523664398744</v>
       </c>
       <c r="D2062" t="n">
-        <v>-5.226453484292345</v>
+        <v>-5.214933373282151</v>
       </c>
       <c r="E2062" t="n">
-        <v>1.816585846368058</v>
+        <v>1.821193890772136</v>
       </c>
       <c r="F2062" t="n">
-        <v>0.7484612532306549</v>
+        <v>0.7599813642408502</v>
       </c>
       <c r="G2062" t="n">
-        <v>4.356600416337137</v>
+        <v>4.363512482943254</v>
       </c>
     </row>
     <row r="2063">
@@ -49000,16 +49000,16 @@
         <v>3.913257482146471</v>
       </c>
       <c r="D2063" t="n">
-        <v>-5.281822646424539</v>
+        <v>-5.270302535414345</v>
       </c>
       <c r="E2063" t="n">
-        <v>1.800171999262907</v>
+        <v>1.804780043666985</v>
       </c>
       <c r="F2063" t="n">
-        <v>0.7484612532306549</v>
+        <v>0.7599813642408502</v>
       </c>
       <c r="G2063" t="n">
-        <v>4.362334234084864</v>
+        <v>4.369246300690981</v>
       </c>
     </row>
     <row r="2064">
@@ -49023,16 +49023,16 @@
         <v>3.912795845489403</v>
       </c>
       <c r="D2064" t="n">
-        <v>-5.300041113422147</v>
+        <v>-5.288521002411954</v>
       </c>
       <c r="E2064" t="n">
-        <v>1.792422975806796</v>
+        <v>1.797031020210874</v>
       </c>
       <c r="F2064" t="n">
-        <v>0.7233548159748128</v>
+        <v>0.734874926985008</v>
       </c>
       <c r="G2064" t="n">
-        <v>4.346808735074291</v>
+        <v>4.353720801680408</v>
       </c>
     </row>
     <row r="2065">
@@ -49046,16 +49046,16 @@
         <v>3.932670238339722</v>
       </c>
       <c r="D2065" t="n">
-        <v>-5.211834279274569</v>
+        <v>-5.200314168264375</v>
       </c>
       <c r="E2065" t="n">
-        <v>1.847580102316146</v>
+        <v>1.852188146720224</v>
       </c>
       <c r="F2065" t="n">
-        <v>0.7233548159748128</v>
+        <v>0.734874926985008</v>
       </c>
       <c r="G2065" t="n">
-        <v>4.36668312792461</v>
+        <v>4.373595194530727</v>
       </c>
     </row>
     <row r="2066">
@@ -49069,16 +49069,16 @@
         <v>3.91637093886445</v>
       </c>
       <c r="D2066" t="n">
-        <v>-5.10579928406926</v>
+        <v>-5.094279173059066</v>
       </c>
       <c r="E2066" t="n">
-        <v>1.873694800922998</v>
+        <v>1.878302845327076</v>
       </c>
       <c r="F2066" t="n">
-        <v>0.7233548159748128</v>
+        <v>0.734874926985008</v>
       </c>
       <c r="G2066" t="n">
-        <v>4.350383828449337</v>
+        <v>4.357295895055455</v>
       </c>
     </row>
     <row r="2067">
@@ -49092,16 +49092,16 @@
         <v>3.918801888328495</v>
       </c>
       <c r="D2067" t="n">
-        <v>-4.922587620936165</v>
+        <v>-4.911067509925971</v>
       </c>
       <c r="E2067" t="n">
-        <v>1.949410415640282</v>
+        <v>1.954018460044359</v>
       </c>
       <c r="F2067" t="n">
-        <v>0.7233548159748128</v>
+        <v>0.734874926985008</v>
       </c>
       <c r="G2067" t="n">
-        <v>4.352814777913383</v>
+        <v>4.359726844519501</v>
       </c>
     </row>
     <row r="2068">
@@ -49115,16 +49115,16 @@
         <v>3.901746294407872</v>
       </c>
       <c r="D2068" t="n">
-        <v>-4.850866173922314</v>
+        <v>-4.83934606291212</v>
       </c>
       <c r="E2068" t="n">
-        <v>1.961043400525199</v>
+        <v>1.965651444929277</v>
       </c>
       <c r="F2068" t="n">
-        <v>0.7950762629886634</v>
+        <v>0.8065963739988586</v>
       </c>
       <c r="G2068" t="n">
-        <v>4.378792052201071</v>
+        <v>4.385704118807188</v>
       </c>
     </row>
     <row r="2069">
@@ -49138,16 +49138,16 @@
         <v>3.848662040329044</v>
       </c>
       <c r="D2069" t="n">
-        <v>-4.828493148314608</v>
+        <v>-4.816973037304414</v>
       </c>
       <c r="E2069" t="n">
-        <v>1.916908356689453</v>
+        <v>1.92151640109353</v>
       </c>
       <c r="F2069" t="n">
-        <v>0.806332014101565</v>
+        <v>0.8178521251117602</v>
       </c>
       <c r="G2069" t="n">
-        <v>4.332461248789984</v>
+        <v>4.3393733153961</v>
       </c>
     </row>
     <row r="2070">
@@ -49161,16 +49161,16 @@
         <v>4.0338602452144</v>
       </c>
       <c r="D2070" t="n">
-        <v>-4.861509444225352</v>
+        <v>-4.849989333215158</v>
       </c>
       <c r="E2070" t="n">
-        <v>2.08890004321051</v>
+        <v>2.093508087614588</v>
       </c>
       <c r="F2070" t="n">
-        <v>0.7368946374348133</v>
+        <v>0.7484147484450085</v>
       </c>
       <c r="G2070" t="n">
-        <v>4.475997027675288</v>
+        <v>4.482909094281405</v>
       </c>
     </row>
     <row r="2071">
@@ -49184,16 +49184,16 @@
         <v>4.025781471042649</v>
       </c>
       <c r="D2071" t="n">
-        <v>-4.849981808575744</v>
+        <v>-4.83846169756555</v>
       </c>
       <c r="E2071" t="n">
-        <v>2.085432323298603</v>
+        <v>2.090040367702681</v>
       </c>
       <c r="F2071" t="n">
-        <v>0.7958952956361758</v>
+        <v>0.807415406646371</v>
       </c>
       <c r="G2071" t="n">
-        <v>4.503318648424354</v>
+        <v>4.510230715030471</v>
       </c>
     </row>
     <row r="2072">
@@ -49207,16 +49207,16 @@
         <v>4.029449583564437</v>
       </c>
       <c r="D2072" t="n">
-        <v>-4.947323309918112</v>
+        <v>-4.935803198907919</v>
       </c>
       <c r="E2072" t="n">
-        <v>2.050163835283445</v>
+        <v>2.054771879687522</v>
       </c>
       <c r="F2072" t="n">
-        <v>0.7514751134706874</v>
+        <v>0.7629952244808826</v>
       </c>
       <c r="G2072" t="n">
-        <v>4.48033465164685</v>
+        <v>4.487246718252967</v>
       </c>
     </row>
     <row r="2073">
@@ -49230,16 +49230,16 @@
         <v>4.030700665757275</v>
       </c>
       <c r="D2073" t="n">
-        <v>-5.033179339258079</v>
+        <v>-5.021659228247885</v>
       </c>
       <c r="E2073" t="n">
-        <v>2.017072505740296</v>
+        <v>2.021680550144374</v>
       </c>
       <c r="F2073" t="n">
-        <v>0.7090990442445524</v>
+        <v>0.7206191552547476</v>
       </c>
       <c r="G2073" t="n">
-        <v>4.456160092304007</v>
+        <v>4.463072158910125</v>
       </c>
     </row>
     <row r="2074">
@@ -49253,16 +49253,16 @@
         <v>4.013119867577777</v>
       </c>
       <c r="D2074" t="n">
-        <v>-5.042016136674198</v>
+        <v>-5.030496025664005</v>
       </c>
       <c r="E2074" t="n">
-        <v>1.99595698859435</v>
+        <v>2.000565032998427</v>
       </c>
       <c r="F2074" t="n">
-        <v>0.7016568716032017</v>
+        <v>0.7131769826133969</v>
       </c>
       <c r="G2074" t="n">
-        <v>4.434113990539698</v>
+        <v>4.441026057145816</v>
       </c>
     </row>
     <row r="2075">
@@ -49276,16 +49276,16 @@
         <v>4.023284378622827</v>
       </c>
       <c r="D2075" t="n">
-        <v>-5.133398699239657</v>
+        <v>-5.121878588229463</v>
       </c>
       <c r="E2075" t="n">
-        <v>1.969568474613216</v>
+        <v>1.974176519017294</v>
       </c>
       <c r="F2075" t="n">
-        <v>0.665091986883857</v>
+        <v>0.6766120978940522</v>
       </c>
       <c r="G2075" t="n">
-        <v>4.422339570753141</v>
+        <v>4.429251637359259</v>
       </c>
     </row>
     <row r="2076">
@@ -49296,19 +49296,19 @@
         <v>3.673978374889187</v>
       </c>
       <c r="C2076" t="n">
-        <v>4.125412636447095</v>
+        <v>4.144444094190696</v>
       </c>
       <c r="D2076" t="n">
-        <v>-5.121691981252651</v>
+        <v>-5.110171870242457</v>
       </c>
       <c r="E2076" t="n">
-        <v>2.076379419632286</v>
+        <v>2.100018921779965</v>
       </c>
       <c r="F2076" t="n">
-        <v>0.6767987048708634</v>
+        <v>0.6883188158810586</v>
       </c>
       <c r="G2076" t="n">
-        <v>4.531491859369613</v>
+        <v>4.557435383719332</v>
       </c>
     </row>
     <row r="2077">
@@ -49319,19 +49319,19 @@
         <v>3.682476099409563</v>
       </c>
       <c r="C2077" t="n">
-        <v>4.1284449751785</v>
+        <v>4.147476432922101</v>
       </c>
       <c r="D2077" t="n">
-        <v>-5.192604054994929</v>
+        <v>-5.181083943984735</v>
       </c>
       <c r="E2077" t="n">
-        <v>2.05104692886678</v>
+        <v>2.074686431014459</v>
       </c>
       <c r="F2077" t="n">
-        <v>0.6767987048708634</v>
+        <v>0.6883188158810586</v>
       </c>
       <c r="G2077" t="n">
-        <v>4.534524198101018</v>
+        <v>4.560467722450737</v>
       </c>
     </row>
     <row r="2078">
@@ -49342,19 +49342,19 @@
         <v>3.672895177452569</v>
       </c>
       <c r="C2078" t="n">
-        <v>4.341349808456558</v>
+        <v>4.360381266200159</v>
       </c>
       <c r="D2078" t="n">
-        <v>-5.202920153161281</v>
+        <v>-5.191400042151087</v>
       </c>
       <c r="E2078" t="n">
-        <v>2.259825322878298</v>
+        <v>2.283464825025976</v>
       </c>
       <c r="F2078" t="n">
-        <v>0.6767987048708634</v>
+        <v>0.6883188158810586</v>
       </c>
       <c r="G2078" t="n">
-        <v>4.747429031379076</v>
+        <v>4.773372555728795</v>
       </c>
     </row>
     <row r="2079">
@@ -49365,19 +49365,19 @@
         <v>3.623960959762282</v>
       </c>
       <c r="C2079" t="n">
-        <v>4.340528475368647</v>
+        <v>4.359559933112249</v>
       </c>
       <c r="D2079" t="n">
-        <v>-5.202826185143908</v>
+        <v>-5.191306074133714</v>
       </c>
       <c r="E2079" t="n">
-        <v>2.259041576997336</v>
+        <v>2.282681079145015</v>
       </c>
       <c r="F2079" t="n">
-        <v>0.6771685662181813</v>
+        <v>0.6886886772283766</v>
       </c>
       <c r="G2079" t="n">
-        <v>4.746829615099556</v>
+        <v>4.772773139449275</v>
       </c>
     </row>
     <row r="2080">
@@ -49388,19 +49388,19 @@
         <v>3.633213467988013</v>
       </c>
       <c r="C2080" t="n">
-        <v>4.334760461313001</v>
+        <v>4.353791919056603</v>
       </c>
       <c r="D2080" t="n">
-        <v>-5.351192412800053</v>
+        <v>-5.339672301789859</v>
       </c>
       <c r="E2080" t="n">
-        <v>2.193927071879232</v>
+        <v>2.217566574026911</v>
       </c>
       <c r="F2080" t="n">
-        <v>0.6771685662181813</v>
+        <v>0.6886886772283766</v>
       </c>
       <c r="G2080" t="n">
-        <v>4.74106160104391</v>
+        <v>4.767005125393629</v>
       </c>
     </row>
     <row r="2081">
@@ -49411,19 +49411,19 @@
         <v>3.64790724274092</v>
       </c>
       <c r="C2081" t="n">
-        <v>4.334760461313001</v>
+        <v>4.353791919056603</v>
       </c>
       <c r="D2081" t="n">
-        <v>-5.350243989682014</v>
+        <v>-5.338723878671821</v>
       </c>
       <c r="E2081" t="n">
-        <v>2.194306441126447</v>
+        <v>2.217945943274126</v>
       </c>
       <c r="F2081" t="n">
-        <v>0.6771685662181813</v>
+        <v>0.6886886772283766</v>
       </c>
       <c r="G2081" t="n">
-        <v>4.74106160104391</v>
+        <v>4.767005125393629</v>
       </c>
     </row>
     <row r="2082">
@@ -49434,19 +49434,19 @@
         <v>3.881065366663623</v>
       </c>
       <c r="C2082" t="n">
-        <v>4.347488069294093</v>
+        <v>4.366519527037695</v>
       </c>
       <c r="D2082" t="n">
-        <v>-5.450513807641036</v>
+        <v>-5.438993696630842</v>
       </c>
       <c r="E2082" t="n">
-        <v>2.166926121923931</v>
+        <v>2.19056562407161</v>
       </c>
       <c r="F2082" t="n">
-        <v>0.6771685662181813</v>
+        <v>0.6886886772283766</v>
       </c>
       <c r="G2082" t="n">
-        <v>4.753789209025002</v>
+        <v>4.779732733374721</v>
       </c>
     </row>
     <row r="2083">
@@ -49457,19 +49457,19 @@
         <v>3.717071158424767</v>
       </c>
       <c r="C2083" t="n">
-        <v>4.349434067718481</v>
+        <v>4.368465525462082</v>
       </c>
       <c r="D2083" t="n">
-        <v>-5.444521560852224</v>
+        <v>-5.43300144984203</v>
       </c>
       <c r="E2083" t="n">
-        <v>2.171269019063844</v>
+        <v>2.194908521211522</v>
       </c>
       <c r="F2083" t="n">
-        <v>0.6771685662181813</v>
+        <v>0.6886886772283766</v>
       </c>
       <c r="G2083" t="n">
-        <v>4.75573520744939</v>
+        <v>4.781678731799109</v>
       </c>
     </row>
     <row r="2084">
@@ -49480,19 +49480,19 @@
         <v>3.741942347149216</v>
       </c>
       <c r="C2084" t="n">
-        <v>4.34308820373625</v>
+        <v>4.362119661479851</v>
       </c>
       <c r="D2084" t="n">
-        <v>-5.355963599721457</v>
+        <v>-5.344443488711263</v>
       </c>
       <c r="E2084" t="n">
-        <v>2.200346339533919</v>
+        <v>2.223985841681598</v>
       </c>
       <c r="F2084" t="n">
-        <v>0.6771685662181813</v>
+        <v>0.6886886772283766</v>
       </c>
       <c r="G2084" t="n">
-        <v>4.749389343467159</v>
+        <v>4.775332867816878</v>
       </c>
     </row>
     <row r="2085">
@@ -49503,19 +49503,19 @@
         <v>3.735300721383088</v>
       </c>
       <c r="C2085" t="n">
-        <v>4.342396881175246</v>
+        <v>4.361428338918847</v>
       </c>
       <c r="D2085" t="n">
-        <v>-5.338204522218382</v>
+        <v>-5.326684411208189</v>
       </c>
       <c r="E2085" t="n">
-        <v>2.206758647974145</v>
+        <v>2.230398150121824</v>
       </c>
       <c r="F2085" t="n">
-        <v>0.6771685662181813</v>
+        <v>0.6886886772283766</v>
       </c>
       <c r="G2085" t="n">
-        <v>4.748698020906154</v>
+        <v>4.774641545255873</v>
       </c>
     </row>
     <row r="2086">
@@ -49526,19 +49526,19 @@
         <v>3.778232147720994</v>
       </c>
       <c r="C2086" t="n">
-        <v>4.355179067083832</v>
+        <v>4.374210524827434</v>
       </c>
       <c r="D2086" t="n">
-        <v>-5.238574371169315</v>
+        <v>-5.227054260159121</v>
       </c>
       <c r="E2086" t="n">
-        <v>2.259392894302358</v>
+        <v>2.283032396450037</v>
       </c>
       <c r="F2086" t="n">
-        <v>0.7767987172672488</v>
+        <v>0.788318828277444</v>
       </c>
       <c r="G2086" t="n">
-        <v>4.821258297444182</v>
+        <v>4.847201821793901</v>
       </c>
     </row>
     <row r="2087">
@@ -49549,19 +49549,19 @@
         <v>3.775357097455268</v>
       </c>
       <c r="C2087" t="n">
-        <v>4.544333332582559</v>
+        <v>4.56336479032616</v>
       </c>
       <c r="D2087" t="n">
-        <v>-5.287973879858326</v>
+        <v>-5.276453768848132</v>
       </c>
       <c r="E2087" t="n">
-        <v>2.42878735632548</v>
+        <v>2.452426858473159</v>
       </c>
       <c r="F2087" t="n">
-        <v>0.7870575506989935</v>
+        <v>0.7985776617091888</v>
       </c>
       <c r="G2087" t="n">
-        <v>5.016567863001955</v>
+        <v>5.042511387351674</v>
       </c>
     </row>
     <row r="2088">
@@ -49572,19 +49572,19 @@
         <v>3.749078058963129</v>
       </c>
       <c r="C2088" t="n">
-        <v>4.531522005685421</v>
+        <v>4.550553463429022</v>
       </c>
       <c r="D2088" t="n">
-        <v>-5.08128940621595</v>
+        <v>-5.069769295205756</v>
       </c>
       <c r="E2088" t="n">
-        <v>2.498649818885293</v>
+        <v>2.522289321032972</v>
       </c>
       <c r="F2088" t="n">
-        <v>0.993742024341369</v>
+        <v>1.005262135351564</v>
       </c>
       <c r="G2088" t="n">
-        <v>5.127767220290242</v>
+        <v>5.153710744639961</v>
       </c>
     </row>
     <row r="2089">
@@ -49595,19 +49595,19 @@
         <v>3.740284389162539</v>
       </c>
       <c r="C2089" t="n">
-        <v>4.533523519339526</v>
+        <v>4.552554977083127</v>
       </c>
       <c r="D2089" t="n">
-        <v>-5.115446301213476</v>
+        <v>-5.103926190203282</v>
       </c>
       <c r="E2089" t="n">
-        <v>2.486988574540387</v>
+        <v>2.510628076688066</v>
       </c>
       <c r="F2089" t="n">
-        <v>0.9101582548005566</v>
+        <v>0.9216783658107518</v>
       </c>
       <c r="G2089" t="n">
-        <v>5.07961847221986</v>
+        <v>5.105561996569579</v>
       </c>
     </row>
     <row r="2090">
@@ -49618,19 +49618,19 @@
         <v>3.78248211565238</v>
       </c>
       <c r="C2090" t="n">
-        <v>4.887020633329193</v>
+        <v>4.906052091072794</v>
       </c>
       <c r="D2090" t="n">
-        <v>-5.022856822152019</v>
+        <v>-5.011336711141825</v>
       </c>
       <c r="E2090" t="n">
-        <v>2.877521480154638</v>
+        <v>2.901160982302316</v>
       </c>
       <c r="F2090" t="n">
-        <v>0.9101582548005566</v>
+        <v>0.9216783658107518</v>
       </c>
       <c r="G2090" t="n">
-        <v>5.433115586209527</v>
+        <v>5.459059110559246</v>
       </c>
     </row>
     <row r="2091">
@@ -49638,22 +49638,22 @@
         <v>45553</v>
       </c>
       <c r="B2091" t="n">
-        <v>3.80905590510867</v>
+        <v>3.809055905108669</v>
       </c>
       <c r="C2091" t="n">
-        <v>4.891583744896296</v>
+        <v>4.910615202639898</v>
       </c>
       <c r="D2091" t="n">
-        <v>-5.096017425925164</v>
+        <v>-5.08449731491497</v>
       </c>
       <c r="E2091" t="n">
-        <v>2.852820350212483</v>
+        <v>2.876459852360162</v>
       </c>
       <c r="F2091" t="n">
-        <v>0.8821370547663134</v>
+        <v>0.8936571657765087</v>
       </c>
       <c r="G2091" t="n">
-        <v>5.420865977756085</v>
+        <v>5.446809502105803</v>
       </c>
     </row>
     <row r="2092">
@@ -49661,22 +49661,22 @@
         <v>45554</v>
       </c>
       <c r="B2092" t="n">
-        <v>3.835202441103561</v>
+        <v>3.83520244110356</v>
       </c>
       <c r="C2092" t="n">
-        <v>4.941413686219824</v>
+        <v>4.960445143963425</v>
       </c>
       <c r="D2092" t="n">
-        <v>-5.043801116128822</v>
+        <v>-5.032281005118628</v>
       </c>
       <c r="E2092" t="n">
-        <v>2.923536815454547</v>
+        <v>2.947176317602226</v>
       </c>
       <c r="F2092" t="n">
-        <v>0.8821370547663134</v>
+        <v>0.8936571657765087</v>
       </c>
       <c r="G2092" t="n">
-        <v>5.470695919079613</v>
+        <v>5.496639443429331</v>
       </c>
     </row>
     <row r="2093">
@@ -49687,19 +49687,19 @@
         <v>3.821827147047742</v>
       </c>
       <c r="C2093" t="n">
-        <v>4.950227656429835</v>
+        <v>4.969259114173436</v>
       </c>
       <c r="D2093" t="n">
-        <v>-5.011903599043577</v>
+        <v>-5.000383488033383</v>
       </c>
       <c r="E2093" t="n">
-        <v>2.945109792498656</v>
+        <v>2.968749294646335</v>
       </c>
       <c r="F2093" t="n">
-        <v>0.9140345718515592</v>
+        <v>0.9255546828617545</v>
       </c>
       <c r="G2093" t="n">
-        <v>5.49864839954077</v>
+        <v>5.524591923890489</v>
       </c>
     </row>
     <row r="2094">
@@ -49710,19 +49710,19 @@
         <v>3.825268416650751</v>
       </c>
       <c r="C2094" t="n">
-        <v>4.945865240469032</v>
+        <v>4.964896698212633</v>
       </c>
       <c r="D2094" t="n">
-        <v>-5.026658923243717</v>
+        <v>-5.015138812233523</v>
       </c>
       <c r="E2094" t="n">
-        <v>2.934845246857797</v>
+        <v>2.958484749005476</v>
       </c>
       <c r="F2094" t="n">
-        <v>0.9140345718515592</v>
+        <v>0.9255546828617545</v>
       </c>
       <c r="G2094" t="n">
-        <v>5.494285983579967</v>
+        <v>5.520229507929686</v>
       </c>
     </row>
     <row r="2095">
@@ -49733,19 +49733,19 @@
         <v>3.845044666135745</v>
       </c>
       <c r="C2095" t="n">
-        <v>4.936789743885312</v>
+        <v>4.955821201628913</v>
       </c>
       <c r="D2095" t="n">
-        <v>-4.977194299873806</v>
+        <v>-4.965674188863612</v>
       </c>
       <c r="E2095" t="n">
-        <v>2.945555599622041</v>
+        <v>2.96919510176972</v>
       </c>
       <c r="F2095" t="n">
-        <v>0.9634991952214709</v>
+        <v>0.9750193062316661</v>
       </c>
       <c r="G2095" t="n">
-        <v>5.514889261018195</v>
+        <v>5.540832785367913</v>
       </c>
     </row>
     <row r="2096">
@@ -49756,19 +49756,19 @@
         <v>3.825931790479219</v>
       </c>
       <c r="C2096" t="n">
-        <v>4.933197411600246</v>
+        <v>4.952228869343847</v>
       </c>
       <c r="D2096" t="n">
-        <v>-4.81408630772019</v>
+        <v>-4.802566196709996</v>
       </c>
       <c r="E2096" t="n">
-        <v>3.007206464198422</v>
+        <v>3.030845966346101</v>
       </c>
       <c r="F2096" t="n">
-        <v>1.126607187375086</v>
+        <v>1.138127298385281</v>
       </c>
       <c r="G2096" t="n">
-        <v>5.609161724025298</v>
+        <v>5.635105248375017</v>
       </c>
     </row>
     <row r="2097">
@@ -49779,19 +49779,19 @@
         <v>3.847096478844243</v>
       </c>
       <c r="C2097" t="n">
-        <v>4.942244448291374</v>
+        <v>4.961275906034976</v>
       </c>
       <c r="D2097" t="n">
-        <v>-4.681278682223024</v>
+        <v>-4.66975857121283</v>
       </c>
       <c r="E2097" t="n">
-        <v>3.069376551088417</v>
+        <v>3.093016053236096</v>
       </c>
       <c r="F2097" t="n">
-        <v>1.126607187375086</v>
+        <v>1.138127298385281</v>
       </c>
       <c r="G2097" t="n">
-        <v>5.618208760716426</v>
+        <v>5.644152285066145</v>
       </c>
     </row>
     <row r="2098">
@@ -49802,19 +49802,19 @@
         <v>3.832425987790947</v>
       </c>
       <c r="C2098" t="n">
-        <v>4.943101913277496</v>
+        <v>4.962133371021097</v>
       </c>
       <c r="D2098" t="n">
-        <v>-4.743986598697582</v>
+        <v>-4.732466487687388</v>
       </c>
       <c r="E2098" t="n">
-        <v>3.045150849484715</v>
+        <v>3.068790351632394</v>
       </c>
       <c r="F2098" t="n">
-        <v>1.063899270900528</v>
+        <v>1.075419381910724</v>
       </c>
       <c r="G2098" t="n">
-        <v>5.581441475817813</v>
+        <v>5.607385000167532</v>
       </c>
     </row>
     <row r="2099">
@@ -49825,19 +49825,19 @@
         <v>3.861579399578993</v>
       </c>
       <c r="C2099" t="n">
-        <v>4.906011330067848</v>
+        <v>4.925042787811449</v>
       </c>
       <c r="D2099" t="n">
-        <v>-4.695978474853889</v>
+        <v>-4.684458363843695</v>
       </c>
       <c r="E2099" t="n">
-        <v>3.027263515812544</v>
+        <v>3.050903017960223</v>
       </c>
       <c r="F2099" t="n">
-        <v>1.063899270900528</v>
+        <v>1.075419381910724</v>
       </c>
       <c r="G2099" t="n">
-        <v>5.544350892608166</v>
+        <v>5.570294416957884</v>
       </c>
     </row>
     <row r="2100">
@@ -49848,19 +49848,19 @@
         <v>3.872253907629881</v>
       </c>
       <c r="C2100" t="n">
-        <v>4.909943583625799</v>
+        <v>4.9289750413694</v>
       </c>
       <c r="D2100" t="n">
-        <v>-4.617152817670299</v>
+        <v>-4.605632706660105</v>
       </c>
       <c r="E2100" t="n">
-        <v>3.062726032243931</v>
+        <v>3.08636553439161</v>
       </c>
       <c r="F2100" t="n">
-        <v>1.142724928084119</v>
+        <v>1.154245039094314</v>
       </c>
       <c r="G2100" t="n">
-        <v>5.59557854047627</v>
+        <v>5.621522064825989</v>
       </c>
     </row>
     <row r="2101">
@@ -49871,19 +49871,19 @@
         <v>3.868502531686404</v>
       </c>
       <c r="C2101" t="n">
-        <v>4.904842676232835</v>
+        <v>4.923874133976437</v>
       </c>
       <c r="D2101" t="n">
-        <v>-4.425218016416425</v>
+        <v>-4.413697905406231</v>
       </c>
       <c r="E2101" t="n">
-        <v>3.134399045352517</v>
+        <v>3.158038547500197</v>
       </c>
       <c r="F2101" t="n">
-        <v>1.142724928084119</v>
+        <v>1.154245039094314</v>
       </c>
       <c r="G2101" t="n">
-        <v>5.590477633083307</v>
+        <v>5.616421157433026</v>
       </c>
     </row>
     <row r="2102">
@@ -49891,22 +49891,22 @@
         <v>45564</v>
       </c>
       <c r="B2102" t="n">
-        <v>3.849324044046709</v>
+        <v>3.849324044046708</v>
       </c>
       <c r="C2102" t="n">
-        <v>4.900196585621931</v>
+        <v>4.919228043365532</v>
       </c>
       <c r="D2102" t="n">
-        <v>-4.415001042633214</v>
+        <v>-4.295524527388304</v>
       </c>
       <c r="E2102" t="n">
-        <v>3.133839744254897</v>
+        <v>3.200661808096462</v>
       </c>
       <c r="F2102" t="n">
-        <v>1.152941901867329</v>
+        <v>1.272418417112241</v>
       </c>
       <c r="G2102" t="n">
-        <v>5.591961726742329</v>
+        <v>5.682679093632877</v>
       </c>
     </row>
     <row r="2103">
@@ -49914,22 +49914,22 @@
         <v>45565</v>
       </c>
       <c r="B2103" t="n">
-        <v>3.765338746849089</v>
+        <v>3.901107459027854</v>
       </c>
       <c r="C2103" t="n">
-        <v>4.845407776679131</v>
+        <v>5.057055841698706</v>
       </c>
       <c r="D2103" t="n">
-        <v>-4.415001042633214</v>
+        <v>-4.295524527388304</v>
       </c>
       <c r="E2103" t="n">
-        <v>3.133839744254897</v>
+        <v>3.200661808096462</v>
       </c>
       <c r="F2103" t="n">
-        <v>1.152941901867329</v>
+        <v>1.272418417112241</v>
       </c>
       <c r="G2103" t="n">
-        <v>4.838471573665499</v>
+        <v>5.050119638685074</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240930.xlsx
+++ b/tame_output/ON/bt/strategyON_20240930.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>57.8%</t>
+          <t>54.1%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -610,7 +610,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>64.8%</t>
+          <t>64.9%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.2%</t>
+          <t>17.8%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>62.0%</t>
+          <t>48.8%</t>
         </is>
       </c>
     </row>
@@ -758,22 +758,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>118.5%</t>
+          <t>110.8%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>44.0%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.67</t>
+          <t>2.52</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>58.6%</t>
+          <t>58.5%</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -791,12 +791,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>39.6%</t>
+          <t>39.7%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>47.9%</t>
+          <t>47.2%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>10.7%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>99.4%</t>
+          <t>93.1%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>36.3%</t>
+          <t>36.0%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.7</t>
+          <t>2.6</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-8.4%</t>
+          <t>-8.2%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>39.8%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>194.1%</t>
+          <t>172.6%</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-75.1%</t>
+          <t>-75.7%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -949,7 +949,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>122.9%</t>
+          <t>123.0%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -982,7 +982,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-34.7%</t>
+          <t>-35.2%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>21.9%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-71.1%</t>
+          <t>-71.9%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>421.8%</t>
+          <t>420.8%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-7.1%</t>
+          <t>-6.8%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-591.1%</t>
+          <t>-604.5%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>45.5%</t>
+          <t>43.8%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>59.9%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>57.7%</t>
+          <t>57.5%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1140,7 +1140,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>-8.5%</t>
+          <t>-8.7%</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>14.4%</t>
+          <t>14.2%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-33.5%</t>
+          <t>-33.6%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>40.1%</t>
+          <t>38.7%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>50.1%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-4.0%</t>
+          <t>-3.9%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15.4%</t>
+          <t>15.3%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-56.2%</t>
+          <t>-63.4%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-2.4%</t>
+          <t>-2.7%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>3.8%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>45.8%</t>
+          <t>45.4%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-403.0%</t>
+          <t>-399.9%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-96.8%</t>
+          <t>-97.9%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>90.1%</t>
+          <t>67.0%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>63.5%</t>
+          <t>67.1%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>72.3%</t>
+          <t>79.8%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>56.9%</t>
+          <t>56.8%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1447,7 +1447,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>13.2%</t>
+          <t>12.8%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>81.6%</t>
+          <t>57.0%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>53.0%</t>
+          <t>55.8%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-17.1%</t>
+          <t>-15.5%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>35.8%</t>
+          <t>36.7%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>59.0%</t>
+          <t>37.5%</t>
         </is>
       </c>
     </row>
@@ -47729,7 +47729,7 @@
         <v>45470</v>
       </c>
       <c r="B2008" t="n">
-        <v>3.727898186347699</v>
+        <v>3.7278981863477</v>
       </c>
       <c r="C2008" t="n">
         <v>3.207242866402009</v>
@@ -47752,7 +47752,7 @@
         <v>45471</v>
       </c>
       <c r="B2009" t="n">
-        <v>3.710654104887744</v>
+        <v>3.710654104887745</v>
       </c>
       <c r="C2009" t="n">
         <v>3.202063096004871</v>
@@ -47775,7 +47775,7 @@
         <v>45472</v>
       </c>
       <c r="B2010" t="n">
-        <v>3.712897612343061</v>
+        <v>3.712897612343062</v>
       </c>
       <c r="C2010" t="n">
         <v>3.200497106215023</v>
@@ -47798,7 +47798,7 @@
         <v>45473</v>
       </c>
       <c r="B2011" t="n">
-        <v>3.754596135389344</v>
+        <v>3.754596135389345</v>
       </c>
       <c r="C2011" t="n">
         <v>3.213570513080942</v>
@@ -47821,7 +47821,7 @@
         <v>45474</v>
       </c>
       <c r="B2012" t="n">
-        <v>3.749882691378388</v>
+        <v>3.749882691378387</v>
       </c>
       <c r="C2012" t="n">
         <v>3.205575709863882</v>
@@ -47890,7 +47890,7 @@
         <v>45477</v>
       </c>
       <c r="B2015" t="n">
-        <v>3.619348081585934</v>
+        <v>3.619348081585933</v>
       </c>
       <c r="C2015" t="n">
         <v>3.267570154558586</v>
@@ -47913,7 +47913,7 @@
         <v>45478</v>
       </c>
       <c r="B2016" t="n">
-        <v>3.640750087814664</v>
+        <v>3.640750087814663</v>
       </c>
       <c r="C2016" t="n">
         <v>3.407881873560433</v>
@@ -47936,7 +47936,7 @@
         <v>45479</v>
       </c>
       <c r="B2017" t="n">
-        <v>3.668289004237093</v>
+        <v>3.668289004237092</v>
       </c>
       <c r="C2017" t="n">
         <v>3.476862142706073</v>
@@ -47959,7 +47959,7 @@
         <v>45480</v>
       </c>
       <c r="B2018" t="n">
-        <v>3.619923016423386</v>
+        <v>3.619923016423385</v>
       </c>
       <c r="C2018" t="n">
         <v>3.462913344826194</v>
@@ -47982,7 +47982,7 @@
         <v>45481</v>
       </c>
       <c r="B2019" t="n">
-        <v>3.656332733609752</v>
+        <v>3.656332733609751</v>
       </c>
       <c r="C2019" t="n">
         <v>3.474783833881608</v>
@@ -48005,7 +48005,7 @@
         <v>45482</v>
       </c>
       <c r="B2020" t="n">
-        <v>3.674028535973155</v>
+        <v>3.674028535973154</v>
       </c>
       <c r="C2020" t="n">
         <v>3.475994368400552</v>
@@ -48051,7 +48051,7 @@
         <v>45484</v>
       </c>
       <c r="B2022" t="n">
-        <v>3.652149152916197</v>
+        <v>3.652149152916196</v>
       </c>
       <c r="C2022" t="n">
         <v>3.475193963364063</v>
@@ -48074,7 +48074,7 @@
         <v>45485</v>
       </c>
       <c r="B2023" t="n">
-        <v>3.667962306830325</v>
+        <v>3.667962306830324</v>
       </c>
       <c r="C2023" t="n">
         <v>3.637398020063107</v>
@@ -48097,7 +48097,7 @@
         <v>45486</v>
       </c>
       <c r="B2024" t="n">
-        <v>3.696539468071547</v>
+        <v>3.696539468071546</v>
       </c>
       <c r="C2024" t="n">
         <v>3.632244658026921</v>
@@ -48120,7 +48120,7 @@
         <v>45487</v>
       </c>
       <c r="B2025" t="n">
-        <v>3.750044015868142</v>
+        <v>3.750044015868141</v>
       </c>
       <c r="C2025" t="n">
         <v>3.642474075595412</v>
@@ -48149,16 +48149,16 @@
         <v>3.651399714051315</v>
       </c>
       <c r="D2026" t="n">
-        <v>-5.767420677701326</v>
+        <v>-5.778940788711521</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.344075018657036</v>
+        <v>1.339466974252959</v>
       </c>
       <c r="F2026" t="n">
-        <v>-0.118358665182984</v>
+        <v>-0.1298787761931792</v>
       </c>
       <c r="G2026" t="n">
-        <v>3.580384514941525</v>
+        <v>3.573472448335407</v>
       </c>
     </row>
     <row r="2027">
@@ -48172,16 +48172,16 @@
         <v>3.64355260129549</v>
       </c>
       <c r="D2027" t="n">
-        <v>-5.657414394224104</v>
+        <v>-5.668934505234299</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.3802304192921</v>
+        <v>1.375622374888022</v>
       </c>
       <c r="F2027" t="n">
-        <v>-0.09515409326570884</v>
+        <v>-0.106674204275904</v>
       </c>
       <c r="G2027" t="n">
-        <v>3.586460145336065</v>
+        <v>3.579548078729948</v>
       </c>
     </row>
     <row r="2028">
@@ -48189,22 +48189,22 @@
         <v>45490</v>
       </c>
       <c r="B2028" t="n">
-        <v>3.785563924818518</v>
+        <v>3.785563924818517</v>
       </c>
       <c r="C2028" t="n">
         <v>3.647802612017464</v>
       </c>
       <c r="D2028" t="n">
-        <v>-5.514354818483179</v>
+        <v>-5.525874929493373</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.441704260310445</v>
+        <v>1.437096215906367</v>
       </c>
       <c r="F2028" t="n">
-        <v>-0.08714066667572956</v>
+        <v>-0.09866077768592474</v>
       </c>
       <c r="G2028" t="n">
-        <v>3.595518212012027</v>
+        <v>3.588606145405909</v>
       </c>
     </row>
     <row r="2029">
@@ -48212,22 +48212,22 @@
         <v>45491</v>
       </c>
       <c r="B2029" t="n">
-        <v>3.777237412051785</v>
+        <v>3.777237412051783</v>
       </c>
       <c r="C2029" t="n">
         <v>3.6550634949</v>
       </c>
       <c r="D2029" t="n">
-        <v>-5.212908093011341</v>
+        <v>-5.224428204021535</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.569543833381716</v>
+        <v>1.564935788977638</v>
       </c>
       <c r="F2029" t="n">
-        <v>0.2143060587961077</v>
+        <v>0.2027859477859125</v>
       </c>
       <c r="G2029" t="n">
-        <v>3.783647130177665</v>
+        <v>3.776735063571548</v>
       </c>
     </row>
     <row r="2030">
@@ -48235,22 +48235,22 @@
         <v>45492</v>
       </c>
       <c r="B2030" t="n">
-        <v>3.812635940679622</v>
+        <v>3.812635940679621</v>
       </c>
       <c r="C2030" t="n">
         <v>3.656034672652711</v>
       </c>
       <c r="D2030" t="n">
-        <v>-5.237498337246525</v>
+        <v>-5.249018448256719</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.560678913440353</v>
+        <v>1.556070869036275</v>
       </c>
       <c r="F2030" t="n">
-        <v>0.2143060587961077</v>
+        <v>0.2027859477859125</v>
       </c>
       <c r="G2030" t="n">
-        <v>3.784618307930376</v>
+        <v>3.777706241324259</v>
       </c>
     </row>
     <row r="2031">
@@ -48258,22 +48258,22 @@
         <v>45493</v>
       </c>
       <c r="B2031" t="n">
-        <v>3.821184182474157</v>
+        <v>3.821184182474155</v>
       </c>
       <c r="C2031" t="n">
         <v>3.656877577032466</v>
       </c>
       <c r="D2031" t="n">
-        <v>-5.186459961240005</v>
+        <v>-5.197980072250199</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.581937168222717</v>
+        <v>1.577329123818639</v>
       </c>
       <c r="F2031" t="n">
-        <v>0.2143060587961077</v>
+        <v>0.2027859477859125</v>
       </c>
       <c r="G2031" t="n">
-        <v>3.785461212310131</v>
+        <v>3.778549145704014</v>
       </c>
     </row>
     <row r="2032">
@@ -48281,22 +48281,22 @@
         <v>45494</v>
       </c>
       <c r="B2032" t="n">
-        <v>3.831734516969541</v>
+        <v>3.831734516969539</v>
       </c>
       <c r="C2032" t="n">
         <v>3.675915675906612</v>
       </c>
       <c r="D2032" t="n">
-        <v>-5.157611284416545</v>
+        <v>-5.169131395426739</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.612514737826246</v>
+        <v>1.607906693422168</v>
       </c>
       <c r="F2032" t="n">
-        <v>0.243154735619568</v>
+        <v>0.2316346246093728</v>
       </c>
       <c r="G2032" t="n">
-        <v>3.821808517278353</v>
+        <v>3.814896450672236</v>
       </c>
     </row>
     <row r="2033">
@@ -48304,22 +48304,22 @@
         <v>45495</v>
       </c>
       <c r="B2033" t="n">
-        <v>3.825752932700475</v>
+        <v>3.825752932700473</v>
       </c>
       <c r="C2033" t="n">
         <v>3.492099672030546</v>
       </c>
       <c r="D2033" t="n">
-        <v>-5.060976372397905</v>
+        <v>-5.072496483408099</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.467352698757637</v>
+        <v>1.462744654353559</v>
       </c>
       <c r="F2033" t="n">
-        <v>0.3397896476382079</v>
+        <v>0.3282695366280127</v>
       </c>
       <c r="G2033" t="n">
-        <v>3.695973460613471</v>
+        <v>3.689061394007354</v>
       </c>
     </row>
     <row r="2034">
@@ -48327,22 +48327,22 @@
         <v>45496</v>
       </c>
       <c r="B2034" t="n">
-        <v>3.804688961077638</v>
+        <v>3.804688961077636</v>
       </c>
       <c r="C2034" t="n">
         <v>3.495601716104511</v>
       </c>
       <c r="D2034" t="n">
-        <v>-4.991938361449437</v>
+        <v>-5.003458472459631</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.498469947210988</v>
+        <v>1.49386190280691</v>
       </c>
       <c r="F2034" t="n">
-        <v>0.408827658586676</v>
+        <v>0.3973075475764808</v>
       </c>
       <c r="G2034" t="n">
-        <v>3.740898311256516</v>
+        <v>3.733986244650399</v>
       </c>
     </row>
     <row r="2035">
@@ -48356,16 +48356,16 @@
         <v>3.480028535180593</v>
       </c>
       <c r="D2035" t="n">
-        <v>-4.973151261080498</v>
+        <v>-4.984671372090692</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.490411606434646</v>
+        <v>1.485803562030568</v>
       </c>
       <c r="F2035" t="n">
-        <v>0.4276147589556145</v>
+        <v>0.4160946479454193</v>
       </c>
       <c r="G2035" t="n">
-        <v>3.736597390553962</v>
+        <v>3.729685323947845</v>
       </c>
     </row>
     <row r="2036">
@@ -48373,22 +48373,22 @@
         <v>45498</v>
       </c>
       <c r="B2036" t="n">
-        <v>3.821030660077626</v>
+        <v>3.821030660077624</v>
       </c>
       <c r="C2036" t="n">
         <v>3.479216245617023</v>
       </c>
       <c r="D2036" t="n">
-        <v>-4.896052659538626</v>
+        <v>-4.907572770548819</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.520438757487825</v>
+        <v>1.515830713083747</v>
       </c>
       <c r="F2036" t="n">
-        <v>0.4276147589556145</v>
+        <v>0.4160946479454193</v>
       </c>
       <c r="G2036" t="n">
-        <v>3.735785100990392</v>
+        <v>3.728873034384275</v>
       </c>
     </row>
     <row r="2037">
@@ -48396,22 +48396,22 @@
         <v>45499</v>
       </c>
       <c r="B2037" t="n">
-        <v>3.832307024147908</v>
+        <v>3.832307024147906</v>
       </c>
       <c r="C2037" t="n">
         <v>3.489085024742095</v>
       </c>
       <c r="D2037" t="n">
-        <v>-4.906437854428515</v>
+        <v>-4.917957965438709</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.526153458656941</v>
+        <v>1.521545414252864</v>
       </c>
       <c r="F2037" t="n">
-        <v>0.4172295640657251</v>
+        <v>0.40570945305553</v>
       </c>
       <c r="G2037" t="n">
-        <v>3.739422763181531</v>
+        <v>3.732510696575413</v>
       </c>
     </row>
     <row r="2038">
@@ -48425,16 +48425,16 @@
         <v>3.55992203051852</v>
       </c>
       <c r="D2038" t="n">
-        <v>-4.92502601315074</v>
+        <v>-4.936546124160934</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.589555200944476</v>
+        <v>1.584947156540399</v>
       </c>
       <c r="F2038" t="n">
-        <v>0.3986414053434998</v>
+        <v>0.3871212943333046</v>
       </c>
       <c r="G2038" t="n">
-        <v>3.799106873724621</v>
+        <v>3.792194807118503</v>
       </c>
     </row>
     <row r="2039">
@@ -48442,22 +48442,22 @@
         <v>45501</v>
       </c>
       <c r="B2039" t="n">
-        <v>3.855120535496552</v>
+        <v>3.855120535496551</v>
       </c>
       <c r="C2039" t="n">
         <v>3.556791041336819</v>
       </c>
       <c r="D2039" t="n">
-        <v>-4.925324559846776</v>
+        <v>-4.93684467085697</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.586304793084361</v>
+        <v>1.581696748680283</v>
       </c>
       <c r="F2039" t="n">
-        <v>0.3983428586474639</v>
+        <v>0.3868227476372687</v>
       </c>
       <c r="G2039" t="n">
-        <v>3.795796756525298</v>
+        <v>3.78888468991918</v>
       </c>
     </row>
     <row r="2040">
@@ -48465,22 +48465,22 @@
         <v>45502</v>
       </c>
       <c r="B2040" t="n">
-        <v>3.815643212108853</v>
+        <v>3.815643212108852</v>
       </c>
       <c r="C2040" t="n">
         <v>3.56132193627621</v>
       </c>
       <c r="D2040" t="n">
-        <v>-4.824501426156348</v>
+        <v>-4.836021537166542</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.631164941499923</v>
+        <v>1.626556897095845</v>
       </c>
       <c r="F2040" t="n">
-        <v>0.4108070741318177</v>
+        <v>0.3992869631216225</v>
       </c>
       <c r="G2040" t="n">
-        <v>3.807806180755301</v>
+        <v>3.800894114149184</v>
       </c>
     </row>
     <row r="2041">
@@ -48488,22 +48488,22 @@
         <v>45503</v>
       </c>
       <c r="B2041" t="n">
-        <v>3.807356168121462</v>
+        <v>3.807356168121463</v>
       </c>
       <c r="C2041" t="n">
         <v>3.561451189754754</v>
       </c>
       <c r="D2041" t="n">
-        <v>-4.63372006540394</v>
+        <v>-4.645240176414134</v>
       </c>
       <c r="E2041" t="n">
-        <v>1.707606739279429</v>
+        <v>1.702998694875352</v>
       </c>
       <c r="F2041" t="n">
-        <v>0.6015884348842251</v>
+        <v>0.5900683238740299</v>
       </c>
       <c r="G2041" t="n">
-        <v>3.922404250685289</v>
+        <v>3.915492184079172</v>
       </c>
     </row>
     <row r="2042">
@@ -48511,22 +48511,22 @@
         <v>45504</v>
       </c>
       <c r="B2042" t="n">
-        <v>3.775233033906075</v>
+        <v>3.775233033906076</v>
       </c>
       <c r="C2042" t="n">
         <v>3.54128803549235</v>
       </c>
       <c r="D2042" t="n">
-        <v>-4.526756707554519</v>
+        <v>-4.538276818564713</v>
       </c>
       <c r="E2042" t="n">
-        <v>1.730228928156795</v>
+        <v>1.725620883752717</v>
       </c>
       <c r="F2042" t="n">
-        <v>0.6600530428440265</v>
+        <v>0.6485329318338313</v>
       </c>
       <c r="G2042" t="n">
-        <v>3.937319861198766</v>
+        <v>3.930407794592649</v>
       </c>
     </row>
     <row r="2043">
@@ -48540,16 +48540,16 @@
         <v>3.576254972104409</v>
       </c>
       <c r="D2043" t="n">
-        <v>-4.471426119652756</v>
+        <v>-4.48294623066295</v>
       </c>
       <c r="E2043" t="n">
-        <v>1.787328099929558</v>
+        <v>1.782720055525481</v>
       </c>
       <c r="F2043" t="n">
-        <v>0.7153836307457887</v>
+        <v>0.7038635197355935</v>
       </c>
       <c r="G2043" t="n">
-        <v>4.005485150551882</v>
+        <v>3.998573083945764</v>
       </c>
     </row>
     <row r="2044">
@@ -48563,16 +48563,16 @@
         <v>3.569941540005846</v>
       </c>
       <c r="D2044" t="n">
-        <v>-4.459371992739793</v>
+        <v>-4.470892103749987</v>
       </c>
       <c r="E2044" t="n">
-        <v>1.785836318596181</v>
+        <v>1.781228274192103</v>
       </c>
       <c r="F2044" t="n">
-        <v>0.7274377576587515</v>
+        <v>0.7159176466485563</v>
       </c>
       <c r="G2044" t="n">
-        <v>4.006404194601098</v>
+        <v>3.99949212799498</v>
       </c>
     </row>
     <row r="2045">
@@ -48580,22 +48580,22 @@
         <v>45507</v>
       </c>
       <c r="B2045" t="n">
-        <v>3.725010844811004</v>
+        <v>3.725010844811005</v>
       </c>
       <c r="C2045" t="n">
         <v>3.571822170189982</v>
       </c>
       <c r="D2045" t="n">
-        <v>-4.500527112308014</v>
+        <v>-4.512047223318208</v>
       </c>
       <c r="E2045" t="n">
-        <v>1.771254900953029</v>
+        <v>1.766646856548951</v>
       </c>
       <c r="F2045" t="n">
-        <v>0.6862826380905306</v>
+        <v>0.6747625270803354</v>
       </c>
       <c r="G2045" t="n">
-        <v>3.9835917530443</v>
+        <v>3.976679686438183</v>
       </c>
     </row>
     <row r="2046">
@@ -48603,22 +48603,22 @@
         <v>45508</v>
       </c>
       <c r="B2046" t="n">
-        <v>3.612322444382915</v>
+        <v>3.612322444382916</v>
       </c>
       <c r="C2046" t="n">
         <v>3.584673196067865</v>
       </c>
       <c r="D2046" t="n">
-        <v>-4.432478549616484</v>
+        <v>-4.443998660626678</v>
       </c>
       <c r="E2046" t="n">
-        <v>1.811325351907523</v>
+        <v>1.806717307503445</v>
       </c>
       <c r="F2046" t="n">
-        <v>0.7543312007820604</v>
+        <v>0.7428110897718652</v>
       </c>
       <c r="G2046" t="n">
-        <v>4.037271916537101</v>
+        <v>4.030359849930984</v>
       </c>
     </row>
     <row r="2047">
@@ -48626,22 +48626,22 @@
         <v>45509</v>
       </c>
       <c r="B2047" t="n">
-        <v>3.645256780013422</v>
+        <v>3.645256780013423</v>
       </c>
       <c r="C2047" t="n">
         <v>3.604875866241459</v>
       </c>
       <c r="D2047" t="n">
-        <v>-4.664078942785985</v>
+        <v>-4.675599053796179</v>
       </c>
       <c r="E2047" t="n">
-        <v>1.738887864813317</v>
+        <v>1.734279820409239</v>
       </c>
       <c r="F2047" t="n">
-        <v>0.7543312007820604</v>
+        <v>0.7428110897718652</v>
       </c>
       <c r="G2047" t="n">
-        <v>4.057474586710695</v>
+        <v>4.050562520104578</v>
       </c>
     </row>
     <row r="2048">
@@ -48649,22 +48649,22 @@
         <v>45510</v>
       </c>
       <c r="B2048" t="n">
-        <v>3.666747201498967</v>
+        <v>3.666747201498965</v>
       </c>
       <c r="C2048" t="n">
         <v>3.588482102308341</v>
       </c>
       <c r="D2048" t="n">
-        <v>-4.714130488315204</v>
+        <v>-4.725650599325398</v>
       </c>
       <c r="E2048" t="n">
-        <v>1.702473482668511</v>
+        <v>1.697865438264434</v>
       </c>
       <c r="F2048" t="n">
-        <v>0.7543312007820604</v>
+        <v>0.7428110897718652</v>
       </c>
       <c r="G2048" t="n">
-        <v>4.041080822777578</v>
+        <v>4.03416875617146</v>
       </c>
     </row>
     <row r="2049">
@@ -48672,22 +48672,22 @@
         <v>45511</v>
       </c>
       <c r="B2049" t="n">
-        <v>3.670048702800096</v>
+        <v>3.670048702800094</v>
       </c>
       <c r="C2049" t="n">
         <v>3.548734015901807</v>
       </c>
       <c r="D2049" t="n">
-        <v>-4.889237320891649</v>
+        <v>-4.900757431901843</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.5926826632314</v>
+        <v>1.588074618827322</v>
       </c>
       <c r="F2049" t="n">
-        <v>0.7543312007820604</v>
+        <v>0.7428110897718652</v>
       </c>
       <c r="G2049" t="n">
-        <v>4.001332736371044</v>
+        <v>3.994420669764927</v>
       </c>
     </row>
     <row r="2050">
@@ -48695,22 +48695,22 @@
         <v>45512</v>
       </c>
       <c r="B2050" t="n">
-        <v>3.745573148660848</v>
+        <v>3.745573148660847</v>
       </c>
       <c r="C2050" t="n">
         <v>3.555756634898747</v>
       </c>
       <c r="D2050" t="n">
-        <v>-4.693137167461126</v>
+        <v>-4.70465727847132</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.678145343600549</v>
+        <v>1.673537299196472</v>
       </c>
       <c r="F2050" t="n">
-        <v>0.9504313542125833</v>
+        <v>0.9389112432023881</v>
       </c>
       <c r="G2050" t="n">
-        <v>4.126015447426298</v>
+        <v>4.119103380820181</v>
       </c>
     </row>
     <row r="2051">
@@ -48718,22 +48718,22 @@
         <v>45513</v>
       </c>
       <c r="B2051" t="n">
-        <v>3.730570473395085</v>
+        <v>3.730570473395083</v>
       </c>
       <c r="C2051" t="n">
         <v>3.654927634471652</v>
       </c>
       <c r="D2051" t="n">
-        <v>-4.540111775347841</v>
+        <v>-4.551631886358035</v>
       </c>
       <c r="E2051" t="n">
-        <v>1.838526500018767</v>
+        <v>1.83391845561469</v>
       </c>
       <c r="F2051" t="n">
-        <v>1.103456746325867</v>
+        <v>1.091936635315672</v>
       </c>
       <c r="G2051" t="n">
-        <v>4.317001682267173</v>
+        <v>4.310089615661055</v>
       </c>
     </row>
     <row r="2052">
@@ -48741,22 +48741,22 @@
         <v>45514</v>
       </c>
       <c r="B2052" t="n">
-        <v>3.741278332791147</v>
+        <v>3.741278332791145</v>
       </c>
       <c r="C2052" t="n">
         <v>3.842393859379944</v>
       </c>
       <c r="D2052" t="n">
-        <v>-4.568419089221112</v>
+        <v>-4.579939200231306</v>
       </c>
       <c r="E2052" t="n">
-        <v>2.014669799377752</v>
+        <v>2.010061754973674</v>
       </c>
       <c r="F2052" t="n">
-        <v>1.103456746325867</v>
+        <v>1.091936635315672</v>
       </c>
       <c r="G2052" t="n">
-        <v>4.504467907175465</v>
+        <v>4.497555840569348</v>
       </c>
     </row>
     <row r="2053">
@@ -48764,22 +48764,22 @@
         <v>45515</v>
       </c>
       <c r="B2053" t="n">
-        <v>3.699115615620433</v>
+        <v>3.699115615620431</v>
       </c>
       <c r="C2053" t="n">
         <v>3.811796810734027</v>
       </c>
       <c r="D2053" t="n">
-        <v>-4.735012314334634</v>
+        <v>-4.746532425344828</v>
       </c>
       <c r="E2053" t="n">
-        <v>1.917435460686426</v>
+        <v>1.912827416282348</v>
       </c>
       <c r="F2053" t="n">
-        <v>0.9368635212123448</v>
+        <v>0.9253434102021496</v>
       </c>
       <c r="G2053" t="n">
-        <v>4.373914923461435</v>
+        <v>4.367002856855317</v>
       </c>
     </row>
     <row r="2054">
@@ -48787,22 +48787,22 @@
         <v>45516</v>
       </c>
       <c r="B2054" t="n">
-        <v>3.708182519285645</v>
+        <v>3.708182519285644</v>
       </c>
       <c r="C2054" t="n">
         <v>3.815473213395745</v>
       </c>
       <c r="D2054" t="n">
-        <v>-4.711976520973068</v>
+        <v>-4.723496631983262</v>
       </c>
       <c r="E2054" t="n">
-        <v>1.93032618069277</v>
+        <v>1.925718136288692</v>
       </c>
       <c r="F2054" t="n">
-        <v>0.9368635212123448</v>
+        <v>0.9253434102021496</v>
       </c>
       <c r="G2054" t="n">
-        <v>4.377591326123152</v>
+        <v>4.370679259517035</v>
       </c>
     </row>
     <row r="2055">
@@ -48810,22 +48810,22 @@
         <v>45517</v>
       </c>
       <c r="B2055" t="n">
-        <v>3.740581401399467</v>
+        <v>3.740581401399465</v>
       </c>
       <c r="C2055" t="n">
         <v>3.81309126851924</v>
       </c>
       <c r="D2055" t="n">
-        <v>-4.682730540517372</v>
+        <v>-4.694250651527565</v>
       </c>
       <c r="E2055" t="n">
-        <v>1.939642627998543</v>
+        <v>1.935034583594466</v>
       </c>
       <c r="F2055" t="n">
-        <v>0.9368635212123448</v>
+        <v>0.9253434102021496</v>
       </c>
       <c r="G2055" t="n">
-        <v>4.375209381246647</v>
+        <v>4.368297314640531</v>
       </c>
     </row>
     <row r="2056">
@@ -48833,22 +48833,22 @@
         <v>45518</v>
       </c>
       <c r="B2056" t="n">
-        <v>3.699404642256368</v>
+        <v>3.699404642256367</v>
       </c>
       <c r="C2056" t="n">
         <v>3.810384507676875</v>
       </c>
       <c r="D2056" t="n">
-        <v>-4.789656088395223</v>
+        <v>-4.801176199405417</v>
       </c>
       <c r="E2056" t="n">
-        <v>1.894165648005038</v>
+        <v>1.889557603600961</v>
       </c>
       <c r="F2056" t="n">
-        <v>0.8299379733344935</v>
+        <v>0.8184178623242983</v>
       </c>
       <c r="G2056" t="n">
-        <v>4.308347291677571</v>
+        <v>4.301435225071454</v>
       </c>
     </row>
     <row r="2057">
@@ -48856,22 +48856,22 @@
         <v>45519</v>
       </c>
       <c r="B2057" t="n">
-        <v>3.689942600700998</v>
+        <v>3.689942600700996</v>
       </c>
       <c r="C2057" t="n">
         <v>3.811813309820109</v>
       </c>
       <c r="D2057" t="n">
-        <v>-4.934674646902471</v>
+        <v>-4.946194757912665</v>
       </c>
       <c r="E2057" t="n">
-        <v>1.837587026745373</v>
+        <v>1.832978982341295</v>
       </c>
       <c r="F2057" t="n">
-        <v>0.6849194148272449</v>
+        <v>0.6733993038170497</v>
       </c>
       <c r="G2057" t="n">
-        <v>4.222764958716457</v>
+        <v>4.215852892110339</v>
       </c>
     </row>
     <row r="2058">
@@ -48879,22 +48879,22 @@
         <v>45520</v>
       </c>
       <c r="B2058" t="n">
-        <v>3.71185242968701</v>
+        <v>3.711852429687008</v>
       </c>
       <c r="C2058" t="n">
         <v>3.911744549077862</v>
       </c>
       <c r="D2058" t="n">
-        <v>-5.053016412687189</v>
+        <v>-5.064536523697383</v>
       </c>
       <c r="E2058" t="n">
-        <v>1.890181559689239</v>
+        <v>1.885573515285161</v>
       </c>
       <c r="F2058" t="n">
-        <v>0.695605453390135</v>
+        <v>0.6840853423799398</v>
       </c>
       <c r="G2058" t="n">
-        <v>4.329107821111943</v>
+        <v>4.322195754505826</v>
       </c>
     </row>
     <row r="2059">
@@ -48902,22 +48902,22 @@
         <v>45521</v>
       </c>
       <c r="B2059" t="n">
-        <v>3.7148790517908</v>
+        <v>3.714879051790798</v>
       </c>
       <c r="C2059" t="n">
         <v>3.909530246203802</v>
       </c>
       <c r="D2059" t="n">
-        <v>-5.104426835007897</v>
+        <v>-5.115946946018091</v>
       </c>
       <c r="E2059" t="n">
-        <v>1.867403087886895</v>
+        <v>1.862795043482817</v>
       </c>
       <c r="F2059" t="n">
-        <v>0.695605453390135</v>
+        <v>0.6840853423799398</v>
       </c>
       <c r="G2059" t="n">
-        <v>4.326893518237883</v>
+        <v>4.319981451631766</v>
       </c>
     </row>
     <row r="2060">
@@ -48925,22 +48925,22 @@
         <v>45522</v>
       </c>
       <c r="B2060" t="n">
-        <v>3.704757949437327</v>
+        <v>3.704757949437326</v>
       </c>
       <c r="C2060" t="n">
         <v>3.909433374278091</v>
       </c>
       <c r="D2060" t="n">
-        <v>-5.183846286215648</v>
+        <v>-5.195366397225842</v>
       </c>
       <c r="E2060" t="n">
-        <v>1.835538435478083</v>
+        <v>1.830930391074006</v>
       </c>
       <c r="F2060" t="n">
-        <v>0.695605453390135</v>
+        <v>0.6840853423799398</v>
       </c>
       <c r="G2060" t="n">
-        <v>4.326796646312172</v>
+        <v>4.319884579706055</v>
       </c>
     </row>
     <row r="2061">
@@ -48954,16 +48954,16 @@
         <v>3.909427267836134</v>
       </c>
       <c r="D2061" t="n">
-        <v>-5.279309284132866</v>
+        <v>-5.299162878886071</v>
       </c>
       <c r="E2061" t="n">
-        <v>1.797347129869239</v>
+        <v>1.789405691967957</v>
       </c>
       <c r="F2061" t="n">
-        <v>0.695605453390135</v>
+        <v>0.6840853423799398</v>
       </c>
       <c r="G2061" t="n">
-        <v>4.326790539870215</v>
+        <v>4.319878473264098</v>
       </c>
     </row>
     <row r="2062">
@@ -48977,16 +48977,16 @@
         <v>3.907523664398744</v>
       </c>
       <c r="D2062" t="n">
-        <v>-5.214933373282151</v>
+        <v>-5.234786968035356</v>
       </c>
       <c r="E2062" t="n">
-        <v>1.821193890772136</v>
+        <v>1.813252452870854</v>
       </c>
       <c r="F2062" t="n">
-        <v>0.7599813642408502</v>
+        <v>0.7484612532306549</v>
       </c>
       <c r="G2062" t="n">
-        <v>4.363512482943254</v>
+        <v>4.356600416337137</v>
       </c>
     </row>
     <row r="2063">
@@ -49000,16 +49000,16 @@
         <v>3.913257482146471</v>
       </c>
       <c r="D2063" t="n">
-        <v>-5.270302535414345</v>
+        <v>-5.29015613016755</v>
       </c>
       <c r="E2063" t="n">
-        <v>1.804780043666985</v>
+        <v>1.796838605765703</v>
       </c>
       <c r="F2063" t="n">
-        <v>0.7599813642408502</v>
+        <v>0.7484612532306549</v>
       </c>
       <c r="G2063" t="n">
-        <v>4.369246300690981</v>
+        <v>4.362334234084864</v>
       </c>
     </row>
     <row r="2064">
@@ -49023,16 +49023,16 @@
         <v>3.912795845489403</v>
       </c>
       <c r="D2064" t="n">
-        <v>-5.288521002411954</v>
+        <v>-5.308374597165159</v>
       </c>
       <c r="E2064" t="n">
-        <v>1.797031020210874</v>
+        <v>1.789089582309592</v>
       </c>
       <c r="F2064" t="n">
-        <v>0.734874926985008</v>
+        <v>0.7233548159748128</v>
       </c>
       <c r="G2064" t="n">
-        <v>4.353720801680408</v>
+        <v>4.346808735074291</v>
       </c>
     </row>
     <row r="2065">
@@ -49046,16 +49046,16 @@
         <v>3.932670238339722</v>
       </c>
       <c r="D2065" t="n">
-        <v>-5.200314168264375</v>
+        <v>-5.220167763017581</v>
       </c>
       <c r="E2065" t="n">
-        <v>1.852188146720224</v>
+        <v>1.844246708818942</v>
       </c>
       <c r="F2065" t="n">
-        <v>0.734874926985008</v>
+        <v>0.7233548159748128</v>
       </c>
       <c r="G2065" t="n">
-        <v>4.373595194530727</v>
+        <v>4.36668312792461</v>
       </c>
     </row>
     <row r="2066">
@@ -49063,22 +49063,22 @@
         <v>45528</v>
       </c>
       <c r="B2066" t="n">
-        <v>3.794486844016437</v>
+        <v>3.794486844016435</v>
       </c>
       <c r="C2066" t="n">
         <v>3.91637093886445</v>
       </c>
       <c r="D2066" t="n">
-        <v>-5.094279173059066</v>
+        <v>-5.114132767812271</v>
       </c>
       <c r="E2066" t="n">
-        <v>1.878302845327076</v>
+        <v>1.870361407425793</v>
       </c>
       <c r="F2066" t="n">
-        <v>0.734874926985008</v>
+        <v>0.7233548159748128</v>
       </c>
       <c r="G2066" t="n">
-        <v>4.357295895055455</v>
+        <v>4.350383828449337</v>
       </c>
     </row>
     <row r="2067">
@@ -49086,22 +49086,22 @@
         <v>45529</v>
       </c>
       <c r="B2067" t="n">
-        <v>3.794705093307669</v>
+        <v>3.794705093307666</v>
       </c>
       <c r="C2067" t="n">
         <v>3.918801888328495</v>
       </c>
       <c r="D2067" t="n">
-        <v>-4.911067509925971</v>
+        <v>-4.930921104679176</v>
       </c>
       <c r="E2067" t="n">
-        <v>1.954018460044359</v>
+        <v>1.946077022143077</v>
       </c>
       <c r="F2067" t="n">
-        <v>0.734874926985008</v>
+        <v>0.7233548159748128</v>
       </c>
       <c r="G2067" t="n">
-        <v>4.359726844519501</v>
+        <v>4.352814777913383</v>
       </c>
     </row>
     <row r="2068">
@@ -49109,22 +49109,22 @@
         <v>45530</v>
       </c>
       <c r="B2068" t="n">
-        <v>3.77684655786355</v>
+        <v>3.776846557863547</v>
       </c>
       <c r="C2068" t="n">
         <v>3.901746294407872</v>
       </c>
       <c r="D2068" t="n">
-        <v>-4.83934606291212</v>
+        <v>-4.859199657665325</v>
       </c>
       <c r="E2068" t="n">
-        <v>1.965651444929277</v>
+        <v>1.957710007027995</v>
       </c>
       <c r="F2068" t="n">
-        <v>0.8065963739988586</v>
+        <v>0.7950762629886634</v>
       </c>
       <c r="G2068" t="n">
-        <v>4.385704118807188</v>
+        <v>4.378792052201071</v>
       </c>
     </row>
     <row r="2069">
@@ -49132,22 +49132,22 @@
         <v>45531</v>
       </c>
       <c r="B2069" t="n">
-        <v>3.72378970539411</v>
+        <v>3.723789705394108</v>
       </c>
       <c r="C2069" t="n">
         <v>3.848662040329044</v>
       </c>
       <c r="D2069" t="n">
-        <v>-4.816973037304414</v>
+        <v>-4.836826632057619</v>
       </c>
       <c r="E2069" t="n">
-        <v>1.92151640109353</v>
+        <v>1.913574963192249</v>
       </c>
       <c r="F2069" t="n">
-        <v>0.8178521251117602</v>
+        <v>0.806332014101565</v>
       </c>
       <c r="G2069" t="n">
-        <v>4.3393733153961</v>
+        <v>4.332461248789984</v>
       </c>
     </row>
     <row r="2070">
@@ -49155,22 +49155,22 @@
         <v>45532</v>
       </c>
       <c r="B2070" t="n">
-        <v>3.715607446456727</v>
+        <v>3.715607446456724</v>
       </c>
       <c r="C2070" t="n">
         <v>4.0338602452144</v>
       </c>
       <c r="D2070" t="n">
-        <v>-4.849989333215158</v>
+        <v>-4.869842927968364</v>
       </c>
       <c r="E2070" t="n">
-        <v>2.093508087614588</v>
+        <v>2.085566649713306</v>
       </c>
       <c r="F2070" t="n">
-        <v>0.7484147484450085</v>
+        <v>0.7368946374348133</v>
       </c>
       <c r="G2070" t="n">
-        <v>4.482909094281405</v>
+        <v>4.475997027675288</v>
       </c>
     </row>
     <row r="2071">
@@ -49178,22 +49178,22 @@
         <v>45533</v>
       </c>
       <c r="B2071" t="n">
-        <v>3.713762536883674</v>
+        <v>3.713762536883673</v>
       </c>
       <c r="C2071" t="n">
         <v>4.025781471042649</v>
       </c>
       <c r="D2071" t="n">
-        <v>-4.83846169756555</v>
+        <v>-4.858315292318755</v>
       </c>
       <c r="E2071" t="n">
-        <v>2.090040367702681</v>
+        <v>2.082098929801399</v>
       </c>
       <c r="F2071" t="n">
-        <v>0.807415406646371</v>
+        <v>0.7958952956361758</v>
       </c>
       <c r="G2071" t="n">
-        <v>4.510230715030471</v>
+        <v>4.503318648424354</v>
       </c>
     </row>
     <row r="2072">
@@ -49207,16 +49207,16 @@
         <v>4.029449583564437</v>
       </c>
       <c r="D2072" t="n">
-        <v>-4.935803198907919</v>
+        <v>-4.955656793661124</v>
       </c>
       <c r="E2072" t="n">
-        <v>2.054771879687522</v>
+        <v>2.04683044178624</v>
       </c>
       <c r="F2072" t="n">
-        <v>0.7629952244808826</v>
+        <v>0.7514751134706874</v>
       </c>
       <c r="G2072" t="n">
-        <v>4.487246718252967</v>
+        <v>4.48033465164685</v>
       </c>
     </row>
     <row r="2073">
@@ -49230,16 +49230,16 @@
         <v>4.030700665757275</v>
       </c>
       <c r="D2073" t="n">
-        <v>-5.021659228247885</v>
+        <v>-5.04151282300109</v>
       </c>
       <c r="E2073" t="n">
-        <v>2.021680550144374</v>
+        <v>2.013739112243091</v>
       </c>
       <c r="F2073" t="n">
-        <v>0.7206191552547476</v>
+        <v>0.7090990442445524</v>
       </c>
       <c r="G2073" t="n">
-        <v>4.463072158910125</v>
+        <v>4.456160092304007</v>
       </c>
     </row>
     <row r="2074">
@@ -49247,22 +49247,22 @@
         <v>45536</v>
       </c>
       <c r="B2074" t="n">
-        <v>3.691835499610379</v>
+        <v>3.691835499610377</v>
       </c>
       <c r="C2074" t="n">
         <v>4.013119867577777</v>
       </c>
       <c r="D2074" t="n">
-        <v>-5.030496025664005</v>
+        <v>-5.05034962041721</v>
       </c>
       <c r="E2074" t="n">
-        <v>2.000565032998427</v>
+        <v>1.992623595097145</v>
       </c>
       <c r="F2074" t="n">
-        <v>0.7131769826133969</v>
+        <v>0.7016568716032017</v>
       </c>
       <c r="G2074" t="n">
-        <v>4.441026057145816</v>
+        <v>4.434113990539698</v>
       </c>
     </row>
     <row r="2075">
@@ -49270,22 +49270,22 @@
         <v>45537</v>
       </c>
       <c r="B2075" t="n">
-        <v>3.715544411667452</v>
+        <v>3.71554441166745</v>
       </c>
       <c r="C2075" t="n">
         <v>4.023284378622827</v>
       </c>
       <c r="D2075" t="n">
-        <v>-5.121878588229463</v>
+        <v>-5.141732182982668</v>
       </c>
       <c r="E2075" t="n">
-        <v>1.974176519017294</v>
+        <v>1.966235081116011</v>
       </c>
       <c r="F2075" t="n">
-        <v>0.6766120978940522</v>
+        <v>0.665091986883857</v>
       </c>
       <c r="G2075" t="n">
-        <v>4.429251637359259</v>
+        <v>4.422339570753141</v>
       </c>
     </row>
     <row r="2076">
@@ -49296,19 +49296,19 @@
         <v>3.673978374889187</v>
       </c>
       <c r="C2076" t="n">
-        <v>4.144444094190696</v>
+        <v>4.125412636447095</v>
       </c>
       <c r="D2076" t="n">
-        <v>-5.110171870242457</v>
+        <v>-5.130025464995662</v>
       </c>
       <c r="E2076" t="n">
-        <v>2.100018921779965</v>
+        <v>2.073046026135082</v>
       </c>
       <c r="F2076" t="n">
-        <v>0.6883188158810586</v>
+        <v>0.6767987048708634</v>
       </c>
       <c r="G2076" t="n">
-        <v>4.557435383719332</v>
+        <v>4.531491859369613</v>
       </c>
     </row>
     <row r="2077">
@@ -49319,19 +49319,19 @@
         <v>3.682476099409563</v>
       </c>
       <c r="C2077" t="n">
-        <v>4.147476432922101</v>
+        <v>4.1284449751785</v>
       </c>
       <c r="D2077" t="n">
-        <v>-5.181083943984735</v>
+        <v>-5.200937538737939</v>
       </c>
       <c r="E2077" t="n">
-        <v>2.074686431014459</v>
+        <v>2.047713535369576</v>
       </c>
       <c r="F2077" t="n">
-        <v>0.6883188158810586</v>
+        <v>0.6767987048708634</v>
       </c>
       <c r="G2077" t="n">
-        <v>4.560467722450737</v>
+        <v>4.534524198101018</v>
       </c>
     </row>
     <row r="2078">
@@ -49339,22 +49339,22 @@
         <v>45540</v>
       </c>
       <c r="B2078" t="n">
-        <v>3.672895177452569</v>
+        <v>3.672895177452567</v>
       </c>
       <c r="C2078" t="n">
-        <v>4.360381266200159</v>
+        <v>4.341349808456558</v>
       </c>
       <c r="D2078" t="n">
-        <v>-5.191400042151087</v>
+        <v>-5.211253636904291</v>
       </c>
       <c r="E2078" t="n">
-        <v>2.283464825025976</v>
+        <v>2.256491929381093</v>
       </c>
       <c r="F2078" t="n">
-        <v>0.6883188158810586</v>
+        <v>0.6767987048708634</v>
       </c>
       <c r="G2078" t="n">
-        <v>4.773372555728795</v>
+        <v>4.747429031379076</v>
       </c>
     </row>
     <row r="2079">
@@ -49362,22 +49362,22 @@
         <v>45541</v>
       </c>
       <c r="B2079" t="n">
-        <v>3.623960959762282</v>
+        <v>3.623960959762283</v>
       </c>
       <c r="C2079" t="n">
-        <v>4.359559933112249</v>
+        <v>4.340528475368647</v>
       </c>
       <c r="D2079" t="n">
-        <v>-5.191306074133714</v>
+        <v>-5.211159668886919</v>
       </c>
       <c r="E2079" t="n">
-        <v>2.282681079145015</v>
+        <v>2.255708183500132</v>
       </c>
       <c r="F2079" t="n">
-        <v>0.6886886772283766</v>
+        <v>0.6771685662181813</v>
       </c>
       <c r="G2079" t="n">
-        <v>4.772773139449275</v>
+        <v>4.746829615099556</v>
       </c>
     </row>
     <row r="2080">
@@ -49385,22 +49385,22 @@
         <v>45542</v>
       </c>
       <c r="B2080" t="n">
-        <v>3.633213467988013</v>
+        <v>3.633213467988014</v>
       </c>
       <c r="C2080" t="n">
-        <v>4.353791919056603</v>
+        <v>4.334760461313001</v>
       </c>
       <c r="D2080" t="n">
-        <v>-5.339672301789859</v>
+        <v>-5.359525896543063</v>
       </c>
       <c r="E2080" t="n">
-        <v>2.217566574026911</v>
+        <v>2.190593678382028</v>
       </c>
       <c r="F2080" t="n">
-        <v>0.6886886772283766</v>
+        <v>0.6771685662181813</v>
       </c>
       <c r="G2080" t="n">
-        <v>4.767005125393629</v>
+        <v>4.74106160104391</v>
       </c>
     </row>
     <row r="2081">
@@ -49408,22 +49408,22 @@
         <v>45543</v>
       </c>
       <c r="B2081" t="n">
-        <v>3.64790724274092</v>
+        <v>3.647907242740918</v>
       </c>
       <c r="C2081" t="n">
-        <v>4.353791919056603</v>
+        <v>4.334760461313001</v>
       </c>
       <c r="D2081" t="n">
-        <v>-5.338723878671821</v>
+        <v>-5.358577473425025</v>
       </c>
       <c r="E2081" t="n">
-        <v>2.217945943274126</v>
+        <v>2.190973047629243</v>
       </c>
       <c r="F2081" t="n">
-        <v>0.6886886772283766</v>
+        <v>0.6771685662181813</v>
       </c>
       <c r="G2081" t="n">
-        <v>4.767005125393629</v>
+        <v>4.74106160104391</v>
       </c>
     </row>
     <row r="2082">
@@ -49431,22 +49431,22 @@
         <v>45544</v>
       </c>
       <c r="B2082" t="n">
-        <v>3.881065366663623</v>
+        <v>3.881065366663622</v>
       </c>
       <c r="C2082" t="n">
-        <v>4.366519527037695</v>
+        <v>4.347488069294093</v>
       </c>
       <c r="D2082" t="n">
-        <v>-5.438993696630842</v>
+        <v>-5.458847291384046</v>
       </c>
       <c r="E2082" t="n">
-        <v>2.19056562407161</v>
+        <v>2.163592728426727</v>
       </c>
       <c r="F2082" t="n">
-        <v>0.6886886772283766</v>
+        <v>0.6771685662181813</v>
       </c>
       <c r="G2082" t="n">
-        <v>4.779732733374721</v>
+        <v>4.753789209025002</v>
       </c>
     </row>
     <row r="2083">
@@ -49454,22 +49454,22 @@
         <v>45545</v>
       </c>
       <c r="B2083" t="n">
-        <v>3.717071158424767</v>
+        <v>3.717071158424766</v>
       </c>
       <c r="C2083" t="n">
-        <v>4.368465525462082</v>
+        <v>4.349434067718481</v>
       </c>
       <c r="D2083" t="n">
-        <v>-5.43300144984203</v>
+        <v>-5.452855044595235</v>
       </c>
       <c r="E2083" t="n">
-        <v>2.194908521211522</v>
+        <v>2.167935625566639</v>
       </c>
       <c r="F2083" t="n">
-        <v>0.6886886772283766</v>
+        <v>0.6771685662181813</v>
       </c>
       <c r="G2083" t="n">
-        <v>4.781678731799109</v>
+        <v>4.75573520744939</v>
       </c>
     </row>
     <row r="2084">
@@ -49477,22 +49477,22 @@
         <v>45546</v>
       </c>
       <c r="B2084" t="n">
-        <v>3.741942347149216</v>
+        <v>3.741942347149214</v>
       </c>
       <c r="C2084" t="n">
-        <v>4.362119661479851</v>
+        <v>4.34308820373625</v>
       </c>
       <c r="D2084" t="n">
-        <v>-5.344443488711263</v>
+        <v>-5.364297083464467</v>
       </c>
       <c r="E2084" t="n">
-        <v>2.223985841681598</v>
+        <v>2.197012946036715</v>
       </c>
       <c r="F2084" t="n">
-        <v>0.6886886772283766</v>
+        <v>0.6771685662181813</v>
       </c>
       <c r="G2084" t="n">
-        <v>4.775332867816878</v>
+        <v>4.749389343467159</v>
       </c>
     </row>
     <row r="2085">
@@ -49500,22 +49500,22 @@
         <v>45547</v>
       </c>
       <c r="B2085" t="n">
-        <v>3.735300721383088</v>
+        <v>3.735300721383086</v>
       </c>
       <c r="C2085" t="n">
-        <v>4.361428338918847</v>
+        <v>4.342396881175246</v>
       </c>
       <c r="D2085" t="n">
-        <v>-5.326684411208189</v>
+        <v>-5.346538005961393</v>
       </c>
       <c r="E2085" t="n">
-        <v>2.230398150121824</v>
+        <v>2.203425254476941</v>
       </c>
       <c r="F2085" t="n">
-        <v>0.6886886772283766</v>
+        <v>0.6771685662181813</v>
       </c>
       <c r="G2085" t="n">
-        <v>4.774641545255873</v>
+        <v>4.748698020906154</v>
       </c>
     </row>
     <row r="2086">
@@ -49523,22 +49523,22 @@
         <v>45548</v>
       </c>
       <c r="B2086" t="n">
-        <v>3.778232147720994</v>
+        <v>3.778232147720992</v>
       </c>
       <c r="C2086" t="n">
-        <v>4.374210524827434</v>
+        <v>4.355179067083832</v>
       </c>
       <c r="D2086" t="n">
-        <v>-5.227054260159121</v>
+        <v>-5.246907854912325</v>
       </c>
       <c r="E2086" t="n">
-        <v>2.283032396450037</v>
+        <v>2.256059500805154</v>
       </c>
       <c r="F2086" t="n">
-        <v>0.788318828277444</v>
+        <v>0.7767987172672488</v>
       </c>
       <c r="G2086" t="n">
-        <v>4.847201821793901</v>
+        <v>4.821258297444182</v>
       </c>
     </row>
     <row r="2087">
@@ -49546,22 +49546,22 @@
         <v>45549</v>
       </c>
       <c r="B2087" t="n">
-        <v>3.775357097455268</v>
+        <v>3.775357097455267</v>
       </c>
       <c r="C2087" t="n">
-        <v>4.56336479032616</v>
+        <v>4.544333332582559</v>
       </c>
       <c r="D2087" t="n">
-        <v>-5.276453768848132</v>
+        <v>-5.296307363601336</v>
       </c>
       <c r="E2087" t="n">
-        <v>2.452426858473159</v>
+        <v>2.425453962828276</v>
       </c>
       <c r="F2087" t="n">
-        <v>0.7985776617091888</v>
+        <v>0.7870575506989935</v>
       </c>
       <c r="G2087" t="n">
-        <v>5.042511387351674</v>
+        <v>5.016567863001955</v>
       </c>
     </row>
     <row r="2088">
@@ -49569,22 +49569,22 @@
         <v>45550</v>
       </c>
       <c r="B2088" t="n">
-        <v>3.749078058963129</v>
+        <v>3.749078058963128</v>
       </c>
       <c r="C2088" t="n">
-        <v>4.550553463429022</v>
+        <v>4.531522005685421</v>
       </c>
       <c r="D2088" t="n">
-        <v>-5.069769295205756</v>
+        <v>-5.08962288995896</v>
       </c>
       <c r="E2088" t="n">
-        <v>2.522289321032972</v>
+        <v>2.495316425388089</v>
       </c>
       <c r="F2088" t="n">
-        <v>1.005262135351564</v>
+        <v>0.993742024341369</v>
       </c>
       <c r="G2088" t="n">
-        <v>5.153710744639961</v>
+        <v>5.127767220290242</v>
       </c>
     </row>
     <row r="2089">
@@ -49592,22 +49592,22 @@
         <v>45551</v>
       </c>
       <c r="B2089" t="n">
-        <v>3.740284389162539</v>
+        <v>3.740284389162538</v>
       </c>
       <c r="C2089" t="n">
-        <v>4.552554977083127</v>
+        <v>4.533523519339526</v>
       </c>
       <c r="D2089" t="n">
-        <v>-5.103926190203282</v>
+        <v>-5.123779784956486</v>
       </c>
       <c r="E2089" t="n">
-        <v>2.510628076688066</v>
+        <v>2.483655181043183</v>
       </c>
       <c r="F2089" t="n">
-        <v>0.9216783658107518</v>
+        <v>0.9101582548005566</v>
       </c>
       <c r="G2089" t="n">
-        <v>5.105561996569579</v>
+        <v>5.07961847221986</v>
       </c>
     </row>
     <row r="2090">
@@ -49615,22 +49615,22 @@
         <v>45552</v>
       </c>
       <c r="B2090" t="n">
-        <v>3.78248211565238</v>
+        <v>3.782482115652378</v>
       </c>
       <c r="C2090" t="n">
-        <v>4.906052091072794</v>
+        <v>4.887020633329193</v>
       </c>
       <c r="D2090" t="n">
-        <v>-5.011336711141825</v>
+        <v>-5.03119030589503</v>
       </c>
       <c r="E2090" t="n">
-        <v>2.901160982302316</v>
+        <v>2.874188086657433</v>
       </c>
       <c r="F2090" t="n">
-        <v>0.9216783658107518</v>
+        <v>0.9101582548005566</v>
       </c>
       <c r="G2090" t="n">
-        <v>5.459059110559246</v>
+        <v>5.433115586209527</v>
       </c>
     </row>
     <row r="2091">
@@ -49638,22 +49638,22 @@
         <v>45553</v>
       </c>
       <c r="B2091" t="n">
-        <v>3.809055905108669</v>
+        <v>3.809055905108668</v>
       </c>
       <c r="C2091" t="n">
-        <v>4.910615202639898</v>
+        <v>4.891583744896296</v>
       </c>
       <c r="D2091" t="n">
-        <v>-5.08449731491497</v>
+        <v>-5.104350909668175</v>
       </c>
       <c r="E2091" t="n">
-        <v>2.876459852360162</v>
+        <v>2.849486956715279</v>
       </c>
       <c r="F2091" t="n">
-        <v>0.8936571657765087</v>
+        <v>0.8821370547663134</v>
       </c>
       <c r="G2091" t="n">
-        <v>5.446809502105803</v>
+        <v>5.420865977756085</v>
       </c>
     </row>
     <row r="2092">
@@ -49664,19 +49664,19 @@
         <v>3.83520244110356</v>
       </c>
       <c r="C2092" t="n">
-        <v>4.960445143963425</v>
+        <v>4.941413686219824</v>
       </c>
       <c r="D2092" t="n">
-        <v>-5.032281005118628</v>
+        <v>-5.166254803819686</v>
       </c>
       <c r="E2092" t="n">
-        <v>2.947176317602226</v>
+        <v>2.874555340378202</v>
       </c>
       <c r="F2092" t="n">
-        <v>0.8936571657765087</v>
+        <v>0.8821370547663134</v>
       </c>
       <c r="G2092" t="n">
-        <v>5.496639443429331</v>
+        <v>5.470695919079613</v>
       </c>
     </row>
     <row r="2093">
@@ -49684,22 +49684,22 @@
         <v>45555</v>
       </c>
       <c r="B2093" t="n">
-        <v>3.821827147047742</v>
+        <v>3.821827147047741</v>
       </c>
       <c r="C2093" t="n">
-        <v>4.969259114173436</v>
+        <v>4.950227656429835</v>
       </c>
       <c r="D2093" t="n">
-        <v>-5.000383488033383</v>
+        <v>-5.13435728673444</v>
       </c>
       <c r="E2093" t="n">
-        <v>2.968749294646335</v>
+        <v>2.896128317422311</v>
       </c>
       <c r="F2093" t="n">
-        <v>0.9255546828617545</v>
+        <v>0.9140345718515592</v>
       </c>
       <c r="G2093" t="n">
-        <v>5.524591923890489</v>
+        <v>5.49864839954077</v>
       </c>
     </row>
     <row r="2094">
@@ -49710,19 +49710,19 @@
         <v>3.825268416650751</v>
       </c>
       <c r="C2094" t="n">
-        <v>4.964896698212633</v>
+        <v>4.945865240469032</v>
       </c>
       <c r="D2094" t="n">
-        <v>-5.015138812233523</v>
+        <v>-5.149112610934581</v>
       </c>
       <c r="E2094" t="n">
-        <v>2.958484749005476</v>
+        <v>2.885863771781451</v>
       </c>
       <c r="F2094" t="n">
-        <v>0.9255546828617545</v>
+        <v>0.9140345718515592</v>
       </c>
       <c r="G2094" t="n">
-        <v>5.520229507929686</v>
+        <v>5.494285983579967</v>
       </c>
     </row>
     <row r="2095">
@@ -49733,19 +49733,19 @@
         <v>3.845044666135745</v>
       </c>
       <c r="C2095" t="n">
-        <v>4.955821201628913</v>
+        <v>4.936789743885312</v>
       </c>
       <c r="D2095" t="n">
-        <v>-4.965674188863612</v>
+        <v>-5.099647987564669</v>
       </c>
       <c r="E2095" t="n">
-        <v>2.96919510176972</v>
+        <v>2.896574124545696</v>
       </c>
       <c r="F2095" t="n">
-        <v>0.9750193062316661</v>
+        <v>0.9634991952214709</v>
       </c>
       <c r="G2095" t="n">
-        <v>5.540832785367913</v>
+        <v>5.514889261018195</v>
       </c>
     </row>
     <row r="2096">
@@ -49756,19 +49756,19 @@
         <v>3.825931790479219</v>
       </c>
       <c r="C2096" t="n">
-        <v>4.952228869343847</v>
+        <v>4.933197411600246</v>
       </c>
       <c r="D2096" t="n">
-        <v>-4.802566196709996</v>
+        <v>-4.936539995411054</v>
       </c>
       <c r="E2096" t="n">
-        <v>3.030845966346101</v>
+        <v>2.958224989122077</v>
       </c>
       <c r="F2096" t="n">
-        <v>1.138127298385281</v>
+        <v>1.126607187375086</v>
       </c>
       <c r="G2096" t="n">
-        <v>5.635105248375017</v>
+        <v>5.609161724025298</v>
       </c>
     </row>
     <row r="2097">
@@ -49776,22 +49776,22 @@
         <v>45559</v>
       </c>
       <c r="B2097" t="n">
-        <v>3.847096478844243</v>
+        <v>3.84709647884424</v>
       </c>
       <c r="C2097" t="n">
-        <v>4.961275906034976</v>
+        <v>4.942244448291374</v>
       </c>
       <c r="D2097" t="n">
-        <v>-4.66975857121283</v>
+        <v>-4.803732369913887</v>
       </c>
       <c r="E2097" t="n">
-        <v>3.093016053236096</v>
+        <v>3.020395076012071</v>
       </c>
       <c r="F2097" t="n">
-        <v>1.138127298385281</v>
+        <v>1.126607187375086</v>
       </c>
       <c r="G2097" t="n">
-        <v>5.644152285066145</v>
+        <v>5.618208760716426</v>
       </c>
     </row>
     <row r="2098">
@@ -49799,22 +49799,22 @@
         <v>45560</v>
       </c>
       <c r="B2098" t="n">
-        <v>3.832425987790947</v>
+        <v>3.832425987790944</v>
       </c>
       <c r="C2098" t="n">
-        <v>4.962133371021097</v>
+        <v>4.943101913277496</v>
       </c>
       <c r="D2098" t="n">
-        <v>-4.732466487687388</v>
+        <v>-4.866440286388445</v>
       </c>
       <c r="E2098" t="n">
-        <v>3.068790351632394</v>
+        <v>2.99616937440837</v>
       </c>
       <c r="F2098" t="n">
-        <v>1.075419381910724</v>
+        <v>1.063899270900528</v>
       </c>
       <c r="G2098" t="n">
-        <v>5.607385000167532</v>
+        <v>5.581441475817813</v>
       </c>
     </row>
     <row r="2099">
@@ -49822,22 +49822,22 @@
         <v>45561</v>
       </c>
       <c r="B2099" t="n">
-        <v>3.861579399578993</v>
+        <v>3.861579399578991</v>
       </c>
       <c r="C2099" t="n">
-        <v>4.925042787811449</v>
+        <v>4.906011330067848</v>
       </c>
       <c r="D2099" t="n">
-        <v>-4.684458363843695</v>
+        <v>-4.818432162544752</v>
       </c>
       <c r="E2099" t="n">
-        <v>3.050903017960223</v>
+        <v>2.978282040736199</v>
       </c>
       <c r="F2099" t="n">
-        <v>1.075419381910724</v>
+        <v>1.063899270900528</v>
       </c>
       <c r="G2099" t="n">
-        <v>5.570294416957884</v>
+        <v>5.544350892608166</v>
       </c>
     </row>
     <row r="2100">
@@ -49845,22 +49845,22 @@
         <v>45562</v>
       </c>
       <c r="B2100" t="n">
-        <v>3.872253907629881</v>
+        <v>3.872253907629879</v>
       </c>
       <c r="C2100" t="n">
-        <v>4.9289750413694</v>
+        <v>4.909943583625799</v>
       </c>
       <c r="D2100" t="n">
-        <v>-4.605632706660105</v>
+        <v>-4.739606505361162</v>
       </c>
       <c r="E2100" t="n">
-        <v>3.08636553439161</v>
+        <v>3.013744557167586</v>
       </c>
       <c r="F2100" t="n">
-        <v>1.154245039094314</v>
+        <v>1.142724928084119</v>
       </c>
       <c r="G2100" t="n">
-        <v>5.621522064825989</v>
+        <v>5.59557854047627</v>
       </c>
     </row>
     <row r="2101">
@@ -49868,22 +49868,22 @@
         <v>45563</v>
       </c>
       <c r="B2101" t="n">
-        <v>3.868502531686404</v>
+        <v>3.868502531686402</v>
       </c>
       <c r="C2101" t="n">
-        <v>4.923874133976437</v>
+        <v>4.904842676232835</v>
       </c>
       <c r="D2101" t="n">
-        <v>-4.413697905406231</v>
+        <v>-4.547671704107288</v>
       </c>
       <c r="E2101" t="n">
-        <v>3.158038547500197</v>
+        <v>3.085417570276172</v>
       </c>
       <c r="F2101" t="n">
-        <v>1.154245039094314</v>
+        <v>1.142724928084119</v>
       </c>
       <c r="G2101" t="n">
-        <v>5.616421157433026</v>
+        <v>5.590477633083307</v>
       </c>
     </row>
     <row r="2102">
@@ -49891,22 +49891,22 @@
         <v>45564</v>
       </c>
       <c r="B2102" t="n">
-        <v>3.849324044046708</v>
+        <v>3.849324044046709</v>
       </c>
       <c r="C2102" t="n">
-        <v>4.919228043365532</v>
+        <v>4.900196585621931</v>
       </c>
       <c r="D2102" t="n">
-        <v>-4.295524527388304</v>
+        <v>-4.429498326089361</v>
       </c>
       <c r="E2102" t="n">
-        <v>3.200661808096462</v>
+        <v>3.128040830872439</v>
       </c>
       <c r="F2102" t="n">
-        <v>1.272418417112241</v>
+        <v>1.260898306102046</v>
       </c>
       <c r="G2102" t="n">
-        <v>5.682679093632877</v>
+        <v>5.656735569283159</v>
       </c>
     </row>
     <row r="2103">
@@ -49914,22 +49914,22 @@
         <v>45565</v>
       </c>
       <c r="B2103" t="n">
-        <v>3.901107459027854</v>
+        <v>3.768853341214586</v>
       </c>
       <c r="C2103" t="n">
-        <v>5.057055841698706</v>
+        <v>4.842086405475865</v>
       </c>
       <c r="D2103" t="n">
-        <v>-4.295524527388304</v>
+        <v>-4.429498326089361</v>
       </c>
       <c r="E2103" t="n">
-        <v>3.200661808096462</v>
+        <v>3.128040830872439</v>
       </c>
       <c r="F2103" t="n">
-        <v>1.272418417112241</v>
+        <v>1.260898306102046</v>
       </c>
       <c r="G2103" t="n">
-        <v>5.050119638685074</v>
+        <v>4.835150202462233</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240930.xlsx
+++ b/tame_output/ON/bt/strategyON_20240930.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>54.1%</t>
+          <t>54.0%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>64.9%</t>
+          <t>65.0%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>48.8%</t>
+          <t>48.3%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>110.8%</t>
+          <t>110.9%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>44.0%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.52</t>
+          <t>2.50</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -791,12 +791,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>39.7%</t>
+          <t>40.3%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>47.2%</t>
+          <t>47.4%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -849,12 +849,12 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>93.1%</t>
+          <t>92.9%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>36.0%</t>
+          <t>36.3%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-8.2%</t>
+          <t>-8.3%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>172.6%</t>
+          <t>173.6%</t>
         </is>
       </c>
     </row>
@@ -982,7 +982,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-35.2%</t>
+          <t>-34.7%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-604.5%</t>
+          <t>-604.0%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>43.8%</t>
+          <t>45.6%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.3%</t>
+          <t>57.4%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>14.2%</t>
+          <t>14.4%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>38.7%</t>
+          <t>40.5%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-3.9%</t>
+          <t>-4.2%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15.3%</t>
+          <t>15.2%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-63.4%</t>
+          <t>-56.0%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>67.0%</t>
+          <t>57.1%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>67.1%</t>
+          <t>68.5%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>79.8%</t>
+          <t>82.5%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1447,7 +1447,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
+          <t>48.1%</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
           <t>57.0%</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>55.8%</t>
-        </is>
-      </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>37.5%</t>
+          <t>38.5%</t>
         </is>
       </c>
     </row>
@@ -47775,7 +47775,7 @@
         <v>45472</v>
       </c>
       <c r="B2010" t="n">
-        <v>3.712897612343062</v>
+        <v>3.712897612343063</v>
       </c>
       <c r="C2010" t="n">
         <v>3.200497106215023</v>
@@ -47798,7 +47798,7 @@
         <v>45473</v>
       </c>
       <c r="B2011" t="n">
-        <v>3.754596135389345</v>
+        <v>3.754596135389346</v>
       </c>
       <c r="C2011" t="n">
         <v>3.213570513080942</v>
@@ -48954,10 +48954,10 @@
         <v>3.909427267836134</v>
       </c>
       <c r="D2061" t="n">
-        <v>-5.299162878886071</v>
+        <v>-5.29082939514306</v>
       </c>
       <c r="E2061" t="n">
-        <v>1.789405691967957</v>
+        <v>1.792739085465162</v>
       </c>
       <c r="F2061" t="n">
         <v>0.6840853423799398</v>
@@ -48977,10 +48977,10 @@
         <v>3.907523664398744</v>
       </c>
       <c r="D2062" t="n">
-        <v>-5.234786968035356</v>
+        <v>-5.226453484292345</v>
       </c>
       <c r="E2062" t="n">
-        <v>1.813252452870854</v>
+        <v>1.816585846368058</v>
       </c>
       <c r="F2062" t="n">
         <v>0.7484612532306549</v>
@@ -49000,10 +49000,10 @@
         <v>3.913257482146471</v>
       </c>
       <c r="D2063" t="n">
-        <v>-5.29015613016755</v>
+        <v>-5.281822646424539</v>
       </c>
       <c r="E2063" t="n">
-        <v>1.796838605765703</v>
+        <v>1.800171999262907</v>
       </c>
       <c r="F2063" t="n">
         <v>0.7484612532306549</v>
@@ -49023,10 +49023,10 @@
         <v>3.912795845489403</v>
       </c>
       <c r="D2064" t="n">
-        <v>-5.308374597165159</v>
+        <v>-5.300041113422147</v>
       </c>
       <c r="E2064" t="n">
-        <v>1.789089582309592</v>
+        <v>1.792422975806796</v>
       </c>
       <c r="F2064" t="n">
         <v>0.7233548159748128</v>
@@ -49046,10 +49046,10 @@
         <v>3.932670238339722</v>
       </c>
       <c r="D2065" t="n">
-        <v>-5.220167763017581</v>
+        <v>-5.211834279274569</v>
       </c>
       <c r="E2065" t="n">
-        <v>1.844246708818942</v>
+        <v>1.847580102316146</v>
       </c>
       <c r="F2065" t="n">
         <v>0.7233548159748128</v>
@@ -49069,10 +49069,10 @@
         <v>3.91637093886445</v>
       </c>
       <c r="D2066" t="n">
-        <v>-5.114132767812271</v>
+        <v>-5.10579928406926</v>
       </c>
       <c r="E2066" t="n">
-        <v>1.870361407425793</v>
+        <v>1.873694800922998</v>
       </c>
       <c r="F2066" t="n">
         <v>0.7233548159748128</v>
@@ -49092,10 +49092,10 @@
         <v>3.918801888328495</v>
       </c>
       <c r="D2067" t="n">
-        <v>-4.930921104679176</v>
+        <v>-4.922587620936165</v>
       </c>
       <c r="E2067" t="n">
-        <v>1.946077022143077</v>
+        <v>1.949410415640282</v>
       </c>
       <c r="F2067" t="n">
         <v>0.7233548159748128</v>
@@ -49115,10 +49115,10 @@
         <v>3.901746294407872</v>
       </c>
       <c r="D2068" t="n">
-        <v>-4.859199657665325</v>
+        <v>-4.850866173922314</v>
       </c>
       <c r="E2068" t="n">
-        <v>1.957710007027995</v>
+        <v>1.961043400525199</v>
       </c>
       <c r="F2068" t="n">
         <v>0.7950762629886634</v>
@@ -49138,10 +49138,10 @@
         <v>3.848662040329044</v>
       </c>
       <c r="D2069" t="n">
-        <v>-4.836826632057619</v>
+        <v>-4.828493148314608</v>
       </c>
       <c r="E2069" t="n">
-        <v>1.913574963192249</v>
+        <v>1.916908356689453</v>
       </c>
       <c r="F2069" t="n">
         <v>0.806332014101565</v>
@@ -49161,10 +49161,10 @@
         <v>4.0338602452144</v>
       </c>
       <c r="D2070" t="n">
-        <v>-4.869842927968364</v>
+        <v>-4.861509444225352</v>
       </c>
       <c r="E2070" t="n">
-        <v>2.085566649713306</v>
+        <v>2.08890004321051</v>
       </c>
       <c r="F2070" t="n">
         <v>0.7368946374348133</v>
@@ -49184,10 +49184,10 @@
         <v>4.025781471042649</v>
       </c>
       <c r="D2071" t="n">
-        <v>-4.858315292318755</v>
+        <v>-4.849981808575744</v>
       </c>
       <c r="E2071" t="n">
-        <v>2.082098929801399</v>
+        <v>2.085432323298603</v>
       </c>
       <c r="F2071" t="n">
         <v>0.7958952956361758</v>
@@ -49204,19 +49204,19 @@
         <v>3.717150699236294</v>
       </c>
       <c r="C2072" t="n">
-        <v>4.029449583564437</v>
+        <v>4.101138160843282</v>
       </c>
       <c r="D2072" t="n">
-        <v>-4.955656793661124</v>
+        <v>-4.947323309918112</v>
       </c>
       <c r="E2072" t="n">
-        <v>2.04683044178624</v>
+        <v>2.121852412562289</v>
       </c>
       <c r="F2072" t="n">
         <v>0.7514751134706874</v>
       </c>
       <c r="G2072" t="n">
-        <v>4.48033465164685</v>
+        <v>4.552023228925695</v>
       </c>
     </row>
     <row r="2073">
@@ -49227,19 +49227,19 @@
         <v>3.70520107942768</v>
       </c>
       <c r="C2073" t="n">
-        <v>4.030700665757275</v>
+        <v>4.10238924303612</v>
       </c>
       <c r="D2073" t="n">
-        <v>-5.04151282300109</v>
+        <v>-5.033179339258079</v>
       </c>
       <c r="E2073" t="n">
-        <v>2.013739112243091</v>
+        <v>2.08876108301914</v>
       </c>
       <c r="F2073" t="n">
         <v>0.7090990442445524</v>
       </c>
       <c r="G2073" t="n">
-        <v>4.456160092304007</v>
+        <v>4.527848669582851</v>
       </c>
     </row>
     <row r="2074">
@@ -49250,19 +49250,19 @@
         <v>3.691835499610377</v>
       </c>
       <c r="C2074" t="n">
-        <v>4.013119867577777</v>
+        <v>4.084808444856622</v>
       </c>
       <c r="D2074" t="n">
-        <v>-5.05034962041721</v>
+        <v>-5.042016136674198</v>
       </c>
       <c r="E2074" t="n">
-        <v>1.992623595097145</v>
+        <v>2.067645565873194</v>
       </c>
       <c r="F2074" t="n">
         <v>0.7016568716032017</v>
       </c>
       <c r="G2074" t="n">
-        <v>4.434113990539698</v>
+        <v>4.505802567818542</v>
       </c>
     </row>
     <row r="2075">
@@ -49273,19 +49273,19 @@
         <v>3.71554441166745</v>
       </c>
       <c r="C2075" t="n">
-        <v>4.023284378622827</v>
+        <v>4.094972955901671</v>
       </c>
       <c r="D2075" t="n">
-        <v>-5.141732182982668</v>
+        <v>-5.133398699239657</v>
       </c>
       <c r="E2075" t="n">
-        <v>1.966235081116011</v>
+        <v>2.04125705189206</v>
       </c>
       <c r="F2075" t="n">
         <v>0.665091986883857</v>
       </c>
       <c r="G2075" t="n">
-        <v>4.422339570753141</v>
+        <v>4.494028148031985</v>
       </c>
     </row>
     <row r="2076">
@@ -49296,19 +49296,19 @@
         <v>3.673978374889187</v>
       </c>
       <c r="C2076" t="n">
-        <v>4.125412636447095</v>
+        <v>4.197101213725938</v>
       </c>
       <c r="D2076" t="n">
-        <v>-5.130025464995662</v>
+        <v>-5.121691981252651</v>
       </c>
       <c r="E2076" t="n">
-        <v>2.073046026135082</v>
+        <v>2.14806799691113</v>
       </c>
       <c r="F2076" t="n">
         <v>0.6767987048708634</v>
       </c>
       <c r="G2076" t="n">
-        <v>4.531491859369613</v>
+        <v>4.603180436648456</v>
       </c>
     </row>
     <row r="2077">
@@ -49319,19 +49319,19 @@
         <v>3.682476099409563</v>
       </c>
       <c r="C2077" t="n">
-        <v>4.1284449751785</v>
+        <v>4.200133552457343</v>
       </c>
       <c r="D2077" t="n">
-        <v>-5.200937538737939</v>
+        <v>-5.192604054994929</v>
       </c>
       <c r="E2077" t="n">
-        <v>2.047713535369576</v>
+        <v>2.122735506145624</v>
       </c>
       <c r="F2077" t="n">
         <v>0.6767987048708634</v>
       </c>
       <c r="G2077" t="n">
-        <v>4.534524198101018</v>
+        <v>4.606212775379861</v>
       </c>
     </row>
     <row r="2078">
@@ -49342,19 +49342,19 @@
         <v>3.672895177452567</v>
       </c>
       <c r="C2078" t="n">
-        <v>4.341349808456558</v>
+        <v>4.413038385735401</v>
       </c>
       <c r="D2078" t="n">
-        <v>-5.211253636904291</v>
+        <v>-5.202920153161281</v>
       </c>
       <c r="E2078" t="n">
-        <v>2.256491929381093</v>
+        <v>2.331513900157141</v>
       </c>
       <c r="F2078" t="n">
         <v>0.6767987048708634</v>
       </c>
       <c r="G2078" t="n">
-        <v>4.747429031379076</v>
+        <v>4.819117608657919</v>
       </c>
     </row>
     <row r="2079">
@@ -49365,19 +49365,19 @@
         <v>3.623960959762283</v>
       </c>
       <c r="C2079" t="n">
-        <v>4.340528475368647</v>
+        <v>4.412217052647491</v>
       </c>
       <c r="D2079" t="n">
-        <v>-5.211159668886919</v>
+        <v>-5.202826185143908</v>
       </c>
       <c r="E2079" t="n">
-        <v>2.255708183500132</v>
+        <v>2.33073015427618</v>
       </c>
       <c r="F2079" t="n">
         <v>0.6771685662181813</v>
       </c>
       <c r="G2079" t="n">
-        <v>4.746829615099556</v>
+        <v>4.8185181923784</v>
       </c>
     </row>
     <row r="2080">
@@ -49388,19 +49388,19 @@
         <v>3.633213467988014</v>
       </c>
       <c r="C2080" t="n">
-        <v>4.334760461313001</v>
+        <v>4.406449038591845</v>
       </c>
       <c r="D2080" t="n">
-        <v>-5.359525896543063</v>
+        <v>-5.351192412800053</v>
       </c>
       <c r="E2080" t="n">
-        <v>2.190593678382028</v>
+        <v>2.265615649158076</v>
       </c>
       <c r="F2080" t="n">
         <v>0.6771685662181813</v>
       </c>
       <c r="G2080" t="n">
-        <v>4.74106160104391</v>
+        <v>4.812750178322753</v>
       </c>
     </row>
     <row r="2081">
@@ -49411,19 +49411,19 @@
         <v>3.647907242740918</v>
       </c>
       <c r="C2081" t="n">
-        <v>4.334760461313001</v>
+        <v>4.406449038591845</v>
       </c>
       <c r="D2081" t="n">
-        <v>-5.358577473425025</v>
+        <v>-5.350243989682014</v>
       </c>
       <c r="E2081" t="n">
-        <v>2.190973047629243</v>
+        <v>2.265995018405291</v>
       </c>
       <c r="F2081" t="n">
         <v>0.6771685662181813</v>
       </c>
       <c r="G2081" t="n">
-        <v>4.74106160104391</v>
+        <v>4.812750178322753</v>
       </c>
     </row>
     <row r="2082">
@@ -49434,19 +49434,19 @@
         <v>3.881065366663622</v>
       </c>
       <c r="C2082" t="n">
-        <v>4.347488069294093</v>
+        <v>4.419176646572937</v>
       </c>
       <c r="D2082" t="n">
-        <v>-5.458847291384046</v>
+        <v>-5.450513807641036</v>
       </c>
       <c r="E2082" t="n">
-        <v>2.163592728426727</v>
+        <v>2.238614699202774</v>
       </c>
       <c r="F2082" t="n">
         <v>0.6771685662181813</v>
       </c>
       <c r="G2082" t="n">
-        <v>4.753789209025002</v>
+        <v>4.825477786303845</v>
       </c>
     </row>
     <row r="2083">
@@ -49457,19 +49457,19 @@
         <v>3.717071158424766</v>
       </c>
       <c r="C2083" t="n">
-        <v>4.349434067718481</v>
+        <v>4.421122644997324</v>
       </c>
       <c r="D2083" t="n">
-        <v>-5.452855044595235</v>
+        <v>-5.444521560852224</v>
       </c>
       <c r="E2083" t="n">
-        <v>2.167935625566639</v>
+        <v>2.242957596342687</v>
       </c>
       <c r="F2083" t="n">
         <v>0.6771685662181813</v>
       </c>
       <c r="G2083" t="n">
-        <v>4.75573520744939</v>
+        <v>4.827423784728233</v>
       </c>
     </row>
     <row r="2084">
@@ -49480,19 +49480,19 @@
         <v>3.741942347149214</v>
       </c>
       <c r="C2084" t="n">
-        <v>4.34308820373625</v>
+        <v>4.414776781015093</v>
       </c>
       <c r="D2084" t="n">
-        <v>-5.364297083464467</v>
+        <v>-5.355963599721457</v>
       </c>
       <c r="E2084" t="n">
-        <v>2.197012946036715</v>
+        <v>2.272034916812763</v>
       </c>
       <c r="F2084" t="n">
         <v>0.6771685662181813</v>
       </c>
       <c r="G2084" t="n">
-        <v>4.749389343467159</v>
+        <v>4.821077920746002</v>
       </c>
     </row>
     <row r="2085">
@@ -49503,19 +49503,19 @@
         <v>3.735300721383086</v>
       </c>
       <c r="C2085" t="n">
-        <v>4.342396881175246</v>
+        <v>4.414085458454089</v>
       </c>
       <c r="D2085" t="n">
-        <v>-5.346538005961393</v>
+        <v>-5.338204522218382</v>
       </c>
       <c r="E2085" t="n">
-        <v>2.203425254476941</v>
+        <v>2.278447225252988</v>
       </c>
       <c r="F2085" t="n">
         <v>0.6771685662181813</v>
       </c>
       <c r="G2085" t="n">
-        <v>4.748698020906154</v>
+        <v>4.820386598184998</v>
       </c>
     </row>
     <row r="2086">
@@ -49526,19 +49526,19 @@
         <v>3.778232147720992</v>
       </c>
       <c r="C2086" t="n">
-        <v>4.355179067083832</v>
+        <v>4.426867644362676</v>
       </c>
       <c r="D2086" t="n">
-        <v>-5.246907854912325</v>
+        <v>-5.238574371169315</v>
       </c>
       <c r="E2086" t="n">
-        <v>2.256059500805154</v>
+        <v>2.331081471581202</v>
       </c>
       <c r="F2086" t="n">
         <v>0.7767987172672488</v>
       </c>
       <c r="G2086" t="n">
-        <v>4.821258297444182</v>
+        <v>4.892946874723025</v>
       </c>
     </row>
     <row r="2087">
@@ -49549,19 +49549,19 @@
         <v>3.775357097455267</v>
       </c>
       <c r="C2087" t="n">
-        <v>4.544333332582559</v>
+        <v>4.616021909861402</v>
       </c>
       <c r="D2087" t="n">
-        <v>-5.296307363601336</v>
+        <v>-5.287973879858326</v>
       </c>
       <c r="E2087" t="n">
-        <v>2.425453962828276</v>
+        <v>2.500475933604324</v>
       </c>
       <c r="F2087" t="n">
         <v>0.7870575506989935</v>
       </c>
       <c r="G2087" t="n">
-        <v>5.016567863001955</v>
+        <v>5.088256440280799</v>
       </c>
     </row>
     <row r="2088">
@@ -49572,19 +49572,19 @@
         <v>3.749078058963128</v>
       </c>
       <c r="C2088" t="n">
-        <v>4.531522005685421</v>
+        <v>4.603210582964264</v>
       </c>
       <c r="D2088" t="n">
-        <v>-5.08962288995896</v>
+        <v>-5.08128940621595</v>
       </c>
       <c r="E2088" t="n">
-        <v>2.495316425388089</v>
+        <v>2.570338396164136</v>
       </c>
       <c r="F2088" t="n">
         <v>0.993742024341369</v>
       </c>
       <c r="G2088" t="n">
-        <v>5.127767220290242</v>
+        <v>5.199455797569086</v>
       </c>
     </row>
     <row r="2089">
@@ -49595,19 +49595,19 @@
         <v>3.740284389162538</v>
       </c>
       <c r="C2089" t="n">
-        <v>4.533523519339526</v>
+        <v>4.605212096618369</v>
       </c>
       <c r="D2089" t="n">
-        <v>-5.123779784956486</v>
+        <v>-5.115446301213476</v>
       </c>
       <c r="E2089" t="n">
-        <v>2.483655181043183</v>
+        <v>2.558677151819231</v>
       </c>
       <c r="F2089" t="n">
         <v>0.9101582548005566</v>
       </c>
       <c r="G2089" t="n">
-        <v>5.07961847221986</v>
+        <v>5.151307049498703</v>
       </c>
     </row>
     <row r="2090">
@@ -49618,19 +49618,19 @@
         <v>3.782482115652378</v>
       </c>
       <c r="C2090" t="n">
-        <v>4.887020633329193</v>
+        <v>4.958709210608037</v>
       </c>
       <c r="D2090" t="n">
-        <v>-5.03119030589503</v>
+        <v>-5.022856822152019</v>
       </c>
       <c r="E2090" t="n">
-        <v>2.874188086657433</v>
+        <v>2.949210057433481</v>
       </c>
       <c r="F2090" t="n">
         <v>0.9101582548005566</v>
       </c>
       <c r="G2090" t="n">
-        <v>5.433115586209527</v>
+        <v>5.50480416348837</v>
       </c>
     </row>
     <row r="2091">
@@ -49641,19 +49641,19 @@
         <v>3.809055905108668</v>
       </c>
       <c r="C2091" t="n">
-        <v>4.891583744896296</v>
+        <v>4.96327232217514</v>
       </c>
       <c r="D2091" t="n">
-        <v>-5.104350909668175</v>
+        <v>-5.096017425925164</v>
       </c>
       <c r="E2091" t="n">
-        <v>2.849486956715279</v>
+        <v>2.924508927491326</v>
       </c>
       <c r="F2091" t="n">
         <v>0.8821370547663134</v>
       </c>
       <c r="G2091" t="n">
-        <v>5.420865977756085</v>
+        <v>5.492554555034928</v>
       </c>
     </row>
     <row r="2092">
@@ -49664,19 +49664,19 @@
         <v>3.83520244110356</v>
       </c>
       <c r="C2092" t="n">
-        <v>4.941413686219824</v>
+        <v>5.013102263498667</v>
       </c>
       <c r="D2092" t="n">
-        <v>-5.166254803819686</v>
+        <v>-5.161115069002456</v>
       </c>
       <c r="E2092" t="n">
-        <v>2.874555340378202</v>
+        <v>2.948299811583937</v>
       </c>
       <c r="F2092" t="n">
         <v>0.8821370547663134</v>
       </c>
       <c r="G2092" t="n">
-        <v>5.470695919079613</v>
+        <v>5.542384496358456</v>
       </c>
     </row>
     <row r="2093">
@@ -49687,19 +49687,19 @@
         <v>3.821827147047741</v>
       </c>
       <c r="C2093" t="n">
-        <v>4.950227656429835</v>
+        <v>5.021916233708678</v>
       </c>
       <c r="D2093" t="n">
-        <v>-5.13435728673444</v>
+        <v>-5.12921755191721</v>
       </c>
       <c r="E2093" t="n">
-        <v>2.896128317422311</v>
+        <v>2.969872788628046</v>
       </c>
       <c r="F2093" t="n">
         <v>0.9140345718515592</v>
       </c>
       <c r="G2093" t="n">
-        <v>5.49864839954077</v>
+        <v>5.570336976819614</v>
       </c>
     </row>
     <row r="2094">
@@ -49710,19 +49710,19 @@
         <v>3.825268416650751</v>
       </c>
       <c r="C2094" t="n">
-        <v>4.945865240469032</v>
+        <v>5.017553817747875</v>
       </c>
       <c r="D2094" t="n">
-        <v>-5.149112610934581</v>
+        <v>-5.143972876117351</v>
       </c>
       <c r="E2094" t="n">
-        <v>2.885863771781451</v>
+        <v>2.959608242987187</v>
       </c>
       <c r="F2094" t="n">
         <v>0.9140345718515592</v>
       </c>
       <c r="G2094" t="n">
-        <v>5.494285983579967</v>
+        <v>5.565974560858811</v>
       </c>
     </row>
     <row r="2095">
@@ -49733,19 +49733,19 @@
         <v>3.845044666135745</v>
       </c>
       <c r="C2095" t="n">
-        <v>4.936789743885312</v>
+        <v>5.008478321164155</v>
       </c>
       <c r="D2095" t="n">
-        <v>-5.099647987564669</v>
+        <v>-5.094508252747439</v>
       </c>
       <c r="E2095" t="n">
-        <v>2.896574124545696</v>
+        <v>2.970318595751432</v>
       </c>
       <c r="F2095" t="n">
         <v>0.9634991952214709</v>
       </c>
       <c r="G2095" t="n">
-        <v>5.514889261018195</v>
+        <v>5.586577838297038</v>
       </c>
     </row>
     <row r="2096">
@@ -49756,19 +49756,19 @@
         <v>3.825931790479219</v>
       </c>
       <c r="C2096" t="n">
-        <v>4.933197411600246</v>
+        <v>5.00488598887909</v>
       </c>
       <c r="D2096" t="n">
-        <v>-4.936539995411054</v>
+        <v>-4.931400260593824</v>
       </c>
       <c r="E2096" t="n">
-        <v>2.958224989122077</v>
+        <v>3.031969460327812</v>
       </c>
       <c r="F2096" t="n">
         <v>1.126607187375086</v>
       </c>
       <c r="G2096" t="n">
-        <v>5.609161724025298</v>
+        <v>5.680850301304141</v>
       </c>
     </row>
     <row r="2097">
@@ -49779,19 +49779,19 @@
         <v>3.84709647884424</v>
       </c>
       <c r="C2097" t="n">
-        <v>4.942244448291374</v>
+        <v>5.013933025570218</v>
       </c>
       <c r="D2097" t="n">
-        <v>-4.803732369913887</v>
+        <v>-4.798592635096657</v>
       </c>
       <c r="E2097" t="n">
-        <v>3.020395076012071</v>
+        <v>3.094139547217807</v>
       </c>
       <c r="F2097" t="n">
         <v>1.126607187375086</v>
       </c>
       <c r="G2097" t="n">
-        <v>5.618208760716426</v>
+        <v>5.689897337995269</v>
       </c>
     </row>
     <row r="2098">
@@ -49802,19 +49802,19 @@
         <v>3.832425987790944</v>
       </c>
       <c r="C2098" t="n">
-        <v>4.943101913277496</v>
+        <v>5.014790490556339</v>
       </c>
       <c r="D2098" t="n">
-        <v>-4.866440286388445</v>
+        <v>-4.861300551571215</v>
       </c>
       <c r="E2098" t="n">
-        <v>2.99616937440837</v>
+        <v>3.069913845614105</v>
       </c>
       <c r="F2098" t="n">
         <v>1.063899270900528</v>
       </c>
       <c r="G2098" t="n">
-        <v>5.581441475817813</v>
+        <v>5.653130053096657</v>
       </c>
     </row>
     <row r="2099">
@@ -49825,19 +49825,19 @@
         <v>3.861579399578991</v>
       </c>
       <c r="C2099" t="n">
-        <v>4.906011330067848</v>
+        <v>4.977699907346691</v>
       </c>
       <c r="D2099" t="n">
-        <v>-4.818432162544752</v>
+        <v>-4.813292427727522</v>
       </c>
       <c r="E2099" t="n">
-        <v>2.978282040736199</v>
+        <v>3.052026511941935</v>
       </c>
       <c r="F2099" t="n">
         <v>1.063899270900528</v>
       </c>
       <c r="G2099" t="n">
-        <v>5.544350892608166</v>
+        <v>5.616039469887009</v>
       </c>
     </row>
     <row r="2100">
@@ -49848,19 +49848,19 @@
         <v>3.872253907629879</v>
       </c>
       <c r="C2100" t="n">
-        <v>4.909943583625799</v>
+        <v>4.981632160904642</v>
       </c>
       <c r="D2100" t="n">
-        <v>-4.739606505361162</v>
+        <v>-4.734466770543932</v>
       </c>
       <c r="E2100" t="n">
-        <v>3.013744557167586</v>
+        <v>3.087489028373321</v>
       </c>
       <c r="F2100" t="n">
         <v>1.142724928084119</v>
       </c>
       <c r="G2100" t="n">
-        <v>5.59557854047627</v>
+        <v>5.667267117755113</v>
       </c>
     </row>
     <row r="2101">
@@ -49871,19 +49871,19 @@
         <v>3.868502531686402</v>
       </c>
       <c r="C2101" t="n">
-        <v>4.904842676232835</v>
+        <v>4.976531253511679</v>
       </c>
       <c r="D2101" t="n">
-        <v>-4.547671704107288</v>
+        <v>-4.542531969290058</v>
       </c>
       <c r="E2101" t="n">
-        <v>3.085417570276172</v>
+        <v>3.159162041481907</v>
       </c>
       <c r="F2101" t="n">
         <v>1.142724928084119</v>
       </c>
       <c r="G2101" t="n">
-        <v>5.590477633083307</v>
+        <v>5.66216621036215</v>
       </c>
     </row>
     <row r="2102">
@@ -49891,22 +49891,22 @@
         <v>45564</v>
       </c>
       <c r="B2102" t="n">
-        <v>3.849324044046709</v>
+        <v>3.84932404404671</v>
       </c>
       <c r="C2102" t="n">
-        <v>4.900196585621931</v>
+        <v>4.971885162900774</v>
       </c>
       <c r="D2102" t="n">
-        <v>-4.429498326089361</v>
+        <v>-4.424358591272131</v>
       </c>
       <c r="E2102" t="n">
-        <v>3.128040830872439</v>
+        <v>3.201785302078173</v>
       </c>
       <c r="F2102" t="n">
         <v>1.260898306102046</v>
       </c>
       <c r="G2102" t="n">
-        <v>5.656735569283159</v>
+        <v>5.728424146562002</v>
       </c>
     </row>
     <row r="2103">
@@ -49914,22 +49914,22 @@
         <v>45565</v>
       </c>
       <c r="B2103" t="n">
-        <v>3.768853341214586</v>
+        <v>3.764159573175336</v>
       </c>
       <c r="C2103" t="n">
-        <v>4.842086405475865</v>
+        <v>4.852269311997898</v>
       </c>
       <c r="D2103" t="n">
-        <v>-4.429498326089361</v>
+        <v>-4.424358591272131</v>
       </c>
       <c r="E2103" t="n">
-        <v>3.128040830872439</v>
+        <v>3.201785302078173</v>
       </c>
       <c r="F2103" t="n">
         <v>1.260898306102046</v>
       </c>
       <c r="G2103" t="n">
-        <v>4.835150202462233</v>
+        <v>4.845333108984266</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240930.xlsx
+++ b/tame_output/ON/bt/strategyON_20240930.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>54.0%</t>
+          <t>57.3%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.1%</t>
+          <t>66.0%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>65.0%</t>
+          <t>64.8%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>17.8%</t>
+          <t>18.1%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>48.3%</t>
+          <t>60.0%</t>
         </is>
       </c>
     </row>
@@ -758,22 +758,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>110.9%</t>
+          <t>113.2%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>44.0%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.50</t>
+          <t>2.58</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>58.5%</t>
+          <t>58.6%</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -791,12 +791,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>40.3%</t>
+          <t>39.6%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>47.4%</t>
+          <t>47.2%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>10.7%</t>
+          <t>10.8%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -849,12 +849,12 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>92.9%</t>
+          <t>95.0%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>36.3%</t>
+          <t>36.0%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-8.3%</t>
+          <t>-8.4%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>173.6%</t>
+          <t>178.9%</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-75.7%</t>
+          <t>-75.9%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>107.7%</t>
+          <t>107.9%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.3%</t>
+          <t>52.2%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>123.0%</t>
+          <t>123.2%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>91.6%</t>
+          <t>91.7%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>21.9%</t>
+          <t>22.1%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-47.9%</t>
+          <t>-48.3%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1012,7 +1012,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>89.4%</t>
+          <t>89.5%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>420.8%</t>
+          <t>421.8%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-6.8%</t>
+          <t>-6.7%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-604.0%</t>
+          <t>-607.2%</t>
         </is>
       </c>
     </row>
@@ -1074,22 +1074,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>45.6%</t>
+          <t>43.5%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>59.9%</t>
+          <t>60.0%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.4%</t>
+          <t>57.3%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>63.0%</t>
+          <t>63.1%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>57.5%</t>
+          <t>57.6%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1140,7 +1140,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>-8.7%</t>
+          <t>-9.6%</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>14.4%</t>
+          <t>14.3%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-33.6%</t>
+          <t>-33.9%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>40.5%</t>
+          <t>38.3%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>50.1%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-4.2%</t>
+          <t>-4.0%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-56.0%</t>
+          <t>-63.9%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-2.7%</t>
+          <t>-3.4%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.3%</t>
+          <t>66.6%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>62.3%</t>
+          <t>62.7%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>73.4%</t>
+          <t>73.7%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.3%</t>
+          <t>10.2%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>3.8%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.2%</t>
+          <t>55.5%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>45.4%</t>
+          <t>44.9%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-399.9%</t>
+          <t>-373.9%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-97.9%</t>
+          <t>-100.8%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>57.1%</t>
+          <t>124.6%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>68.5%</t>
+          <t>57.9%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>82.5%</t>
+          <t>59.9%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1447,7 +1447,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.8%</t>
+          <t>14.2%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>48.1%</t>
+          <t>113.1%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>57.0%</t>
+          <t>48.3%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>2.3</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-15.5%</t>
+          <t>-17.1%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>36.7%</t>
+          <t>36.6%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>38.5%</t>
+          <t>118.4%</t>
         </is>
       </c>
     </row>
@@ -47775,22 +47775,22 @@
         <v>45472</v>
       </c>
       <c r="B2010" t="n">
-        <v>3.712897612343063</v>
+        <v>3.712897612343061</v>
       </c>
       <c r="C2010" t="n">
         <v>3.200497106215023</v>
       </c>
       <c r="D2010" t="n">
-        <v>-3.392100260732303</v>
+        <v>-3.445452894286067</v>
       </c>
       <c r="E2010" t="n">
-        <v>1.843300577608354</v>
+        <v>1.821959524186849</v>
       </c>
       <c r="F2010" t="n">
-        <v>0.6423788432672118</v>
+        <v>0.5915193896396682</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.585924412175351</v>
+        <v>3.555408739998825</v>
       </c>
     </row>
     <row r="2011">
@@ -47798,22 +47798,22 @@
         <v>45473</v>
       </c>
       <c r="B2011" t="n">
-        <v>3.754596135389346</v>
+        <v>3.754596135389344</v>
       </c>
       <c r="C2011" t="n">
         <v>3.213570513080942</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.500400922602422</v>
+        <v>-3.553753556156186</v>
       </c>
       <c r="E2011" t="n">
-        <v>1.813053719726225</v>
+        <v>1.791712666304719</v>
       </c>
       <c r="F2011" t="n">
-        <v>0.6423788432672118</v>
+        <v>0.5915193896396682</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.598997819041269</v>
+        <v>3.568482146864743</v>
       </c>
     </row>
     <row r="2012">
@@ -47827,16 +47827,16 @@
         <v>3.205575709863882</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.518204894323167</v>
+        <v>-3.57155752787693</v>
       </c>
       <c r="E2012" t="n">
-        <v>1.797937327820867</v>
+        <v>1.776596274399362</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.5718442203620107</v>
+        <v>0.5209847667344671</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.548682242081089</v>
+        <v>3.518166569904563</v>
       </c>
     </row>
     <row r="2013">
@@ -47850,16 +47850,16 @@
         <v>3.204099750990884</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.546105681432639</v>
+        <v>-3.599458314986403</v>
       </c>
       <c r="E2013" t="n">
-        <v>1.78530105410408</v>
+        <v>1.763960000682575</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.5372472962190759</v>
+        <v>0.4863878425915323</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.52644812872233</v>
+        <v>3.495932456545804</v>
       </c>
     </row>
     <row r="2014">
@@ -47873,16 +47873,16 @@
         <v>3.200864194968083</v>
       </c>
       <c r="D2014" t="n">
-        <v>-3.668631784135533</v>
+        <v>-3.721984417689297</v>
       </c>
       <c r="E2014" t="n">
-        <v>1.733055057000121</v>
+        <v>1.711714003578616</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.414721193516182</v>
+        <v>0.3638617398886385</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.449696911077792</v>
+        <v>3.419181238901266</v>
       </c>
     </row>
     <row r="2015">
@@ -47896,16 +47896,16 @@
         <v>3.267570154558586</v>
       </c>
       <c r="D2015" t="n">
-        <v>-3.899146280321122</v>
+        <v>-3.952498913874886</v>
       </c>
       <c r="E2015" t="n">
-        <v>1.70755521811639</v>
+        <v>1.686214164694884</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.1842066973305932</v>
+        <v>0.1333472437030497</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.378094172956942</v>
+        <v>3.347578500780417</v>
       </c>
     </row>
     <row r="2016">
@@ -47919,16 +47919,16 @@
         <v>3.407881873560433</v>
       </c>
       <c r="D2016" t="n">
-        <v>-4.247891365545565</v>
+        <v>-4.30124399909933</v>
       </c>
       <c r="E2016" t="n">
-        <v>1.708368903028459</v>
+        <v>1.687027849606954</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.07545874341169545</v>
+        <v>0.02459928978415193</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.453157119607451</v>
+        <v>3.422641447430925</v>
       </c>
     </row>
     <row r="2017">
@@ -47942,16 +47942,16 @@
         <v>3.476862142706073</v>
       </c>
       <c r="D2017" t="n">
-        <v>-4.401877783321706</v>
+        <v>-4.45523041687547</v>
       </c>
       <c r="E2017" t="n">
-        <v>1.715754605063643</v>
+        <v>1.694413551642137</v>
       </c>
       <c r="F2017" t="n">
-        <v>0.07545874341169545</v>
+        <v>0.02459928978415193</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.522137388753091</v>
+        <v>3.491621716576565</v>
       </c>
     </row>
     <row r="2018">
@@ -47965,16 +47965,16 @@
         <v>3.462913344826194</v>
       </c>
       <c r="D2018" t="n">
-        <v>-4.606477218184715</v>
+        <v>-4.659829851738479</v>
       </c>
       <c r="E2018" t="n">
-        <v>1.61996603323856</v>
+        <v>1.598624979817055</v>
       </c>
       <c r="F2018" t="n">
-        <v>0.07545874341169545</v>
+        <v>0.02459928978415193</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.508188590873212</v>
+        <v>3.477672918696685</v>
       </c>
     </row>
     <row r="2019">
@@ -47988,16 +47988,16 @@
         <v>3.474783833881608</v>
       </c>
       <c r="D2019" t="n">
-        <v>-4.858952372192439</v>
+        <v>-4.912305005746203</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.530846460690884</v>
+        <v>1.509505407269379</v>
       </c>
       <c r="F2019" t="n">
-        <v>0.07545874341169545</v>
+        <v>0.02459928978415193</v>
       </c>
       <c r="G2019" t="n">
-        <v>3.520059079928626</v>
+        <v>3.489543407752099</v>
       </c>
     </row>
     <row r="2020">
@@ -48011,16 +48011,16 @@
         <v>3.475994368400552</v>
       </c>
       <c r="D2020" t="n">
-        <v>-5.151848128671851</v>
+        <v>-5.205200762225616</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.414898692618063</v>
+        <v>1.393557639196558</v>
       </c>
       <c r="F2020" t="n">
-        <v>0.07545874341169545</v>
+        <v>0.02459928978415193</v>
       </c>
       <c r="G2020" t="n">
-        <v>3.521269614447569</v>
+        <v>3.490753942271043</v>
       </c>
     </row>
     <row r="2021">
@@ -48034,16 +48034,16 @@
         <v>3.480116110627873</v>
       </c>
       <c r="D2021" t="n">
-        <v>-5.338512256806659</v>
+        <v>-5.391864890360424</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.344354783591462</v>
+        <v>1.323013730169956</v>
       </c>
       <c r="F2021" t="n">
-        <v>0.04871977258713556</v>
+        <v>-0.002139681040407959</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.509347974180155</v>
+        <v>3.478832302003629</v>
       </c>
     </row>
     <row r="2022">
@@ -48057,16 +48057,16 @@
         <v>3.475193963364063</v>
       </c>
       <c r="D2022" t="n">
-        <v>-5.484532943720621</v>
+        <v>-5.537885577274386</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.281024361562066</v>
+        <v>1.259683308140561</v>
       </c>
       <c r="F2022" t="n">
-        <v>0.03963668079327859</v>
+        <v>-0.01122277283426493</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.49897597184003</v>
+        <v>3.468460299663504</v>
       </c>
     </row>
     <row r="2023">
@@ -48080,16 +48080,16 @@
         <v>3.637398020063107</v>
       </c>
       <c r="D2023" t="n">
-        <v>-5.576246952830207</v>
+        <v>-5.629599586383971</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.406542814617276</v>
+        <v>1.38520176119577</v>
       </c>
       <c r="F2023" t="n">
-        <v>0.03963668079327859</v>
+        <v>-0.01122277283426493</v>
       </c>
       <c r="G2023" t="n">
-        <v>3.661180028539074</v>
+        <v>3.630664356362548</v>
       </c>
     </row>
     <row r="2024">
@@ -48103,16 +48103,16 @@
         <v>3.632244658026921</v>
       </c>
       <c r="D2024" t="n">
-        <v>-5.607898611890176</v>
+        <v>-5.661251245443941</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.388728788957102</v>
+        <v>1.367387735535597</v>
       </c>
       <c r="F2024" t="n">
-        <v>0.03446822354883838</v>
+        <v>-0.01639123007870513</v>
       </c>
       <c r="G2024" t="n">
-        <v>3.652925592156224</v>
+        <v>3.622409919979698</v>
       </c>
     </row>
     <row r="2025">
@@ -48126,16 +48126,16 @@
         <v>3.642474075595412</v>
       </c>
       <c r="D2025" t="n">
-        <v>-5.676964666463113</v>
+        <v>-5.730317300016877</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.371331784696419</v>
+        <v>1.349990731274913</v>
       </c>
       <c r="F2025" t="n">
-        <v>-0.02790265394477165</v>
+        <v>-0.07876210757231517</v>
       </c>
       <c r="G2025" t="n">
-        <v>3.625732483228549</v>
+        <v>3.595216811052024</v>
       </c>
     </row>
     <row r="2026">
@@ -48143,22 +48143,22 @@
         <v>45488</v>
       </c>
       <c r="B2026" t="n">
-        <v>3.783632867332688</v>
+        <v>3.783632867332687</v>
       </c>
       <c r="C2026" t="n">
         <v>3.651399714051315</v>
       </c>
       <c r="D2026" t="n">
-        <v>-5.778940788711521</v>
+        <v>-5.832293422265285</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.339466974252959</v>
+        <v>1.318125920831453</v>
       </c>
       <c r="F2026" t="n">
-        <v>-0.1298787761931792</v>
+        <v>-0.1807382298207227</v>
       </c>
       <c r="G2026" t="n">
-        <v>3.573472448335407</v>
+        <v>3.542956776158881</v>
       </c>
     </row>
     <row r="2027">
@@ -48166,22 +48166,22 @@
         <v>45489</v>
       </c>
       <c r="B2027" t="n">
-        <v>3.798296784231805</v>
+        <v>3.798296784231803</v>
       </c>
       <c r="C2027" t="n">
         <v>3.64355260129549</v>
       </c>
       <c r="D2027" t="n">
-        <v>-5.668934505234299</v>
+        <v>-5.722287138788063</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.375622374888022</v>
+        <v>1.354281321466517</v>
       </c>
       <c r="F2027" t="n">
-        <v>-0.106674204275904</v>
+        <v>-0.1575336579034475</v>
       </c>
       <c r="G2027" t="n">
-        <v>3.579548078729948</v>
+        <v>3.549032406553422</v>
       </c>
     </row>
     <row r="2028">
@@ -48195,16 +48195,16 @@
         <v>3.647802612017464</v>
       </c>
       <c r="D2028" t="n">
-        <v>-5.525874929493373</v>
+        <v>-5.579227563047137</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.437096215906367</v>
+        <v>1.415755162484861</v>
       </c>
       <c r="F2028" t="n">
-        <v>-0.09866077768592474</v>
+        <v>-0.1495202313134683</v>
       </c>
       <c r="G2028" t="n">
-        <v>3.588606145405909</v>
+        <v>3.558090473229384</v>
       </c>
     </row>
     <row r="2029">
@@ -48218,16 +48218,16 @@
         <v>3.6550634949</v>
       </c>
       <c r="D2029" t="n">
-        <v>-5.224428204021535</v>
+        <v>-5.2777808375753</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.564935788977638</v>
+        <v>1.543594735556133</v>
       </c>
       <c r="F2029" t="n">
-        <v>0.2027859477859125</v>
+        <v>0.151926494158369</v>
       </c>
       <c r="G2029" t="n">
-        <v>3.776735063571548</v>
+        <v>3.746219391395022</v>
       </c>
     </row>
     <row r="2030">
@@ -48241,16 +48241,16 @@
         <v>3.656034672652711</v>
       </c>
       <c r="D2030" t="n">
-        <v>-5.249018448256719</v>
+        <v>-5.302371081810484</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.556070869036275</v>
+        <v>1.53472981561477</v>
       </c>
       <c r="F2030" t="n">
-        <v>0.2027859477859125</v>
+        <v>0.151926494158369</v>
       </c>
       <c r="G2030" t="n">
-        <v>3.777706241324259</v>
+        <v>3.747190569147733</v>
       </c>
     </row>
     <row r="2031">
@@ -48264,16 +48264,16 @@
         <v>3.656877577032466</v>
       </c>
       <c r="D2031" t="n">
-        <v>-5.197980072250199</v>
+        <v>-5.251332705803963</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.577329123818639</v>
+        <v>1.555988070397133</v>
       </c>
       <c r="F2031" t="n">
-        <v>0.2027859477859125</v>
+        <v>0.151926494158369</v>
       </c>
       <c r="G2031" t="n">
-        <v>3.778549145704014</v>
+        <v>3.748033473527488</v>
       </c>
     </row>
     <row r="2032">
@@ -48287,16 +48287,16 @@
         <v>3.675915675906612</v>
       </c>
       <c r="D2032" t="n">
-        <v>-5.169131395426739</v>
+        <v>-5.222484028980503</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.607906693422168</v>
+        <v>1.586565640000662</v>
       </c>
       <c r="F2032" t="n">
-        <v>0.2316346246093728</v>
+        <v>0.1807751709818293</v>
       </c>
       <c r="G2032" t="n">
-        <v>3.814896450672236</v>
+        <v>3.78438077849571</v>
       </c>
     </row>
     <row r="2033">
@@ -48310,16 +48310,16 @@
         <v>3.492099672030546</v>
       </c>
       <c r="D2033" t="n">
-        <v>-5.072496483408099</v>
+        <v>-5.125849116961863</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.462744654353559</v>
+        <v>1.441403600932053</v>
       </c>
       <c r="F2033" t="n">
-        <v>0.3282695366280127</v>
+        <v>0.2774100830004692</v>
       </c>
       <c r="G2033" t="n">
-        <v>3.689061394007354</v>
+        <v>3.658545721830828</v>
       </c>
     </row>
     <row r="2034">
@@ -48333,16 +48333,16 @@
         <v>3.495601716104511</v>
       </c>
       <c r="D2034" t="n">
-        <v>-5.003458472459631</v>
+        <v>-5.056811106013395</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.49386190280691</v>
+        <v>1.472520849385405</v>
       </c>
       <c r="F2034" t="n">
-        <v>0.3973075475764808</v>
+        <v>0.3464480939489373</v>
       </c>
       <c r="G2034" t="n">
-        <v>3.733986244650399</v>
+        <v>3.703470572473873</v>
       </c>
     </row>
     <row r="2035">
@@ -48350,22 +48350,22 @@
         <v>45497</v>
       </c>
       <c r="B2035" t="n">
-        <v>3.775028860833455</v>
+        <v>3.775028860833454</v>
       </c>
       <c r="C2035" t="n">
         <v>3.480028535180593</v>
       </c>
       <c r="D2035" t="n">
-        <v>-4.984671372090692</v>
+        <v>-5.038024005644457</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.485803562030568</v>
+        <v>1.464462508609063</v>
       </c>
       <c r="F2035" t="n">
-        <v>0.4160946479454193</v>
+        <v>0.3652351943178758</v>
       </c>
       <c r="G2035" t="n">
-        <v>3.729685323947845</v>
+        <v>3.699169651771319</v>
       </c>
     </row>
     <row r="2036">
@@ -48379,16 +48379,16 @@
         <v>3.479216245617023</v>
       </c>
       <c r="D2036" t="n">
-        <v>-4.907572770548819</v>
+        <v>-5.078228649799133</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.515830713083747</v>
+        <v>1.447568361383622</v>
       </c>
       <c r="F2036" t="n">
-        <v>0.4160946479454193</v>
+        <v>0.3652351943178758</v>
       </c>
       <c r="G2036" t="n">
-        <v>3.728873034384275</v>
+        <v>3.698357362207748</v>
       </c>
     </row>
     <row r="2037">
@@ -48402,16 +48402,16 @@
         <v>3.489085024742095</v>
       </c>
       <c r="D2037" t="n">
-        <v>-4.917957965438709</v>
+        <v>-5.088613844689022</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.521545414252864</v>
+        <v>1.453283062552738</v>
       </c>
       <c r="F2037" t="n">
-        <v>0.40570945305553</v>
+        <v>0.3548499994279865</v>
       </c>
       <c r="G2037" t="n">
-        <v>3.732510696575413</v>
+        <v>3.701995024398888</v>
       </c>
     </row>
     <row r="2038">
@@ -48425,16 +48425,16 @@
         <v>3.55992203051852</v>
       </c>
       <c r="D2038" t="n">
-        <v>-4.936546124160934</v>
+        <v>-5.107202003411247</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.584947156540399</v>
+        <v>1.516684804840274</v>
       </c>
       <c r="F2038" t="n">
-        <v>0.3871212943333046</v>
+        <v>0.3362618407057611</v>
       </c>
       <c r="G2038" t="n">
-        <v>3.792194807118503</v>
+        <v>3.761679134941977</v>
       </c>
     </row>
     <row r="2039">
@@ -48448,16 +48448,16 @@
         <v>3.556791041336819</v>
       </c>
       <c r="D2039" t="n">
-        <v>-4.93684467085697</v>
+        <v>-5.107500550107283</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.581696748680283</v>
+        <v>1.513434396980158</v>
       </c>
       <c r="F2039" t="n">
-        <v>0.3868227476372687</v>
+        <v>0.3359632940097252</v>
       </c>
       <c r="G2039" t="n">
-        <v>3.78888468991918</v>
+        <v>3.758369017742654</v>
       </c>
     </row>
     <row r="2040">
@@ -48471,16 +48471,16 @@
         <v>3.56132193627621</v>
       </c>
       <c r="D2040" t="n">
-        <v>-4.836021537166542</v>
+        <v>-5.006677416416855</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.626556897095845</v>
+        <v>1.55829454539572</v>
       </c>
       <c r="F2040" t="n">
-        <v>0.3992869631216225</v>
+        <v>0.348427509494079</v>
       </c>
       <c r="G2040" t="n">
-        <v>3.800894114149184</v>
+        <v>3.770378441972658</v>
       </c>
     </row>
     <row r="2041">
@@ -48488,22 +48488,22 @@
         <v>45503</v>
       </c>
       <c r="B2041" t="n">
-        <v>3.807356168121463</v>
+        <v>3.807356168121461</v>
       </c>
       <c r="C2041" t="n">
         <v>3.561451189754754</v>
       </c>
       <c r="D2041" t="n">
-        <v>-4.645240176414134</v>
+        <v>-4.815896055664448</v>
       </c>
       <c r="E2041" t="n">
-        <v>1.702998694875352</v>
+        <v>1.634736343175227</v>
       </c>
       <c r="F2041" t="n">
-        <v>0.5900683238740299</v>
+        <v>0.5392088702464863</v>
       </c>
       <c r="G2041" t="n">
-        <v>3.915492184079172</v>
+        <v>3.884976511902646</v>
       </c>
     </row>
     <row r="2042">
@@ -48511,22 +48511,22 @@
         <v>45504</v>
       </c>
       <c r="B2042" t="n">
-        <v>3.775233033906076</v>
+        <v>3.775233033906074</v>
       </c>
       <c r="C2042" t="n">
         <v>3.54128803549235</v>
       </c>
       <c r="D2042" t="n">
-        <v>-4.538276818564713</v>
+        <v>-4.708932697815026</v>
       </c>
       <c r="E2042" t="n">
-        <v>1.725620883752717</v>
+        <v>1.657358532052592</v>
       </c>
       <c r="F2042" t="n">
-        <v>0.6485329318338313</v>
+        <v>0.5976734782062878</v>
       </c>
       <c r="G2042" t="n">
-        <v>3.930407794592649</v>
+        <v>3.899892122416123</v>
       </c>
     </row>
     <row r="2043">
@@ -48534,22 +48534,22 @@
         <v>45505</v>
       </c>
       <c r="B2043" t="n">
-        <v>3.785761685912981</v>
+        <v>3.78576168591298</v>
       </c>
       <c r="C2043" t="n">
         <v>3.576254972104409</v>
       </c>
       <c r="D2043" t="n">
-        <v>-4.48294623066295</v>
+        <v>-4.653602109913264</v>
       </c>
       <c r="E2043" t="n">
-        <v>1.782720055525481</v>
+        <v>1.714457703825355</v>
       </c>
       <c r="F2043" t="n">
-        <v>0.7038635197355935</v>
+        <v>0.65300406610805</v>
       </c>
       <c r="G2043" t="n">
-        <v>3.998573083945764</v>
+        <v>3.968057411769239</v>
       </c>
     </row>
     <row r="2044">
@@ -48557,22 +48557,22 @@
         <v>45506</v>
       </c>
       <c r="B2044" t="n">
-        <v>3.74376795653989</v>
+        <v>3.743767956539889</v>
       </c>
       <c r="C2044" t="n">
         <v>3.569941540005846</v>
       </c>
       <c r="D2044" t="n">
-        <v>-4.470892103749987</v>
+        <v>-4.641547983000301</v>
       </c>
       <c r="E2044" t="n">
-        <v>1.781228274192103</v>
+        <v>1.712965922491978</v>
       </c>
       <c r="F2044" t="n">
-        <v>0.7159176466485563</v>
+        <v>0.6650581930210128</v>
       </c>
       <c r="G2044" t="n">
-        <v>3.99949212799498</v>
+        <v>3.968976455818455</v>
       </c>
     </row>
     <row r="2045">
@@ -48580,22 +48580,22 @@
         <v>45507</v>
       </c>
       <c r="B2045" t="n">
-        <v>3.725010844811005</v>
+        <v>3.725010844811004</v>
       </c>
       <c r="C2045" t="n">
         <v>3.571822170189982</v>
       </c>
       <c r="D2045" t="n">
-        <v>-4.512047223318208</v>
+        <v>-4.682703102568522</v>
       </c>
       <c r="E2045" t="n">
-        <v>1.766646856548951</v>
+        <v>1.698384504848826</v>
       </c>
       <c r="F2045" t="n">
-        <v>0.6747625270803354</v>
+        <v>0.6239030734527918</v>
       </c>
       <c r="G2045" t="n">
-        <v>3.976679686438183</v>
+        <v>3.946164014261657</v>
       </c>
     </row>
     <row r="2046">
@@ -48603,22 +48603,22 @@
         <v>45508</v>
       </c>
       <c r="B2046" t="n">
-        <v>3.612322444382916</v>
+        <v>3.612322444382914</v>
       </c>
       <c r="C2046" t="n">
         <v>3.584673196067865</v>
       </c>
       <c r="D2046" t="n">
-        <v>-4.443998660626678</v>
+        <v>-4.614654539876992</v>
       </c>
       <c r="E2046" t="n">
-        <v>1.806717307503445</v>
+        <v>1.73845495580332</v>
       </c>
       <c r="F2046" t="n">
-        <v>0.7428110897718652</v>
+        <v>0.6919516361443216</v>
       </c>
       <c r="G2046" t="n">
-        <v>4.030359849930984</v>
+        <v>3.999844177754458</v>
       </c>
     </row>
     <row r="2047">
@@ -48626,22 +48626,22 @@
         <v>45509</v>
       </c>
       <c r="B2047" t="n">
-        <v>3.645256780013423</v>
+        <v>3.645256780013421</v>
       </c>
       <c r="C2047" t="n">
         <v>3.604875866241459</v>
       </c>
       <c r="D2047" t="n">
-        <v>-4.675599053796179</v>
+        <v>-4.846254933046493</v>
       </c>
       <c r="E2047" t="n">
-        <v>1.734279820409239</v>
+        <v>1.666017468709114</v>
       </c>
       <c r="F2047" t="n">
-        <v>0.7428110897718652</v>
+        <v>0.6919516361443216</v>
       </c>
       <c r="G2047" t="n">
-        <v>4.050562520104578</v>
+        <v>4.020046847928052</v>
       </c>
     </row>
     <row r="2048">
@@ -48649,22 +48649,22 @@
         <v>45510</v>
       </c>
       <c r="B2048" t="n">
-        <v>3.666747201498965</v>
+        <v>3.666747201498966</v>
       </c>
       <c r="C2048" t="n">
         <v>3.588482102308341</v>
       </c>
       <c r="D2048" t="n">
-        <v>-4.725650599325398</v>
+        <v>-4.896306478575712</v>
       </c>
       <c r="E2048" t="n">
-        <v>1.697865438264434</v>
+        <v>1.629603086564308</v>
       </c>
       <c r="F2048" t="n">
-        <v>0.7428110897718652</v>
+        <v>0.6919516361443216</v>
       </c>
       <c r="G2048" t="n">
-        <v>4.03416875617146</v>
+        <v>4.003653083994934</v>
       </c>
     </row>
     <row r="2049">
@@ -48672,22 +48672,22 @@
         <v>45511</v>
       </c>
       <c r="B2049" t="n">
-        <v>3.670048702800094</v>
+        <v>3.670048702800095</v>
       </c>
       <c r="C2049" t="n">
         <v>3.548734015901807</v>
       </c>
       <c r="D2049" t="n">
-        <v>-4.900757431901843</v>
+        <v>-5.071413311152156</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.588074618827322</v>
+        <v>1.519812267127197</v>
       </c>
       <c r="F2049" t="n">
-        <v>0.7428110897718652</v>
+        <v>0.6919516361443216</v>
       </c>
       <c r="G2049" t="n">
-        <v>3.994420669764927</v>
+        <v>3.963904997588401</v>
       </c>
     </row>
     <row r="2050">
@@ -48701,16 +48701,16 @@
         <v>3.555756634898747</v>
       </c>
       <c r="D2050" t="n">
-        <v>-4.70465727847132</v>
+        <v>-4.875313157721633</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.673537299196472</v>
+        <v>1.605274947496346</v>
       </c>
       <c r="F2050" t="n">
-        <v>0.9389112432023881</v>
+        <v>0.8880517895748445</v>
       </c>
       <c r="G2050" t="n">
-        <v>4.119103380820181</v>
+        <v>4.088587708643654</v>
       </c>
     </row>
     <row r="2051">
@@ -48718,22 +48718,22 @@
         <v>45513</v>
       </c>
       <c r="B2051" t="n">
-        <v>3.730570473395083</v>
+        <v>3.730570473395085</v>
       </c>
       <c r="C2051" t="n">
         <v>3.654927634471652</v>
       </c>
       <c r="D2051" t="n">
-        <v>-4.551631886358035</v>
+        <v>-4.722287765608349</v>
       </c>
       <c r="E2051" t="n">
-        <v>1.83391845561469</v>
+        <v>1.765656103914564</v>
       </c>
       <c r="F2051" t="n">
-        <v>1.091936635315672</v>
+        <v>1.041077181688129</v>
       </c>
       <c r="G2051" t="n">
-        <v>4.310089615661055</v>
+        <v>4.27957394348453</v>
       </c>
     </row>
     <row r="2052">
@@ -48741,22 +48741,22 @@
         <v>45514</v>
       </c>
       <c r="B2052" t="n">
-        <v>3.741278332791145</v>
+        <v>3.741278332791147</v>
       </c>
       <c r="C2052" t="n">
         <v>3.842393859379944</v>
       </c>
       <c r="D2052" t="n">
-        <v>-4.579939200231306</v>
+        <v>-4.750595079481619</v>
       </c>
       <c r="E2052" t="n">
-        <v>2.010061754973674</v>
+        <v>1.941799403273549</v>
       </c>
       <c r="F2052" t="n">
-        <v>1.091936635315672</v>
+        <v>1.041077181688129</v>
       </c>
       <c r="G2052" t="n">
-        <v>4.497555840569348</v>
+        <v>4.467040168392822</v>
       </c>
     </row>
     <row r="2053">
@@ -48764,22 +48764,22 @@
         <v>45515</v>
       </c>
       <c r="B2053" t="n">
-        <v>3.699115615620431</v>
+        <v>3.699115615620433</v>
       </c>
       <c r="C2053" t="n">
         <v>3.811796810734027</v>
       </c>
       <c r="D2053" t="n">
-        <v>-4.746532425344828</v>
+        <v>-4.917188304595141</v>
       </c>
       <c r="E2053" t="n">
-        <v>1.912827416282348</v>
+        <v>1.844565064582223</v>
       </c>
       <c r="F2053" t="n">
-        <v>0.9253434102021496</v>
+        <v>0.8744839565746061</v>
       </c>
       <c r="G2053" t="n">
-        <v>4.367002856855317</v>
+        <v>4.336487184678791</v>
       </c>
     </row>
     <row r="2054">
@@ -48787,22 +48787,22 @@
         <v>45516</v>
       </c>
       <c r="B2054" t="n">
-        <v>3.708182519285644</v>
+        <v>3.708182519285645</v>
       </c>
       <c r="C2054" t="n">
         <v>3.815473213395745</v>
       </c>
       <c r="D2054" t="n">
-        <v>-4.723496631983262</v>
+        <v>-4.894152511233576</v>
       </c>
       <c r="E2054" t="n">
-        <v>1.925718136288692</v>
+        <v>1.857455784588567</v>
       </c>
       <c r="F2054" t="n">
-        <v>0.9253434102021496</v>
+        <v>0.8744839565746061</v>
       </c>
       <c r="G2054" t="n">
-        <v>4.370679259517035</v>
+        <v>4.340163587340509</v>
       </c>
     </row>
     <row r="2055">
@@ -48810,22 +48810,22 @@
         <v>45517</v>
       </c>
       <c r="B2055" t="n">
-        <v>3.740581401399465</v>
+        <v>3.740581401399467</v>
       </c>
       <c r="C2055" t="n">
         <v>3.81309126851924</v>
       </c>
       <c r="D2055" t="n">
-        <v>-4.694250651527565</v>
+        <v>-4.864906530777879</v>
       </c>
       <c r="E2055" t="n">
-        <v>1.935034583594466</v>
+        <v>1.866772231894341</v>
       </c>
       <c r="F2055" t="n">
-        <v>0.9253434102021496</v>
+        <v>0.8744839565746061</v>
       </c>
       <c r="G2055" t="n">
-        <v>4.368297314640531</v>
+        <v>4.337781642464004</v>
       </c>
     </row>
     <row r="2056">
@@ -48833,22 +48833,22 @@
         <v>45518</v>
       </c>
       <c r="B2056" t="n">
-        <v>3.699404642256367</v>
+        <v>3.699404642256368</v>
       </c>
       <c r="C2056" t="n">
         <v>3.810384507676875</v>
       </c>
       <c r="D2056" t="n">
-        <v>-4.801176199405417</v>
+        <v>-4.97183207865573</v>
       </c>
       <c r="E2056" t="n">
-        <v>1.889557603600961</v>
+        <v>1.821295251900835</v>
       </c>
       <c r="F2056" t="n">
-        <v>0.8184178623242983</v>
+        <v>0.7675584086967547</v>
       </c>
       <c r="G2056" t="n">
-        <v>4.301435225071454</v>
+        <v>4.270919552894928</v>
       </c>
     </row>
     <row r="2057">
@@ -48856,22 +48856,22 @@
         <v>45519</v>
       </c>
       <c r="B2057" t="n">
-        <v>3.689942600700996</v>
+        <v>3.689942600700998</v>
       </c>
       <c r="C2057" t="n">
         <v>3.811813309820109</v>
       </c>
       <c r="D2057" t="n">
-        <v>-4.946194757912665</v>
+        <v>-5.116850637162979</v>
       </c>
       <c r="E2057" t="n">
-        <v>1.832978982341295</v>
+        <v>1.76471663064117</v>
       </c>
       <c r="F2057" t="n">
-        <v>0.6733993038170497</v>
+        <v>0.6225398501895062</v>
       </c>
       <c r="G2057" t="n">
-        <v>4.215852892110339</v>
+        <v>4.185337219933813</v>
       </c>
     </row>
     <row r="2058">
@@ -48879,22 +48879,22 @@
         <v>45520</v>
       </c>
       <c r="B2058" t="n">
-        <v>3.711852429687008</v>
+        <v>3.71185242968701</v>
       </c>
       <c r="C2058" t="n">
         <v>3.911744549077862</v>
       </c>
       <c r="D2058" t="n">
-        <v>-5.064536523697383</v>
+        <v>-5.235192402947696</v>
       </c>
       <c r="E2058" t="n">
-        <v>1.885573515285161</v>
+        <v>1.817311163585036</v>
       </c>
       <c r="F2058" t="n">
-        <v>0.6840853423799398</v>
+        <v>0.6332258887523963</v>
       </c>
       <c r="G2058" t="n">
-        <v>4.322195754505826</v>
+        <v>4.2916800823293</v>
       </c>
     </row>
     <row r="2059">
@@ -48902,22 +48902,22 @@
         <v>45521</v>
       </c>
       <c r="B2059" t="n">
-        <v>3.714879051790798</v>
+        <v>3.7148790517908</v>
       </c>
       <c r="C2059" t="n">
         <v>3.909530246203802</v>
       </c>
       <c r="D2059" t="n">
-        <v>-5.115946946018091</v>
+        <v>-5.286602825268404</v>
       </c>
       <c r="E2059" t="n">
-        <v>1.862795043482817</v>
+        <v>1.794532691782692</v>
       </c>
       <c r="F2059" t="n">
-        <v>0.6840853423799398</v>
+        <v>0.6332258887523963</v>
       </c>
       <c r="G2059" t="n">
-        <v>4.319981451631766</v>
+        <v>4.28946577945524</v>
       </c>
     </row>
     <row r="2060">
@@ -48925,22 +48925,22 @@
         <v>45522</v>
       </c>
       <c r="B2060" t="n">
-        <v>3.704757949437326</v>
+        <v>3.704757949437328</v>
       </c>
       <c r="C2060" t="n">
         <v>3.909433374278091</v>
       </c>
       <c r="D2060" t="n">
-        <v>-5.195366397225842</v>
+        <v>-5.366022276476156</v>
       </c>
       <c r="E2060" t="n">
-        <v>1.830930391074006</v>
+        <v>1.76266803937388</v>
       </c>
       <c r="F2060" t="n">
-        <v>0.6840853423799398</v>
+        <v>0.6332258887523963</v>
       </c>
       <c r="G2060" t="n">
-        <v>4.319884579706055</v>
+        <v>4.289368907529528</v>
       </c>
     </row>
     <row r="2061">
@@ -48954,16 +48954,16 @@
         <v>3.909427267836134</v>
       </c>
       <c r="D2061" t="n">
-        <v>-5.29082939514306</v>
+        <v>-5.461485274393374</v>
       </c>
       <c r="E2061" t="n">
-        <v>1.792739085465162</v>
+        <v>1.724476733765036</v>
       </c>
       <c r="F2061" t="n">
-        <v>0.6840853423799398</v>
+        <v>0.6332258887523963</v>
       </c>
       <c r="G2061" t="n">
-        <v>4.319878473264098</v>
+        <v>4.289362801087572</v>
       </c>
     </row>
     <row r="2062">
@@ -48977,16 +48977,16 @@
         <v>3.907523664398744</v>
       </c>
       <c r="D2062" t="n">
-        <v>-5.226453484292345</v>
+        <v>-5.397109363542659</v>
       </c>
       <c r="E2062" t="n">
-        <v>1.816585846368058</v>
+        <v>1.748323494667933</v>
       </c>
       <c r="F2062" t="n">
-        <v>0.7484612532306549</v>
+        <v>0.6976017996031114</v>
       </c>
       <c r="G2062" t="n">
-        <v>4.356600416337137</v>
+        <v>4.326084744160611</v>
       </c>
     </row>
     <row r="2063">
@@ -49000,16 +49000,16 @@
         <v>3.913257482146471</v>
       </c>
       <c r="D2063" t="n">
-        <v>-5.281822646424539</v>
+        <v>-5.452478525674852</v>
       </c>
       <c r="E2063" t="n">
-        <v>1.800171999262907</v>
+        <v>1.731909647562782</v>
       </c>
       <c r="F2063" t="n">
-        <v>0.7484612532306549</v>
+        <v>0.6976017996031114</v>
       </c>
       <c r="G2063" t="n">
-        <v>4.362334234084864</v>
+        <v>4.331818561908338</v>
       </c>
     </row>
     <row r="2064">
@@ -49023,16 +49023,16 @@
         <v>3.912795845489403</v>
       </c>
       <c r="D2064" t="n">
-        <v>-5.300041113422147</v>
+        <v>-5.470696992672461</v>
       </c>
       <c r="E2064" t="n">
-        <v>1.792422975806796</v>
+        <v>1.724160624106671</v>
       </c>
       <c r="F2064" t="n">
-        <v>0.7233548159748128</v>
+        <v>0.6724953623472693</v>
       </c>
       <c r="G2064" t="n">
-        <v>4.346808735074291</v>
+        <v>4.316293062897765</v>
       </c>
     </row>
     <row r="2065">
@@ -49046,16 +49046,16 @@
         <v>3.932670238339722</v>
       </c>
       <c r="D2065" t="n">
-        <v>-5.211834279274569</v>
+        <v>-5.382490158524883</v>
       </c>
       <c r="E2065" t="n">
-        <v>1.847580102316146</v>
+        <v>1.779317750616021</v>
       </c>
       <c r="F2065" t="n">
-        <v>0.7233548159748128</v>
+        <v>0.6724953623472693</v>
       </c>
       <c r="G2065" t="n">
-        <v>4.36668312792461</v>
+        <v>4.336167455748084</v>
       </c>
     </row>
     <row r="2066">
@@ -49063,22 +49063,22 @@
         <v>45528</v>
       </c>
       <c r="B2066" t="n">
-        <v>3.794486844016435</v>
+        <v>3.794486844016437</v>
       </c>
       <c r="C2066" t="n">
         <v>3.91637093886445</v>
       </c>
       <c r="D2066" t="n">
-        <v>-5.10579928406926</v>
+        <v>-5.276455163319573</v>
       </c>
       <c r="E2066" t="n">
-        <v>1.873694800922998</v>
+        <v>1.805432449222872</v>
       </c>
       <c r="F2066" t="n">
-        <v>0.7233548159748128</v>
+        <v>0.6724953623472693</v>
       </c>
       <c r="G2066" t="n">
-        <v>4.350383828449337</v>
+        <v>4.319868156272812</v>
       </c>
     </row>
     <row r="2067">
@@ -49086,22 +49086,22 @@
         <v>45529</v>
       </c>
       <c r="B2067" t="n">
-        <v>3.794705093307666</v>
+        <v>3.794705093307669</v>
       </c>
       <c r="C2067" t="n">
         <v>3.918801888328495</v>
       </c>
       <c r="D2067" t="n">
-        <v>-4.922587620936165</v>
+        <v>-5.093243500186478</v>
       </c>
       <c r="E2067" t="n">
-        <v>1.949410415640282</v>
+        <v>1.881148063940156</v>
       </c>
       <c r="F2067" t="n">
-        <v>0.7233548159748128</v>
+        <v>0.6724953623472693</v>
       </c>
       <c r="G2067" t="n">
-        <v>4.352814777913383</v>
+        <v>4.322299105736858</v>
       </c>
     </row>
     <row r="2068">
@@ -49109,22 +49109,22 @@
         <v>45530</v>
       </c>
       <c r="B2068" t="n">
-        <v>3.776846557863547</v>
+        <v>3.77684655786355</v>
       </c>
       <c r="C2068" t="n">
         <v>3.901746294407872</v>
       </c>
       <c r="D2068" t="n">
-        <v>-4.850866173922314</v>
+        <v>-5.021522053172627</v>
       </c>
       <c r="E2068" t="n">
-        <v>1.961043400525199</v>
+        <v>1.892781048825074</v>
       </c>
       <c r="F2068" t="n">
-        <v>0.7950762629886634</v>
+        <v>0.7442168093611199</v>
       </c>
       <c r="G2068" t="n">
-        <v>4.378792052201071</v>
+        <v>4.348276380024545</v>
       </c>
     </row>
     <row r="2069">
@@ -49132,22 +49132,22 @@
         <v>45531</v>
       </c>
       <c r="B2069" t="n">
-        <v>3.723789705394108</v>
+        <v>3.72378970539411</v>
       </c>
       <c r="C2069" t="n">
         <v>3.848662040329044</v>
       </c>
       <c r="D2069" t="n">
-        <v>-4.828493148314608</v>
+        <v>-4.999149027564921</v>
       </c>
       <c r="E2069" t="n">
-        <v>1.916908356689453</v>
+        <v>1.848646004989328</v>
       </c>
       <c r="F2069" t="n">
-        <v>0.806332014101565</v>
+        <v>0.7554725604740214</v>
       </c>
       <c r="G2069" t="n">
-        <v>4.332461248789984</v>
+        <v>4.301945576613457</v>
       </c>
     </row>
     <row r="2070">
@@ -49155,22 +49155,22 @@
         <v>45532</v>
       </c>
       <c r="B2070" t="n">
-        <v>3.715607446456724</v>
+        <v>3.715607446456727</v>
       </c>
       <c r="C2070" t="n">
         <v>4.0338602452144</v>
       </c>
       <c r="D2070" t="n">
-        <v>-4.861509444225352</v>
+        <v>-5.032165323475666</v>
       </c>
       <c r="E2070" t="n">
-        <v>2.08890004321051</v>
+        <v>2.020637691510385</v>
       </c>
       <c r="F2070" t="n">
-        <v>0.7368946374348133</v>
+        <v>0.6860351838072698</v>
       </c>
       <c r="G2070" t="n">
-        <v>4.475997027675288</v>
+        <v>4.445481355498762</v>
       </c>
     </row>
     <row r="2071">
@@ -49178,22 +49178,22 @@
         <v>45533</v>
       </c>
       <c r="B2071" t="n">
-        <v>3.713762536883673</v>
+        <v>3.713762536883674</v>
       </c>
       <c r="C2071" t="n">
         <v>4.025781471042649</v>
       </c>
       <c r="D2071" t="n">
-        <v>-4.849981808575744</v>
+        <v>-5.020637687826057</v>
       </c>
       <c r="E2071" t="n">
-        <v>2.085432323298603</v>
+        <v>2.017169971598478</v>
       </c>
       <c r="F2071" t="n">
-        <v>0.7958952956361758</v>
+        <v>0.7450358420086323</v>
       </c>
       <c r="G2071" t="n">
-        <v>4.503318648424354</v>
+        <v>4.472802976247828</v>
       </c>
     </row>
     <row r="2072">
@@ -49204,19 +49204,19 @@
         <v>3.717150699236294</v>
       </c>
       <c r="C2072" t="n">
-        <v>4.101138160843282</v>
+        <v>4.029449583564437</v>
       </c>
       <c r="D2072" t="n">
-        <v>-4.947323309918112</v>
+        <v>-5.117979189168426</v>
       </c>
       <c r="E2072" t="n">
-        <v>2.121852412562289</v>
+        <v>1.981901483583319</v>
       </c>
       <c r="F2072" t="n">
-        <v>0.7514751134706874</v>
+        <v>0.7006156598431439</v>
       </c>
       <c r="G2072" t="n">
-        <v>4.552023228925695</v>
+        <v>4.449818979470324</v>
       </c>
     </row>
     <row r="2073">
@@ -49227,19 +49227,19 @@
         <v>3.70520107942768</v>
       </c>
       <c r="C2073" t="n">
-        <v>4.10238924303612</v>
+        <v>4.030700665757275</v>
       </c>
       <c r="D2073" t="n">
-        <v>-5.033179339258079</v>
+        <v>-5.203835218508392</v>
       </c>
       <c r="E2073" t="n">
-        <v>2.08876108301914</v>
+        <v>1.94881015404017</v>
       </c>
       <c r="F2073" t="n">
-        <v>0.7090990442445524</v>
+        <v>0.6582395906170089</v>
       </c>
       <c r="G2073" t="n">
-        <v>4.527848669582851</v>
+        <v>4.425644420127481</v>
       </c>
     </row>
     <row r="2074">
@@ -49247,22 +49247,22 @@
         <v>45536</v>
       </c>
       <c r="B2074" t="n">
-        <v>3.691835499610377</v>
+        <v>3.691835499610379</v>
       </c>
       <c r="C2074" t="n">
-        <v>4.084808444856622</v>
+        <v>4.013119867577777</v>
       </c>
       <c r="D2074" t="n">
-        <v>-5.042016136674198</v>
+        <v>-5.212672015924512</v>
       </c>
       <c r="E2074" t="n">
-        <v>2.067645565873194</v>
+        <v>1.927694636894225</v>
       </c>
       <c r="F2074" t="n">
-        <v>0.7016568716032017</v>
+        <v>0.6507974179756582</v>
       </c>
       <c r="G2074" t="n">
-        <v>4.505802567818542</v>
+        <v>4.403598318363173</v>
       </c>
     </row>
     <row r="2075">
@@ -49270,22 +49270,22 @@
         <v>45537</v>
       </c>
       <c r="B2075" t="n">
-        <v>3.71554441166745</v>
+        <v>3.715544411667452</v>
       </c>
       <c r="C2075" t="n">
-        <v>4.094972955901671</v>
+        <v>4.023284378622827</v>
       </c>
       <c r="D2075" t="n">
-        <v>-5.133398699239657</v>
+        <v>-5.30405457848997</v>
       </c>
       <c r="E2075" t="n">
-        <v>2.04125705189206</v>
+        <v>1.901306122913091</v>
       </c>
       <c r="F2075" t="n">
-        <v>0.665091986883857</v>
+        <v>0.6142325332563134</v>
       </c>
       <c r="G2075" t="n">
-        <v>4.494028148031985</v>
+        <v>4.391823898576615</v>
       </c>
     </row>
     <row r="2076">
@@ -49296,19 +49296,19 @@
         <v>3.673978374889187</v>
       </c>
       <c r="C2076" t="n">
-        <v>4.197101213725938</v>
+        <v>4.125412636447095</v>
       </c>
       <c r="D2076" t="n">
-        <v>-5.121691981252651</v>
+        <v>-5.292347860502964</v>
       </c>
       <c r="E2076" t="n">
-        <v>2.14806799691113</v>
+        <v>2.008117067932161</v>
       </c>
       <c r="F2076" t="n">
-        <v>0.6767987048708634</v>
+        <v>0.6259392512433198</v>
       </c>
       <c r="G2076" t="n">
-        <v>4.603180436648456</v>
+        <v>4.500976187193087</v>
       </c>
     </row>
     <row r="2077">
@@ -49319,19 +49319,19 @@
         <v>3.682476099409563</v>
       </c>
       <c r="C2077" t="n">
-        <v>4.200133552457343</v>
+        <v>4.1284449751785</v>
       </c>
       <c r="D2077" t="n">
-        <v>-5.192604054994929</v>
+        <v>-5.363259934245242</v>
       </c>
       <c r="E2077" t="n">
-        <v>2.122735506145624</v>
+        <v>1.982784577166655</v>
       </c>
       <c r="F2077" t="n">
-        <v>0.6767987048708634</v>
+        <v>0.6259392512433198</v>
       </c>
       <c r="G2077" t="n">
-        <v>4.606212775379861</v>
+        <v>4.504008525924492</v>
       </c>
     </row>
     <row r="2078">
@@ -49339,22 +49339,22 @@
         <v>45540</v>
       </c>
       <c r="B2078" t="n">
-        <v>3.672895177452567</v>
+        <v>3.672895177452569</v>
       </c>
       <c r="C2078" t="n">
-        <v>4.413038385735401</v>
+        <v>4.341349808456558</v>
       </c>
       <c r="D2078" t="n">
-        <v>-5.202920153161281</v>
+        <v>-5.373576032411594</v>
       </c>
       <c r="E2078" t="n">
-        <v>2.331513900157141</v>
+        <v>2.191562971178172</v>
       </c>
       <c r="F2078" t="n">
-        <v>0.6767987048708634</v>
+        <v>0.6259392512433198</v>
       </c>
       <c r="G2078" t="n">
-        <v>4.819117608657919</v>
+        <v>4.71691335920255</v>
       </c>
     </row>
     <row r="2079">
@@ -49362,22 +49362,22 @@
         <v>45541</v>
       </c>
       <c r="B2079" t="n">
-        <v>3.623960959762283</v>
+        <v>3.623960959762282</v>
       </c>
       <c r="C2079" t="n">
-        <v>4.412217052647491</v>
+        <v>4.340528475368647</v>
       </c>
       <c r="D2079" t="n">
-        <v>-5.202826185143908</v>
+        <v>-5.373482064394222</v>
       </c>
       <c r="E2079" t="n">
-        <v>2.33073015427618</v>
+        <v>2.190779225297211</v>
       </c>
       <c r="F2079" t="n">
-        <v>0.6771685662181813</v>
+        <v>0.6263091125906378</v>
       </c>
       <c r="G2079" t="n">
-        <v>4.8185181923784</v>
+        <v>4.716313942923031</v>
       </c>
     </row>
     <row r="2080">
@@ -49385,22 +49385,22 @@
         <v>45542</v>
       </c>
       <c r="B2080" t="n">
-        <v>3.633213467988014</v>
+        <v>3.633213467988013</v>
       </c>
       <c r="C2080" t="n">
-        <v>4.406449038591845</v>
+        <v>4.334760461313001</v>
       </c>
       <c r="D2080" t="n">
-        <v>-5.351192412800053</v>
+        <v>-5.521848292050366</v>
       </c>
       <c r="E2080" t="n">
-        <v>2.265615649158076</v>
+        <v>2.125664720179107</v>
       </c>
       <c r="F2080" t="n">
-        <v>0.6771685662181813</v>
+        <v>0.6263091125906378</v>
       </c>
       <c r="G2080" t="n">
-        <v>4.812750178322753</v>
+        <v>4.710545928867385</v>
       </c>
     </row>
     <row r="2081">
@@ -49408,22 +49408,22 @@
         <v>45543</v>
       </c>
       <c r="B2081" t="n">
-        <v>3.647907242740918</v>
+        <v>3.64790724274092</v>
       </c>
       <c r="C2081" t="n">
-        <v>4.406449038591845</v>
+        <v>4.334760461313001</v>
       </c>
       <c r="D2081" t="n">
-        <v>-5.350243989682014</v>
+        <v>-5.520899868932328</v>
       </c>
       <c r="E2081" t="n">
-        <v>2.265995018405291</v>
+        <v>2.126044089426322</v>
       </c>
       <c r="F2081" t="n">
-        <v>0.6771685662181813</v>
+        <v>0.6263091125906378</v>
       </c>
       <c r="G2081" t="n">
-        <v>4.812750178322753</v>
+        <v>4.710545928867385</v>
       </c>
     </row>
     <row r="2082">
@@ -49431,22 +49431,22 @@
         <v>45544</v>
       </c>
       <c r="B2082" t="n">
-        <v>3.881065366663622</v>
+        <v>3.881065366663623</v>
       </c>
       <c r="C2082" t="n">
-        <v>4.419176646572937</v>
+        <v>4.347488069294093</v>
       </c>
       <c r="D2082" t="n">
-        <v>-5.450513807641036</v>
+        <v>-5.621169686891349</v>
       </c>
       <c r="E2082" t="n">
-        <v>2.238614699202774</v>
+        <v>2.098663770223806</v>
       </c>
       <c r="F2082" t="n">
-        <v>0.6771685662181813</v>
+        <v>0.6263091125906378</v>
       </c>
       <c r="G2082" t="n">
-        <v>4.825477786303845</v>
+        <v>4.723273536848477</v>
       </c>
     </row>
     <row r="2083">
@@ -49454,22 +49454,22 @@
         <v>45545</v>
       </c>
       <c r="B2083" t="n">
-        <v>3.717071158424766</v>
+        <v>3.717071158424767</v>
       </c>
       <c r="C2083" t="n">
-        <v>4.421122644997324</v>
+        <v>4.349434067718481</v>
       </c>
       <c r="D2083" t="n">
-        <v>-5.444521560852224</v>
+        <v>-5.615177440102538</v>
       </c>
       <c r="E2083" t="n">
-        <v>2.242957596342687</v>
+        <v>2.103006667363718</v>
       </c>
       <c r="F2083" t="n">
-        <v>0.6771685662181813</v>
+        <v>0.6263091125906378</v>
       </c>
       <c r="G2083" t="n">
-        <v>4.827423784728233</v>
+        <v>4.725219535272864</v>
       </c>
     </row>
     <row r="2084">
@@ -49477,22 +49477,22 @@
         <v>45546</v>
       </c>
       <c r="B2084" t="n">
-        <v>3.741942347149214</v>
+        <v>3.741942347149216</v>
       </c>
       <c r="C2084" t="n">
-        <v>4.414776781015093</v>
+        <v>4.34308820373625</v>
       </c>
       <c r="D2084" t="n">
-        <v>-5.355963599721457</v>
+        <v>-5.52661947897177</v>
       </c>
       <c r="E2084" t="n">
-        <v>2.272034916812763</v>
+        <v>2.132083987833794</v>
       </c>
       <c r="F2084" t="n">
-        <v>0.6771685662181813</v>
+        <v>0.6263091125906378</v>
       </c>
       <c r="G2084" t="n">
-        <v>4.821077920746002</v>
+        <v>4.718873671290633</v>
       </c>
     </row>
     <row r="2085">
@@ -49500,22 +49500,22 @@
         <v>45547</v>
       </c>
       <c r="B2085" t="n">
-        <v>3.735300721383086</v>
+        <v>3.735300721383088</v>
       </c>
       <c r="C2085" t="n">
-        <v>4.414085458454089</v>
+        <v>4.342396881175246</v>
       </c>
       <c r="D2085" t="n">
-        <v>-5.338204522218382</v>
+        <v>-5.508860401468696</v>
       </c>
       <c r="E2085" t="n">
-        <v>2.278447225252988</v>
+        <v>2.138496296274019</v>
       </c>
       <c r="F2085" t="n">
-        <v>0.6771685662181813</v>
+        <v>0.6263091125906378</v>
       </c>
       <c r="G2085" t="n">
-        <v>4.820386598184998</v>
+        <v>4.718182348729629</v>
       </c>
     </row>
     <row r="2086">
@@ -49523,22 +49523,22 @@
         <v>45548</v>
       </c>
       <c r="B2086" t="n">
-        <v>3.778232147720992</v>
+        <v>3.778232147720994</v>
       </c>
       <c r="C2086" t="n">
-        <v>4.426867644362676</v>
+        <v>4.355179067083832</v>
       </c>
       <c r="D2086" t="n">
-        <v>-5.238574371169315</v>
+        <v>-5.409230250419628</v>
       </c>
       <c r="E2086" t="n">
-        <v>2.331081471581202</v>
+        <v>2.191130542602233</v>
       </c>
       <c r="F2086" t="n">
-        <v>0.7767987172672488</v>
+        <v>0.7259392636397053</v>
       </c>
       <c r="G2086" t="n">
-        <v>4.892946874723025</v>
+        <v>4.790742625267656</v>
       </c>
     </row>
     <row r="2087">
@@ -49546,22 +49546,22 @@
         <v>45549</v>
       </c>
       <c r="B2087" t="n">
-        <v>3.775357097455267</v>
+        <v>3.775357097455268</v>
       </c>
       <c r="C2087" t="n">
-        <v>4.616021909861402</v>
+        <v>4.544333332582559</v>
       </c>
       <c r="D2087" t="n">
-        <v>-5.287973879858326</v>
+        <v>-5.458629759108639</v>
       </c>
       <c r="E2087" t="n">
-        <v>2.500475933604324</v>
+        <v>2.360525004625355</v>
       </c>
       <c r="F2087" t="n">
-        <v>0.7870575506989935</v>
+        <v>0.73619809707145</v>
       </c>
       <c r="G2087" t="n">
-        <v>5.088256440280799</v>
+        <v>4.986052190825429</v>
       </c>
     </row>
     <row r="2088">
@@ -49569,22 +49569,22 @@
         <v>45550</v>
       </c>
       <c r="B2088" t="n">
-        <v>3.749078058963128</v>
+        <v>3.749078058963129</v>
       </c>
       <c r="C2088" t="n">
-        <v>4.603210582964264</v>
+        <v>4.531522005685421</v>
       </c>
       <c r="D2088" t="n">
-        <v>-5.08128940621595</v>
+        <v>-5.251945285466263</v>
       </c>
       <c r="E2088" t="n">
-        <v>2.570338396164136</v>
+        <v>2.430387467185168</v>
       </c>
       <c r="F2088" t="n">
-        <v>0.993742024341369</v>
+        <v>0.9428825707138256</v>
       </c>
       <c r="G2088" t="n">
-        <v>5.199455797569086</v>
+        <v>5.097251548113716</v>
       </c>
     </row>
     <row r="2089">
@@ -49592,22 +49592,22 @@
         <v>45551</v>
       </c>
       <c r="B2089" t="n">
-        <v>3.740284389162538</v>
+        <v>3.740284389162539</v>
       </c>
       <c r="C2089" t="n">
-        <v>4.605212096618369</v>
+        <v>4.533523519339526</v>
       </c>
       <c r="D2089" t="n">
-        <v>-5.115446301213476</v>
+        <v>-5.286102180463789</v>
       </c>
       <c r="E2089" t="n">
-        <v>2.558677151819231</v>
+        <v>2.418726222840262</v>
       </c>
       <c r="F2089" t="n">
-        <v>0.9101582548005566</v>
+        <v>0.8592988011730132</v>
       </c>
       <c r="G2089" t="n">
-        <v>5.151307049498703</v>
+        <v>5.049102800043334</v>
       </c>
     </row>
     <row r="2090">
@@ -49615,22 +49615,22 @@
         <v>45552</v>
       </c>
       <c r="B2090" t="n">
-        <v>3.782482115652378</v>
+        <v>3.78248211565238</v>
       </c>
       <c r="C2090" t="n">
-        <v>4.958709210608037</v>
+        <v>4.887020633329193</v>
       </c>
       <c r="D2090" t="n">
-        <v>-5.022856822152019</v>
+        <v>-5.193512701402333</v>
       </c>
       <c r="E2090" t="n">
-        <v>2.949210057433481</v>
+        <v>2.809259128454512</v>
       </c>
       <c r="F2090" t="n">
-        <v>0.9101582548005566</v>
+        <v>0.8592988011730132</v>
       </c>
       <c r="G2090" t="n">
-        <v>5.50480416348837</v>
+        <v>5.402599914033002</v>
       </c>
     </row>
     <row r="2091">
@@ -49638,22 +49638,22 @@
         <v>45553</v>
       </c>
       <c r="B2091" t="n">
-        <v>3.809055905108668</v>
+        <v>3.80905590510867</v>
       </c>
       <c r="C2091" t="n">
-        <v>4.96327232217514</v>
+        <v>4.891583744896296</v>
       </c>
       <c r="D2091" t="n">
-        <v>-5.096017425925164</v>
+        <v>-5.266673305175478</v>
       </c>
       <c r="E2091" t="n">
-        <v>2.924508927491326</v>
+        <v>2.784557998512357</v>
       </c>
       <c r="F2091" t="n">
-        <v>0.8821370547663134</v>
+        <v>0.8312776011387701</v>
       </c>
       <c r="G2091" t="n">
-        <v>5.492554555034928</v>
+        <v>5.390350305579559</v>
       </c>
     </row>
     <row r="2092">
@@ -49661,22 +49661,22 @@
         <v>45554</v>
       </c>
       <c r="B2092" t="n">
-        <v>3.83520244110356</v>
+        <v>3.835202441103561</v>
       </c>
       <c r="C2092" t="n">
-        <v>5.013102263498667</v>
+        <v>4.941413686219824</v>
       </c>
       <c r="D2092" t="n">
-        <v>-5.161115069002456</v>
+        <v>-5.214456995379136</v>
       </c>
       <c r="E2092" t="n">
-        <v>2.948299811583937</v>
+        <v>2.855274463754422</v>
       </c>
       <c r="F2092" t="n">
-        <v>0.8821370547663134</v>
+        <v>0.8312776011387701</v>
       </c>
       <c r="G2092" t="n">
-        <v>5.542384496358456</v>
+        <v>5.440180246903086</v>
       </c>
     </row>
     <row r="2093">
@@ -49684,22 +49684,22 @@
         <v>45555</v>
       </c>
       <c r="B2093" t="n">
-        <v>3.821827147047741</v>
+        <v>3.821827147047742</v>
       </c>
       <c r="C2093" t="n">
-        <v>5.021916233708678</v>
+        <v>4.950227656429835</v>
       </c>
       <c r="D2093" t="n">
-        <v>-5.12921755191721</v>
+        <v>-5.18255947829389</v>
       </c>
       <c r="E2093" t="n">
-        <v>2.969872788628046</v>
+        <v>2.876847440798531</v>
       </c>
       <c r="F2093" t="n">
-        <v>0.9140345718515592</v>
+        <v>0.8631751182240159</v>
       </c>
       <c r="G2093" t="n">
-        <v>5.570336976819614</v>
+        <v>5.468132727364245</v>
       </c>
     </row>
     <row r="2094">
@@ -49710,19 +49710,19 @@
         <v>3.825268416650751</v>
       </c>
       <c r="C2094" t="n">
-        <v>5.017553817747875</v>
+        <v>4.945865240469032</v>
       </c>
       <c r="D2094" t="n">
-        <v>-5.143972876117351</v>
+        <v>-5.197314802494031</v>
       </c>
       <c r="E2094" t="n">
-        <v>2.959608242987187</v>
+        <v>2.866582895157671</v>
       </c>
       <c r="F2094" t="n">
-        <v>0.9140345718515592</v>
+        <v>0.8631751182240159</v>
       </c>
       <c r="G2094" t="n">
-        <v>5.565974560858811</v>
+        <v>5.463770311403442</v>
       </c>
     </row>
     <row r="2095">
@@ -49733,19 +49733,19 @@
         <v>3.845044666135745</v>
       </c>
       <c r="C2095" t="n">
-        <v>5.008478321164155</v>
+        <v>4.936789743885312</v>
       </c>
       <c r="D2095" t="n">
-        <v>-5.094508252747439</v>
+        <v>-5.147850179124119</v>
       </c>
       <c r="E2095" t="n">
-        <v>2.970318595751432</v>
+        <v>2.877293247921916</v>
       </c>
       <c r="F2095" t="n">
-        <v>0.9634991952214709</v>
+        <v>0.9126397415939276</v>
       </c>
       <c r="G2095" t="n">
-        <v>5.586577838297038</v>
+        <v>5.484373588841668</v>
       </c>
     </row>
     <row r="2096">
@@ -49756,19 +49756,19 @@
         <v>3.825931790479219</v>
       </c>
       <c r="C2096" t="n">
-        <v>5.00488598887909</v>
+        <v>4.933197411600246</v>
       </c>
       <c r="D2096" t="n">
-        <v>-4.931400260593824</v>
+        <v>-4.984742186970504</v>
       </c>
       <c r="E2096" t="n">
-        <v>3.031969460327812</v>
+        <v>2.938944112498297</v>
       </c>
       <c r="F2096" t="n">
-        <v>1.126607187375086</v>
+        <v>1.075747733747543</v>
       </c>
       <c r="G2096" t="n">
-        <v>5.680850301304141</v>
+        <v>5.578646051848772</v>
       </c>
     </row>
     <row r="2097">
@@ -49776,22 +49776,22 @@
         <v>45559</v>
       </c>
       <c r="B2097" t="n">
-        <v>3.84709647884424</v>
+        <v>3.847096478844243</v>
       </c>
       <c r="C2097" t="n">
-        <v>5.013933025570218</v>
+        <v>4.942244448291374</v>
       </c>
       <c r="D2097" t="n">
-        <v>-4.798592635096657</v>
+        <v>-4.851934561473337</v>
       </c>
       <c r="E2097" t="n">
-        <v>3.094139547217807</v>
+        <v>3.001114199388291</v>
       </c>
       <c r="F2097" t="n">
-        <v>1.126607187375086</v>
+        <v>1.075747733747543</v>
       </c>
       <c r="G2097" t="n">
-        <v>5.689897337995269</v>
+        <v>5.587693088539901</v>
       </c>
     </row>
     <row r="2098">
@@ -49799,22 +49799,22 @@
         <v>45560</v>
       </c>
       <c r="B2098" t="n">
-        <v>3.832425987790944</v>
+        <v>3.832425987790947</v>
       </c>
       <c r="C2098" t="n">
-        <v>5.014790490556339</v>
+        <v>4.943101913277496</v>
       </c>
       <c r="D2098" t="n">
-        <v>-4.861300551571215</v>
+        <v>-4.914642477947895</v>
       </c>
       <c r="E2098" t="n">
-        <v>3.069913845614105</v>
+        <v>2.97688849778459</v>
       </c>
       <c r="F2098" t="n">
-        <v>1.063899270900528</v>
+        <v>1.013039817272985</v>
       </c>
       <c r="G2098" t="n">
-        <v>5.653130053096657</v>
+        <v>5.550925803641287</v>
       </c>
     </row>
     <row r="2099">
@@ -49822,22 +49822,22 @@
         <v>45561</v>
       </c>
       <c r="B2099" t="n">
-        <v>3.861579399578991</v>
+        <v>3.861579399578993</v>
       </c>
       <c r="C2099" t="n">
-        <v>4.977699907346691</v>
+        <v>4.906011330067848</v>
       </c>
       <c r="D2099" t="n">
-        <v>-4.813292427727522</v>
+        <v>-4.866634354104202</v>
       </c>
       <c r="E2099" t="n">
-        <v>3.052026511941935</v>
+        <v>2.959001164112419</v>
       </c>
       <c r="F2099" t="n">
-        <v>1.063899270900528</v>
+        <v>1.013039817272985</v>
       </c>
       <c r="G2099" t="n">
-        <v>5.616039469887009</v>
+        <v>5.513835220431639</v>
       </c>
     </row>
     <row r="2100">
@@ -49845,22 +49845,22 @@
         <v>45562</v>
       </c>
       <c r="B2100" t="n">
-        <v>3.872253907629879</v>
+        <v>3.872253907629881</v>
       </c>
       <c r="C2100" t="n">
-        <v>4.981632160904642</v>
+        <v>4.909943583625799</v>
       </c>
       <c r="D2100" t="n">
-        <v>-4.734466770543932</v>
+        <v>-4.787808696920612</v>
       </c>
       <c r="E2100" t="n">
-        <v>3.087489028373321</v>
+        <v>2.994463680543806</v>
       </c>
       <c r="F2100" t="n">
-        <v>1.142724928084119</v>
+        <v>1.091865474456576</v>
       </c>
       <c r="G2100" t="n">
-        <v>5.667267117755113</v>
+        <v>5.565062868299744</v>
       </c>
     </row>
     <row r="2101">
@@ -49868,22 +49868,22 @@
         <v>45563</v>
       </c>
       <c r="B2101" t="n">
-        <v>3.868502531686402</v>
+        <v>3.868502531686404</v>
       </c>
       <c r="C2101" t="n">
-        <v>4.976531253511679</v>
+        <v>4.904842676232835</v>
       </c>
       <c r="D2101" t="n">
-        <v>-4.542531969290058</v>
+        <v>-4.595873895666738</v>
       </c>
       <c r="E2101" t="n">
-        <v>3.159162041481907</v>
+        <v>3.066136693652392</v>
       </c>
       <c r="F2101" t="n">
-        <v>1.142724928084119</v>
+        <v>1.091865474456576</v>
       </c>
       <c r="G2101" t="n">
-        <v>5.66216621036215</v>
+        <v>5.559961960906781</v>
       </c>
     </row>
     <row r="2102">
@@ -49891,22 +49891,22 @@
         <v>45564</v>
       </c>
       <c r="B2102" t="n">
-        <v>3.84932404404671</v>
+        <v>3.849324044046711</v>
       </c>
       <c r="C2102" t="n">
-        <v>4.971885162900774</v>
+        <v>4.900196585621931</v>
       </c>
       <c r="D2102" t="n">
-        <v>-4.424358591272131</v>
+        <v>-4.443536665593511</v>
       </c>
       <c r="E2102" t="n">
-        <v>3.201785302078173</v>
+        <v>3.122425495070778</v>
       </c>
       <c r="F2102" t="n">
-        <v>1.260898306102046</v>
+        <v>1.244202704529803</v>
       </c>
       <c r="G2102" t="n">
-        <v>5.728424146562002</v>
+        <v>5.646718208339813</v>
       </c>
     </row>
     <row r="2103">
@@ -49914,22 +49914,22 @@
         <v>45565</v>
       </c>
       <c r="B2103" t="n">
-        <v>3.764159573175336</v>
+        <v>3.881147636442992</v>
       </c>
       <c r="C2103" t="n">
-        <v>4.852269311997898</v>
+        <v>4.905655517817662</v>
       </c>
       <c r="D2103" t="n">
-        <v>-4.424358591272131</v>
+        <v>-4.456226604532315</v>
       </c>
       <c r="E2103" t="n">
-        <v>3.201785302078173</v>
+        <v>3.122808451690988</v>
       </c>
       <c r="F2103" t="n">
-        <v>1.260898306102046</v>
+        <v>1.231512765590999</v>
       </c>
       <c r="G2103" t="n">
-        <v>4.845333108984266</v>
+        <v>5.644563177172262</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240930.xlsx
+++ b/tame_output/ON/bt/strategyON_20240930.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>57.3%</t>
+          <t>56.6%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -610,7 +610,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>0.86</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>67.3%</t>
+          <t>67.2%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>57.6%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>113.2%</t>
+          <t>110.3%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>44.0%</t>
+          <t>43.3%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.58</t>
+          <t>2.55</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>47.2%</t>
+          <t>46.2%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>10.8%</t>
+          <t>10.7%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -849,12 +849,12 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>95.0%</t>
+          <t>92.4%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>36.0%</t>
+          <t>35.4%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-8.4%</t>
+          <t>-8.1%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>178.9%</t>
+          <t>169.7%</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-75.9%</t>
+          <t>-75.1%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>107.9%</t>
+          <t>107.7%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.2%</t>
+          <t>52.3%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>123.2%</t>
+          <t>123.0%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>91.7%</t>
+          <t>91.6%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>22.1%</t>
+          <t>22.3%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-48.3%</t>
+          <t>-47.9%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-71.9%</t>
+          <t>-71.1%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>89.5%</t>
+          <t>89.4%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-6.7%</t>
+          <t>-7.1%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-607.2%</t>
+          <t>-588.9%</t>
         </is>
       </c>
     </row>
@@ -1074,12 +1074,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>43.5%</t>
+          <t>43.4%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>59.5%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>63.1%</t>
+          <t>63.0%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>57.6%</t>
+          <t>56.8%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1140,7 +1140,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>-9.6%</t>
+          <t>-8.7%</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>14.2%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-33.9%</t>
+          <t>-33.6%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>38.3%</t>
+          <t>38.1%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>50.1%</t>
+          <t>49.7%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-4.0%</t>
+          <t>-3.4%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15.2%</t>
+          <t>15.6%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-63.9%</t>
+          <t>-65.9%</t>
         </is>
       </c>
     </row>
@@ -1232,22 +1232,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-3.4%</t>
+          <t>-2.5%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.6%</t>
+          <t>66.2%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.9%</t>
+          <t>55.0%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>62.7%</t>
+          <t>62.4%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>73.7%</t>
+          <t>73.1%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.2%</t>
+          <t>10.5%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-26.1%</t>
+          <t>-24.7%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>4.2%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.5%</t>
+          <t>55.2%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>44.9%</t>
+          <t>46.2%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-373.9%</t>
+          <t>-399.4%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-100.8%</t>
+          <t>-97.1%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>124.6%</t>
+          <t>122.7%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>57.9%</t>
+          <t>57.3%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>2.14</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>59.9%</t>
+          <t>59.7%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>56.8%</t>
+          <t>55.9%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>14.2%</t>
+          <t>14.1%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>113.1%</t>
+          <t>111.2%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>48.3%</t>
+          <t>47.7%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-17.1%</t>
+          <t>-16.8%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>36.6%</t>
+          <t>36.8%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>118.4%</t>
+          <t>111.4%</t>
         </is>
       </c>
     </row>
@@ -47781,16 +47781,16 @@
         <v>3.200497106215023</v>
       </c>
       <c r="D2010" t="n">
-        <v>-3.445452894286067</v>
+        <v>-3.392100260732303</v>
       </c>
       <c r="E2010" t="n">
-        <v>1.821959524186849</v>
+        <v>1.843300577608354</v>
       </c>
       <c r="F2010" t="n">
-        <v>0.5915193896396682</v>
+        <v>0.6423788432672118</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.555408739998825</v>
+        <v>3.585924412175351</v>
       </c>
     </row>
     <row r="2011">
@@ -47804,16 +47804,16 @@
         <v>3.213570513080942</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.553753556156186</v>
+        <v>-3.500400922602422</v>
       </c>
       <c r="E2011" t="n">
-        <v>1.791712666304719</v>
+        <v>1.813053719726225</v>
       </c>
       <c r="F2011" t="n">
-        <v>0.5915193896396682</v>
+        <v>0.6423788432672118</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.568482146864743</v>
+        <v>3.598997819041269</v>
       </c>
     </row>
     <row r="2012">
@@ -47827,16 +47827,16 @@
         <v>3.205575709863882</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.57155752787693</v>
+        <v>-3.518204894323167</v>
       </c>
       <c r="E2012" t="n">
-        <v>1.776596274399362</v>
+        <v>1.797937327820867</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.5209847667344671</v>
+        <v>0.5718442203620107</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.518166569904563</v>
+        <v>3.548682242081089</v>
       </c>
     </row>
     <row r="2013">
@@ -47850,16 +47850,16 @@
         <v>3.204099750990884</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.599458314986403</v>
+        <v>-3.546105681432639</v>
       </c>
       <c r="E2013" t="n">
-        <v>1.763960000682575</v>
+        <v>1.78530105410408</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.4863878425915323</v>
+        <v>0.5372472962190759</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.495932456545804</v>
+        <v>3.52644812872233</v>
       </c>
     </row>
     <row r="2014">
@@ -47873,16 +47873,16 @@
         <v>3.200864194968083</v>
       </c>
       <c r="D2014" t="n">
-        <v>-3.721984417689297</v>
+        <v>-3.668631784135533</v>
       </c>
       <c r="E2014" t="n">
-        <v>1.711714003578616</v>
+        <v>1.733055057000121</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.3638617398886385</v>
+        <v>0.414721193516182</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.419181238901266</v>
+        <v>3.449696911077792</v>
       </c>
     </row>
     <row r="2015">
@@ -47896,16 +47896,16 @@
         <v>3.267570154558586</v>
       </c>
       <c r="D2015" t="n">
-        <v>-3.952498913874886</v>
+        <v>-3.899146280321122</v>
       </c>
       <c r="E2015" t="n">
-        <v>1.686214164694884</v>
+        <v>1.70755521811639</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.1333472437030497</v>
+        <v>0.1842066973305932</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.347578500780417</v>
+        <v>3.378094172956942</v>
       </c>
     </row>
     <row r="2016">
@@ -47919,16 +47919,16 @@
         <v>3.407881873560433</v>
       </c>
       <c r="D2016" t="n">
-        <v>-4.30124399909933</v>
+        <v>-4.247891365545565</v>
       </c>
       <c r="E2016" t="n">
-        <v>1.687027849606954</v>
+        <v>1.708368903028459</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.02459928978415193</v>
+        <v>0.07545874341169545</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.422641447430925</v>
+        <v>3.453157119607451</v>
       </c>
     </row>
     <row r="2017">
@@ -47942,16 +47942,16 @@
         <v>3.476862142706073</v>
       </c>
       <c r="D2017" t="n">
-        <v>-4.45523041687547</v>
+        <v>-4.401877783321706</v>
       </c>
       <c r="E2017" t="n">
-        <v>1.694413551642137</v>
+        <v>1.715754605063643</v>
       </c>
       <c r="F2017" t="n">
-        <v>0.02459928978415193</v>
+        <v>0.07545874341169545</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.491621716576565</v>
+        <v>3.522137388753091</v>
       </c>
     </row>
     <row r="2018">
@@ -47965,16 +47965,16 @@
         <v>3.462913344826194</v>
       </c>
       <c r="D2018" t="n">
-        <v>-4.659829851738479</v>
+        <v>-4.606477218184715</v>
       </c>
       <c r="E2018" t="n">
-        <v>1.598624979817055</v>
+        <v>1.61996603323856</v>
       </c>
       <c r="F2018" t="n">
-        <v>0.02459928978415193</v>
+        <v>0.07545874341169545</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.477672918696685</v>
+        <v>3.508188590873212</v>
       </c>
     </row>
     <row r="2019">
@@ -47988,16 +47988,16 @@
         <v>3.474783833881608</v>
       </c>
       <c r="D2019" t="n">
-        <v>-4.912305005746203</v>
+        <v>-4.858952372192439</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.509505407269379</v>
+        <v>1.530846460690884</v>
       </c>
       <c r="F2019" t="n">
-        <v>0.02459928978415193</v>
+        <v>0.07545874341169545</v>
       </c>
       <c r="G2019" t="n">
-        <v>3.489543407752099</v>
+        <v>3.520059079928626</v>
       </c>
     </row>
     <row r="2020">
@@ -48011,16 +48011,16 @@
         <v>3.475994368400552</v>
       </c>
       <c r="D2020" t="n">
-        <v>-5.205200762225616</v>
+        <v>-5.151848128671851</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.393557639196558</v>
+        <v>1.414898692618063</v>
       </c>
       <c r="F2020" t="n">
-        <v>0.02459928978415193</v>
+        <v>0.07545874341169545</v>
       </c>
       <c r="G2020" t="n">
-        <v>3.490753942271043</v>
+        <v>3.521269614447569</v>
       </c>
     </row>
     <row r="2021">
@@ -48034,16 +48034,16 @@
         <v>3.480116110627873</v>
       </c>
       <c r="D2021" t="n">
-        <v>-5.391864890360424</v>
+        <v>-5.338512256806659</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.323013730169956</v>
+        <v>1.344354783591462</v>
       </c>
       <c r="F2021" t="n">
-        <v>-0.002139681040407959</v>
+        <v>0.04871977258713556</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.478832302003629</v>
+        <v>3.509347974180155</v>
       </c>
     </row>
     <row r="2022">
@@ -48057,16 +48057,16 @@
         <v>3.475193963364063</v>
       </c>
       <c r="D2022" t="n">
-        <v>-5.537885577274386</v>
+        <v>-5.484532943720621</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.259683308140561</v>
+        <v>1.281024361562066</v>
       </c>
       <c r="F2022" t="n">
-        <v>-0.01122277283426493</v>
+        <v>0.03963668079327859</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.468460299663504</v>
+        <v>3.49897597184003</v>
       </c>
     </row>
     <row r="2023">
@@ -48080,16 +48080,16 @@
         <v>3.637398020063107</v>
       </c>
       <c r="D2023" t="n">
-        <v>-5.629599586383971</v>
+        <v>-5.576246952830207</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.38520176119577</v>
+        <v>1.406542814617276</v>
       </c>
       <c r="F2023" t="n">
-        <v>-0.01122277283426493</v>
+        <v>0.03963668079327859</v>
       </c>
       <c r="G2023" t="n">
-        <v>3.630664356362548</v>
+        <v>3.661180028539074</v>
       </c>
     </row>
     <row r="2024">
@@ -48103,16 +48103,16 @@
         <v>3.632244658026921</v>
       </c>
       <c r="D2024" t="n">
-        <v>-5.661251245443941</v>
+        <v>-5.607898611890176</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.367387735535597</v>
+        <v>1.388728788957102</v>
       </c>
       <c r="F2024" t="n">
-        <v>-0.01639123007870513</v>
+        <v>0.03446822354883838</v>
       </c>
       <c r="G2024" t="n">
-        <v>3.622409919979698</v>
+        <v>3.652925592156224</v>
       </c>
     </row>
     <row r="2025">
@@ -48126,16 +48126,16 @@
         <v>3.642474075595412</v>
       </c>
       <c r="D2025" t="n">
-        <v>-5.730317300016877</v>
+        <v>-5.676964666463113</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.349990731274913</v>
+        <v>1.371331784696419</v>
       </c>
       <c r="F2025" t="n">
-        <v>-0.07876210757231517</v>
+        <v>-0.02790265394477165</v>
       </c>
       <c r="G2025" t="n">
-        <v>3.595216811052024</v>
+        <v>3.625732483228549</v>
       </c>
     </row>
     <row r="2026">
@@ -48149,16 +48149,16 @@
         <v>3.651399714051315</v>
       </c>
       <c r="D2026" t="n">
-        <v>-5.832293422265285</v>
+        <v>-5.778940788711521</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.318125920831453</v>
+        <v>1.339466974252959</v>
       </c>
       <c r="F2026" t="n">
-        <v>-0.1807382298207227</v>
+        <v>-0.1298787761931792</v>
       </c>
       <c r="G2026" t="n">
-        <v>3.542956776158881</v>
+        <v>3.573472448335407</v>
       </c>
     </row>
     <row r="2027">
@@ -48172,16 +48172,16 @@
         <v>3.64355260129549</v>
       </c>
       <c r="D2027" t="n">
-        <v>-5.722287138788063</v>
+        <v>-5.668934505234299</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.354281321466517</v>
+        <v>1.375622374888022</v>
       </c>
       <c r="F2027" t="n">
-        <v>-0.1575336579034475</v>
+        <v>-0.106674204275904</v>
       </c>
       <c r="G2027" t="n">
-        <v>3.549032406553422</v>
+        <v>3.579548078729948</v>
       </c>
     </row>
     <row r="2028">
@@ -48195,16 +48195,16 @@
         <v>3.647802612017464</v>
       </c>
       <c r="D2028" t="n">
-        <v>-5.579227563047137</v>
+        <v>-5.525874929493373</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.415755162484861</v>
+        <v>1.437096215906367</v>
       </c>
       <c r="F2028" t="n">
-        <v>-0.1495202313134683</v>
+        <v>-0.09866077768592474</v>
       </c>
       <c r="G2028" t="n">
-        <v>3.558090473229384</v>
+        <v>3.588606145405909</v>
       </c>
     </row>
     <row r="2029">
@@ -48218,16 +48218,16 @@
         <v>3.6550634949</v>
       </c>
       <c r="D2029" t="n">
-        <v>-5.2777808375753</v>
+        <v>-5.224428204021535</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.543594735556133</v>
+        <v>1.564935788977638</v>
       </c>
       <c r="F2029" t="n">
-        <v>0.151926494158369</v>
+        <v>0.2027859477859125</v>
       </c>
       <c r="G2029" t="n">
-        <v>3.746219391395022</v>
+        <v>3.776735063571548</v>
       </c>
     </row>
     <row r="2030">
@@ -48241,16 +48241,16 @@
         <v>3.656034672652711</v>
       </c>
       <c r="D2030" t="n">
-        <v>-5.302371081810484</v>
+        <v>-5.249018448256719</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.53472981561477</v>
+        <v>1.556070869036275</v>
       </c>
       <c r="F2030" t="n">
-        <v>0.151926494158369</v>
+        <v>0.2027859477859125</v>
       </c>
       <c r="G2030" t="n">
-        <v>3.747190569147733</v>
+        <v>3.777706241324259</v>
       </c>
     </row>
     <row r="2031">
@@ -48264,16 +48264,16 @@
         <v>3.656877577032466</v>
       </c>
       <c r="D2031" t="n">
-        <v>-5.251332705803963</v>
+        <v>-5.197980072250199</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.555988070397133</v>
+        <v>1.577329123818639</v>
       </c>
       <c r="F2031" t="n">
-        <v>0.151926494158369</v>
+        <v>0.2027859477859125</v>
       </c>
       <c r="G2031" t="n">
-        <v>3.748033473527488</v>
+        <v>3.778549145704014</v>
       </c>
     </row>
     <row r="2032">
@@ -48287,16 +48287,16 @@
         <v>3.675915675906612</v>
       </c>
       <c r="D2032" t="n">
-        <v>-5.222484028980503</v>
+        <v>-5.169131395426739</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.586565640000662</v>
+        <v>1.607906693422168</v>
       </c>
       <c r="F2032" t="n">
-        <v>0.1807751709818293</v>
+        <v>0.2316346246093728</v>
       </c>
       <c r="G2032" t="n">
-        <v>3.78438077849571</v>
+        <v>3.814896450672236</v>
       </c>
     </row>
     <row r="2033">
@@ -48310,16 +48310,16 @@
         <v>3.492099672030546</v>
       </c>
       <c r="D2033" t="n">
-        <v>-5.125849116961863</v>
+        <v>-5.072496483408099</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.441403600932053</v>
+        <v>1.462744654353559</v>
       </c>
       <c r="F2033" t="n">
-        <v>0.2774100830004692</v>
+        <v>0.3282695366280127</v>
       </c>
       <c r="G2033" t="n">
-        <v>3.658545721830828</v>
+        <v>3.689061394007354</v>
       </c>
     </row>
     <row r="2034">
@@ -48333,16 +48333,16 @@
         <v>3.495601716104511</v>
       </c>
       <c r="D2034" t="n">
-        <v>-5.056811106013395</v>
+        <v>-5.003458472459631</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.472520849385405</v>
+        <v>1.49386190280691</v>
       </c>
       <c r="F2034" t="n">
-        <v>0.3464480939489373</v>
+        <v>0.3973075475764808</v>
       </c>
       <c r="G2034" t="n">
-        <v>3.703470572473873</v>
+        <v>3.733986244650399</v>
       </c>
     </row>
     <row r="2035">
@@ -48356,16 +48356,16 @@
         <v>3.480028535180593</v>
       </c>
       <c r="D2035" t="n">
-        <v>-5.038024005644457</v>
+        <v>-4.984671372090692</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.464462508609063</v>
+        <v>1.485803562030568</v>
       </c>
       <c r="F2035" t="n">
-        <v>0.3652351943178758</v>
+        <v>0.4160946479454193</v>
       </c>
       <c r="G2035" t="n">
-        <v>3.699169651771319</v>
+        <v>3.729685323947845</v>
       </c>
     </row>
     <row r="2036">
@@ -48379,16 +48379,16 @@
         <v>3.479216245617023</v>
       </c>
       <c r="D2036" t="n">
-        <v>-5.078228649799133</v>
+        <v>-4.907572770548819</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.447568361383622</v>
+        <v>1.515830713083747</v>
       </c>
       <c r="F2036" t="n">
-        <v>0.3652351943178758</v>
+        <v>0.4160946479454193</v>
       </c>
       <c r="G2036" t="n">
-        <v>3.698357362207748</v>
+        <v>3.728873034384275</v>
       </c>
     </row>
     <row r="2037">
@@ -48402,16 +48402,16 @@
         <v>3.489085024742095</v>
       </c>
       <c r="D2037" t="n">
-        <v>-5.088613844689022</v>
+        <v>-4.917957965438709</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.453283062552738</v>
+        <v>1.521545414252864</v>
       </c>
       <c r="F2037" t="n">
-        <v>0.3548499994279865</v>
+        <v>0.40570945305553</v>
       </c>
       <c r="G2037" t="n">
-        <v>3.701995024398888</v>
+        <v>3.732510696575413</v>
       </c>
     </row>
     <row r="2038">
@@ -48425,16 +48425,16 @@
         <v>3.55992203051852</v>
       </c>
       <c r="D2038" t="n">
-        <v>-5.107202003411247</v>
+        <v>-4.936546124160934</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.516684804840274</v>
+        <v>1.584947156540399</v>
       </c>
       <c r="F2038" t="n">
-        <v>0.3362618407057611</v>
+        <v>0.3871212943333046</v>
       </c>
       <c r="G2038" t="n">
-        <v>3.761679134941977</v>
+        <v>3.792194807118503</v>
       </c>
     </row>
     <row r="2039">
@@ -48448,16 +48448,16 @@
         <v>3.556791041336819</v>
       </c>
       <c r="D2039" t="n">
-        <v>-5.107500550107283</v>
+        <v>-4.93684467085697</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.513434396980158</v>
+        <v>1.581696748680283</v>
       </c>
       <c r="F2039" t="n">
-        <v>0.3359632940097252</v>
+        <v>0.3868227476372687</v>
       </c>
       <c r="G2039" t="n">
-        <v>3.758369017742654</v>
+        <v>3.78888468991918</v>
       </c>
     </row>
     <row r="2040">
@@ -48471,16 +48471,16 @@
         <v>3.56132193627621</v>
       </c>
       <c r="D2040" t="n">
-        <v>-5.006677416416855</v>
+        <v>-4.836021537166542</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.55829454539572</v>
+        <v>1.626556897095845</v>
       </c>
       <c r="F2040" t="n">
-        <v>0.348427509494079</v>
+        <v>0.3992869631216225</v>
       </c>
       <c r="G2040" t="n">
-        <v>3.770378441972658</v>
+        <v>3.800894114149184</v>
       </c>
     </row>
     <row r="2041">
@@ -48494,16 +48494,16 @@
         <v>3.561451189754754</v>
       </c>
       <c r="D2041" t="n">
-        <v>-4.815896055664448</v>
+        <v>-4.645240176414134</v>
       </c>
       <c r="E2041" t="n">
-        <v>1.634736343175227</v>
+        <v>1.702998694875352</v>
       </c>
       <c r="F2041" t="n">
-        <v>0.5392088702464863</v>
+        <v>0.5648444093125009</v>
       </c>
       <c r="G2041" t="n">
-        <v>3.884976511902646</v>
+        <v>3.900357835342255</v>
       </c>
     </row>
     <row r="2042">
@@ -48517,16 +48517,16 @@
         <v>3.54128803549235</v>
       </c>
       <c r="D2042" t="n">
-        <v>-4.708932697815026</v>
+        <v>-4.538276818564713</v>
       </c>
       <c r="E2042" t="n">
-        <v>1.657358532052592</v>
+        <v>1.725620883752717</v>
       </c>
       <c r="F2042" t="n">
-        <v>0.5976734782062878</v>
+        <v>0.6233090172723024</v>
       </c>
       <c r="G2042" t="n">
-        <v>3.899892122416123</v>
+        <v>3.915273445855732</v>
       </c>
     </row>
     <row r="2043">
@@ -48540,16 +48540,16 @@
         <v>3.576254972104409</v>
       </c>
       <c r="D2043" t="n">
-        <v>-4.653602109913264</v>
+        <v>-4.48294623066295</v>
       </c>
       <c r="E2043" t="n">
-        <v>1.714457703825355</v>
+        <v>1.782720055525481</v>
       </c>
       <c r="F2043" t="n">
-        <v>0.65300406610805</v>
+        <v>0.6786396051740645</v>
       </c>
       <c r="G2043" t="n">
-        <v>3.968057411769239</v>
+        <v>3.983438735208847</v>
       </c>
     </row>
     <row r="2044">
@@ -48563,16 +48563,16 @@
         <v>3.569941540005846</v>
       </c>
       <c r="D2044" t="n">
-        <v>-4.641547983000301</v>
+        <v>-4.470892103749987</v>
       </c>
       <c r="E2044" t="n">
-        <v>1.712965922491978</v>
+        <v>1.781228274192103</v>
       </c>
       <c r="F2044" t="n">
-        <v>0.6650581930210128</v>
+        <v>0.6906937320870273</v>
       </c>
       <c r="G2044" t="n">
-        <v>3.968976455818455</v>
+        <v>3.984357779258063</v>
       </c>
     </row>
     <row r="2045">
@@ -48586,16 +48586,16 @@
         <v>3.571822170189982</v>
       </c>
       <c r="D2045" t="n">
-        <v>-4.682703102568522</v>
+        <v>-4.512047223318208</v>
       </c>
       <c r="E2045" t="n">
-        <v>1.698384504848826</v>
+        <v>1.766646856548951</v>
       </c>
       <c r="F2045" t="n">
-        <v>0.6239030734527918</v>
+        <v>0.6495386125188064</v>
       </c>
       <c r="G2045" t="n">
-        <v>3.946164014261657</v>
+        <v>3.961545337701266</v>
       </c>
     </row>
     <row r="2046">
@@ -48609,16 +48609,16 @@
         <v>3.584673196067865</v>
       </c>
       <c r="D2046" t="n">
-        <v>-4.614654539876992</v>
+        <v>-4.443998660626678</v>
       </c>
       <c r="E2046" t="n">
-        <v>1.73845495580332</v>
+        <v>1.806717307503445</v>
       </c>
       <c r="F2046" t="n">
-        <v>0.6919516361443216</v>
+        <v>0.7175871752103362</v>
       </c>
       <c r="G2046" t="n">
-        <v>3.999844177754458</v>
+        <v>4.015225501194067</v>
       </c>
     </row>
     <row r="2047">
@@ -48632,16 +48632,16 @@
         <v>3.604875866241459</v>
       </c>
       <c r="D2047" t="n">
-        <v>-4.846254933046493</v>
+        <v>-4.675599053796179</v>
       </c>
       <c r="E2047" t="n">
-        <v>1.666017468709114</v>
+        <v>1.734279820409239</v>
       </c>
       <c r="F2047" t="n">
-        <v>0.6919516361443216</v>
+        <v>0.7175871752103362</v>
       </c>
       <c r="G2047" t="n">
-        <v>4.020046847928052</v>
+        <v>4.035428171367661</v>
       </c>
     </row>
     <row r="2048">
@@ -48655,16 +48655,16 @@
         <v>3.588482102308341</v>
       </c>
       <c r="D2048" t="n">
-        <v>-4.896306478575712</v>
+        <v>-4.725650599325398</v>
       </c>
       <c r="E2048" t="n">
-        <v>1.629603086564308</v>
+        <v>1.697865438264434</v>
       </c>
       <c r="F2048" t="n">
-        <v>0.6919516361443216</v>
+        <v>0.7175871752103362</v>
       </c>
       <c r="G2048" t="n">
-        <v>4.003653083994934</v>
+        <v>4.019034407434543</v>
       </c>
     </row>
     <row r="2049">
@@ -48678,16 +48678,16 @@
         <v>3.548734015901807</v>
       </c>
       <c r="D2049" t="n">
-        <v>-5.071413311152156</v>
+        <v>-4.900757431901843</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.519812267127197</v>
+        <v>1.588074618827322</v>
       </c>
       <c r="F2049" t="n">
-        <v>0.6919516361443216</v>
+        <v>0.7175871752103362</v>
       </c>
       <c r="G2049" t="n">
-        <v>3.963904997588401</v>
+        <v>3.97928632102801</v>
       </c>
     </row>
     <row r="2050">
@@ -48701,16 +48701,16 @@
         <v>3.555756634898747</v>
       </c>
       <c r="D2050" t="n">
-        <v>-4.875313157721633</v>
+        <v>-4.70465727847132</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.605274947496346</v>
+        <v>1.673537299196472</v>
       </c>
       <c r="F2050" t="n">
-        <v>0.8880517895748445</v>
+        <v>0.9136873286408591</v>
       </c>
       <c r="G2050" t="n">
-        <v>4.088587708643654</v>
+        <v>4.103969032083263</v>
       </c>
     </row>
     <row r="2051">
@@ -48724,16 +48724,16 @@
         <v>3.654927634471652</v>
       </c>
       <c r="D2051" t="n">
-        <v>-4.722287765608349</v>
+        <v>-4.551631886358035</v>
       </c>
       <c r="E2051" t="n">
-        <v>1.765656103914564</v>
+        <v>1.83391845561469</v>
       </c>
       <c r="F2051" t="n">
-        <v>1.041077181688129</v>
+        <v>1.066712720754143</v>
       </c>
       <c r="G2051" t="n">
-        <v>4.27957394348453</v>
+        <v>4.294955266924138</v>
       </c>
     </row>
     <row r="2052">
@@ -48747,16 +48747,16 @@
         <v>3.842393859379944</v>
       </c>
       <c r="D2052" t="n">
-        <v>-4.750595079481619</v>
+        <v>-4.579939200231306</v>
       </c>
       <c r="E2052" t="n">
-        <v>1.941799403273549</v>
+        <v>2.010061754973674</v>
       </c>
       <c r="F2052" t="n">
-        <v>1.041077181688129</v>
+        <v>1.066712720754143</v>
       </c>
       <c r="G2052" t="n">
-        <v>4.467040168392822</v>
+        <v>4.482421491832431</v>
       </c>
     </row>
     <row r="2053">
@@ -48770,16 +48770,16 @@
         <v>3.811796810734027</v>
       </c>
       <c r="D2053" t="n">
-        <v>-4.917188304595141</v>
+        <v>-4.746532425344828</v>
       </c>
       <c r="E2053" t="n">
-        <v>1.844565064582223</v>
+        <v>1.912827416282348</v>
       </c>
       <c r="F2053" t="n">
-        <v>0.8744839565746061</v>
+        <v>0.9001194956406209</v>
       </c>
       <c r="G2053" t="n">
-        <v>4.336487184678791</v>
+        <v>4.3518685081184</v>
       </c>
     </row>
     <row r="2054">
@@ -48793,16 +48793,16 @@
         <v>3.815473213395745</v>
       </c>
       <c r="D2054" t="n">
-        <v>-4.894152511233576</v>
+        <v>-4.723496631983262</v>
       </c>
       <c r="E2054" t="n">
-        <v>1.857455784588567</v>
+        <v>1.925718136288692</v>
       </c>
       <c r="F2054" t="n">
-        <v>0.8744839565746061</v>
+        <v>0.9001194956406209</v>
       </c>
       <c r="G2054" t="n">
-        <v>4.340163587340509</v>
+        <v>4.355544910780118</v>
       </c>
     </row>
     <row r="2055">
@@ -48816,16 +48816,16 @@
         <v>3.81309126851924</v>
       </c>
       <c r="D2055" t="n">
-        <v>-4.864906530777879</v>
+        <v>-4.694250651527565</v>
       </c>
       <c r="E2055" t="n">
-        <v>1.866772231894341</v>
+        <v>1.935034583594466</v>
       </c>
       <c r="F2055" t="n">
-        <v>0.8744839565746061</v>
+        <v>0.9001194956406209</v>
       </c>
       <c r="G2055" t="n">
-        <v>4.337781642464004</v>
+        <v>4.353162965903613</v>
       </c>
     </row>
     <row r="2056">
@@ -48839,16 +48839,16 @@
         <v>3.810384507676875</v>
       </c>
       <c r="D2056" t="n">
-        <v>-4.97183207865573</v>
+        <v>-4.801176199405417</v>
       </c>
       <c r="E2056" t="n">
-        <v>1.821295251900835</v>
+        <v>1.889557603600961</v>
       </c>
       <c r="F2056" t="n">
-        <v>0.7675584086967547</v>
+        <v>0.7931939477627695</v>
       </c>
       <c r="G2056" t="n">
-        <v>4.270919552894928</v>
+        <v>4.286300876334537</v>
       </c>
     </row>
     <row r="2057">
@@ -48862,16 +48862,16 @@
         <v>3.811813309820109</v>
       </c>
       <c r="D2057" t="n">
-        <v>-5.116850637162979</v>
+        <v>-4.946194757912665</v>
       </c>
       <c r="E2057" t="n">
-        <v>1.76471663064117</v>
+        <v>1.832978982341295</v>
       </c>
       <c r="F2057" t="n">
-        <v>0.6225398501895062</v>
+        <v>0.648175389255521</v>
       </c>
       <c r="G2057" t="n">
-        <v>4.185337219933813</v>
+        <v>4.200718543373422</v>
       </c>
     </row>
     <row r="2058">
@@ -48885,16 +48885,16 @@
         <v>3.911744549077862</v>
       </c>
       <c r="D2058" t="n">
-        <v>-5.235192402947696</v>
+        <v>-5.064536523697383</v>
       </c>
       <c r="E2058" t="n">
-        <v>1.817311163585036</v>
+        <v>1.885573515285161</v>
       </c>
       <c r="F2058" t="n">
-        <v>0.6332258887523963</v>
+        <v>0.6588614278184111</v>
       </c>
       <c r="G2058" t="n">
-        <v>4.2916800823293</v>
+        <v>4.307061405768909</v>
       </c>
     </row>
     <row r="2059">
@@ -48908,16 +48908,16 @@
         <v>3.909530246203802</v>
       </c>
       <c r="D2059" t="n">
-        <v>-5.286602825268404</v>
+        <v>-5.115946946018091</v>
       </c>
       <c r="E2059" t="n">
-        <v>1.794532691782692</v>
+        <v>1.862795043482817</v>
       </c>
       <c r="F2059" t="n">
-        <v>0.6332258887523963</v>
+        <v>0.6588614278184111</v>
       </c>
       <c r="G2059" t="n">
-        <v>4.28946577945524</v>
+        <v>4.304847102894849</v>
       </c>
     </row>
     <row r="2060">
@@ -48931,16 +48931,16 @@
         <v>3.909433374278091</v>
       </c>
       <c r="D2060" t="n">
-        <v>-5.366022276476156</v>
+        <v>-5.195366397225842</v>
       </c>
       <c r="E2060" t="n">
-        <v>1.76266803937388</v>
+        <v>1.830930391074006</v>
       </c>
       <c r="F2060" t="n">
-        <v>0.6332258887523963</v>
+        <v>0.6588614278184111</v>
       </c>
       <c r="G2060" t="n">
-        <v>4.289368907529528</v>
+        <v>4.304750230969137</v>
       </c>
     </row>
     <row r="2061">
@@ -48954,16 +48954,16 @@
         <v>3.909427267836134</v>
       </c>
       <c r="D2061" t="n">
-        <v>-5.461485274393374</v>
+        <v>-5.29082939514306</v>
       </c>
       <c r="E2061" t="n">
-        <v>1.724476733765036</v>
+        <v>1.792739085465162</v>
       </c>
       <c r="F2061" t="n">
-        <v>0.6332258887523963</v>
+        <v>0.6588614278184111</v>
       </c>
       <c r="G2061" t="n">
-        <v>4.289362801087572</v>
+        <v>4.304744124527181</v>
       </c>
     </row>
     <row r="2062">
@@ -48977,16 +48977,16 @@
         <v>3.907523664398744</v>
       </c>
       <c r="D2062" t="n">
-        <v>-5.397109363542659</v>
+        <v>-5.226453484292345</v>
       </c>
       <c r="E2062" t="n">
-        <v>1.748323494667933</v>
+        <v>1.816585846368058</v>
       </c>
       <c r="F2062" t="n">
-        <v>0.6976017996031114</v>
+        <v>0.7232373386691262</v>
       </c>
       <c r="G2062" t="n">
-        <v>4.326084744160611</v>
+        <v>4.34146606760022</v>
       </c>
     </row>
     <row r="2063">
@@ -49000,16 +49000,16 @@
         <v>3.913257482146471</v>
       </c>
       <c r="D2063" t="n">
-        <v>-5.452478525674852</v>
+        <v>-5.281822646424539</v>
       </c>
       <c r="E2063" t="n">
-        <v>1.731909647562782</v>
+        <v>1.800171999262907</v>
       </c>
       <c r="F2063" t="n">
-        <v>0.6976017996031114</v>
+        <v>0.7232373386691262</v>
       </c>
       <c r="G2063" t="n">
-        <v>4.331818561908338</v>
+        <v>4.347199885347947</v>
       </c>
     </row>
     <row r="2064">
@@ -49023,16 +49023,16 @@
         <v>3.912795845489403</v>
       </c>
       <c r="D2064" t="n">
-        <v>-5.470696992672461</v>
+        <v>-5.300041113422147</v>
       </c>
       <c r="E2064" t="n">
-        <v>1.724160624106671</v>
+        <v>1.792422975806796</v>
       </c>
       <c r="F2064" t="n">
-        <v>0.6724953623472693</v>
+        <v>0.698130901413284</v>
       </c>
       <c r="G2064" t="n">
-        <v>4.316293062897765</v>
+        <v>4.331674386337374</v>
       </c>
     </row>
     <row r="2065">
@@ -49046,16 +49046,16 @@
         <v>3.932670238339722</v>
       </c>
       <c r="D2065" t="n">
-        <v>-5.382490158524883</v>
+        <v>-5.211834279274569</v>
       </c>
       <c r="E2065" t="n">
-        <v>1.779317750616021</v>
+        <v>1.847580102316146</v>
       </c>
       <c r="F2065" t="n">
-        <v>0.6724953623472693</v>
+        <v>0.698130901413284</v>
       </c>
       <c r="G2065" t="n">
-        <v>4.336167455748084</v>
+        <v>4.351548779187692</v>
       </c>
     </row>
     <row r="2066">
@@ -49069,16 +49069,16 @@
         <v>3.91637093886445</v>
       </c>
       <c r="D2066" t="n">
-        <v>-5.276455163319573</v>
+        <v>-5.10579928406926</v>
       </c>
       <c r="E2066" t="n">
-        <v>1.805432449222872</v>
+        <v>1.873694800922998</v>
       </c>
       <c r="F2066" t="n">
-        <v>0.6724953623472693</v>
+        <v>0.698130901413284</v>
       </c>
       <c r="G2066" t="n">
-        <v>4.319868156272812</v>
+        <v>4.33524947971242</v>
       </c>
     </row>
     <row r="2067">
@@ -49092,16 +49092,16 @@
         <v>3.918801888328495</v>
       </c>
       <c r="D2067" t="n">
-        <v>-5.093243500186478</v>
+        <v>-4.922587620936165</v>
       </c>
       <c r="E2067" t="n">
-        <v>1.881148063940156</v>
+        <v>1.949410415640282</v>
       </c>
       <c r="F2067" t="n">
-        <v>0.6724953623472693</v>
+        <v>0.698130901413284</v>
       </c>
       <c r="G2067" t="n">
-        <v>4.322299105736858</v>
+        <v>4.337680429176466</v>
       </c>
     </row>
     <row r="2068">
@@ -49115,16 +49115,16 @@
         <v>3.901746294407872</v>
       </c>
       <c r="D2068" t="n">
-        <v>-5.021522053172627</v>
+        <v>-4.850866173922314</v>
       </c>
       <c r="E2068" t="n">
-        <v>1.892781048825074</v>
+        <v>1.961043400525199</v>
       </c>
       <c r="F2068" t="n">
-        <v>0.7442168093611199</v>
+        <v>0.7698523484271347</v>
       </c>
       <c r="G2068" t="n">
-        <v>4.348276380024545</v>
+        <v>4.363657703464153</v>
       </c>
     </row>
     <row r="2069">
@@ -49138,16 +49138,16 @@
         <v>3.848662040329044</v>
       </c>
       <c r="D2069" t="n">
-        <v>-4.999149027564921</v>
+        <v>-4.828493148314608</v>
       </c>
       <c r="E2069" t="n">
-        <v>1.848646004989328</v>
+        <v>1.916908356689453</v>
       </c>
       <c r="F2069" t="n">
-        <v>0.7554725604740214</v>
+        <v>0.7811080995400362</v>
       </c>
       <c r="G2069" t="n">
-        <v>4.301945576613457</v>
+        <v>4.317326900053066</v>
       </c>
     </row>
     <row r="2070">
@@ -49161,16 +49161,16 @@
         <v>4.0338602452144</v>
       </c>
       <c r="D2070" t="n">
-        <v>-5.032165323475666</v>
+        <v>-4.861509444225352</v>
       </c>
       <c r="E2070" t="n">
-        <v>2.020637691510385</v>
+        <v>2.08890004321051</v>
       </c>
       <c r="F2070" t="n">
-        <v>0.6860351838072698</v>
+        <v>0.7116707228732846</v>
       </c>
       <c r="G2070" t="n">
-        <v>4.445481355498762</v>
+        <v>4.460862678938371</v>
       </c>
     </row>
     <row r="2071">
@@ -49184,16 +49184,16 @@
         <v>4.025781471042649</v>
       </c>
       <c r="D2071" t="n">
-        <v>-5.020637687826057</v>
+        <v>-4.849981808575744</v>
       </c>
       <c r="E2071" t="n">
-        <v>2.017169971598478</v>
+        <v>2.085432323298603</v>
       </c>
       <c r="F2071" t="n">
-        <v>0.7450358420086323</v>
+        <v>0.7706713810746471</v>
       </c>
       <c r="G2071" t="n">
-        <v>4.472802976247828</v>
+        <v>4.488184299687437</v>
       </c>
     </row>
     <row r="2072">
@@ -49207,16 +49207,16 @@
         <v>4.029449583564437</v>
       </c>
       <c r="D2072" t="n">
-        <v>-5.117979189168426</v>
+        <v>-4.947323309918112</v>
       </c>
       <c r="E2072" t="n">
-        <v>1.981901483583319</v>
+        <v>2.050163835283445</v>
       </c>
       <c r="F2072" t="n">
-        <v>0.7006156598431439</v>
+        <v>0.7262511989091587</v>
       </c>
       <c r="G2072" t="n">
-        <v>4.449818979470324</v>
+        <v>4.465200302909933</v>
       </c>
     </row>
     <row r="2073">
@@ -49230,16 +49230,16 @@
         <v>4.030700665757275</v>
       </c>
       <c r="D2073" t="n">
-        <v>-5.203835218508392</v>
+        <v>-5.033179339258079</v>
       </c>
       <c r="E2073" t="n">
-        <v>1.94881015404017</v>
+        <v>2.017072505740296</v>
       </c>
       <c r="F2073" t="n">
-        <v>0.6582395906170089</v>
+        <v>0.6838751296830237</v>
       </c>
       <c r="G2073" t="n">
-        <v>4.425644420127481</v>
+        <v>4.44102574356709</v>
       </c>
     </row>
     <row r="2074">
@@ -49253,16 +49253,16 @@
         <v>4.013119867577777</v>
       </c>
       <c r="D2074" t="n">
-        <v>-5.212672015924512</v>
+        <v>-5.042016136674198</v>
       </c>
       <c r="E2074" t="n">
-        <v>1.927694636894225</v>
+        <v>1.99595698859435</v>
       </c>
       <c r="F2074" t="n">
-        <v>0.6507974179756582</v>
+        <v>0.6764329570416729</v>
       </c>
       <c r="G2074" t="n">
-        <v>4.403598318363173</v>
+        <v>4.418979641802781</v>
       </c>
     </row>
     <row r="2075">
@@ -49276,16 +49276,16 @@
         <v>4.023284378622827</v>
       </c>
       <c r="D2075" t="n">
-        <v>-5.30405457848997</v>
+        <v>-5.133398699239657</v>
       </c>
       <c r="E2075" t="n">
-        <v>1.901306122913091</v>
+        <v>1.969568474613216</v>
       </c>
       <c r="F2075" t="n">
-        <v>0.6142325332563134</v>
+        <v>0.6398680723223282</v>
       </c>
       <c r="G2075" t="n">
-        <v>4.391823898576615</v>
+        <v>4.407205222016224</v>
       </c>
     </row>
     <row r="2076">
@@ -49299,16 +49299,16 @@
         <v>4.125412636447095</v>
       </c>
       <c r="D2076" t="n">
-        <v>-5.292347860502964</v>
+        <v>-5.121691981252651</v>
       </c>
       <c r="E2076" t="n">
-        <v>2.008117067932161</v>
+        <v>2.076379419632286</v>
       </c>
       <c r="F2076" t="n">
-        <v>0.6259392512433198</v>
+        <v>0.6515747903093346</v>
       </c>
       <c r="G2076" t="n">
-        <v>4.500976187193087</v>
+        <v>4.516357510632696</v>
       </c>
     </row>
     <row r="2077">
@@ -49322,16 +49322,16 @@
         <v>4.1284449751785</v>
       </c>
       <c r="D2077" t="n">
-        <v>-5.363259934245242</v>
+        <v>-5.192604054994929</v>
       </c>
       <c r="E2077" t="n">
-        <v>1.982784577166655</v>
+        <v>2.05104692886678</v>
       </c>
       <c r="F2077" t="n">
-        <v>0.6259392512433198</v>
+        <v>0.6515747903093346</v>
       </c>
       <c r="G2077" t="n">
-        <v>4.504008525924492</v>
+        <v>4.519389849364101</v>
       </c>
     </row>
     <row r="2078">
@@ -49342,19 +49342,19 @@
         <v>3.672895177452569</v>
       </c>
       <c r="C2078" t="n">
-        <v>4.341349808456558</v>
+        <v>4.240897415501431</v>
       </c>
       <c r="D2078" t="n">
-        <v>-5.373576032411594</v>
+        <v>-5.202920153161281</v>
       </c>
       <c r="E2078" t="n">
-        <v>2.191562971178172</v>
+        <v>2.159372929923171</v>
       </c>
       <c r="F2078" t="n">
-        <v>0.6259392512433198</v>
+        <v>0.6515747903093346</v>
       </c>
       <c r="G2078" t="n">
-        <v>4.71691335920255</v>
+        <v>4.631842289687032</v>
       </c>
     </row>
     <row r="2079">
@@ -49365,19 +49365,19 @@
         <v>3.623960959762282</v>
       </c>
       <c r="C2079" t="n">
-        <v>4.340528475368647</v>
+        <v>4.240076082413521</v>
       </c>
       <c r="D2079" t="n">
-        <v>-5.373482064394222</v>
+        <v>-5.202826185143908</v>
       </c>
       <c r="E2079" t="n">
-        <v>2.190779225297211</v>
+        <v>2.15858918404221</v>
       </c>
       <c r="F2079" t="n">
-        <v>0.6263091125906378</v>
+        <v>0.6519446516566526</v>
       </c>
       <c r="G2079" t="n">
-        <v>4.716313942923031</v>
+        <v>4.631242873407513</v>
       </c>
     </row>
     <row r="2080">
@@ -49388,19 +49388,19 @@
         <v>3.633213467988013</v>
       </c>
       <c r="C2080" t="n">
-        <v>4.334760461313001</v>
+        <v>4.234308068357874</v>
       </c>
       <c r="D2080" t="n">
-        <v>-5.521848292050366</v>
+        <v>-5.351192412800053</v>
       </c>
       <c r="E2080" t="n">
-        <v>2.125664720179107</v>
+        <v>2.093474678924105</v>
       </c>
       <c r="F2080" t="n">
-        <v>0.6263091125906378</v>
+        <v>0.6519446516566526</v>
       </c>
       <c r="G2080" t="n">
-        <v>4.710545928867385</v>
+        <v>4.625474859351867</v>
       </c>
     </row>
     <row r="2081">
@@ -49411,19 +49411,19 @@
         <v>3.64790724274092</v>
       </c>
       <c r="C2081" t="n">
-        <v>4.334760461313001</v>
+        <v>4.234308068357874</v>
       </c>
       <c r="D2081" t="n">
-        <v>-5.520899868932328</v>
+        <v>-5.350243989682014</v>
       </c>
       <c r="E2081" t="n">
-        <v>2.126044089426322</v>
+        <v>2.093854048171321</v>
       </c>
       <c r="F2081" t="n">
-        <v>0.6263091125906378</v>
+        <v>0.6519446516566526</v>
       </c>
       <c r="G2081" t="n">
-        <v>4.710545928867385</v>
+        <v>4.625474859351867</v>
       </c>
     </row>
     <row r="2082">
@@ -49434,19 +49434,19 @@
         <v>3.881065366663623</v>
       </c>
       <c r="C2082" t="n">
-        <v>4.347488069294093</v>
+        <v>4.247035676338967</v>
       </c>
       <c r="D2082" t="n">
-        <v>-5.621169686891349</v>
+        <v>-5.450513807641036</v>
       </c>
       <c r="E2082" t="n">
-        <v>2.098663770223806</v>
+        <v>2.066473728968804</v>
       </c>
       <c r="F2082" t="n">
-        <v>0.6263091125906378</v>
+        <v>0.6519446516566526</v>
       </c>
       <c r="G2082" t="n">
-        <v>4.723273536848477</v>
+        <v>4.638202467332959</v>
       </c>
     </row>
     <row r="2083">
@@ -49457,19 +49457,19 @@
         <v>3.717071158424767</v>
       </c>
       <c r="C2083" t="n">
-        <v>4.349434067718481</v>
+        <v>4.248981674763354</v>
       </c>
       <c r="D2083" t="n">
-        <v>-5.615177440102538</v>
+        <v>-5.444521560852224</v>
       </c>
       <c r="E2083" t="n">
-        <v>2.103006667363718</v>
+        <v>2.070816626108717</v>
       </c>
       <c r="F2083" t="n">
-        <v>0.6263091125906378</v>
+        <v>0.6519446516566526</v>
       </c>
       <c r="G2083" t="n">
-        <v>4.725219535272864</v>
+        <v>4.640148465757346</v>
       </c>
     </row>
     <row r="2084">
@@ -49480,19 +49480,19 @@
         <v>3.741942347149216</v>
       </c>
       <c r="C2084" t="n">
-        <v>4.34308820373625</v>
+        <v>4.242635810781123</v>
       </c>
       <c r="D2084" t="n">
-        <v>-5.52661947897177</v>
+        <v>-5.355963599721457</v>
       </c>
       <c r="E2084" t="n">
-        <v>2.132083987833794</v>
+        <v>2.099893946578792</v>
       </c>
       <c r="F2084" t="n">
-        <v>0.6263091125906378</v>
+        <v>0.6519446516566526</v>
       </c>
       <c r="G2084" t="n">
-        <v>4.718873671290633</v>
+        <v>4.633802601775115</v>
       </c>
     </row>
     <row r="2085">
@@ -49503,19 +49503,19 @@
         <v>3.735300721383088</v>
       </c>
       <c r="C2085" t="n">
-        <v>4.342396881175246</v>
+        <v>4.241944488220119</v>
       </c>
       <c r="D2085" t="n">
-        <v>-5.508860401468696</v>
+        <v>-5.338204522218382</v>
       </c>
       <c r="E2085" t="n">
-        <v>2.138496296274019</v>
+        <v>2.106306255019018</v>
       </c>
       <c r="F2085" t="n">
-        <v>0.6263091125906378</v>
+        <v>0.6519446516566526</v>
       </c>
       <c r="G2085" t="n">
-        <v>4.718182348729629</v>
+        <v>4.633111279214111</v>
       </c>
     </row>
     <row r="2086">
@@ -49526,19 +49526,19 @@
         <v>3.778232147720994</v>
       </c>
       <c r="C2086" t="n">
-        <v>4.355179067083832</v>
+        <v>4.254726674128706</v>
       </c>
       <c r="D2086" t="n">
-        <v>-5.409230250419628</v>
+        <v>-5.238574371169315</v>
       </c>
       <c r="E2086" t="n">
-        <v>2.191130542602233</v>
+        <v>2.158940501347232</v>
       </c>
       <c r="F2086" t="n">
-        <v>0.7259392636397053</v>
+        <v>0.7515748027057201</v>
       </c>
       <c r="G2086" t="n">
-        <v>4.790742625267656</v>
+        <v>4.705671555752138</v>
       </c>
     </row>
     <row r="2087">
@@ -49549,19 +49549,19 @@
         <v>3.775357097455268</v>
       </c>
       <c r="C2087" t="n">
-        <v>4.544333332582559</v>
+        <v>4.443880939627432</v>
       </c>
       <c r="D2087" t="n">
-        <v>-5.458629759108639</v>
+        <v>-5.287973879858326</v>
       </c>
       <c r="E2087" t="n">
-        <v>2.360525004625355</v>
+        <v>2.328334963370354</v>
       </c>
       <c r="F2087" t="n">
-        <v>0.73619809707145</v>
+        <v>0.7618336361374648</v>
       </c>
       <c r="G2087" t="n">
-        <v>4.986052190825429</v>
+        <v>4.900981121309911</v>
       </c>
     </row>
     <row r="2088">
@@ -49572,19 +49572,19 @@
         <v>3.749078058963129</v>
       </c>
       <c r="C2088" t="n">
-        <v>4.531522005685421</v>
+        <v>4.431069612730294</v>
       </c>
       <c r="D2088" t="n">
-        <v>-5.251945285466263</v>
+        <v>-5.08128940621595</v>
       </c>
       <c r="E2088" t="n">
-        <v>2.430387467185168</v>
+        <v>2.398197425930166</v>
       </c>
       <c r="F2088" t="n">
-        <v>0.9428825707138256</v>
+        <v>0.9685181097798404</v>
       </c>
       <c r="G2088" t="n">
-        <v>5.097251548113716</v>
+        <v>5.012180478598198</v>
       </c>
     </row>
     <row r="2089">
@@ -49595,19 +49595,19 @@
         <v>3.740284389162539</v>
       </c>
       <c r="C2089" t="n">
-        <v>4.533523519339526</v>
+        <v>4.433071126384399</v>
       </c>
       <c r="D2089" t="n">
-        <v>-5.286102180463789</v>
+        <v>-5.115446301213476</v>
       </c>
       <c r="E2089" t="n">
-        <v>2.418726222840262</v>
+        <v>2.386536181585261</v>
       </c>
       <c r="F2089" t="n">
-        <v>0.8592988011730132</v>
+        <v>0.884934340239028</v>
       </c>
       <c r="G2089" t="n">
-        <v>5.049102800043334</v>
+        <v>4.964031730527816</v>
       </c>
     </row>
     <row r="2090">
@@ -49618,19 +49618,19 @@
         <v>3.78248211565238</v>
       </c>
       <c r="C2090" t="n">
-        <v>4.887020633329193</v>
+        <v>4.786568240374066</v>
       </c>
       <c r="D2090" t="n">
-        <v>-5.193512701402333</v>
+        <v>-5.022856822152019</v>
       </c>
       <c r="E2090" t="n">
-        <v>2.809259128454512</v>
+        <v>2.777069087199511</v>
       </c>
       <c r="F2090" t="n">
-        <v>0.8592988011730132</v>
+        <v>0.884934340239028</v>
       </c>
       <c r="G2090" t="n">
-        <v>5.402599914033002</v>
+        <v>5.317528844517484</v>
       </c>
     </row>
     <row r="2091">
@@ -49641,19 +49641,19 @@
         <v>3.80905590510867</v>
       </c>
       <c r="C2091" t="n">
-        <v>4.891583744896296</v>
+        <v>4.79113135194117</v>
       </c>
       <c r="D2091" t="n">
-        <v>-5.266673305175478</v>
+        <v>-5.096017425925164</v>
       </c>
       <c r="E2091" t="n">
-        <v>2.784557998512357</v>
+        <v>2.752367957257356</v>
       </c>
       <c r="F2091" t="n">
-        <v>0.8312776011387701</v>
+        <v>0.8569131402047849</v>
       </c>
       <c r="G2091" t="n">
-        <v>5.390350305579559</v>
+        <v>5.305279236064041</v>
       </c>
     </row>
     <row r="2092">
@@ -49661,22 +49661,22 @@
         <v>45554</v>
       </c>
       <c r="B2092" t="n">
-        <v>3.835202441103561</v>
+        <v>3.83520244110356</v>
       </c>
       <c r="C2092" t="n">
-        <v>4.941413686219824</v>
+        <v>4.840961293264697</v>
       </c>
       <c r="D2092" t="n">
-        <v>-5.214456995379136</v>
+        <v>-5.043801116128822</v>
       </c>
       <c r="E2092" t="n">
-        <v>2.855274463754422</v>
+        <v>2.82308442249942</v>
       </c>
       <c r="F2092" t="n">
-        <v>0.8312776011387701</v>
+        <v>0.8569131402047849</v>
       </c>
       <c r="G2092" t="n">
-        <v>5.440180246903086</v>
+        <v>5.355109177387568</v>
       </c>
     </row>
     <row r="2093">
@@ -49687,19 +49687,19 @@
         <v>3.821827147047742</v>
       </c>
       <c r="C2093" t="n">
-        <v>4.950227656429835</v>
+        <v>4.849775263474708</v>
       </c>
       <c r="D2093" t="n">
-        <v>-5.18255947829389</v>
+        <v>-5.011903599043577</v>
       </c>
       <c r="E2093" t="n">
-        <v>2.876847440798531</v>
+        <v>2.844657399543529</v>
       </c>
       <c r="F2093" t="n">
-        <v>0.8631751182240159</v>
+        <v>0.8888106572900307</v>
       </c>
       <c r="G2093" t="n">
-        <v>5.468132727364245</v>
+        <v>5.383061657848726</v>
       </c>
     </row>
     <row r="2094">
@@ -49710,19 +49710,19 @@
         <v>3.825268416650751</v>
       </c>
       <c r="C2094" t="n">
-        <v>4.945865240469032</v>
+        <v>4.845412847513905</v>
       </c>
       <c r="D2094" t="n">
-        <v>-5.197314802494031</v>
+        <v>-5.026658923243717</v>
       </c>
       <c r="E2094" t="n">
-        <v>2.866582895157671</v>
+        <v>2.83439285390267</v>
       </c>
       <c r="F2094" t="n">
-        <v>0.8631751182240159</v>
+        <v>0.8888106572900307</v>
       </c>
       <c r="G2094" t="n">
-        <v>5.463770311403442</v>
+        <v>5.378699241887924</v>
       </c>
     </row>
     <row r="2095">
@@ -49733,19 +49733,19 @@
         <v>3.845044666135745</v>
       </c>
       <c r="C2095" t="n">
-        <v>4.936789743885312</v>
+        <v>4.836337350930185</v>
       </c>
       <c r="D2095" t="n">
-        <v>-5.147850179124119</v>
+        <v>-4.977194299873806</v>
       </c>
       <c r="E2095" t="n">
-        <v>2.877293247921916</v>
+        <v>2.845103206666915</v>
       </c>
       <c r="F2095" t="n">
-        <v>0.9126397415939276</v>
+        <v>0.9382752806599424</v>
       </c>
       <c r="G2095" t="n">
-        <v>5.484373588841668</v>
+        <v>5.399302519326151</v>
       </c>
     </row>
     <row r="2096">
@@ -49756,19 +49756,19 @@
         <v>3.825931790479219</v>
       </c>
       <c r="C2096" t="n">
-        <v>4.933197411600246</v>
+        <v>4.832745018645119</v>
       </c>
       <c r="D2096" t="n">
-        <v>-4.984742186970504</v>
+        <v>-4.81408630772019</v>
       </c>
       <c r="E2096" t="n">
-        <v>2.938944112498297</v>
+        <v>2.906754071243295</v>
       </c>
       <c r="F2096" t="n">
-        <v>1.075747733747543</v>
+        <v>1.101383272813558</v>
       </c>
       <c r="G2096" t="n">
-        <v>5.578646051848772</v>
+        <v>5.493574982333254</v>
       </c>
     </row>
     <row r="2097">
@@ -49779,19 +49779,19 @@
         <v>3.847096478844243</v>
       </c>
       <c r="C2097" t="n">
-        <v>4.942244448291374</v>
+        <v>4.841792055336247</v>
       </c>
       <c r="D2097" t="n">
-        <v>-4.851934561473337</v>
+        <v>-4.681278682223024</v>
       </c>
       <c r="E2097" t="n">
-        <v>3.001114199388291</v>
+        <v>2.96892415813329</v>
       </c>
       <c r="F2097" t="n">
-        <v>1.075747733747543</v>
+        <v>1.101383272813558</v>
       </c>
       <c r="G2097" t="n">
-        <v>5.587693088539901</v>
+        <v>5.502622019024383</v>
       </c>
     </row>
     <row r="2098">
@@ -49802,19 +49802,19 @@
         <v>3.832425987790947</v>
       </c>
       <c r="C2098" t="n">
-        <v>4.943101913277496</v>
+        <v>4.842649520322369</v>
       </c>
       <c r="D2098" t="n">
-        <v>-4.914642477947895</v>
+        <v>-4.743986598697582</v>
       </c>
       <c r="E2098" t="n">
-        <v>2.97688849778459</v>
+        <v>2.944698456529588</v>
       </c>
       <c r="F2098" t="n">
-        <v>1.013039817272985</v>
+        <v>1.038675356339</v>
       </c>
       <c r="G2098" t="n">
-        <v>5.550925803641287</v>
+        <v>5.465854734125769</v>
       </c>
     </row>
     <row r="2099">
@@ -49825,19 +49825,19 @@
         <v>3.861579399578993</v>
       </c>
       <c r="C2099" t="n">
-        <v>4.906011330067848</v>
+        <v>4.805558937112721</v>
       </c>
       <c r="D2099" t="n">
-        <v>-4.866634354104202</v>
+        <v>-4.695978474853889</v>
       </c>
       <c r="E2099" t="n">
-        <v>2.959001164112419</v>
+        <v>2.926811122857417</v>
       </c>
       <c r="F2099" t="n">
-        <v>1.013039817272985</v>
+        <v>1.038675356339</v>
       </c>
       <c r="G2099" t="n">
-        <v>5.513835220431639</v>
+        <v>5.428764150916122</v>
       </c>
     </row>
     <row r="2100">
@@ -49848,19 +49848,19 @@
         <v>3.872253907629881</v>
       </c>
       <c r="C2100" t="n">
-        <v>4.909943583625799</v>
+        <v>4.809491190670672</v>
       </c>
       <c r="D2100" t="n">
-        <v>-4.787808696920612</v>
+        <v>-4.617152817670299</v>
       </c>
       <c r="E2100" t="n">
-        <v>2.994463680543806</v>
+        <v>2.962273639288804</v>
       </c>
       <c r="F2100" t="n">
-        <v>1.091865474456576</v>
+        <v>1.11750101352259</v>
       </c>
       <c r="G2100" t="n">
-        <v>5.565062868299744</v>
+        <v>5.479991798784226</v>
       </c>
     </row>
     <row r="2101">
@@ -49871,19 +49871,19 @@
         <v>3.868502531686404</v>
       </c>
       <c r="C2101" t="n">
-        <v>4.904842676232835</v>
+        <v>4.804390283277709</v>
       </c>
       <c r="D2101" t="n">
-        <v>-4.595873895666738</v>
+        <v>-4.425218016416425</v>
       </c>
       <c r="E2101" t="n">
-        <v>3.066136693652392</v>
+        <v>3.033946652397391</v>
       </c>
       <c r="F2101" t="n">
-        <v>1.091865474456576</v>
+        <v>1.11750101352259</v>
       </c>
       <c r="G2101" t="n">
-        <v>5.559961960906781</v>
+        <v>5.474890891391263</v>
       </c>
     </row>
     <row r="2102">
@@ -49891,22 +49891,22 @@
         <v>45564</v>
       </c>
       <c r="B2102" t="n">
-        <v>3.849324044046711</v>
+        <v>3.84932404404671</v>
       </c>
       <c r="C2102" t="n">
-        <v>4.900196585621931</v>
+        <v>4.799744192666804</v>
       </c>
       <c r="D2102" t="n">
-        <v>-4.443536665593511</v>
+        <v>-4.295242052378442</v>
       </c>
       <c r="E2102" t="n">
-        <v>3.122425495070778</v>
+        <v>3.081290947401679</v>
       </c>
       <c r="F2102" t="n">
-        <v>1.244202704529803</v>
+        <v>1.247476977560574</v>
       </c>
       <c r="G2102" t="n">
-        <v>5.646718208339813</v>
+        <v>5.548230379203148</v>
       </c>
     </row>
     <row r="2103">
@@ -49914,22 +49914,22 @@
         <v>45565</v>
       </c>
       <c r="B2103" t="n">
-        <v>3.881147636442992</v>
+        <v>3.856919583139137</v>
       </c>
       <c r="C2103" t="n">
-        <v>4.905655517817662</v>
+        <v>4.813098243493824</v>
       </c>
       <c r="D2103" t="n">
-        <v>-4.456226604532315</v>
+        <v>-4.273609845481642</v>
       </c>
       <c r="E2103" t="n">
-        <v>3.122808451690988</v>
+        <v>3.103297880987419</v>
       </c>
       <c r="F2103" t="n">
-        <v>1.231512765590999</v>
+        <v>1.269109184457374</v>
       </c>
       <c r="G2103" t="n">
-        <v>5.644563177172262</v>
+        <v>5.574563754168249</v>
       </c>
     </row>
   </sheetData>
